--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lecoi\Nextcloud\AD Wine Trade\-- VINOM\AAA &amp; VINOM\Tarifs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38DEFFB-FEB2-44A0-B5FF-E0C56ACD2BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D46E61B-962E-4FEB-AA94-5686A66E07E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7350,7 +7350,7 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="13.109375" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
@@ -24847,10 +24847,10 @@
         <v>958</v>
       </c>
       <c r="D429" t="s">
-        <v>1149</v>
+        <v>698</v>
       </c>
       <c r="E429" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F429" t="s">
         <v>1150</v>
@@ -26940,7 +26940,7 @@
         <v>2244</v>
       </c>
       <c r="B481" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C481" t="s">
         <v>1272</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lecoi\Nextcloud\AD Wine Trade\-- VINOM\AAA &amp; VINOM\Tarifs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9493A8-091F-4A38-939E-B6C23B7A3123}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C74DB958-37A5-C44A-864A-CA43B4AA3EAA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10714" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10712" uniqueCount="2245">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6782,7 +6782,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6795,17 +6795,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -7163,192 +7166,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -7361,19 +7364,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R517"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="6.5703125" customWidth="1"/>
+    <col min="11" max="11" width="6.5" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
@@ -7382,7 +7385,7 @@
     <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -7438,7 +7441,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -7479,7 +7482,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -7517,7 +7520,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -7561,7 +7564,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -7646,7 +7649,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -7690,7 +7693,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -7728,7 +7731,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -7766,7 +7769,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -7807,7 +7810,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -7889,7 +7892,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -7933,7 +7936,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -7977,7 +7980,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -8015,7 +8018,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>103</v>
       </c>
@@ -8056,7 +8059,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -8097,7 +8100,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -8138,7 +8141,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -8214,7 +8217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -8252,7 +8255,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -8290,7 +8293,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>125</v>
       </c>
@@ -8331,7 +8334,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -8369,7 +8372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8407,7 +8410,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -8445,7 +8448,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -8486,7 +8489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -8527,7 +8530,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -8568,7 +8571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -8609,7 +8612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>149</v>
       </c>
@@ -8650,7 +8653,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -8685,7 +8688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8726,7 +8729,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -8767,7 +8770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -8805,7 +8808,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>163</v>
       </c>
@@ -8843,7 +8846,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -8884,7 +8887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -8928,7 +8931,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -8969,7 +8972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>176</v>
       </c>
@@ -9013,7 +9016,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>181</v>
       </c>
@@ -9054,7 +9057,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>184</v>
       </c>
@@ -9092,7 +9095,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>188</v>
       </c>
@@ -9130,7 +9133,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -9168,7 +9171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>193</v>
       </c>
@@ -9209,7 +9212,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -9250,7 +9253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -9288,7 +9291,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -9329,7 +9332,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -9367,7 +9370,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>208</v>
       </c>
@@ -9405,7 +9408,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>209</v>
       </c>
@@ -9443,7 +9446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>213</v>
       </c>
@@ -9481,7 +9484,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>216</v>
       </c>
@@ -9525,7 +9528,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -9563,7 +9566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>222</v>
       </c>
@@ -9604,7 +9607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>224</v>
       </c>
@@ -9642,7 +9645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>226</v>
       </c>
@@ -9683,7 +9686,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>229</v>
       </c>
@@ -9718,7 +9721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>230</v>
       </c>
@@ -9759,7 +9762,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>234</v>
       </c>
@@ -9797,7 +9800,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>236</v>
       </c>
@@ -9841,7 +9844,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>240</v>
       </c>
@@ -9879,7 +9882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>243</v>
       </c>
@@ -9917,7 +9920,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>246</v>
       </c>
@@ -9955,7 +9958,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>247</v>
       </c>
@@ -9993,7 +9996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>250</v>
       </c>
@@ -10031,7 +10034,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>253</v>
       </c>
@@ -10069,7 +10072,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>256</v>
       </c>
@@ -10107,7 +10110,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>259</v>
       </c>
@@ -10148,7 +10151,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>263</v>
       </c>
@@ -10189,7 +10192,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>267</v>
       </c>
@@ -10233,7 +10236,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>272</v>
       </c>
@@ -10271,7 +10274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>276</v>
       </c>
@@ -10309,7 +10312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>280</v>
       </c>
@@ -10347,7 +10350,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>282</v>
       </c>
@@ -10382,7 +10385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>285</v>
       </c>
@@ -10420,7 +10423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>288</v>
       </c>
@@ -10461,7 +10464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>292</v>
       </c>
@@ -10499,7 +10502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>294</v>
       </c>
@@ -10537,7 +10540,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>296</v>
       </c>
@@ -10575,7 +10578,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>300</v>
       </c>
@@ -10613,7 +10616,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>304</v>
       </c>
@@ -10654,7 +10657,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>306</v>
       </c>
@@ -10692,7 +10695,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>308</v>
       </c>
@@ -10730,7 +10733,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>311</v>
       </c>
@@ -10765,7 +10768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>314</v>
       </c>
@@ -10803,7 +10806,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>319</v>
       </c>
@@ -10835,7 +10838,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>322</v>
       </c>
@@ -10873,7 +10876,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>15401623</v>
       </c>
@@ -10908,7 +10911,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>326</v>
       </c>
@@ -10949,7 +10952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>329</v>
       </c>
@@ -10990,7 +10993,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>331</v>
       </c>
@@ -11031,7 +11034,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>337</v>
       </c>
@@ -11072,7 +11075,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>340</v>
       </c>
@@ -11113,7 +11116,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>343</v>
       </c>
@@ -11157,7 +11160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>345</v>
       </c>
@@ -11198,7 +11201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>348</v>
       </c>
@@ -11239,7 +11242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>349</v>
       </c>
@@ -11280,7 +11283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>25000124</v>
       </c>
@@ -11321,7 +11324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>355</v>
       </c>
@@ -11362,7 +11365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>357</v>
       </c>
@@ -11403,7 +11406,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>359</v>
       </c>
@@ -11444,7 +11447,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>362</v>
       </c>
@@ -11485,7 +11488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>365</v>
       </c>
@@ -11526,7 +11529,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>366</v>
       </c>
@@ -11567,7 +11570,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>369</v>
       </c>
@@ -11605,7 +11608,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>35800124</v>
       </c>
@@ -11640,7 +11643,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>35800224</v>
       </c>
@@ -11675,7 +11678,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>377</v>
       </c>
@@ -11713,7 +11716,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>378</v>
       </c>
@@ -11751,7 +11754,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>380</v>
       </c>
@@ -11795,7 +11798,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>384</v>
       </c>
@@ -11836,7 +11839,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>387</v>
       </c>
@@ -11880,7 +11883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>389</v>
       </c>
@@ -11918,7 +11921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>391</v>
       </c>
@@ -11956,7 +11959,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>394</v>
       </c>
@@ -11994,7 +11997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>395</v>
       </c>
@@ -12038,7 +12041,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>399</v>
       </c>
@@ -12082,7 +12085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>402</v>
       </c>
@@ -12114,7 +12117,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>405</v>
       </c>
@@ -12146,7 +12149,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>407</v>
       </c>
@@ -12187,7 +12190,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>409</v>
       </c>
@@ -12228,7 +12231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>411</v>
       </c>
@@ -12266,7 +12269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>412</v>
       </c>
@@ -12304,7 +12307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>415</v>
       </c>
@@ -12345,7 +12348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>418</v>
       </c>
@@ -12386,7 +12389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>422</v>
       </c>
@@ -12427,7 +12430,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>424</v>
       </c>
@@ -12468,7 +12471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>427</v>
       </c>
@@ -12509,7 +12512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>430</v>
       </c>
@@ -12550,7 +12553,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>435</v>
       </c>
@@ -12591,7 +12594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>438</v>
       </c>
@@ -12632,7 +12635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>441</v>
       </c>
@@ -12676,7 +12679,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>444</v>
       </c>
@@ -12717,7 +12720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>447</v>
       </c>
@@ -12755,7 +12758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>449</v>
       </c>
@@ -12796,7 +12799,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>451</v>
       </c>
@@ -12834,7 +12837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>454</v>
       </c>
@@ -12875,7 +12878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>456</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>457</v>
       </c>
@@ -12957,7 +12960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>460</v>
       </c>
@@ -12998,7 +13001,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>462</v>
       </c>
@@ -13039,7 +13042,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>465</v>
       </c>
@@ -13080,7 +13083,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>469</v>
       </c>
@@ -13124,7 +13127,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>472</v>
       </c>
@@ -13165,7 +13168,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>473</v>
       </c>
@@ -13203,7 +13206,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>476</v>
       </c>
@@ -13244,7 +13247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>479</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>481</v>
       </c>
@@ -13314,7 +13317,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>482</v>
       </c>
@@ -13355,7 +13358,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>484</v>
       </c>
@@ -13399,7 +13402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>487</v>
       </c>
@@ -13434,7 +13437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>491</v>
       </c>
@@ -13475,7 +13478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>495</v>
       </c>
@@ -13516,7 +13519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>498</v>
       </c>
@@ -13557,7 +13560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>501</v>
       </c>
@@ -13598,7 +13601,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>504</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>506</v>
       </c>
@@ -13680,7 +13683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>509</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>513</v>
       </c>
@@ -13765,7 +13768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>514</v>
       </c>
@@ -13806,7 +13809,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>517</v>
       </c>
@@ -13847,7 +13850,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>521</v>
       </c>
@@ -13888,7 +13891,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>524</v>
       </c>
@@ -13929,7 +13932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>527</v>
       </c>
@@ -13973,7 +13976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>530</v>
       </c>
@@ -14008,7 +14011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>531</v>
       </c>
@@ -14043,7 +14046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>533</v>
       </c>
@@ -14081,7 +14084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>534</v>
       </c>
@@ -14122,7 +14125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>536</v>
       </c>
@@ -14163,7 +14166,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>539</v>
       </c>
@@ -14201,7 +14204,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>541</v>
       </c>
@@ -14242,7 +14245,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>544</v>
       </c>
@@ -14277,7 +14280,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>546</v>
       </c>
@@ -14321,7 +14324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>548</v>
       </c>
@@ -14362,7 +14365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>551</v>
       </c>
@@ -14403,7 +14406,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>553</v>
       </c>
@@ -14444,7 +14447,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>554</v>
       </c>
@@ -14488,7 +14491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>558</v>
       </c>
@@ -14529,7 +14532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>560</v>
       </c>
@@ -14573,7 +14576,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>25002122</v>
       </c>
@@ -14611,7 +14614,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>563</v>
       </c>
@@ -14652,7 +14655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>567</v>
       </c>
@@ -14693,7 +14696,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>569</v>
       </c>
@@ -14734,7 +14737,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>572</v>
       </c>
@@ -14775,7 +14778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>576</v>
       </c>
@@ -14816,7 +14819,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>580</v>
       </c>
@@ -14857,7 +14860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>582</v>
       </c>
@@ -14898,7 +14901,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>586</v>
       </c>
@@ -14939,7 +14942,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>588</v>
       </c>
@@ -14980,7 +14983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>590</v>
       </c>
@@ -15021,7 +15024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>594</v>
       </c>
@@ -15062,7 +15065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>597</v>
       </c>
@@ -15100,7 +15103,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>599</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>601</v>
       </c>
@@ -15182,7 +15185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>603</v>
       </c>
@@ -15223,7 +15226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>606</v>
       </c>
@@ -15267,7 +15270,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>609</v>
       </c>
@@ -15308,7 +15311,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>612</v>
       </c>
@@ -15349,7 +15352,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>615</v>
       </c>
@@ -15390,7 +15393,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>617</v>
       </c>
@@ -15434,7 +15437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>621</v>
       </c>
@@ -15475,7 +15478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>623</v>
       </c>
@@ -15516,7 +15519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>625</v>
       </c>
@@ -15560,7 +15563,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>627</v>
       </c>
@@ -15601,7 +15604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>628</v>
       </c>
@@ -15645,7 +15648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>630</v>
       </c>
@@ -15686,7 +15689,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>632</v>
       </c>
@@ -15727,7 +15730,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>634</v>
       </c>
@@ -15768,7 +15771,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>635</v>
       </c>
@@ -15809,7 +15812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>636</v>
       </c>
@@ -15850,7 +15853,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>641</v>
       </c>
@@ -15891,7 +15894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>643</v>
       </c>
@@ -15932,7 +15935,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>647</v>
       </c>
@@ -15973,7 +15976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>650</v>
       </c>
@@ -16014,7 +16017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>653</v>
       </c>
@@ -16055,7 +16058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>654</v>
       </c>
@@ -16096,7 +16099,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>657</v>
       </c>
@@ -16137,7 +16140,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>660</v>
       </c>
@@ -16178,7 +16181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>661</v>
       </c>
@@ -16219,7 +16222,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>662</v>
       </c>
@@ -16260,7 +16263,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>664</v>
       </c>
@@ -16301,7 +16304,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>668</v>
       </c>
@@ -16342,7 +16345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>670</v>
       </c>
@@ -16383,7 +16386,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>672</v>
       </c>
@@ -16424,7 +16427,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>675</v>
       </c>
@@ -16465,7 +16468,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>677</v>
       </c>
@@ -16509,7 +16512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>680</v>
       </c>
@@ -16550,7 +16553,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>682</v>
       </c>
@@ -16591,7 +16594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>684</v>
       </c>
@@ -16632,7 +16635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>687</v>
       </c>
@@ -16676,7 +16679,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>690</v>
       </c>
@@ -16717,7 +16720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>692</v>
       </c>
@@ -16758,7 +16761,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>695</v>
       </c>
@@ -16799,7 +16802,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>699</v>
       </c>
@@ -16840,7 +16843,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>701</v>
       </c>
@@ -16881,7 +16884,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>704</v>
       </c>
@@ -16922,7 +16925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>706</v>
       </c>
@@ -16963,7 +16966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>709</v>
       </c>
@@ -17004,7 +17007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>710</v>
       </c>
@@ -17048,7 +17051,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>711</v>
       </c>
@@ -17089,7 +17092,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>712</v>
       </c>
@@ -17133,7 +17136,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>715</v>
       </c>
@@ -17174,7 +17177,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>717</v>
       </c>
@@ -17215,7 +17218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>719</v>
       </c>
@@ -17256,7 +17259,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>721</v>
       </c>
@@ -17297,7 +17300,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>723</v>
       </c>
@@ -17338,7 +17341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>725</v>
       </c>
@@ -17379,7 +17382,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>727</v>
       </c>
@@ -17420,7 +17423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>13800524</v>
       </c>
@@ -17461,7 +17464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>729</v>
       </c>
@@ -17502,7 +17505,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>731</v>
       </c>
@@ -17543,7 +17546,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>733</v>
       </c>
@@ -17584,7 +17587,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>734</v>
       </c>
@@ -17625,7 +17628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>739</v>
       </c>
@@ -17666,9 +17669,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
-      <c r="A256" t="s">
-        <v>741</v>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>10700325</v>
       </c>
       <c r="B256" t="s">
         <v>56</v>
@@ -17691,8 +17694,8 @@
       <c r="H256" t="s">
         <v>744</v>
       </c>
-      <c r="J256" t="s">
-        <v>376</v>
+      <c r="J256">
+        <v>2025</v>
       </c>
       <c r="K256">
         <v>75</v>
@@ -17707,7 +17710,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>745</v>
       </c>
@@ -17748,7 +17751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>749</v>
       </c>
@@ -17792,7 +17795,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>752</v>
       </c>
@@ -17836,7 +17839,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>755</v>
       </c>
@@ -17880,7 +17883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>759</v>
       </c>
@@ -17924,7 +17927,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>763</v>
       </c>
@@ -17968,7 +17971,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>767</v>
       </c>
@@ -18012,7 +18015,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>772</v>
       </c>
@@ -18056,7 +18059,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:18">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>776</v>
       </c>
@@ -18103,7 +18106,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:18">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>779</v>
       </c>
@@ -18147,7 +18150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:18">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>783</v>
       </c>
@@ -18191,7 +18194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:18">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>786</v>
       </c>
@@ -18235,7 +18238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:18">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>791</v>
       </c>
@@ -18276,7 +18279,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:18">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>14700422</v>
       </c>
@@ -18320,7 +18323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:18">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>795</v>
       </c>
@@ -18361,7 +18364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:18">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>797</v>
       </c>
@@ -18402,7 +18405,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:18">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>800</v>
       </c>
@@ -18437,7 +18440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>803</v>
       </c>
@@ -18478,7 +18481,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>806</v>
       </c>
@@ -18522,7 +18525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>810</v>
       </c>
@@ -18563,7 +18566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>813</v>
       </c>
@@ -18601,7 +18604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:18">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>815</v>
       </c>
@@ -18639,7 +18642,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>817</v>
       </c>
@@ -18680,7 +18683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>820</v>
       </c>
@@ -18721,7 +18724,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:18">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>823</v>
       </c>
@@ -18759,7 +18762,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>826</v>
       </c>
@@ -18800,7 +18803,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>828</v>
       </c>
@@ -18844,7 +18847,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>830</v>
       </c>
@@ -18882,7 +18885,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>831</v>
       </c>
@@ -18923,7 +18926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>833</v>
       </c>
@@ -18964,7 +18967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>836</v>
       </c>
@@ -19005,7 +19008,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>838</v>
       </c>
@@ -19049,7 +19052,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>841</v>
       </c>
@@ -19093,7 +19096,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>845</v>
       </c>
@@ -19134,7 +19137,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>848</v>
       </c>
@@ -19175,7 +19178,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>850</v>
       </c>
@@ -19219,7 +19222,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>852</v>
       </c>
@@ -19263,7 +19266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>854</v>
       </c>
@@ -19307,7 +19310,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>856</v>
       </c>
@@ -19348,7 +19351,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>857</v>
       </c>
@@ -19392,7 +19395,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>858</v>
       </c>
@@ -19433,7 +19436,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>861</v>
       </c>
@@ -19474,7 +19477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>863</v>
       </c>
@@ -19515,7 +19518,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>865</v>
       </c>
@@ -19553,7 +19556,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>866</v>
       </c>
@@ -19597,7 +19600,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>868</v>
       </c>
@@ -19638,7 +19641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>872</v>
       </c>
@@ -19679,7 +19682,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>876</v>
       </c>
@@ -19720,7 +19723,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>879</v>
       </c>
@@ -19764,7 +19767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>881</v>
       </c>
@@ -19808,7 +19811,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>883</v>
       </c>
@@ -19849,7 +19852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>887</v>
       </c>
@@ -19893,7 +19896,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>890</v>
       </c>
@@ -19934,7 +19937,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>891</v>
       </c>
@@ -19975,7 +19978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>894</v>
       </c>
@@ -20019,7 +20022,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>897</v>
       </c>
@@ -20054,7 +20057,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>899</v>
       </c>
@@ -20092,7 +20095,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>901</v>
       </c>
@@ -20136,7 +20139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>903</v>
       </c>
@@ -20180,7 +20183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>905</v>
       </c>
@@ -20215,7 +20218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>907</v>
       </c>
@@ -20253,7 +20256,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>908</v>
       </c>
@@ -20294,7 +20297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>909</v>
       </c>
@@ -20335,7 +20338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>910</v>
       </c>
@@ -20376,7 +20379,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:18">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>911</v>
       </c>
@@ -20417,7 +20420,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:18">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>913</v>
       </c>
@@ -20461,7 +20464,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="323" spans="1:18">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>914</v>
       </c>
@@ -20499,7 +20502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:18">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>915</v>
       </c>
@@ -20543,7 +20546,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:18">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>917</v>
       </c>
@@ -20587,7 +20590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:18">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>921</v>
       </c>
@@ -20631,7 +20634,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:18">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>928</v>
       </c>
@@ -20675,7 +20678,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:18">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>932</v>
       </c>
@@ -20719,7 +20722,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:18">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>934</v>
       </c>
@@ -20763,7 +20766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:18">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>936</v>
       </c>
@@ -20798,7 +20801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:18">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>939</v>
       </c>
@@ -20842,7 +20845,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:18">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>940</v>
       </c>
@@ -20886,7 +20889,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:18">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>942</v>
       </c>
@@ -20930,7 +20933,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:18">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>943</v>
       </c>
@@ -20974,7 +20977,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>947</v>
       </c>
@@ -21009,7 +21012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>949</v>
       </c>
@@ -21044,7 +21047,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>953</v>
       </c>
@@ -21082,7 +21085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>955</v>
       </c>
@@ -21126,7 +21129,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>956</v>
       </c>
@@ -21164,7 +21167,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>959</v>
       </c>
@@ -21205,7 +21208,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>963</v>
       </c>
@@ -21246,7 +21249,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>966</v>
       </c>
@@ -21290,7 +21293,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>970</v>
       </c>
@@ -21334,7 +21337,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>972</v>
       </c>
@@ -21375,7 +21378,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>975</v>
       </c>
@@ -21416,7 +21419,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>977</v>
       </c>
@@ -21460,7 +21463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>980</v>
       </c>
@@ -21501,7 +21504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>982</v>
       </c>
@@ -21542,7 +21545,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>984</v>
       </c>
@@ -21586,7 +21589,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>986</v>
       </c>
@@ -21630,7 +21633,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>989</v>
       </c>
@@ -21668,7 +21671,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>991</v>
       </c>
@@ -21709,7 +21712,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="353" spans="1:18">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>992</v>
       </c>
@@ -21750,7 +21753,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:18">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>993</v>
       </c>
@@ -21794,7 +21797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:18">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>995</v>
       </c>
@@ -21835,7 +21838,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:18">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>1000</v>
       </c>
@@ -21876,7 +21879,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:18">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>1003</v>
       </c>
@@ -21917,7 +21920,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:18">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>1007</v>
       </c>
@@ -21958,7 +21961,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="359" spans="1:18">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1010</v>
       </c>
@@ -21999,7 +22002,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:18">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>1012</v>
       </c>
@@ -22040,7 +22043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:18">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1014</v>
       </c>
@@ -22081,7 +22084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:18">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>1016</v>
       </c>
@@ -22122,7 +22125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:18">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>1019</v>
       </c>
@@ -22166,7 +22169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="364" spans="1:18">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1021</v>
       </c>
@@ -22207,7 +22210,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:18">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1024</v>
       </c>
@@ -22248,7 +22251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:18">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1026</v>
       </c>
@@ -22292,7 +22295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:18">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1029</v>
       </c>
@@ -22333,7 +22336,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:18">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1033</v>
       </c>
@@ -22377,7 +22380,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1037</v>
       </c>
@@ -22418,7 +22421,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1039</v>
       </c>
@@ -22462,7 +22465,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1041</v>
       </c>
@@ -22503,7 +22506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1043</v>
       </c>
@@ -22541,7 +22544,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1046</v>
       </c>
@@ -22582,7 +22585,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1050</v>
       </c>
@@ -22623,7 +22626,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1053</v>
       </c>
@@ -22664,7 +22667,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1056</v>
       </c>
@@ -22705,7 +22708,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1059</v>
       </c>
@@ -22746,7 +22749,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1062</v>
       </c>
@@ -22787,7 +22790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>1065</v>
       </c>
@@ -22831,7 +22834,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1069</v>
       </c>
@@ -22872,7 +22875,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1072</v>
       </c>
@@ -22913,7 +22916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1074</v>
       </c>
@@ -22954,7 +22957,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>1077</v>
       </c>
@@ -22995,7 +22998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>1081</v>
       </c>
@@ -23036,7 +23039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1084</v>
       </c>
@@ -23077,7 +23080,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>1086</v>
       </c>
@@ -23118,7 +23121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1089</v>
       </c>
@@ -23159,7 +23162,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>1091</v>
       </c>
@@ -23200,7 +23203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1093</v>
       </c>
@@ -23238,7 +23241,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>1097</v>
       </c>
@@ -23276,7 +23279,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>53800623</v>
       </c>
@@ -23317,7 +23320,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1102</v>
       </c>
@@ -23358,7 +23361,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1104</v>
       </c>
@@ -23399,7 +23402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1106</v>
       </c>
@@ -23440,7 +23443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>1108</v>
       </c>
@@ -23481,7 +23484,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>1109</v>
       </c>
@@ -23522,7 +23525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>1110</v>
       </c>
@@ -23563,7 +23566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>1112</v>
       </c>
@@ -23604,7 +23607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>1114</v>
       </c>
@@ -23645,7 +23648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>1116</v>
       </c>
@@ -23686,7 +23689,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1118</v>
       </c>
@@ -23727,7 +23730,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>1121</v>
       </c>
@@ -23771,7 +23774,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>1123</v>
       </c>
@@ -23815,7 +23818,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>1125</v>
       </c>
@@ -23856,7 +23859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>1127</v>
       </c>
@@ -23897,7 +23900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>1130</v>
       </c>
@@ -23938,7 +23941,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1134</v>
       </c>
@@ -23979,7 +23982,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1136</v>
       </c>
@@ -24017,7 +24020,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1139</v>
       </c>
@@ -24058,7 +24061,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1141</v>
       </c>
@@ -24099,7 +24102,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1144</v>
       </c>
@@ -24140,7 +24143,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1147</v>
       </c>
@@ -24181,7 +24184,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1149</v>
       </c>
@@ -24225,7 +24228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1151</v>
       </c>
@@ -24266,7 +24269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>1153</v>
       </c>
@@ -24310,7 +24313,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1155</v>
       </c>
@@ -24354,7 +24357,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1157</v>
       </c>
@@ -24398,7 +24401,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>1160</v>
       </c>
@@ -24439,7 +24442,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1164</v>
       </c>
@@ -24477,7 +24480,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>1166</v>
       </c>
@@ -24521,7 +24524,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>1170</v>
       </c>
@@ -24562,7 +24565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>1173</v>
       </c>
@@ -24603,7 +24606,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1175</v>
       </c>
@@ -24644,7 +24647,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>1178</v>
       </c>
@@ -24685,7 +24688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>1181</v>
       </c>
@@ -24726,7 +24729,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1183</v>
       </c>
@@ -24767,7 +24770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>1186</v>
       </c>
@@ -24811,7 +24814,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1190</v>
       </c>
@@ -24852,7 +24855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>16003124</v>
       </c>
@@ -24893,7 +24896,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1194</v>
       </c>
@@ -24937,7 +24940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1196</v>
       </c>
@@ -24981,7 +24984,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>1198</v>
       </c>
@@ -25025,7 +25028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="433" spans="1:16">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1200</v>
       </c>
@@ -25063,7 +25066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="434" spans="1:16">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>1203</v>
       </c>
@@ -25107,7 +25110,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="435" spans="1:16">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1205</v>
       </c>
@@ -25142,7 +25145,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="436" spans="1:16">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>1208</v>
       </c>
@@ -25180,7 +25183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="437" spans="1:16">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1210</v>
       </c>
@@ -25218,7 +25221,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="438" spans="1:16">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>1214</v>
       </c>
@@ -25259,7 +25262,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="439" spans="1:16">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B439" t="s">
         <v>118</v>
       </c>
@@ -25297,7 +25300,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="440" spans="1:16">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>1219</v>
       </c>
@@ -25338,7 +25341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="441" spans="1:16">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>1221</v>
       </c>
@@ -25382,7 +25385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="442" spans="1:16">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>1225</v>
       </c>
@@ -25420,7 +25423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="443" spans="1:16">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>1228</v>
       </c>
@@ -25461,7 +25464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="444" spans="1:16">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1231</v>
       </c>
@@ -25499,7 +25502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="445" spans="1:16">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1232</v>
       </c>
@@ -25540,7 +25543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="446" spans="1:16">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1233</v>
       </c>
@@ -25581,7 +25584,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="447" spans="1:16">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>1234</v>
       </c>
@@ -25622,7 +25625,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="448" spans="1:16">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1236</v>
       </c>
@@ -25663,7 +25666,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="449" spans="1:18">
+    <row r="449" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1239</v>
       </c>
@@ -25704,7 +25707,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="450" spans="1:18">
+    <row r="450" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1240</v>
       </c>
@@ -25745,7 +25748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="451" spans="1:18">
+    <row r="451" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1242</v>
       </c>
@@ -25786,7 +25789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="452" spans="1:18">
+    <row r="452" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1248</v>
       </c>
@@ -25830,7 +25833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="453" spans="1:18">
+    <row r="453" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1251</v>
       </c>
@@ -25871,7 +25874,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="454" spans="1:18">
+    <row r="454" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1253</v>
       </c>
@@ -25912,7 +25915,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="455" spans="1:18">
+    <row r="455" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1257</v>
       </c>
@@ -25953,7 +25956,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="456" spans="1:18">
+    <row r="456" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1261</v>
       </c>
@@ -25994,7 +25997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="457" spans="1:18">
+    <row r="457" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1263</v>
       </c>
@@ -26032,7 +26035,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="458" spans="1:18">
+    <row r="458" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>1266</v>
       </c>
@@ -26076,7 +26079,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="459" spans="1:18">
+    <row r="459" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>1270</v>
       </c>
@@ -26114,7 +26117,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="460" spans="1:18">
+    <row r="460" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>1274</v>
       </c>
@@ -26155,7 +26158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="461" spans="1:18">
+    <row r="461" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1277</v>
       </c>
@@ -26196,7 +26199,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="462" spans="1:18">
+    <row r="462" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>1280</v>
       </c>
@@ -26237,7 +26240,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="463" spans="1:18">
+    <row r="463" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>1282</v>
       </c>
@@ -26278,7 +26281,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="464" spans="1:18">
+    <row r="464" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>1285</v>
       </c>
@@ -26319,7 +26322,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="465" spans="1:16">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>1288</v>
       </c>
@@ -26360,7 +26363,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="466" spans="1:16">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1292</v>
       </c>
@@ -26401,7 +26404,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="467" spans="1:16">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1294</v>
       </c>
@@ -26442,7 +26445,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="468" spans="1:16">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>1296</v>
       </c>
@@ -26483,7 +26486,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="469" spans="1:16">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>1297</v>
       </c>
@@ -26524,7 +26527,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="470" spans="1:16">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1299</v>
       </c>
@@ -26565,7 +26568,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="471" spans="1:16">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>1301</v>
       </c>
@@ -26606,7 +26609,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="472" spans="1:16">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>1303</v>
       </c>
@@ -26647,7 +26650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="473" spans="1:16">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>1305</v>
       </c>
@@ -26688,7 +26691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="474" spans="1:16">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>1307</v>
       </c>
@@ -26729,7 +26732,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="475" spans="1:16">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>1309</v>
       </c>
@@ -26767,7 +26770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="476" spans="1:16">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1313</v>
       </c>
@@ -26802,7 +26805,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="477" spans="1:16">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1315</v>
       </c>
@@ -26837,7 +26840,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="478" spans="1:16">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1318</v>
       </c>
@@ -26875,7 +26878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="479" spans="1:16">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1322</v>
       </c>
@@ -26913,7 +26916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="480" spans="1:16">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1325</v>
       </c>
@@ -26951,7 +26954,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="481" spans="1:16">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1328</v>
       </c>
@@ -26986,7 +26989,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="482" spans="1:16">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1331</v>
       </c>
@@ -27024,7 +27027,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="483" spans="1:16">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1334</v>
       </c>
@@ -27062,7 +27065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="484" spans="1:16">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>1337</v>
       </c>
@@ -27100,7 +27103,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="485" spans="1:16">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1340</v>
       </c>
@@ -27138,7 +27141,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="486" spans="1:16">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>1342</v>
       </c>
@@ -27176,7 +27179,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="487" spans="1:16">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>1344</v>
       </c>
@@ -27214,7 +27217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="488" spans="1:16">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>1345</v>
       </c>
@@ -27252,7 +27255,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="489" spans="1:16">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>1348</v>
       </c>
@@ -27290,7 +27293,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="490" spans="1:16">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>1351</v>
       </c>
@@ -27328,7 +27331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="491" spans="1:16">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1354</v>
       </c>
@@ -27366,7 +27369,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="492" spans="1:16">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>1356</v>
       </c>
@@ -27404,7 +27407,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="493" spans="1:16">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>1359</v>
       </c>
@@ -27442,7 +27445,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="494" spans="1:16">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1361</v>
       </c>
@@ -27480,7 +27483,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="495" spans="1:16">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1363</v>
       </c>
@@ -27518,7 +27521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="496" spans="1:16">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1365</v>
       </c>
@@ -27556,7 +27559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="497" spans="1:16">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1368</v>
       </c>
@@ -27594,7 +27597,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="498" spans="1:16">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1371</v>
       </c>
@@ -27632,7 +27635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="499" spans="1:16">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1373</v>
       </c>
@@ -27670,7 +27673,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="500" spans="1:16">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1375</v>
       </c>
@@ -27711,7 +27714,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="501" spans="1:16">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1378</v>
       </c>
@@ -27752,7 +27755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="502" spans="1:16">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1380</v>
       </c>
@@ -27793,7 +27796,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="503" spans="1:16">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>1382</v>
       </c>
@@ -27834,7 +27837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="504" spans="1:16">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>1384</v>
       </c>
@@ -27875,7 +27878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="505" spans="1:16">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>1386</v>
       </c>
@@ -27913,7 +27916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" spans="1:16">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>1392</v>
       </c>
@@ -27951,7 +27954,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="507" spans="1:16">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>1394</v>
       </c>
@@ -27986,7 +27989,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="508" spans="1:16">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>1398</v>
       </c>
@@ -28021,7 +28024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="509" spans="1:16">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1402</v>
       </c>
@@ -28056,7 +28059,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:16">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>1405</v>
       </c>
@@ -28091,7 +28094,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="511" spans="1:16">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>1409</v>
       </c>
@@ -28126,7 +28129,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="512" spans="1:16">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>1412</v>
       </c>
@@ -28161,7 +28164,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="513" spans="1:16">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>1416</v>
       </c>
@@ -28196,7 +28199,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="514" spans="1:16">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>1419</v>
       </c>
@@ -28234,7 +28237,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="515" spans="1:16">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>1422</v>
       </c>
@@ -28272,7 +28275,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="516" spans="1:16">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>1426</v>
       </c>
@@ -28310,7 +28313,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="517" spans="1:16">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>1431</v>
       </c>
@@ -28356,9 +28359,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1433</v>
       </c>
@@ -28434,15 +28437,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1455</v>
       </c>
@@ -28467,14 +28470,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1460</v>
       </c>
@@ -28485,7 +28488,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1463</v>
       </c>
@@ -28504,7 +28507,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N517"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -28522,7 +28525,7 @@
     <col min="14" max="14" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27.6">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1466</v>
       </c>
@@ -28566,7 +28569,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -28607,7 +28610,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -28651,7 +28654,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -28692,7 +28695,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -28733,7 +28736,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>6</v>
       </c>
@@ -28777,7 +28780,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -28818,7 +28821,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8</v>
       </c>
@@ -28859,7 +28862,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
@@ -28900,7 +28903,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
@@ -28941,7 +28944,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
@@ -28982,7 +28985,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
@@ -29023,7 +29026,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
       </c>
@@ -29064,7 +29067,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>14</v>
       </c>
@@ -29105,7 +29108,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
@@ -29146,7 +29149,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>16</v>
       </c>
@@ -29187,7 +29190,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>17</v>
       </c>
@@ -29228,7 +29231,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>18</v>
       </c>
@@ -29269,7 +29272,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>19</v>
       </c>
@@ -29310,7 +29313,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>20</v>
       </c>
@@ -29351,7 +29354,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>21</v>
       </c>
@@ -29392,7 +29395,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>22</v>
       </c>
@@ -29433,7 +29436,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>23</v>
       </c>
@@ -29474,7 +29477,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>24</v>
       </c>
@@ -29515,7 +29518,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>25</v>
       </c>
@@ -29556,7 +29559,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>26</v>
       </c>
@@ -29597,7 +29600,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>27</v>
       </c>
@@ -29638,7 +29641,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>28</v>
       </c>
@@ -29679,7 +29682,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>29</v>
       </c>
@@ -29720,7 +29723,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>30</v>
       </c>
@@ -29761,7 +29764,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>31</v>
       </c>
@@ -29802,7 +29805,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32</v>
       </c>
@@ -29837,7 +29840,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>33</v>
       </c>
@@ -29878,7 +29881,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34</v>
       </c>
@@ -29919,7 +29922,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>35</v>
       </c>
@@ -29957,7 +29960,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -29995,7 +29998,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>37</v>
       </c>
@@ -30036,7 +30039,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
@@ -30077,7 +30080,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>39</v>
       </c>
@@ -30118,7 +30121,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40</v>
       </c>
@@ -30159,7 +30162,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41</v>
       </c>
@@ -30197,7 +30200,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>42</v>
       </c>
@@ -30235,7 +30238,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>43</v>
       </c>
@@ -30273,7 +30276,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>44</v>
       </c>
@@ -30311,7 +30314,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>45</v>
       </c>
@@ -30352,7 +30355,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>46</v>
       </c>
@@ -30393,7 +30396,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>47</v>
       </c>
@@ -30431,7 +30434,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>48</v>
       </c>
@@ -30469,7 +30472,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>49</v>
       </c>
@@ -30507,7 +30510,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>50</v>
       </c>
@@ -30545,7 +30548,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>51</v>
       </c>
@@ -30583,7 +30586,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>52</v>
       </c>
@@ -30621,7 +30624,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>53</v>
       </c>
@@ -30662,7 +30665,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>54</v>
       </c>
@@ -30700,7 +30703,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>55</v>
       </c>
@@ -30738,7 +30741,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>56</v>
       </c>
@@ -30776,7 +30779,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>57</v>
       </c>
@@ -30817,7 +30820,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>58</v>
       </c>
@@ -30852,7 +30855,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>59</v>
       </c>
@@ -30893,7 +30896,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>60</v>
       </c>
@@ -30931,7 +30934,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>61</v>
       </c>
@@ -30972,7 +30975,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>62</v>
       </c>
@@ -31010,7 +31013,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>63</v>
       </c>
@@ -31048,7 +31051,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>64</v>
       </c>
@@ -31086,7 +31089,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>65</v>
       </c>
@@ -31124,7 +31127,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>66</v>
       </c>
@@ -31162,7 +31165,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>67</v>
       </c>
@@ -31200,7 +31203,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>68</v>
       </c>
@@ -31238,7 +31241,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>69</v>
       </c>
@@ -31279,7 +31282,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>70</v>
       </c>
@@ -31317,7 +31320,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>71</v>
       </c>
@@ -31358,7 +31361,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>72</v>
       </c>
@@ -31399,7 +31402,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>73</v>
       </c>
@@ -31440,7 +31443,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>74</v>
       </c>
@@ -31481,7 +31484,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>75</v>
       </c>
@@ -31519,7 +31522,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>76</v>
       </c>
@@ -31560,7 +31563,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>77</v>
       </c>
@@ -31601,7 +31604,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>78</v>
       </c>
@@ -31642,7 +31645,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>79</v>
       </c>
@@ -31683,7 +31686,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>80</v>
       </c>
@@ -31721,7 +31724,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>81</v>
       </c>
@@ -31762,7 +31765,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>82</v>
       </c>
@@ -31803,7 +31806,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>83</v>
       </c>
@@ -31844,7 +31847,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>84</v>
       </c>
@@ -31885,7 +31888,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>85</v>
       </c>
@@ -31923,7 +31926,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>86</v>
       </c>
@@ -31964,7 +31967,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>87</v>
       </c>
@@ -31999,7 +32002,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>88</v>
       </c>
@@ -32040,7 +32043,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -32068,7 +32071,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>90</v>
       </c>
@@ -32109,7 +32112,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>91</v>
       </c>
@@ -32147,7 +32150,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>92</v>
       </c>
@@ -32188,7 +32191,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>93</v>
       </c>
@@ -32229,7 +32232,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>94</v>
       </c>
@@ -32270,7 +32273,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>95</v>
       </c>
@@ -32311,7 +32314,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>96</v>
       </c>
@@ -32352,7 +32355,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>97</v>
       </c>
@@ -32393,7 +32396,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>98</v>
       </c>
@@ -32434,7 +32437,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -32466,7 +32469,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -32507,7 +32510,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -32548,7 +32551,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -32589,7 +32592,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -32630,7 +32633,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>104</v>
       </c>
@@ -32671,7 +32674,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>105</v>
       </c>
@@ -32712,7 +32715,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>106</v>
       </c>
@@ -32750,7 +32753,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -32778,7 +32781,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -32806,7 +32809,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>109</v>
       </c>
@@ -32844,7 +32847,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>110</v>
       </c>
@@ -32882,7 +32885,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>111</v>
       </c>
@@ -32923,7 +32926,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>112</v>
       </c>
@@ -32964,7 +32967,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>113</v>
       </c>
@@ -33005,7 +33008,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>114</v>
       </c>
@@ -33045,7 +33048,7 @@
       </c>
       <c r="N114" s="5"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>115</v>
       </c>
@@ -33083,7 +33086,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>116</v>
       </c>
@@ -33121,7 +33124,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>117</v>
       </c>
@@ -33162,7 +33165,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>118</v>
       </c>
@@ -33203,7 +33206,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>119</v>
       </c>
@@ -33238,7 +33241,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>120</v>
       </c>
@@ -33273,7 +33276,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>121</v>
       </c>
@@ -33314,7 +33317,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>122</v>
       </c>
@@ -33352,7 +33355,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>123</v>
       </c>
@@ -33387,7 +33390,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>124</v>
       </c>
@@ -33425,7 +33428,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>125</v>
       </c>
@@ -33466,7 +33469,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>126</v>
       </c>
@@ -33507,7 +33510,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>127</v>
       </c>
@@ -33548,7 +33551,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>128</v>
       </c>
@@ -33589,7 +33592,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>129</v>
       </c>
@@ -33630,7 +33633,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>130</v>
       </c>
@@ -33671,7 +33674,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>131</v>
       </c>
@@ -33712,7 +33715,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>132</v>
       </c>
@@ -33753,7 +33756,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>133</v>
       </c>
@@ -33794,7 +33797,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>134</v>
       </c>
@@ -33835,7 +33838,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>135</v>
       </c>
@@ -33873,7 +33876,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>136</v>
       </c>
@@ -33914,7 +33917,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>137</v>
       </c>
@@ -33952,7 +33955,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>138</v>
       </c>
@@ -33993,7 +33996,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>139</v>
       </c>
@@ -34034,7 +34037,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>140</v>
       </c>
@@ -34075,7 +34078,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>141</v>
       </c>
@@ -34116,7 +34119,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>142</v>
       </c>
@@ -34157,7 +34160,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>143</v>
       </c>
@@ -34195,7 +34198,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>144</v>
       </c>
@@ -34236,7 +34239,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>145</v>
       </c>
@@ -34274,7 +34277,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>146</v>
       </c>
@@ -34316,7 +34319,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>147</v>
       </c>
@@ -34360,7 +34363,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>148</v>
       </c>
@@ -34395,7 +34398,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>149</v>
       </c>
@@ -34430,7 +34433,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>150</v>
       </c>
@@ -34471,7 +34474,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>151</v>
       </c>
@@ -34512,7 +34515,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>152</v>
       </c>
@@ -34547,7 +34550,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>153</v>
       </c>
@@ -34588,7 +34591,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>154</v>
       </c>
@@ -34629,7 +34632,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>155</v>
       </c>
@@ -34670,7 +34673,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>156</v>
       </c>
@@ -34708,7 +34711,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>157</v>
       </c>
@@ -34749,7 +34752,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>158</v>
       </c>
@@ -34790,7 +34793,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>159</v>
       </c>
@@ -34831,7 +34834,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>160</v>
       </c>
@@ -34872,7 +34875,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>161</v>
       </c>
@@ -34914,7 +34917,7 @@
       </c>
       <c r="N161" s="5"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>162</v>
       </c>
@@ -34955,7 +34958,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>163</v>
       </c>
@@ -34996,7 +34999,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>164</v>
       </c>
@@ -35037,7 +35040,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>165</v>
       </c>
@@ -35078,7 +35081,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>166</v>
       </c>
@@ -35113,7 +35116,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>167</v>
       </c>
@@ -35148,7 +35151,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>168</v>
       </c>
@@ -35186,7 +35189,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>169</v>
       </c>
@@ -35227,7 +35230,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>170</v>
       </c>
@@ -35268,7 +35271,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>171</v>
       </c>
@@ -35306,7 +35309,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>172</v>
       </c>
@@ -35347,7 +35350,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>173</v>
       </c>
@@ -35382,7 +35385,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>174</v>
       </c>
@@ -35423,7 +35426,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>175</v>
       </c>
@@ -35464,7 +35467,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>176</v>
       </c>
@@ -35505,7 +35508,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>177</v>
       </c>
@@ -35546,7 +35549,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>178</v>
       </c>
@@ -35587,7 +35590,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>179</v>
       </c>
@@ -35628,7 +35631,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>180</v>
       </c>
@@ -35669,7 +35672,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -35699,7 +35702,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>182</v>
       </c>
@@ -35743,7 +35746,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>183</v>
       </c>
@@ -35787,7 +35790,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>184</v>
       </c>
@@ -35828,7 +35831,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>185</v>
       </c>
@@ -35869,7 +35872,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>186</v>
       </c>
@@ -35910,7 +35913,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>187</v>
       </c>
@@ -35951,7 +35954,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>188</v>
       </c>
@@ -35992,7 +35995,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>189</v>
       </c>
@@ -36033,7 +36036,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>190</v>
       </c>
@@ -36074,7 +36077,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>191</v>
       </c>
@@ -36115,7 +36118,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>192</v>
       </c>
@@ -36156,7 +36159,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>193</v>
       </c>
@@ -36194,7 +36197,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>194</v>
       </c>
@@ -36232,7 +36235,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>195</v>
       </c>
@@ -36273,7 +36276,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>196</v>
       </c>
@@ -36315,7 +36318,7 @@
       </c>
       <c r="N196" s="5"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>197</v>
       </c>
@@ -36356,7 +36359,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>198</v>
       </c>
@@ -36397,7 +36400,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>199</v>
       </c>
@@ -36438,7 +36441,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>200</v>
       </c>
@@ -36479,7 +36482,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>201</v>
       </c>
@@ -36520,7 +36523,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>202</v>
       </c>
@@ -36561,7 +36564,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>203</v>
       </c>
@@ -36601,7 +36604,7 @@
       </c>
       <c r="N203" s="5"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>204</v>
       </c>
@@ -36643,7 +36646,7 @@
       </c>
       <c r="N204" s="5"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>205</v>
       </c>
@@ -36684,7 +36687,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>206</v>
       </c>
@@ -36725,7 +36728,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>207</v>
       </c>
@@ -36766,7 +36769,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>208</v>
       </c>
@@ -36807,7 +36810,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>209</v>
       </c>
@@ -36845,7 +36848,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>210</v>
       </c>
@@ -36886,7 +36889,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>211</v>
       </c>
@@ -36927,7 +36930,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>212</v>
       </c>
@@ -36968,7 +36971,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>213</v>
       </c>
@@ -37009,7 +37012,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>214</v>
       </c>
@@ -37047,7 +37050,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>215</v>
       </c>
@@ -37089,7 +37092,7 @@
       </c>
       <c r="N215" s="5"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>216</v>
       </c>
@@ -37130,7 +37133,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>217</v>
       </c>
@@ -37168,7 +37171,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -37200,7 +37203,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>219</v>
       </c>
@@ -37241,7 +37244,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>220</v>
       </c>
@@ -37279,7 +37282,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>221</v>
       </c>
@@ -37320,7 +37323,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>222</v>
       </c>
@@ -37361,7 +37364,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>223</v>
       </c>
@@ -37402,7 +37405,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>224</v>
       </c>
@@ -37443,7 +37446,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>225</v>
       </c>
@@ -37484,7 +37487,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>226</v>
       </c>
@@ -37525,7 +37528,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>227</v>
       </c>
@@ -37566,7 +37569,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>228</v>
       </c>
@@ -37608,7 +37611,7 @@
       </c>
       <c r="N228" s="5"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>229</v>
       </c>
@@ -37649,7 +37652,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>230</v>
       </c>
@@ -37690,7 +37693,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>231</v>
       </c>
@@ -37731,7 +37734,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>232</v>
       </c>
@@ -37772,7 +37775,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>233</v>
       </c>
@@ -37813,7 +37816,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>234</v>
       </c>
@@ -37854,7 +37857,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>235</v>
       </c>
@@ -37895,7 +37898,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>236</v>
       </c>
@@ -37937,7 +37940,7 @@
       </c>
       <c r="N236" s="5"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>237</v>
       </c>
@@ -37978,7 +37981,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>238</v>
       </c>
@@ -38016,7 +38019,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>239</v>
       </c>
@@ -38057,7 +38060,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>240</v>
       </c>
@@ -38098,7 +38101,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>241</v>
       </c>
@@ -38140,7 +38143,7 @@
       </c>
       <c r="N241" s="5"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>242</v>
       </c>
@@ -38182,7 +38185,7 @@
       </c>
       <c r="N242" s="5"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>243</v>
       </c>
@@ -38223,7 +38226,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>244</v>
       </c>
@@ -38264,7 +38267,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>245</v>
       </c>
@@ -38305,7 +38308,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>246</v>
       </c>
@@ -38346,7 +38349,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>247</v>
       </c>
@@ -38384,7 +38387,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>248</v>
       </c>
@@ -38425,7 +38428,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>249</v>
       </c>
@@ -38466,7 +38469,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>250</v>
       </c>
@@ -38510,7 +38513,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -38540,7 +38543,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>252</v>
       </c>
@@ -38581,7 +38584,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>253</v>
       </c>
@@ -38622,7 +38625,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>254</v>
       </c>
@@ -38663,7 +38666,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>255</v>
       </c>
@@ -38704,7 +38707,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>256</v>
       </c>
@@ -38745,7 +38748,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>257</v>
       </c>
@@ -38787,7 +38790,7 @@
       </c>
       <c r="N257" s="5"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>258</v>
       </c>
@@ -38828,7 +38831,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>259</v>
       </c>
@@ -38870,7 +38873,7 @@
       </c>
       <c r="N259" s="5"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>260</v>
       </c>
@@ -38911,7 +38914,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>261</v>
       </c>
@@ -38952,7 +38955,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>262</v>
       </c>
@@ -38993,7 +38996,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>263</v>
       </c>
@@ -39034,7 +39037,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>264</v>
       </c>
@@ -39075,7 +39078,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>265</v>
       </c>
@@ -39116,7 +39119,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>266</v>
       </c>
@@ -39157,7 +39160,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>267</v>
       </c>
@@ -39198,7 +39201,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>268</v>
       </c>
@@ -39239,7 +39242,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>269</v>
       </c>
@@ -39280,7 +39283,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>270</v>
       </c>
@@ -39318,7 +39321,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -39350,7 +39353,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>272</v>
       </c>
@@ -39388,7 +39391,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>273</v>
       </c>
@@ -39426,7 +39429,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>274</v>
       </c>
@@ -39461,7 +39464,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>275</v>
       </c>
@@ -39502,7 +39505,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>276</v>
       </c>
@@ -39543,7 +39546,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>277</v>
       </c>
@@ -39584,7 +39587,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>278</v>
       </c>
@@ -39622,7 +39625,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>279</v>
       </c>
@@ -39660,7 +39663,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>280</v>
       </c>
@@ -39701,7 +39704,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>281</v>
       </c>
@@ -39742,7 +39745,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>282</v>
       </c>
@@ -39782,7 +39785,7 @@
       </c>
       <c r="N282" s="5"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>283</v>
       </c>
@@ -39823,7 +39826,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>284</v>
       </c>
@@ -39865,7 +39868,7 @@
       </c>
       <c r="N284" s="5"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>285</v>
       </c>
@@ -39903,7 +39906,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>286</v>
       </c>
@@ -39944,7 +39947,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>287</v>
       </c>
@@ -39985,7 +39988,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>288</v>
       </c>
@@ -40026,7 +40029,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>289</v>
       </c>
@@ -40067,7 +40070,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>290</v>
       </c>
@@ -40108,7 +40111,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>291</v>
       </c>
@@ -40149,7 +40152,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>292</v>
       </c>
@@ -40190,7 +40193,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>293</v>
       </c>
@@ -40231,7 +40234,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>294</v>
       </c>
@@ -40272,7 +40275,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>295</v>
       </c>
@@ -40313,7 +40316,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>296</v>
       </c>
@@ -40351,7 +40354,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>297</v>
       </c>
@@ -40392,7 +40395,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>298</v>
       </c>
@@ -40430,7 +40433,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>299</v>
       </c>
@@ -40471,7 +40474,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>300</v>
       </c>
@@ -40512,7 +40515,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>301</v>
       </c>
@@ -40550,7 +40553,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>302</v>
       </c>
@@ -40591,7 +40594,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>303</v>
       </c>
@@ -40632,7 +40635,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>304</v>
       </c>
@@ -40673,7 +40676,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>305</v>
       </c>
@@ -40714,7 +40717,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>306</v>
       </c>
@@ -40755,7 +40758,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>307</v>
       </c>
@@ -40796,7 +40799,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>308</v>
       </c>
@@ -40837,7 +40840,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>309</v>
       </c>
@@ -40878,7 +40881,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>310</v>
       </c>
@@ -40919,7 +40922,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>311</v>
       </c>
@@ -40960,7 +40963,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>312</v>
       </c>
@@ -41001,7 +41004,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>313</v>
       </c>
@@ -41036,7 +41039,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>314</v>
       </c>
@@ -41074,7 +41077,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>315</v>
       </c>
@@ -41115,7 +41118,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>316</v>
       </c>
@@ -41156,7 +41159,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>317</v>
       </c>
@@ -41191,7 +41194,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>318</v>
       </c>
@@ -41229,7 +41232,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>319</v>
       </c>
@@ -41270,7 +41273,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>320</v>
       </c>
@@ -41308,7 +41311,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>321</v>
       </c>
@@ -41349,7 +41352,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>322</v>
       </c>
@@ -41390,7 +41393,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>323</v>
       </c>
@@ -41431,7 +41434,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>324</v>
       </c>
@@ -41469,7 +41472,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>325</v>
       </c>
@@ -41510,7 +41513,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>326</v>
       </c>
@@ -41551,7 +41554,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>327</v>
       </c>
@@ -41593,7 +41596,7 @@
       </c>
       <c r="N327" s="5"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>328</v>
       </c>
@@ -41634,7 +41637,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>329</v>
       </c>
@@ -41675,7 +41678,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" s="5">
         <v>330</v>
       </c>
@@ -41717,7 +41720,7 @@
       </c>
       <c r="N330" s="5"/>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>331</v>
       </c>
@@ -41752,7 +41755,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>332</v>
       </c>
@@ -41793,7 +41796,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>333</v>
       </c>
@@ -41834,7 +41837,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>334</v>
       </c>
@@ -41875,7 +41878,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>335</v>
       </c>
@@ -41916,7 +41919,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>336</v>
       </c>
@@ -41951,7 +41954,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>337</v>
       </c>
@@ -41986,7 +41989,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>338</v>
       </c>
@@ -42024,7 +42027,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>339</v>
       </c>
@@ -42065,7 +42068,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>340</v>
       </c>
@@ -42103,7 +42106,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>341</v>
       </c>
@@ -42144,7 +42147,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>342</v>
       </c>
@@ -42185,7 +42188,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>343</v>
       </c>
@@ -42226,7 +42229,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>344</v>
       </c>
@@ -42267,7 +42270,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>345</v>
       </c>
@@ -42308,7 +42311,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>346</v>
       </c>
@@ -42346,7 +42349,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>347</v>
       </c>
@@ -42387,7 +42390,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>348</v>
       </c>
@@ -42428,7 +42431,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>349</v>
       </c>
@@ -42469,7 +42472,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>350</v>
       </c>
@@ -42510,7 +42513,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>351</v>
       </c>
@@ -42551,7 +42554,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>352</v>
       </c>
@@ -42589,7 +42592,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>353</v>
       </c>
@@ -42631,7 +42634,7 @@
       </c>
       <c r="N353" s="5"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>354</v>
       </c>
@@ -42669,7 +42672,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>355</v>
       </c>
@@ -42710,7 +42713,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356" s="5">
         <v>356</v>
       </c>
@@ -42752,7 +42755,7 @@
       </c>
       <c r="N356" s="5"/>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357" s="5">
         <v>357</v>
       </c>
@@ -42794,7 +42797,7 @@
       </c>
       <c r="N357" s="5"/>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358" s="5">
         <v>358</v>
       </c>
@@ -42836,7 +42839,7 @@
       </c>
       <c r="N358" s="5"/>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>359</v>
       </c>
@@ -42877,7 +42880,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>360</v>
       </c>
@@ -42918,7 +42921,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>361</v>
       </c>
@@ -42959,7 +42962,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>362</v>
       </c>
@@ -43000,7 +43003,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>363</v>
       </c>
@@ -43041,7 +43044,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364" s="5">
         <v>364</v>
       </c>
@@ -43085,7 +43088,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365" s="5">
         <v>365</v>
       </c>
@@ -43129,7 +43132,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366" s="5">
         <v>366</v>
       </c>
@@ -43173,7 +43176,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367" s="5">
         <v>367</v>
       </c>
@@ -43217,7 +43220,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>368</v>
       </c>
@@ -43258,7 +43261,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>369</v>
       </c>
@@ -43299,7 +43302,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>370</v>
       </c>
@@ -43340,7 +43343,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>371</v>
       </c>
@@ -43381,7 +43384,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>372</v>
       </c>
@@ -43422,7 +43425,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>373</v>
       </c>
@@ -43460,7 +43463,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>374</v>
       </c>
@@ -43501,7 +43504,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>375</v>
       </c>
@@ -43542,7 +43545,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>376</v>
       </c>
@@ -43583,7 +43586,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>377</v>
       </c>
@@ -43624,7 +43627,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>378</v>
       </c>
@@ -43665,7 +43668,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>379</v>
       </c>
@@ -43706,7 +43709,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>380</v>
       </c>
@@ -43747,7 +43750,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>381</v>
       </c>
@@ -43788,7 +43791,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>382</v>
       </c>
@@ -43829,7 +43832,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>383</v>
       </c>
@@ -43870,7 +43873,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384" s="5">
         <v>384</v>
       </c>
@@ -43914,7 +43917,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385" s="5">
         <v>385</v>
       </c>
@@ -43958,7 +43961,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386" s="5">
         <v>386</v>
       </c>
@@ -44002,7 +44005,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>387</v>
       </c>
@@ -44043,7 +44046,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>388</v>
       </c>
@@ -44084,7 +44087,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>389</v>
       </c>
@@ -44125,7 +44128,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>390</v>
       </c>
@@ -44163,7 +44166,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>391</v>
       </c>
@@ -44201,7 +44204,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" s="6">
         <v>392</v>
       </c>
@@ -44233,7 +44236,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393" s="5">
         <v>393</v>
       </c>
@@ -44275,7 +44278,7 @@
       </c>
       <c r="N393" s="5"/>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394" s="5">
         <v>394</v>
       </c>
@@ -44317,7 +44320,7 @@
       </c>
       <c r="N394" s="5"/>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395" s="5">
         <v>395</v>
       </c>
@@ -44359,7 +44362,7 @@
       </c>
       <c r="N395" s="5"/>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396" s="5">
         <v>396</v>
       </c>
@@ -44401,7 +44404,7 @@
       </c>
       <c r="N396" s="5"/>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397" s="5">
         <v>397</v>
       </c>
@@ -44443,7 +44446,7 @@
       </c>
       <c r="N397" s="5"/>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>398</v>
       </c>
@@ -44484,7 +44487,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>399</v>
       </c>
@@ -44525,7 +44528,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>400</v>
       </c>
@@ -44566,7 +44569,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>401</v>
       </c>
@@ -44607,7 +44610,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="402" spans="1:14">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>402</v>
       </c>
@@ -44648,7 +44651,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="403" spans="1:14">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>403</v>
       </c>
@@ -44689,7 +44692,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="404" spans="1:14">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>404</v>
       </c>
@@ -44730,7 +44733,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="405" spans="1:14">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>405</v>
       </c>
@@ -44771,7 +44774,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="406" spans="1:14">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406" s="5">
         <v>406</v>
       </c>
@@ -44813,7 +44816,7 @@
       </c>
       <c r="N406" s="5"/>
     </row>
-    <row r="407" spans="1:14">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>407</v>
       </c>
@@ -44854,7 +44857,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="408" spans="1:14">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>408</v>
       </c>
@@ -44895,7 +44898,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="409" spans="1:14">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>409</v>
       </c>
@@ -44933,7 +44936,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="410" spans="1:14">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>410</v>
       </c>
@@ -44974,7 +44977,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="411" spans="1:14">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>411</v>
       </c>
@@ -45015,7 +45018,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="412" spans="1:14">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>412</v>
       </c>
@@ -45056,7 +45059,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="413" spans="1:14">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>413</v>
       </c>
@@ -45097,7 +45100,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="414" spans="1:14">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>414</v>
       </c>
@@ -45138,7 +45141,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="415" spans="1:14">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>415</v>
       </c>
@@ -45179,7 +45182,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="416" spans="1:14">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>416</v>
       </c>
@@ -45220,7 +45223,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>417</v>
       </c>
@@ -45261,7 +45264,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>418</v>
       </c>
@@ -45302,7 +45305,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419" s="5">
         <v>419</v>
       </c>
@@ -45344,7 +45347,7 @@
       </c>
       <c r="N419" s="5"/>
     </row>
-    <row r="420" spans="1:14">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>420</v>
       </c>
@@ -45382,7 +45385,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="421" spans="1:14">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>421</v>
       </c>
@@ -45423,7 +45426,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>422</v>
       </c>
@@ -45464,7 +45467,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>423</v>
       </c>
@@ -45505,7 +45508,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>424</v>
       </c>
@@ -45546,7 +45549,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="425" spans="1:14">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>425</v>
       </c>
@@ -45584,7 +45587,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="426" spans="1:14">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>426</v>
       </c>
@@ -45625,7 +45628,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>427</v>
       </c>
@@ -45663,7 +45666,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="428" spans="1:14">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>428</v>
       </c>
@@ -45704,7 +45707,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="429" spans="1:14">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>429</v>
       </c>
@@ -45745,7 +45748,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="430" spans="1:14">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430" s="6">
         <v>430</v>
       </c>
@@ -45775,7 +45778,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>431</v>
       </c>
@@ -45816,7 +45819,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>432</v>
       </c>
@@ -45854,7 +45857,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>433</v>
       </c>
@@ -45895,7 +45898,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>434</v>
       </c>
@@ -45933,7 +45936,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>435</v>
       </c>
@@ -45974,7 +45977,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>436</v>
       </c>
@@ -46009,7 +46012,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>437</v>
       </c>
@@ -46047,7 +46050,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="438" spans="1:14">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>438</v>
       </c>
@@ -46085,7 +46088,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="439" spans="1:14">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>439</v>
       </c>
@@ -46126,7 +46129,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="440" spans="1:14">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440" s="6">
         <v>440</v>
       </c>
@@ -46158,7 +46161,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>441</v>
       </c>
@@ -46199,7 +46202,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>442</v>
       </c>
@@ -46240,7 +46243,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>443</v>
       </c>
@@ -46278,7 +46281,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>444</v>
       </c>
@@ -46319,7 +46322,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>445</v>
       </c>
@@ -46357,7 +46360,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>446</v>
       </c>
@@ -46398,7 +46401,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447" s="5">
         <v>447</v>
       </c>
@@ -46440,7 +46443,7 @@
       </c>
       <c r="N447" s="5"/>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>448</v>
       </c>
@@ -46481,7 +46484,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="449" spans="1:14">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>449</v>
       </c>
@@ -46522,7 +46525,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="450" spans="1:14">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>450</v>
       </c>
@@ -46563,7 +46566,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="451" spans="1:14">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>451</v>
       </c>
@@ -46604,7 +46607,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="452" spans="1:14">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>452</v>
       </c>
@@ -46645,7 +46648,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="453" spans="1:14">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>453</v>
       </c>
@@ -46686,7 +46689,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="454" spans="1:14">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>454</v>
       </c>
@@ -46727,7 +46730,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="455" spans="1:14">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455" s="5">
         <v>455</v>
       </c>
@@ -46769,7 +46772,7 @@
       </c>
       <c r="N455" s="5"/>
     </row>
-    <row r="456" spans="1:14">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>456</v>
       </c>
@@ -46810,7 +46813,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="457" spans="1:14">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>457</v>
       </c>
@@ -46851,7 +46854,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="458" spans="1:14">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>458</v>
       </c>
@@ -46889,7 +46892,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="459" spans="1:14">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>459</v>
       </c>
@@ -46930,7 +46933,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="460" spans="1:14">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>460</v>
       </c>
@@ -46968,7 +46971,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="461" spans="1:14">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>461</v>
       </c>
@@ -47009,7 +47012,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="462" spans="1:14">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>462</v>
       </c>
@@ -47050,7 +47053,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="463" spans="1:14">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>463</v>
       </c>
@@ -47091,7 +47094,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="464" spans="1:14">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>464</v>
       </c>
@@ -47132,7 +47135,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="465" spans="1:14">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>465</v>
       </c>
@@ -47173,7 +47176,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="466" spans="1:14">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>466</v>
       </c>
@@ -47214,7 +47217,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="467" spans="1:14">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>467</v>
       </c>
@@ -47255,7 +47258,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="468" spans="1:14">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468" s="5">
         <v>468</v>
       </c>
@@ -47299,7 +47302,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="469" spans="1:14">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>469</v>
       </c>
@@ -47340,7 +47343,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="470" spans="1:14">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>470</v>
       </c>
@@ -47381,7 +47384,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="471" spans="1:14">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>471</v>
       </c>
@@ -47422,7 +47425,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="472" spans="1:14">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>472</v>
       </c>
@@ -47463,7 +47466,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="473" spans="1:14">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>473</v>
       </c>
@@ -47504,7 +47507,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="474" spans="1:14">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>474</v>
       </c>
@@ -47548,7 +47551,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="475" spans="1:14">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>475</v>
       </c>
@@ -47589,7 +47592,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="476" spans="1:14">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>476</v>
       </c>
@@ -47630,7 +47633,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="477" spans="1:14">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>477</v>
       </c>
@@ -47668,7 +47671,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="478" spans="1:14">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>478</v>
       </c>
@@ -47706,7 +47709,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="479" spans="1:14">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>479</v>
       </c>
@@ -47748,7 +47751,7 @@
       </c>
       <c r="N479" s="5"/>
     </row>
-    <row r="480" spans="1:14">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>480</v>
       </c>
@@ -47789,7 +47792,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>481</v>
       </c>
@@ -47830,7 +47833,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>482</v>
       </c>
@@ -47871,7 +47874,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>483</v>
       </c>
@@ -47912,7 +47915,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A484" s="5">
         <v>484</v>
       </c>
@@ -47956,7 +47959,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="485" spans="1:14">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485" s="5">
         <v>485</v>
       </c>
@@ -48000,7 +48003,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="486" spans="1:14">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>486</v>
       </c>
@@ -48041,7 +48044,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="487" spans="1:14">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>487</v>
       </c>
@@ -48082,7 +48085,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="488" spans="1:14">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>488</v>
       </c>
@@ -48123,7 +48126,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="489" spans="1:14">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>489</v>
       </c>
@@ -48164,7 +48167,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="490" spans="1:14">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>490</v>
       </c>
@@ -48205,7 +48208,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="491" spans="1:14">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>491</v>
       </c>
@@ -48246,7 +48249,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>492</v>
       </c>
@@ -48287,7 +48290,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>493</v>
       </c>
@@ -48328,7 +48331,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494" s="5">
         <v>494</v>
       </c>
@@ -48372,7 +48375,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="495" spans="1:14">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>495</v>
       </c>
@@ -48413,7 +48416,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="496" spans="1:14">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>496</v>
       </c>
@@ -48454,7 +48457,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="497" spans="1:14">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497" s="5">
         <v>497</v>
       </c>
@@ -48496,7 +48499,7 @@
       </c>
       <c r="N497" s="5"/>
     </row>
-    <row r="498" spans="1:14">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>498</v>
       </c>
@@ -48537,7 +48540,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>499</v>
       </c>
@@ -48578,7 +48581,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="500" spans="1:14">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>500</v>
       </c>
@@ -48619,7 +48622,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="501" spans="1:14">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501" s="5">
         <v>501</v>
       </c>
@@ -48661,7 +48664,7 @@
       </c>
       <c r="N501" s="5"/>
     </row>
-    <row r="502" spans="1:14">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>502</v>
       </c>
@@ -48702,7 +48705,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="503" spans="1:14">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503" s="5">
         <v>503</v>
       </c>
@@ -48744,7 +48747,7 @@
       </c>
       <c r="N503" s="5"/>
     </row>
-    <row r="504" spans="1:14">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504" s="5">
         <v>504</v>
       </c>
@@ -48786,7 +48789,7 @@
       </c>
       <c r="N504" s="5"/>
     </row>
-    <row r="505" spans="1:14">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>505</v>
       </c>
@@ -48827,7 +48830,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="506" spans="1:14">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>506</v>
       </c>
@@ -48868,7 +48871,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="507" spans="1:14">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>507</v>
       </c>
@@ -48906,7 +48909,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>508</v>
       </c>
@@ -48944,7 +48947,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>509</v>
       </c>
@@ -48982,7 +48985,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="510" spans="1:14">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>510</v>
       </c>
@@ -49020,7 +49023,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="511" spans="1:14">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>511</v>
       </c>
@@ -49058,7 +49061,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="512" spans="1:14">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A512" s="5">
         <v>512</v>
       </c>
@@ -49100,7 +49103,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="513" spans="1:14">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A513" s="5">
         <v>513</v>
       </c>
@@ -49142,7 +49145,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="514" spans="1:14">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>514</v>
       </c>
@@ -49183,7 +49186,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="515" spans="1:14">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>515</v>
       </c>
@@ -49224,7 +49227,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="516" spans="1:14">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>516</v>
       </c>
@@ -49265,7 +49268,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="517" spans="1:14">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>517</v>
       </c>
@@ -49312,26 +49315,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49591,14 +49574,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C74DB958-37A5-C44A-864A-CA43B4AA3EAA}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F57E1C8-5856-084C-9E76-56E3D282B874}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10712" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10710" uniqueCount="2245">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -18482,8 +18482,8 @@
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
-        <v>806</v>
+      <c r="A275">
+        <v>43800825</v>
       </c>
       <c r="B275" t="s">
         <v>56</v>
@@ -18509,8 +18509,8 @@
       <c r="I275" t="s">
         <v>62</v>
       </c>
-      <c r="J275" t="s">
-        <v>94</v>
+      <c r="J275">
+        <v>2025</v>
       </c>
       <c r="K275">
         <v>75</v>
@@ -49315,6 +49315,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49574,17 +49585,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -49595,6 +49595,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49614,24 +49632,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
   <ds:schemaRefs>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F57E1C8-5856-084C-9E76-56E3D282B874}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A12E1A6-7AAD-5E44-923B-7FB0A29E9075}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7363,7 +7363,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R517"/>
+  <dimension ref="A1:R518"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -28349,6 +28349,11 @@
       </c>
       <c r="P517" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="518" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A518">
+        <v>43902124</v>
       </c>
     </row>
   </sheetData>
@@ -49326,6 +49331,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49585,34 +49599,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49630,12 +49643,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A12E1A6-7AAD-5E44-923B-7FB0A29E9075}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E317EA-D16A-F543-8925-A4DED1921048}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10710" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10717" uniqueCount="2247">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6776,6 +6776,12 @@
   </si>
   <si>
     <t>8805</t>
+  </si>
+  <si>
+    <t>Belleruche</t>
+  </si>
+  <si>
+    <t>M. Chapoutier</t>
   </si>
 </sst>
 </file>
@@ -28355,6 +28361,30 @@
       <c r="A518">
         <v>43902124</v>
       </c>
+      <c r="B518" t="s">
+        <v>118</v>
+      </c>
+      <c r="C518" t="s">
+        <v>564</v>
+      </c>
+      <c r="D518" t="s">
+        <v>665</v>
+      </c>
+      <c r="E518" t="s">
+        <v>80</v>
+      </c>
+      <c r="F518" t="s">
+        <v>595</v>
+      </c>
+      <c r="G518" t="s">
+        <v>2245</v>
+      </c>
+      <c r="H518" t="s">
+        <v>2246</v>
+      </c>
+      <c r="J518">
+        <v>2024</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E317EA-D16A-F543-8925-A4DED1921048}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD28025-7760-2847-8006-254342F7A9C8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28385,6 +28385,12 @@
       <c r="J518">
         <v>2024</v>
       </c>
+      <c r="K518">
+        <v>75</v>
+      </c>
+      <c r="L518">
+        <v>6.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD28025-7760-2847-8006-254342F7A9C8}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6534E50F-0643-1D44-AD86-90ECB0E33379}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10717" uniqueCount="2247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10718" uniqueCount="2247">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7369,7 +7369,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R518"/>
+  <dimension ref="A1:R519"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -28390,6 +28390,14 @@
       </c>
       <c r="L518">
         <v>6.9</v>
+      </c>
+    </row>
+    <row r="519" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A519">
+        <v>24003025</v>
+      </c>
+      <c r="B519" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -49356,26 +49364,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49635,33 +49623,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49679,4 +49661,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6534E50F-0643-1D44-AD86-90ECB0E33379}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EAF0727-C3C9-754D-980B-2A120859072A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10718" uniqueCount="2247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10725" uniqueCount="2249">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6782,6 +6782,12 @@
   </si>
   <si>
     <t>M. Chapoutier</t>
+  </si>
+  <si>
+    <t>Sud Ouest</t>
+  </si>
+  <si>
+    <t>Les Fumées Blanches</t>
   </si>
 </sst>
 </file>
@@ -28399,6 +28405,36 @@
       <c r="B519" t="s">
         <v>118</v>
       </c>
+      <c r="C519" t="s">
+        <v>996</v>
+      </c>
+      <c r="D519" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E519" t="s">
+        <v>58</v>
+      </c>
+      <c r="F519" t="s">
+        <v>59</v>
+      </c>
+      <c r="G519" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H519" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I519" t="s">
+        <v>62</v>
+      </c>
+      <c r="J519">
+        <v>2025</v>
+      </c>
+      <c r="K519">
+        <v>75</v>
+      </c>
+      <c r="L519">
+        <v>6.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B03270A-7D91-DC45-A1A9-67349E84A155}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D5C90A8-2F07-6045-8E8B-A0782173EBEE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10615" uniqueCount="2231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10615" uniqueCount="2232">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6734,6 +6734,9 @@
   </si>
   <si>
     <t>Les Fumées Blanches</t>
+  </si>
+  <si>
+    <t>242002NM</t>
   </si>
 </sst>
 </file>
@@ -41462,7 +41465,7 @@
         <v>1928</v>
       </c>
       <c r="G329" t="s">
-        <v>931</v>
+        <v>2231</v>
       </c>
       <c r="H329" t="s">
         <v>1928</v>
@@ -48920,6 +48923,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49179,17 +49193,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -49200,6 +49203,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49219,24 +49240,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
   <ds:schemaRefs>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB67D5A-6780-5D40-9672-B0E2F4CD1A02}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99AA02A0-F1C2-2C4F-B988-84D4393790E4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10615" uniqueCount="2231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10613" uniqueCount="2231">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -19600,8 +19600,8 @@
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>872</v>
+      <c r="A303">
+        <v>10701525</v>
       </c>
       <c r="B303" t="s">
         <v>56</v>
@@ -19624,8 +19624,8 @@
       <c r="H303" t="s">
         <v>875</v>
       </c>
-      <c r="J303" t="s">
-        <v>94</v>
+      <c r="J303">
+        <v>2025</v>
       </c>
       <c r="K303">
         <v>75</v>
@@ -48920,17 +48920,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49190,6 +49179,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -49200,24 +49200,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49237,6 +49219,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
   <ds:schemaRefs>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C801B1CC-2374-44DC-A0EB-8E476811C43A}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC24D211-707B-EB43-AAC3-451239F6FBEE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10448" uniqueCount="2227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10448" uniqueCount="2228">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6722,13 +6722,16 @@
   </si>
   <si>
     <t>8805</t>
+  </si>
+  <si>
+    <t>Petit Guiraud - 2nd vin du Château Guiraud</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7112,192 +7115,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -7310,19 +7313,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R514"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" customWidth="1"/>
+    <col min="11" max="11" width="6.5" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
@@ -7331,7 +7334,7 @@
     <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -7387,7 +7390,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -7428,7 +7431,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -7466,7 +7469,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>68</v>
       </c>
@@ -7510,7 +7513,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -7551,7 +7554,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -7595,7 +7598,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -7639,7 +7642,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -7677,7 +7680,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -7715,7 +7718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -7756,7 +7759,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -7797,7 +7800,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -7838,7 +7841,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -7882,7 +7885,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -7926,7 +7929,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -7964,7 +7967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>103</v>
       </c>
@@ -8005,7 +8008,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -8046,7 +8049,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -8087,7 +8090,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -8125,7 +8128,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -8163,7 +8166,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -8201,7 +8204,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -8239,7 +8242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>125</v>
       </c>
@@ -8280,7 +8283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -8318,7 +8321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8356,7 +8359,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -8394,7 +8397,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -8435,7 +8438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -8476,7 +8479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -8517,7 +8520,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -8558,7 +8561,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>149</v>
       </c>
@@ -8599,7 +8602,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -8634,7 +8637,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8675,7 +8678,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -8716,7 +8719,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -8754,7 +8757,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>163</v>
       </c>
@@ -8792,7 +8795,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -8877,7 +8880,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -8918,7 +8921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>176</v>
       </c>
@@ -8962,7 +8965,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>181</v>
       </c>
@@ -9003,7 +9006,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>184</v>
       </c>
@@ -9041,7 +9044,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>188</v>
       </c>
@@ -9079,7 +9082,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -9117,7 +9120,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>193</v>
       </c>
@@ -9158,7 +9161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -9199,7 +9202,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -9237,7 +9240,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -9278,7 +9281,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -9316,7 +9319,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>208</v>
       </c>
@@ -9354,7 +9357,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>209</v>
       </c>
@@ -9392,7 +9395,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>213</v>
       </c>
@@ -9430,7 +9433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>216</v>
       </c>
@@ -9474,7 +9477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -9512,7 +9515,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>222</v>
       </c>
@@ -9553,7 +9556,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>224</v>
       </c>
@@ -9591,7 +9594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>226</v>
       </c>
@@ -9632,7 +9635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>229</v>
       </c>
@@ -9667,7 +9670,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>230</v>
       </c>
@@ -9708,7 +9711,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>234</v>
       </c>
@@ -9746,7 +9749,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>236</v>
       </c>
@@ -9790,7 +9793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>240</v>
       </c>
@@ -9828,7 +9831,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>243</v>
       </c>
@@ -9866,7 +9869,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>246</v>
       </c>
@@ -9904,7 +9907,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>247</v>
       </c>
@@ -9942,7 +9945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>250</v>
       </c>
@@ -9980,7 +9983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>253</v>
       </c>
@@ -10018,7 +10021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>256</v>
       </c>
@@ -10056,7 +10059,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>259</v>
       </c>
@@ -10097,7 +10100,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>263</v>
       </c>
@@ -10116,8 +10119,11 @@
       <c r="F70" t="s">
         <v>265</v>
       </c>
+      <c r="G70" t="s">
+        <v>2227</v>
+      </c>
       <c r="H70" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I70" t="s">
         <v>62</v>
@@ -10138,7 +10144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>267</v>
       </c>
@@ -10157,9 +10163,6 @@
       <c r="F71" t="s">
         <v>268</v>
       </c>
-      <c r="G71" t="s">
-        <v>269</v>
-      </c>
       <c r="H71" t="s">
         <v>270</v>
       </c>
@@ -10182,7 +10185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>272</v>
       </c>
@@ -10220,7 +10223,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>276</v>
       </c>
@@ -10258,7 +10261,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>280</v>
       </c>
@@ -10296,7 +10299,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>282</v>
       </c>
@@ -10331,7 +10334,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>285</v>
       </c>
@@ -10369,7 +10372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>288</v>
       </c>
@@ -10410,7 +10413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>292</v>
       </c>
@@ -10448,7 +10451,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>294</v>
       </c>
@@ -10486,7 +10489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>296</v>
       </c>
@@ -10524,7 +10527,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>300</v>
       </c>
@@ -10562,7 +10565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>304</v>
       </c>
@@ -10603,7 +10606,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>306</v>
       </c>
@@ -10641,7 +10644,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>308</v>
       </c>
@@ -10679,7 +10682,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>311</v>
       </c>
@@ -10714,7 +10717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>314</v>
       </c>
@@ -10752,7 +10755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>319</v>
       </c>
@@ -10784,7 +10787,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>322</v>
       </c>
@@ -10822,7 +10825,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>15401623</v>
       </c>
@@ -10857,7 +10860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>326</v>
       </c>
@@ -10898,7 +10901,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>329</v>
       </c>
@@ -10939,7 +10942,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>331</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>337</v>
       </c>
@@ -11021,7 +11024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>340</v>
       </c>
@@ -11062,7 +11065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>343</v>
       </c>
@@ -11106,7 +11109,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>345</v>
       </c>
@@ -11147,7 +11150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>348</v>
       </c>
@@ -11188,7 +11191,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>349</v>
       </c>
@@ -11229,7 +11232,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>25000124</v>
       </c>
@@ -11270,7 +11273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>355</v>
       </c>
@@ -11311,7 +11314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>357</v>
       </c>
@@ -11352,7 +11355,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>359</v>
       </c>
@@ -11393,7 +11396,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>362</v>
       </c>
@@ -11434,7 +11437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>365</v>
       </c>
@@ -11475,7 +11478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>366</v>
       </c>
@@ -11516,7 +11519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>369</v>
       </c>
@@ -11554,7 +11557,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>35800124</v>
       </c>
@@ -11589,7 +11592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>35800224</v>
       </c>
@@ -11624,7 +11627,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>377</v>
       </c>
@@ -11662,7 +11665,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>378</v>
       </c>
@@ -11700,7 +11703,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>380</v>
       </c>
@@ -11744,7 +11747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>384</v>
       </c>
@@ -11785,7 +11788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>387</v>
       </c>
@@ -11829,7 +11832,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>389</v>
       </c>
@@ -11867,7 +11870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>391</v>
       </c>
@@ -11905,7 +11908,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>394</v>
       </c>
@@ -11943,7 +11946,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>395</v>
       </c>
@@ -11987,7 +11990,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>399</v>
       </c>
@@ -12031,7 +12034,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>402</v>
       </c>
@@ -12063,7 +12066,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>405</v>
       </c>
@@ -12095,7 +12098,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>407</v>
       </c>
@@ -12136,7 +12139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>409</v>
       </c>
@@ -12177,7 +12180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>411</v>
       </c>
@@ -12215,7 +12218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>412</v>
       </c>
@@ -12253,7 +12256,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>415</v>
       </c>
@@ -12294,7 +12297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>418</v>
       </c>
@@ -12335,7 +12338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>422</v>
       </c>
@@ -12376,7 +12379,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>424</v>
       </c>
@@ -12417,7 +12420,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>427</v>
       </c>
@@ -12458,7 +12461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>430</v>
       </c>
@@ -12499,7 +12502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>435</v>
       </c>
@@ -12540,7 +12543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>438</v>
       </c>
@@ -12581,7 +12584,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>441</v>
       </c>
@@ -12625,7 +12628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>444</v>
       </c>
@@ -12666,7 +12669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>447</v>
       </c>
@@ -12704,7 +12707,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>449</v>
       </c>
@@ -12745,7 +12748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>451</v>
       </c>
@@ -12783,7 +12786,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>454</v>
       </c>
@@ -12824,7 +12827,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>456</v>
       </c>
@@ -12865,7 +12868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>457</v>
       </c>
@@ -12906,7 +12909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>460</v>
       </c>
@@ -12947,7 +12950,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>462</v>
       </c>
@@ -12988,7 +12991,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>465</v>
       </c>
@@ -13029,7 +13032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>469</v>
       </c>
@@ -13073,7 +13076,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>472</v>
       </c>
@@ -13114,7 +13117,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>473</v>
       </c>
@@ -13152,7 +13155,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>476</v>
       </c>
@@ -13193,7 +13196,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>479</v>
       </c>
@@ -13228,7 +13231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>481</v>
       </c>
@@ -13263,7 +13266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>482</v>
       </c>
@@ -13304,7 +13307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>484</v>
       </c>
@@ -13348,7 +13351,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>487</v>
       </c>
@@ -13383,7 +13386,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>491</v>
       </c>
@@ -13424,7 +13427,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>495</v>
       </c>
@@ -13465,7 +13468,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>498</v>
       </c>
@@ -13506,7 +13509,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>501</v>
       </c>
@@ -13547,7 +13550,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>504</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>506</v>
       </c>
@@ -13629,7 +13632,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>509</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>513</v>
       </c>
@@ -13714,7 +13717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>514</v>
       </c>
@@ -13755,7 +13758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>517</v>
       </c>
@@ -13796,7 +13799,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>521</v>
       </c>
@@ -13837,7 +13840,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>524</v>
       </c>
@@ -13878,7 +13881,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>527</v>
       </c>
@@ -13922,7 +13925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>530</v>
       </c>
@@ -13957,7 +13960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>531</v>
       </c>
@@ -13992,7 +13995,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>533</v>
       </c>
@@ -14030,7 +14033,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>534</v>
       </c>
@@ -14071,7 +14074,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>536</v>
       </c>
@@ -14112,7 +14115,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>539</v>
       </c>
@@ -14150,7 +14153,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>541</v>
       </c>
@@ -14191,7 +14194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>544</v>
       </c>
@@ -14226,7 +14229,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>546</v>
       </c>
@@ -14270,7 +14273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>548</v>
       </c>
@@ -14311,7 +14314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>551</v>
       </c>
@@ -14352,7 +14355,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>553</v>
       </c>
@@ -14393,7 +14396,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>554</v>
       </c>
@@ -14437,7 +14440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>558</v>
       </c>
@@ -14478,7 +14481,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>560</v>
       </c>
@@ -14522,7 +14525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>25002122</v>
       </c>
@@ -14560,7 +14563,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>563</v>
       </c>
@@ -14601,7 +14604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>567</v>
       </c>
@@ -14642,7 +14645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>569</v>
       </c>
@@ -14683,7 +14686,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>572</v>
       </c>
@@ -14724,7 +14727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>576</v>
       </c>
@@ -14765,7 +14768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>580</v>
       </c>
@@ -14806,7 +14809,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>582</v>
       </c>
@@ -14847,7 +14850,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>586</v>
       </c>
@@ -14888,7 +14891,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>588</v>
       </c>
@@ -14929,7 +14932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>590</v>
       </c>
@@ -14970,7 +14973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>594</v>
       </c>
@@ -15011,7 +15014,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>597</v>
       </c>
@@ -15049,7 +15052,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>599</v>
       </c>
@@ -15087,7 +15090,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>601</v>
       </c>
@@ -15131,7 +15134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>603</v>
       </c>
@@ -15172,7 +15175,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>606</v>
       </c>
@@ -15216,7 +15219,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>609</v>
       </c>
@@ -15257,7 +15260,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>612</v>
       </c>
@@ -15298,7 +15301,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>615</v>
       </c>
@@ -15339,7 +15342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>617</v>
       </c>
@@ -15383,7 +15386,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>621</v>
       </c>
@@ -15424,7 +15427,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>623</v>
       </c>
@@ -15465,7 +15468,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>625</v>
       </c>
@@ -15509,7 +15512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>627</v>
       </c>
@@ -15550,7 +15553,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>628</v>
       </c>
@@ -15594,7 +15597,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>630</v>
       </c>
@@ -15635,7 +15638,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>632</v>
       </c>
@@ -15676,7 +15679,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>634</v>
       </c>
@@ -15717,7 +15720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>635</v>
       </c>
@@ -15758,7 +15761,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>636</v>
       </c>
@@ -15799,7 +15802,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>641</v>
       </c>
@@ -15840,7 +15843,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>643</v>
       </c>
@@ -15881,7 +15884,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>647</v>
       </c>
@@ -15922,7 +15925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>650</v>
       </c>
@@ -15963,7 +15966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>653</v>
       </c>
@@ -16004,7 +16007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>654</v>
       </c>
@@ -16045,7 +16048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>657</v>
       </c>
@@ -16086,7 +16089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>660</v>
       </c>
@@ -16127,7 +16130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>661</v>
       </c>
@@ -16168,7 +16171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>662</v>
       </c>
@@ -16209,7 +16212,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>664</v>
       </c>
@@ -16250,7 +16253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>668</v>
       </c>
@@ -16291,7 +16294,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>670</v>
       </c>
@@ -16332,7 +16335,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>672</v>
       </c>
@@ -16373,7 +16376,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>675</v>
       </c>
@@ -16414,7 +16417,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>677</v>
       </c>
@@ -16458,7 +16461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>680</v>
       </c>
@@ -16499,7 +16502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>682</v>
       </c>
@@ -16540,7 +16543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>684</v>
       </c>
@@ -16581,7 +16584,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>687</v>
       </c>
@@ -16625,7 +16628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>690</v>
       </c>
@@ -16666,7 +16669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>692</v>
       </c>
@@ -16707,7 +16710,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>695</v>
       </c>
@@ -16748,7 +16751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>699</v>
       </c>
@@ -16789,7 +16792,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>701</v>
       </c>
@@ -16830,7 +16833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>704</v>
       </c>
@@ -16871,7 +16874,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>706</v>
       </c>
@@ -16912,7 +16915,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>709</v>
       </c>
@@ -16953,7 +16956,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>710</v>
       </c>
@@ -16997,7 +17000,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>711</v>
       </c>
@@ -17038,7 +17041,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>712</v>
       </c>
@@ -17082,7 +17085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>715</v>
       </c>
@@ -17123,7 +17126,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>717</v>
       </c>
@@ -17164,7 +17167,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>719</v>
       </c>
@@ -17205,7 +17208,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>721</v>
       </c>
@@ -17246,7 +17249,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>723</v>
       </c>
@@ -17287,7 +17290,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>725</v>
       </c>
@@ -17328,7 +17331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>727</v>
       </c>
@@ -17369,7 +17372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>13800524</v>
       </c>
@@ -17410,7 +17413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>729</v>
       </c>
@@ -17451,7 +17454,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>731</v>
       </c>
@@ -17492,7 +17495,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>733</v>
       </c>
@@ -17533,7 +17536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>734</v>
       </c>
@@ -17571,7 +17574,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>738</v>
       </c>
@@ -17609,7 +17612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>10700325</v>
       </c>
@@ -17647,7 +17650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>743</v>
       </c>
@@ -17685,7 +17688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>747</v>
       </c>
@@ -17726,7 +17729,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>750</v>
       </c>
@@ -17767,7 +17770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>753</v>
       </c>
@@ -17808,7 +17811,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>757</v>
       </c>
@@ -17849,7 +17852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>761</v>
       </c>
@@ -17890,7 +17893,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>765</v>
       </c>
@@ -17931,7 +17934,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>770</v>
       </c>
@@ -17972,7 +17975,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:18">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>774</v>
       </c>
@@ -18016,7 +18019,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:18">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>777</v>
       </c>
@@ -18057,7 +18060,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:18">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>781</v>
       </c>
@@ -18098,7 +18101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:18">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>784</v>
       </c>
@@ -18139,7 +18142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:18">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>789</v>
       </c>
@@ -18177,7 +18180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:18">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>14700422</v>
       </c>
@@ -18218,7 +18221,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:18">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>793</v>
       </c>
@@ -18256,7 +18259,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:18">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>795</v>
       </c>
@@ -18294,7 +18297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:18">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>798</v>
       </c>
@@ -18326,7 +18329,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>801</v>
       </c>
@@ -18364,7 +18367,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>43800825</v>
       </c>
@@ -18405,7 +18408,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>807</v>
       </c>
@@ -18443,7 +18446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>810</v>
       </c>
@@ -18478,7 +18481,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:18">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>812</v>
       </c>
@@ -18513,7 +18516,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>814</v>
       </c>
@@ -18551,7 +18554,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>817</v>
       </c>
@@ -18589,7 +18592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:18">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>820</v>
       </c>
@@ -18624,7 +18627,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>823</v>
       </c>
@@ -18662,7 +18665,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>825</v>
       </c>
@@ -18703,7 +18706,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>827</v>
       </c>
@@ -18738,7 +18741,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>828</v>
       </c>
@@ -18776,7 +18779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>830</v>
       </c>
@@ -18814,7 +18817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>832</v>
       </c>
@@ -18852,7 +18855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>834</v>
       </c>
@@ -18893,7 +18896,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>837</v>
       </c>
@@ -18934,7 +18937,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>841</v>
       </c>
@@ -18972,7 +18975,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>844</v>
       </c>
@@ -19010,7 +19013,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>846</v>
       </c>
@@ -19051,7 +19054,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>848</v>
       </c>
@@ -19092,7 +19095,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>850</v>
       </c>
@@ -19133,7 +19136,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>852</v>
       </c>
@@ -19171,7 +19174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>853</v>
       </c>
@@ -19212,7 +19215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>854</v>
       </c>
@@ -19250,7 +19253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>857</v>
       </c>
@@ -19288,7 +19291,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>859</v>
       </c>
@@ -19326,7 +19329,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>861</v>
       </c>
@@ -19361,7 +19364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>862</v>
       </c>
@@ -19402,7 +19405,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>864</v>
       </c>
@@ -19440,7 +19443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>10701525</v>
       </c>
@@ -19478,7 +19481,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>871</v>
       </c>
@@ -19516,7 +19519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>874</v>
       </c>
@@ -19557,7 +19560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>876</v>
       </c>
@@ -19598,7 +19601,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>878</v>
       </c>
@@ -19636,7 +19639,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>882</v>
       </c>
@@ -19677,7 +19680,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>885</v>
       </c>
@@ -19715,7 +19718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>886</v>
       </c>
@@ -19753,7 +19756,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>889</v>
       </c>
@@ -19794,7 +19797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>892</v>
       </c>
@@ -19826,7 +19829,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>894</v>
       </c>
@@ -19861,7 +19864,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>896</v>
       </c>
@@ -19902,7 +19905,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>898</v>
       </c>
@@ -19943,7 +19946,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>900</v>
       </c>
@@ -19975,7 +19978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>902</v>
       </c>
@@ -20010,7 +20013,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>903</v>
       </c>
@@ -20048,7 +20051,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>904</v>
       </c>
@@ -20086,7 +20089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>905</v>
       </c>
@@ -20124,7 +20127,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:18">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>906</v>
       </c>
@@ -20162,7 +20165,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:18">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>908</v>
       </c>
@@ -20203,7 +20206,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="323" spans="1:18">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>909</v>
       </c>
@@ -20238,7 +20241,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:18">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>910</v>
       </c>
@@ -20279,7 +20282,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:18">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>912</v>
       </c>
@@ -20320,7 +20323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:18">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>916</v>
       </c>
@@ -20361,7 +20364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:18">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>922</v>
       </c>
@@ -20393,7 +20396,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:18">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>925</v>
       </c>
@@ -20434,7 +20437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:18">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>926</v>
       </c>
@@ -20475,7 +20478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:18">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>930</v>
       </c>
@@ -20507,7 +20510,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:18">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>932</v>
       </c>
@@ -20539,7 +20542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:18">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>935</v>
       </c>
@@ -20574,7 +20577,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:18">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>937</v>
       </c>
@@ -20615,7 +20618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:18">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>938</v>
       </c>
@@ -20650,7 +20653,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>941</v>
       </c>
@@ -20688,7 +20691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>945</v>
       </c>
@@ -20726,7 +20729,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>948</v>
       </c>
@@ -20767,7 +20770,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>952</v>
       </c>
@@ -20808,7 +20811,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>954</v>
       </c>
@@ -20846,7 +20849,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>957</v>
       </c>
@@ -20884,7 +20887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>959</v>
       </c>
@@ -20925,7 +20928,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>962</v>
       </c>
@@ -20963,7 +20966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>964</v>
       </c>
@@ -21001,7 +21004,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>966</v>
       </c>
@@ -21042,7 +21045,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>968</v>
       </c>
@@ -21083,7 +21086,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>971</v>
       </c>
@@ -21118,7 +21121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>973</v>
       </c>
@@ -21156,7 +21159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>974</v>
       </c>
@@ -21194,7 +21197,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>975</v>
       </c>
@@ -21235,7 +21238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>977</v>
       </c>
@@ -21273,7 +21276,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>982</v>
       </c>
@@ -21311,7 +21314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>985</v>
       </c>
@@ -21349,7 +21352,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="353" spans="1:18">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>989</v>
       </c>
@@ -21387,7 +21390,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:18">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>992</v>
       </c>
@@ -21425,7 +21428,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:18">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>994</v>
       </c>
@@ -21463,7 +21466,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:18">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>996</v>
       </c>
@@ -21501,7 +21504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:18">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>998</v>
       </c>
@@ -21539,7 +21542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:18">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>1001</v>
       </c>
@@ -21580,7 +21583,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="359" spans="1:18">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1003</v>
       </c>
@@ -21618,7 +21621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:18">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>1006</v>
       </c>
@@ -21656,7 +21659,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:18">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1008</v>
       </c>
@@ -21697,7 +21700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:18">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>1011</v>
       </c>
@@ -21735,7 +21738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:18">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>1015</v>
       </c>
@@ -21776,7 +21779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:18">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1019</v>
       </c>
@@ -21814,7 +21817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:18">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1021</v>
       </c>
@@ -21855,7 +21858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:18">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1023</v>
       </c>
@@ -21893,7 +21896,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:18">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1025</v>
       </c>
@@ -21928,7 +21931,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:18">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1028</v>
       </c>
@@ -21966,7 +21969,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1032</v>
       </c>
@@ -22004,7 +22007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1035</v>
       </c>
@@ -22042,7 +22045,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1038</v>
       </c>
@@ -22080,7 +22083,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1041</v>
       </c>
@@ -22118,7 +22121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1044</v>
       </c>
@@ -22156,7 +22159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1047</v>
       </c>
@@ -22197,7 +22200,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1051</v>
       </c>
@@ -22235,7 +22238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1054</v>
       </c>
@@ -22273,7 +22276,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1056</v>
       </c>
@@ -22311,7 +22314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1059</v>
       </c>
@@ -22349,7 +22352,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>1063</v>
       </c>
@@ -22387,7 +22390,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1066</v>
       </c>
@@ -22425,7 +22428,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1068</v>
       </c>
@@ -22463,7 +22466,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1071</v>
       </c>
@@ -22501,7 +22504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>1073</v>
       </c>
@@ -22539,7 +22542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>1075</v>
       </c>
@@ -22574,7 +22577,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1079</v>
       </c>
@@ -22609,7 +22612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>53800623</v>
       </c>
@@ -22647,7 +22650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1084</v>
       </c>
@@ -22685,7 +22688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>1086</v>
       </c>
@@ -22723,7 +22726,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1088</v>
       </c>
@@ -22764,7 +22767,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>1090</v>
       </c>
@@ -22805,7 +22808,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>1091</v>
       </c>
@@ -22846,7 +22849,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1092</v>
       </c>
@@ -22887,7 +22890,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1094</v>
       </c>
@@ -22928,7 +22931,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1096</v>
       </c>
@@ -22969,7 +22972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>1098</v>
       </c>
@@ -23010,7 +23013,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>1100</v>
       </c>
@@ -23051,7 +23054,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>1103</v>
       </c>
@@ -23095,7 +23098,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>1105</v>
       </c>
@@ -23139,7 +23142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>1107</v>
       </c>
@@ -23180,7 +23183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>1109</v>
       </c>
@@ -23221,7 +23224,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1112</v>
       </c>
@@ -23262,7 +23265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>1116</v>
       </c>
@@ -23303,7 +23306,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>1118</v>
       </c>
@@ -23341,7 +23344,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>1121</v>
       </c>
@@ -23382,7 +23385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>1123</v>
       </c>
@@ -23423,7 +23426,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>1126</v>
       </c>
@@ -23464,7 +23467,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1129</v>
       </c>
@@ -23505,7 +23508,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1131</v>
       </c>
@@ -23549,7 +23552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1133</v>
       </c>
@@ -23590,7 +23593,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1135</v>
       </c>
@@ -23634,7 +23637,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1137</v>
       </c>
@@ -23678,7 +23681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1139</v>
       </c>
@@ -23722,7 +23725,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1142</v>
       </c>
@@ -23763,7 +23766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1146</v>
       </c>
@@ -23801,7 +23804,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>1148</v>
       </c>
@@ -23845,7 +23848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1152</v>
       </c>
@@ -23886,7 +23889,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1155</v>
       </c>
@@ -23927,7 +23930,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>1157</v>
       </c>
@@ -23968,7 +23971,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1160</v>
       </c>
@@ -24009,7 +24012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>1163</v>
       </c>
@@ -24050,7 +24053,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>1165</v>
       </c>
@@ -24091,7 +24094,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>1168</v>
       </c>
@@ -24135,7 +24138,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1172</v>
       </c>
@@ -24176,7 +24179,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>16003124</v>
       </c>
@@ -24217,7 +24220,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>1177</v>
       </c>
@@ -24261,7 +24264,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1179</v>
       </c>
@@ -24305,7 +24308,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>1181</v>
       </c>
@@ -24349,7 +24352,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1183</v>
       </c>
@@ -24387,7 +24390,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>1186</v>
       </c>
@@ -24431,7 +24434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1188</v>
       </c>
@@ -24466,7 +24469,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1191</v>
       </c>
@@ -24504,7 +24507,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>1193</v>
       </c>
@@ -24542,7 +24545,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="433" spans="1:18">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1197</v>
       </c>
@@ -24583,7 +24586,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="434" spans="1:18">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B434" t="s">
         <v>118</v>
       </c>
@@ -24621,7 +24624,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="435" spans="1:18">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1202</v>
       </c>
@@ -24662,7 +24665,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="436" spans="1:18">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>1204</v>
       </c>
@@ -24706,7 +24709,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="437" spans="1:18">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1208</v>
       </c>
@@ -24744,7 +24747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="438" spans="1:18">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>1211</v>
       </c>
@@ -24785,7 +24788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="439" spans="1:18">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>1214</v>
       </c>
@@ -24823,7 +24826,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="440" spans="1:18">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>1215</v>
       </c>
@@ -24861,7 +24864,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="441" spans="1:18">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>1216</v>
       </c>
@@ -24899,7 +24902,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="442" spans="1:18">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>1217</v>
       </c>
@@ -24937,7 +24940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="443" spans="1:18">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>1219</v>
       </c>
@@ -24975,7 +24978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="444" spans="1:18">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1222</v>
       </c>
@@ -25013,7 +25016,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="445" spans="1:18">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1223</v>
       </c>
@@ -25051,7 +25054,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="446" spans="1:18">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1225</v>
       </c>
@@ -25089,7 +25092,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="447" spans="1:18">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>1230</v>
       </c>
@@ -25130,7 +25133,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="448" spans="1:18">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1233</v>
       </c>
@@ -25168,7 +25171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="449" spans="1:16">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1235</v>
       </c>
@@ -25206,7 +25209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="450" spans="1:16">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1239</v>
       </c>
@@ -25244,7 +25247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="451" spans="1:16">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1243</v>
       </c>
@@ -25282,7 +25285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="452" spans="1:16">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1245</v>
       </c>
@@ -25317,7 +25320,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="453" spans="1:16">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1248</v>
       </c>
@@ -25358,7 +25361,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="454" spans="1:16">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1252</v>
       </c>
@@ -25393,7 +25396,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="455" spans="1:16">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1256</v>
       </c>
@@ -25431,7 +25434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="456" spans="1:16">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1259</v>
       </c>
@@ -25469,7 +25472,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="457" spans="1:16">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1262</v>
       </c>
@@ -25507,7 +25510,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="458" spans="1:16">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>1264</v>
       </c>
@@ -25545,7 +25548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="459" spans="1:16">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>1267</v>
       </c>
@@ -25583,7 +25586,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="460" spans="1:16">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>1270</v>
       </c>
@@ -25621,7 +25624,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="461" spans="1:16">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1274</v>
       </c>
@@ -25659,7 +25662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="462" spans="1:16">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>1276</v>
       </c>
@@ -25697,7 +25700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="463" spans="1:16">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>1278</v>
       </c>
@@ -25735,7 +25738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="464" spans="1:16">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>1279</v>
       </c>
@@ -25773,7 +25776,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="465" spans="1:16">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>1281</v>
       </c>
@@ -25811,7 +25814,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="466" spans="1:16">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1283</v>
       </c>
@@ -25849,7 +25852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="467" spans="1:16">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1285</v>
       </c>
@@ -25887,7 +25890,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="468" spans="1:16">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>1287</v>
       </c>
@@ -25925,7 +25928,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="469" spans="1:16">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>1289</v>
       </c>
@@ -25963,7 +25966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="470" spans="1:16">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1291</v>
       </c>
@@ -26001,7 +26004,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="471" spans="1:16">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>1295</v>
       </c>
@@ -26036,7 +26039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="472" spans="1:16">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>1297</v>
       </c>
@@ -26071,7 +26074,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="473" spans="1:16">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>1300</v>
       </c>
@@ -26109,7 +26112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="474" spans="1:16">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>1304</v>
       </c>
@@ -26147,7 +26150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="475" spans="1:16">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>1307</v>
       </c>
@@ -26185,7 +26188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="476" spans="1:16">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1310</v>
       </c>
@@ -26220,7 +26223,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="477" spans="1:16">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1313</v>
       </c>
@@ -26258,7 +26261,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="478" spans="1:16">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1316</v>
       </c>
@@ -26296,7 +26299,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="479" spans="1:16">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1319</v>
       </c>
@@ -26334,7 +26337,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="480" spans="1:16">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1322</v>
       </c>
@@ -26372,7 +26375,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="481" spans="1:16">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1324</v>
       </c>
@@ -26410,7 +26413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="482" spans="1:16">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1326</v>
       </c>
@@ -26448,7 +26451,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="483" spans="1:16">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1327</v>
       </c>
@@ -26486,7 +26489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="484" spans="1:16">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>1330</v>
       </c>
@@ -26524,7 +26527,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="485" spans="1:16">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1333</v>
       </c>
@@ -26562,7 +26565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="486" spans="1:16">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>1336</v>
       </c>
@@ -26600,7 +26603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="487" spans="1:16">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>1338</v>
       </c>
@@ -26638,7 +26641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="488" spans="1:16">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>1341</v>
       </c>
@@ -26676,7 +26679,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="489" spans="1:16">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>1343</v>
       </c>
@@ -26714,7 +26717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="490" spans="1:16">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>1345</v>
       </c>
@@ -26752,7 +26755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="491" spans="1:16">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1347</v>
       </c>
@@ -26790,7 +26793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="492" spans="1:16">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>1350</v>
       </c>
@@ -26828,7 +26831,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="493" spans="1:16">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>1353</v>
       </c>
@@ -26866,7 +26869,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="494" spans="1:16">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1355</v>
       </c>
@@ -26904,7 +26907,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="495" spans="1:16">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1357</v>
       </c>
@@ -26945,7 +26948,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="496" spans="1:16">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1360</v>
       </c>
@@ -26986,7 +26989,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="497" spans="1:16">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1362</v>
       </c>
@@ -27027,7 +27030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="498" spans="1:16">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1364</v>
       </c>
@@ -27068,7 +27071,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="499" spans="1:16">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1366</v>
       </c>
@@ -27109,7 +27112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="500" spans="1:16">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1368</v>
       </c>
@@ -27147,7 +27150,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="501" spans="1:16">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1374</v>
       </c>
@@ -27185,7 +27188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="502" spans="1:16">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1376</v>
       </c>
@@ -27220,7 +27223,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="503" spans="1:16">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>1380</v>
       </c>
@@ -27255,7 +27258,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="504" spans="1:16">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>1384</v>
       </c>
@@ -27290,7 +27293,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="505" spans="1:16">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>1387</v>
       </c>
@@ -27325,7 +27328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" spans="1:16">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>1391</v>
       </c>
@@ -27360,7 +27363,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="507" spans="1:16">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>1394</v>
       </c>
@@ -27395,7 +27398,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="508" spans="1:16">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>1398</v>
       </c>
@@ -27430,7 +27433,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="509" spans="1:16">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1401</v>
       </c>
@@ -27468,7 +27471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:16">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>1404</v>
       </c>
@@ -27506,7 +27509,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="511" spans="1:16">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>1408</v>
       </c>
@@ -27544,7 +27547,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="512" spans="1:16">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>1413</v>
       </c>
@@ -27582,7 +27585,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="513" spans="1:12">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>43902124</v>
       </c>
@@ -27617,7 +27620,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="514" spans="1:12">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>24003025</v>
       </c>
@@ -27663,9 +27666,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1419</v>
       </c>
@@ -27741,15 +27744,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1441</v>
       </c>
@@ -27774,14 +27777,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1446</v>
       </c>
@@ -27792,7 +27795,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1449</v>
       </c>
@@ -27811,7 +27814,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N512"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -27829,7 +27832,7 @@
     <col min="14" max="14" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1452</v>
       </c>
@@ -27873,7 +27876,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -27914,7 +27917,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -27958,7 +27961,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -27999,7 +28002,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -28040,7 +28043,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>6</v>
       </c>
@@ -28084,7 +28087,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -28125,7 +28128,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8</v>
       </c>
@@ -28166,7 +28169,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
@@ -28207,7 +28210,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
@@ -28248,7 +28251,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
@@ -28289,7 +28292,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
@@ -28330,7 +28333,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
       </c>
@@ -28371,7 +28374,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>14</v>
       </c>
@@ -28412,7 +28415,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
@@ -28453,7 +28456,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>16</v>
       </c>
@@ -28494,7 +28497,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>17</v>
       </c>
@@ -28535,7 +28538,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>18</v>
       </c>
@@ -28576,7 +28579,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>19</v>
       </c>
@@ -28617,7 +28620,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>20</v>
       </c>
@@ -28658,7 +28661,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>21</v>
       </c>
@@ -28699,7 +28702,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>22</v>
       </c>
@@ -28740,7 +28743,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>23</v>
       </c>
@@ -28781,7 +28784,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>24</v>
       </c>
@@ -28822,7 +28825,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>25</v>
       </c>
@@ -28863,7 +28866,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>26</v>
       </c>
@@ -28904,7 +28907,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>27</v>
       </c>
@@ -28945,7 +28948,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>28</v>
       </c>
@@ -28986,7 +28989,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>29</v>
       </c>
@@ -29027,7 +29030,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>30</v>
       </c>
@@ -29068,7 +29071,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>31</v>
       </c>
@@ -29109,7 +29112,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32</v>
       </c>
@@ -29144,7 +29147,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>33</v>
       </c>
@@ -29185,7 +29188,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34</v>
       </c>
@@ -29226,7 +29229,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>35</v>
       </c>
@@ -29264,7 +29267,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -29302,7 +29305,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>37</v>
       </c>
@@ -29343,7 +29346,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
@@ -29384,7 +29387,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>39</v>
       </c>
@@ -29425,7 +29428,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40</v>
       </c>
@@ -29466,7 +29469,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41</v>
       </c>
@@ -29504,7 +29507,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>42</v>
       </c>
@@ -29542,7 +29545,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>43</v>
       </c>
@@ -29580,7 +29583,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>44</v>
       </c>
@@ -29618,7 +29621,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>45</v>
       </c>
@@ -29659,7 +29662,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>46</v>
       </c>
@@ -29700,7 +29703,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>47</v>
       </c>
@@ -29738,7 +29741,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>48</v>
       </c>
@@ -29776,7 +29779,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>49</v>
       </c>
@@ -29814,7 +29817,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>50</v>
       </c>
@@ -29852,7 +29855,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>51</v>
       </c>
@@ -29890,7 +29893,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>52</v>
       </c>
@@ -29928,7 +29931,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>53</v>
       </c>
@@ -29969,7 +29972,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>54</v>
       </c>
@@ -30007,7 +30010,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>55</v>
       </c>
@@ -30045,7 +30048,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>56</v>
       </c>
@@ -30083,7 +30086,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>57</v>
       </c>
@@ -30124,7 +30127,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>58</v>
       </c>
@@ -30159,7 +30162,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>59</v>
       </c>
@@ -30200,7 +30203,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>60</v>
       </c>
@@ -30238,7 +30241,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>61</v>
       </c>
@@ -30279,7 +30282,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>62</v>
       </c>
@@ -30317,7 +30320,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>63</v>
       </c>
@@ -30355,7 +30358,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>64</v>
       </c>
@@ -30393,7 +30396,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>65</v>
       </c>
@@ -30431,7 +30434,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>66</v>
       </c>
@@ -30469,7 +30472,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>67</v>
       </c>
@@ -30507,7 +30510,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>68</v>
       </c>
@@ -30545,7 +30548,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>69</v>
       </c>
@@ -30586,7 +30589,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>70</v>
       </c>
@@ -30624,7 +30627,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>71</v>
       </c>
@@ -30665,7 +30668,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>72</v>
       </c>
@@ -30706,7 +30709,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>73</v>
       </c>
@@ -30747,7 +30750,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>74</v>
       </c>
@@ -30788,7 +30791,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>75</v>
       </c>
@@ -30826,7 +30829,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>76</v>
       </c>
@@ -30867,7 +30870,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>77</v>
       </c>
@@ -30908,7 +30911,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>78</v>
       </c>
@@ -30949,7 +30952,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>79</v>
       </c>
@@ -30990,7 +30993,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>80</v>
       </c>
@@ -31028,7 +31031,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>81</v>
       </c>
@@ -31069,7 +31072,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>82</v>
       </c>
@@ -31110,7 +31113,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>83</v>
       </c>
@@ -31151,7 +31154,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>84</v>
       </c>
@@ -31192,7 +31195,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>85</v>
       </c>
@@ -31230,7 +31233,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>86</v>
       </c>
@@ -31271,7 +31274,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>87</v>
       </c>
@@ -31306,7 +31309,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>88</v>
       </c>
@@ -31347,7 +31350,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -31375,7 +31378,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>90</v>
       </c>
@@ -31416,7 +31419,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>91</v>
       </c>
@@ -31454,7 +31457,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>92</v>
       </c>
@@ -31495,7 +31498,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>93</v>
       </c>
@@ -31536,7 +31539,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>94</v>
       </c>
@@ -31577,7 +31580,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>95</v>
       </c>
@@ -31618,7 +31621,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>96</v>
       </c>
@@ -31659,7 +31662,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>97</v>
       </c>
@@ -31700,7 +31703,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>98</v>
       </c>
@@ -31741,7 +31744,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -31773,7 +31776,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -31814,7 +31817,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -31855,7 +31858,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -31896,7 +31899,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -31937,7 +31940,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>104</v>
       </c>
@@ -31978,7 +31981,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>105</v>
       </c>
@@ -32019,7 +32022,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>106</v>
       </c>
@@ -32057,7 +32060,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -32085,7 +32088,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -32113,7 +32116,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>109</v>
       </c>
@@ -32151,7 +32154,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>110</v>
       </c>
@@ -32189,7 +32192,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>111</v>
       </c>
@@ -32230,7 +32233,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>112</v>
       </c>
@@ -32271,7 +32274,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>113</v>
       </c>
@@ -32312,7 +32315,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>114</v>
       </c>
@@ -32352,7 +32355,7 @@
       </c>
       <c r="N114" s="5"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>115</v>
       </c>
@@ -32390,7 +32393,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>116</v>
       </c>
@@ -32428,7 +32431,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>117</v>
       </c>
@@ -32469,7 +32472,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>118</v>
       </c>
@@ -32510,7 +32513,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>119</v>
       </c>
@@ -32545,7 +32548,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>120</v>
       </c>
@@ -32580,7 +32583,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>121</v>
       </c>
@@ -32621,7 +32624,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>122</v>
       </c>
@@ -32659,7 +32662,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>123</v>
       </c>
@@ -32694,7 +32697,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>124</v>
       </c>
@@ -32732,7 +32735,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>125</v>
       </c>
@@ -32773,7 +32776,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>126</v>
       </c>
@@ -32814,7 +32817,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>127</v>
       </c>
@@ -32855,7 +32858,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>128</v>
       </c>
@@ -32896,7 +32899,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>129</v>
       </c>
@@ -32937,7 +32940,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>130</v>
       </c>
@@ -32978,7 +32981,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>131</v>
       </c>
@@ -33019,7 +33022,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>132</v>
       </c>
@@ -33060,7 +33063,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>133</v>
       </c>
@@ -33101,7 +33104,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>134</v>
       </c>
@@ -33142,7 +33145,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>135</v>
       </c>
@@ -33180,7 +33183,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>136</v>
       </c>
@@ -33221,7 +33224,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>137</v>
       </c>
@@ -33259,7 +33262,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>138</v>
       </c>
@@ -33300,7 +33303,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>139</v>
       </c>
@@ -33341,7 +33344,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>140</v>
       </c>
@@ -33382,7 +33385,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>141</v>
       </c>
@@ -33423,7 +33426,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>142</v>
       </c>
@@ -33464,7 +33467,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>143</v>
       </c>
@@ -33502,7 +33505,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>144</v>
       </c>
@@ -33543,7 +33546,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>145</v>
       </c>
@@ -33581,7 +33584,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>146</v>
       </c>
@@ -33623,7 +33626,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>147</v>
       </c>
@@ -33667,7 +33670,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>148</v>
       </c>
@@ -33702,7 +33705,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>149</v>
       </c>
@@ -33737,7 +33740,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>150</v>
       </c>
@@ -33778,7 +33781,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>151</v>
       </c>
@@ -33819,7 +33822,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>152</v>
       </c>
@@ -33854,7 +33857,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>153</v>
       </c>
@@ -33895,7 +33898,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>154</v>
       </c>
@@ -33936,7 +33939,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>155</v>
       </c>
@@ -33977,7 +33980,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>156</v>
       </c>
@@ -34015,7 +34018,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>157</v>
       </c>
@@ -34056,7 +34059,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>158</v>
       </c>
@@ -34097,7 +34100,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>159</v>
       </c>
@@ -34138,7 +34141,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>160</v>
       </c>
@@ -34179,7 +34182,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>161</v>
       </c>
@@ -34221,7 +34224,7 @@
       </c>
       <c r="N161" s="5"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>162</v>
       </c>
@@ -34262,7 +34265,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>163</v>
       </c>
@@ -34303,7 +34306,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>164</v>
       </c>
@@ -34344,7 +34347,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>165</v>
       </c>
@@ -34385,7 +34388,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>166</v>
       </c>
@@ -34420,7 +34423,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>167</v>
       </c>
@@ -34455,7 +34458,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>168</v>
       </c>
@@ -34493,7 +34496,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>169</v>
       </c>
@@ -34534,7 +34537,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>170</v>
       </c>
@@ -34575,7 +34578,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>171</v>
       </c>
@@ -34613,7 +34616,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>172</v>
       </c>
@@ -34654,7 +34657,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>173</v>
       </c>
@@ -34689,7 +34692,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>174</v>
       </c>
@@ -34730,7 +34733,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>175</v>
       </c>
@@ -34771,7 +34774,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>176</v>
       </c>
@@ -34812,7 +34815,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>177</v>
       </c>
@@ -34853,7 +34856,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>178</v>
       </c>
@@ -34894,7 +34897,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>179</v>
       </c>
@@ -34935,7 +34938,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>180</v>
       </c>
@@ -34976,7 +34979,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -35006,7 +35009,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>182</v>
       </c>
@@ -35050,7 +35053,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>183</v>
       </c>
@@ -35094,7 +35097,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>184</v>
       </c>
@@ -35135,7 +35138,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>185</v>
       </c>
@@ -35176,7 +35179,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>186</v>
       </c>
@@ -35217,7 +35220,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>187</v>
       </c>
@@ -35258,7 +35261,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>188</v>
       </c>
@@ -35299,7 +35302,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>189</v>
       </c>
@@ -35340,7 +35343,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>190</v>
       </c>
@@ -35381,7 +35384,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>191</v>
       </c>
@@ -35422,7 +35425,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>192</v>
       </c>
@@ -35463,7 +35466,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>193</v>
       </c>
@@ -35501,7 +35504,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>194</v>
       </c>
@@ -35539,7 +35542,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>195</v>
       </c>
@@ -35580,7 +35583,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>196</v>
       </c>
@@ -35622,7 +35625,7 @@
       </c>
       <c r="N196" s="5"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>197</v>
       </c>
@@ -35663,7 +35666,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>198</v>
       </c>
@@ -35704,7 +35707,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>199</v>
       </c>
@@ -35745,7 +35748,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>200</v>
       </c>
@@ -35786,7 +35789,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>201</v>
       </c>
@@ -35827,7 +35830,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>202</v>
       </c>
@@ -35868,7 +35871,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>203</v>
       </c>
@@ -35908,7 +35911,7 @@
       </c>
       <c r="N203" s="5"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>204</v>
       </c>
@@ -35950,7 +35953,7 @@
       </c>
       <c r="N204" s="5"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>205</v>
       </c>
@@ -35991,7 +35994,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>206</v>
       </c>
@@ -36032,7 +36035,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>207</v>
       </c>
@@ -36073,7 +36076,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>208</v>
       </c>
@@ -36114,7 +36117,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>209</v>
       </c>
@@ -36152,7 +36155,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>210</v>
       </c>
@@ -36193,7 +36196,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>211</v>
       </c>
@@ -36234,7 +36237,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>212</v>
       </c>
@@ -36275,7 +36278,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>213</v>
       </c>
@@ -36316,7 +36319,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>214</v>
       </c>
@@ -36354,7 +36357,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>215</v>
       </c>
@@ -36396,7 +36399,7 @@
       </c>
       <c r="N215" s="5"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>216</v>
       </c>
@@ -36437,7 +36440,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>217</v>
       </c>
@@ -36475,7 +36478,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -36507,7 +36510,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>219</v>
       </c>
@@ -36548,7 +36551,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>220</v>
       </c>
@@ -36586,7 +36589,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>221</v>
       </c>
@@ -36627,7 +36630,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>222</v>
       </c>
@@ -36668,7 +36671,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>223</v>
       </c>
@@ -36709,7 +36712,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>224</v>
       </c>
@@ -36750,7 +36753,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>225</v>
       </c>
@@ -36791,7 +36794,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>226</v>
       </c>
@@ -36832,7 +36835,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>227</v>
       </c>
@@ -36873,7 +36876,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>228</v>
       </c>
@@ -36915,7 +36918,7 @@
       </c>
       <c r="N228" s="5"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>229</v>
       </c>
@@ -36956,7 +36959,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>230</v>
       </c>
@@ -36997,7 +37000,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>231</v>
       </c>
@@ -37038,7 +37041,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>232</v>
       </c>
@@ -37079,7 +37082,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>233</v>
       </c>
@@ -37120,7 +37123,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>234</v>
       </c>
@@ -37161,7 +37164,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>235</v>
       </c>
@@ -37202,7 +37205,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>236</v>
       </c>
@@ -37244,7 +37247,7 @@
       </c>
       <c r="N236" s="5"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>237</v>
       </c>
@@ -37285,7 +37288,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>238</v>
       </c>
@@ -37323,7 +37326,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>239</v>
       </c>
@@ -37364,7 +37367,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>240</v>
       </c>
@@ -37405,7 +37408,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>241</v>
       </c>
@@ -37447,7 +37450,7 @@
       </c>
       <c r="N241" s="5"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>242</v>
       </c>
@@ -37489,7 +37492,7 @@
       </c>
       <c r="N242" s="5"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>243</v>
       </c>
@@ -37530,7 +37533,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>244</v>
       </c>
@@ -37571,7 +37574,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>245</v>
       </c>
@@ -37612,7 +37615,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>246</v>
       </c>
@@ -37653,7 +37656,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>247</v>
       </c>
@@ -37691,7 +37694,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>248</v>
       </c>
@@ -37732,7 +37735,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>249</v>
       </c>
@@ -37773,7 +37776,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>250</v>
       </c>
@@ -37817,7 +37820,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -37847,7 +37850,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>252</v>
       </c>
@@ -37888,7 +37891,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>253</v>
       </c>
@@ -37929,7 +37932,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>254</v>
       </c>
@@ -37970,7 +37973,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>255</v>
       </c>
@@ -38011,7 +38014,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>256</v>
       </c>
@@ -38052,7 +38055,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>257</v>
       </c>
@@ -38094,7 +38097,7 @@
       </c>
       <c r="N257" s="5"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>258</v>
       </c>
@@ -38135,7 +38138,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>259</v>
       </c>
@@ -38177,7 +38180,7 @@
       </c>
       <c r="N259" s="5"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>260</v>
       </c>
@@ -38218,7 +38221,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>261</v>
       </c>
@@ -38259,7 +38262,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>262</v>
       </c>
@@ -38300,7 +38303,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>263</v>
       </c>
@@ -38341,7 +38344,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>264</v>
       </c>
@@ -38382,7 +38385,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>265</v>
       </c>
@@ -38423,7 +38426,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>266</v>
       </c>
@@ -38464,7 +38467,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>267</v>
       </c>
@@ -38505,7 +38508,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>268</v>
       </c>
@@ -38546,7 +38549,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>269</v>
       </c>
@@ -38587,7 +38590,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>270</v>
       </c>
@@ -38625,7 +38628,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -38657,7 +38660,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>272</v>
       </c>
@@ -38695,7 +38698,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>273</v>
       </c>
@@ -38733,7 +38736,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>274</v>
       </c>
@@ -38768,7 +38771,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>275</v>
       </c>
@@ -38809,7 +38812,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>276</v>
       </c>
@@ -38850,7 +38853,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>277</v>
       </c>
@@ -38891,7 +38894,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>278</v>
       </c>
@@ -38929,7 +38932,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>279</v>
       </c>
@@ -38967,7 +38970,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>280</v>
       </c>
@@ -39008,7 +39011,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>281</v>
       </c>
@@ -39049,7 +39052,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>282</v>
       </c>
@@ -39089,7 +39092,7 @@
       </c>
       <c r="N282" s="5"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>283</v>
       </c>
@@ -39130,7 +39133,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>284</v>
       </c>
@@ -39172,7 +39175,7 @@
       </c>
       <c r="N284" s="5"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>285</v>
       </c>
@@ -39210,7 +39213,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>286</v>
       </c>
@@ -39251,7 +39254,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>287</v>
       </c>
@@ -39292,7 +39295,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>288</v>
       </c>
@@ -39333,7 +39336,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>289</v>
       </c>
@@ -39374,7 +39377,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>290</v>
       </c>
@@ -39415,7 +39418,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>291</v>
       </c>
@@ -39456,7 +39459,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>292</v>
       </c>
@@ -39497,7 +39500,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>293</v>
       </c>
@@ -39538,7 +39541,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>294</v>
       </c>
@@ -39579,7 +39582,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>295</v>
       </c>
@@ -39620,7 +39623,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>296</v>
       </c>
@@ -39658,7 +39661,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>297</v>
       </c>
@@ -39699,7 +39702,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>298</v>
       </c>
@@ -39737,7 +39740,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>299</v>
       </c>
@@ -39778,7 +39781,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>300</v>
       </c>
@@ -39819,7 +39822,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>301</v>
       </c>
@@ -39857,7 +39860,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>302</v>
       </c>
@@ -39898,7 +39901,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>303</v>
       </c>
@@ -39939,7 +39942,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>304</v>
       </c>
@@ -39980,7 +39983,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>305</v>
       </c>
@@ -40021,7 +40024,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>306</v>
       </c>
@@ -40062,7 +40065,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>307</v>
       </c>
@@ -40103,7 +40106,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>308</v>
       </c>
@@ -40144,7 +40147,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>309</v>
       </c>
@@ -40185,7 +40188,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>310</v>
       </c>
@@ -40226,7 +40229,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>311</v>
       </c>
@@ -40267,7 +40270,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>312</v>
       </c>
@@ -40308,7 +40311,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>313</v>
       </c>
@@ -40343,7 +40346,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>314</v>
       </c>
@@ -40381,7 +40384,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>315</v>
       </c>
@@ -40422,7 +40425,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>316</v>
       </c>
@@ -40463,7 +40466,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>317</v>
       </c>
@@ -40498,7 +40501,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>318</v>
       </c>
@@ -40536,7 +40539,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>319</v>
       </c>
@@ -40577,7 +40580,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>320</v>
       </c>
@@ -40615,7 +40618,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>321</v>
       </c>
@@ -40656,7 +40659,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>322</v>
       </c>
@@ -40697,7 +40700,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>323</v>
       </c>
@@ -40738,7 +40741,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>324</v>
       </c>
@@ -40776,7 +40779,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>325</v>
       </c>
@@ -40817,7 +40820,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>326</v>
       </c>
@@ -40858,7 +40861,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>327</v>
       </c>
@@ -40900,7 +40903,7 @@
       </c>
       <c r="N327" s="5"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>331</v>
       </c>
@@ -40935,7 +40938,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>332</v>
       </c>
@@ -40976,7 +40979,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>335</v>
       </c>
@@ -41017,7 +41020,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>336</v>
       </c>
@@ -41052,7 +41055,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>337</v>
       </c>
@@ -41087,7 +41090,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>338</v>
       </c>
@@ -41125,7 +41128,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>339</v>
       </c>
@@ -41166,7 +41169,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>340</v>
       </c>
@@ -41204,7 +41207,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>341</v>
       </c>
@@ -41245,7 +41248,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>342</v>
       </c>
@@ -41286,7 +41289,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>343</v>
       </c>
@@ -41327,7 +41330,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>344</v>
       </c>
@@ -41368,7 +41371,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>345</v>
       </c>
@@ -41409,7 +41412,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>346</v>
       </c>
@@ -41447,7 +41450,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>347</v>
       </c>
@@ -41488,7 +41491,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>348</v>
       </c>
@@ -41529,7 +41532,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>349</v>
       </c>
@@ -41570,7 +41573,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>350</v>
       </c>
@@ -41611,7 +41614,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>351</v>
       </c>
@@ -41652,7 +41655,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>352</v>
       </c>
@@ -41690,7 +41693,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="5">
         <v>353</v>
       </c>
@@ -41732,7 +41735,7 @@
       </c>
       <c r="N348" s="5"/>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>354</v>
       </c>
@@ -41770,7 +41773,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>355</v>
       </c>
@@ -41811,7 +41814,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="5">
         <v>356</v>
       </c>
@@ -41853,7 +41856,7 @@
       </c>
       <c r="N351" s="5"/>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="5">
         <v>357</v>
       </c>
@@ -41895,7 +41898,7 @@
       </c>
       <c r="N352" s="5"/>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>358</v>
       </c>
@@ -41937,7 +41940,7 @@
       </c>
       <c r="N353" s="5"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>359</v>
       </c>
@@ -41978,7 +41981,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>360</v>
       </c>
@@ -42019,7 +42022,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>361</v>
       </c>
@@ -42060,7 +42063,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>362</v>
       </c>
@@ -42101,7 +42104,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>363</v>
       </c>
@@ -42142,7 +42145,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359" s="5">
         <v>364</v>
       </c>
@@ -42186,7 +42189,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360" s="5">
         <v>365</v>
       </c>
@@ -42230,7 +42233,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" s="5">
         <v>366</v>
       </c>
@@ -42274,7 +42277,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" s="5">
         <v>367</v>
       </c>
@@ -42318,7 +42321,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>368</v>
       </c>
@@ -42359,7 +42362,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>369</v>
       </c>
@@ -42400,7 +42403,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>370</v>
       </c>
@@ -42441,7 +42444,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>371</v>
       </c>
@@ -42482,7 +42485,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>372</v>
       </c>
@@ -42523,7 +42526,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>373</v>
       </c>
@@ -42561,7 +42564,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>374</v>
       </c>
@@ -42602,7 +42605,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>375</v>
       </c>
@@ -42643,7 +42646,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>376</v>
       </c>
@@ -42684,7 +42687,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>377</v>
       </c>
@@ -42725,7 +42728,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>378</v>
       </c>
@@ -42766,7 +42769,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>379</v>
       </c>
@@ -42807,7 +42810,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>380</v>
       </c>
@@ -42848,7 +42851,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>381</v>
       </c>
@@ -42889,7 +42892,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>382</v>
       </c>
@@ -42930,7 +42933,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>383</v>
       </c>
@@ -42971,7 +42974,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" s="5">
         <v>384</v>
       </c>
@@ -43015,7 +43018,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" s="5">
         <v>385</v>
       </c>
@@ -43059,7 +43062,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" s="5">
         <v>386</v>
       </c>
@@ -43103,7 +43106,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>387</v>
       </c>
@@ -43144,7 +43147,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>388</v>
       </c>
@@ -43185,7 +43188,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>389</v>
       </c>
@@ -43226,7 +43229,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>390</v>
       </c>
@@ -43264,7 +43267,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>391</v>
       </c>
@@ -43302,7 +43305,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" s="6">
         <v>392</v>
       </c>
@@ -43334,7 +43337,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" s="5">
         <v>393</v>
       </c>
@@ -43376,7 +43379,7 @@
       </c>
       <c r="N388" s="5"/>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" s="5">
         <v>394</v>
       </c>
@@ -43418,7 +43421,7 @@
       </c>
       <c r="N389" s="5"/>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" s="5">
         <v>395</v>
       </c>
@@ -43460,7 +43463,7 @@
       </c>
       <c r="N390" s="5"/>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" s="5">
         <v>396</v>
       </c>
@@ -43502,7 +43505,7 @@
       </c>
       <c r="N391" s="5"/>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" s="5">
         <v>397</v>
       </c>
@@ -43544,7 +43547,7 @@
       </c>
       <c r="N392" s="5"/>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>398</v>
       </c>
@@ -43585,7 +43588,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>399</v>
       </c>
@@ -43626,7 +43629,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>400</v>
       </c>
@@ -43667,7 +43670,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>401</v>
       </c>
@@ -43708,7 +43711,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>402</v>
       </c>
@@ -43749,7 +43752,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>403</v>
       </c>
@@ -43790,7 +43793,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>404</v>
       </c>
@@ -43831,7 +43834,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>405</v>
       </c>
@@ -43872,7 +43875,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401" s="5">
         <v>406</v>
       </c>
@@ -43914,7 +43917,7 @@
       </c>
       <c r="N401" s="5"/>
     </row>
-    <row r="402" spans="1:14">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>407</v>
       </c>
@@ -43955,7 +43958,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="403" spans="1:14">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>408</v>
       </c>
@@ -43996,7 +43999,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="404" spans="1:14">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>409</v>
       </c>
@@ -44034,7 +44037,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="405" spans="1:14">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>410</v>
       </c>
@@ -44075,7 +44078,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="406" spans="1:14">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>411</v>
       </c>
@@ -44116,7 +44119,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="407" spans="1:14">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>412</v>
       </c>
@@ -44157,7 +44160,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="408" spans="1:14">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>413</v>
       </c>
@@ -44198,7 +44201,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="409" spans="1:14">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>414</v>
       </c>
@@ -44239,7 +44242,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="410" spans="1:14">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>415</v>
       </c>
@@ -44280,7 +44283,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="411" spans="1:14">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>416</v>
       </c>
@@ -44321,7 +44324,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="412" spans="1:14">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>417</v>
       </c>
@@ -44362,7 +44365,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="413" spans="1:14">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>418</v>
       </c>
@@ -44403,7 +44406,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="414" spans="1:14">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414" s="5">
         <v>419</v>
       </c>
@@ -44445,7 +44448,7 @@
       </c>
       <c r="N414" s="5"/>
     </row>
-    <row r="415" spans="1:14">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>420</v>
       </c>
@@ -44483,7 +44486,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="416" spans="1:14">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>421</v>
       </c>
@@ -44524,7 +44527,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>422</v>
       </c>
@@ -44565,7 +44568,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>423</v>
       </c>
@@ -44606,7 +44609,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>424</v>
       </c>
@@ -44647,7 +44650,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="420" spans="1:14">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>425</v>
       </c>
@@ -44685,7 +44688,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="421" spans="1:14">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>426</v>
       </c>
@@ -44726,7 +44729,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>427</v>
       </c>
@@ -44764,7 +44767,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>428</v>
       </c>
@@ -44805,7 +44808,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>429</v>
       </c>
@@ -44846,7 +44849,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="425" spans="1:14">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425" s="6">
         <v>430</v>
       </c>
@@ -44876,7 +44879,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="426" spans="1:14">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>431</v>
       </c>
@@ -44917,7 +44920,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>432</v>
       </c>
@@ -44955,7 +44958,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="428" spans="1:14">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>433</v>
       </c>
@@ -44996,7 +44999,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="429" spans="1:14">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>434</v>
       </c>
@@ -45034,7 +45037,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="430" spans="1:14">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>435</v>
       </c>
@@ -45075,7 +45078,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>436</v>
       </c>
@@ -45110,7 +45113,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>437</v>
       </c>
@@ -45148,7 +45151,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>438</v>
       </c>
@@ -45186,7 +45189,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>439</v>
       </c>
@@ -45227,7 +45230,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435" s="6">
         <v>440</v>
       </c>
@@ -45259,7 +45262,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>441</v>
       </c>
@@ -45300,7 +45303,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>442</v>
       </c>
@@ -45341,7 +45344,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="438" spans="1:14">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>443</v>
       </c>
@@ -45379,7 +45382,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="439" spans="1:14">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>444</v>
       </c>
@@ -45420,7 +45423,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="440" spans="1:14">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>445</v>
       </c>
@@ -45458,7 +45461,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>446</v>
       </c>
@@ -45499,7 +45502,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442" s="5">
         <v>447</v>
       </c>
@@ -45541,7 +45544,7 @@
       </c>
       <c r="N442" s="5"/>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>448</v>
       </c>
@@ -45582,7 +45585,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>449</v>
       </c>
@@ -45623,7 +45626,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>450</v>
       </c>
@@ -45664,7 +45667,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>451</v>
       </c>
@@ -45705,7 +45708,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>452</v>
       </c>
@@ -45746,7 +45749,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>453</v>
       </c>
@@ -45787,7 +45790,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="449" spans="1:14">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>454</v>
       </c>
@@ -45828,7 +45831,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="450" spans="1:14">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450" s="5">
         <v>455</v>
       </c>
@@ -45870,7 +45873,7 @@
       </c>
       <c r="N450" s="5"/>
     </row>
-    <row r="451" spans="1:14">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>456</v>
       </c>
@@ -45911,7 +45914,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="452" spans="1:14">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>457</v>
       </c>
@@ -45952,7 +45955,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="453" spans="1:14">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>458</v>
       </c>
@@ -45990,7 +45993,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="454" spans="1:14">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>459</v>
       </c>
@@ -46031,7 +46034,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="455" spans="1:14">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>460</v>
       </c>
@@ -46069,7 +46072,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="456" spans="1:14">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>461</v>
       </c>
@@ -46110,7 +46113,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="457" spans="1:14">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>462</v>
       </c>
@@ -46151,7 +46154,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="458" spans="1:14">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>463</v>
       </c>
@@ -46192,7 +46195,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="459" spans="1:14">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>464</v>
       </c>
@@ -46233,7 +46236,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="460" spans="1:14">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>465</v>
       </c>
@@ -46274,7 +46277,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="461" spans="1:14">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>466</v>
       </c>
@@ -46315,7 +46318,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="462" spans="1:14">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>467</v>
       </c>
@@ -46356,7 +46359,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="463" spans="1:14">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A463" s="5">
         <v>468</v>
       </c>
@@ -46400,7 +46403,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="464" spans="1:14">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>469</v>
       </c>
@@ -46441,7 +46444,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="465" spans="1:14">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>470</v>
       </c>
@@ -46482,7 +46485,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="466" spans="1:14">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>471</v>
       </c>
@@ -46523,7 +46526,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="467" spans="1:14">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>472</v>
       </c>
@@ -46564,7 +46567,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="468" spans="1:14">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>473</v>
       </c>
@@ -46605,7 +46608,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="469" spans="1:14">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469" s="5">
         <v>474</v>
       </c>
@@ -46649,7 +46652,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="470" spans="1:14">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>475</v>
       </c>
@@ -46690,7 +46693,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="471" spans="1:14">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>476</v>
       </c>
@@ -46731,7 +46734,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="472" spans="1:14">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>477</v>
       </c>
@@ -46769,7 +46772,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="473" spans="1:14">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>478</v>
       </c>
@@ -46807,7 +46810,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="474" spans="1:14">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>479</v>
       </c>
@@ -46849,7 +46852,7 @@
       </c>
       <c r="N474" s="5"/>
     </row>
-    <row r="475" spans="1:14">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>480</v>
       </c>
@@ -46890,7 +46893,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="476" spans="1:14">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>481</v>
       </c>
@@ -46931,7 +46934,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="477" spans="1:14">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>482</v>
       </c>
@@ -46972,7 +46975,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="478" spans="1:14">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>483</v>
       </c>
@@ -47013,7 +47016,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="479" spans="1:14">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>484</v>
       </c>
@@ -47057,7 +47060,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="480" spans="1:14">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480" s="5">
         <v>485</v>
       </c>
@@ -47101,7 +47104,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>486</v>
       </c>
@@ -47142,7 +47145,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>487</v>
       </c>
@@ -47183,7 +47186,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>488</v>
       </c>
@@ -47224,7 +47227,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>489</v>
       </c>
@@ -47265,7 +47268,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="485" spans="1:14">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>490</v>
       </c>
@@ -47306,7 +47309,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="486" spans="1:14">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>491</v>
       </c>
@@ -47347,7 +47350,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="487" spans="1:14">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>492</v>
       </c>
@@ -47388,7 +47391,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="488" spans="1:14">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>493</v>
       </c>
@@ -47429,7 +47432,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="489" spans="1:14">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489" s="5">
         <v>494</v>
       </c>
@@ -47473,7 +47476,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="490" spans="1:14">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>495</v>
       </c>
@@ -47514,7 +47517,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="491" spans="1:14">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>496</v>
       </c>
@@ -47555,7 +47558,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492" s="5">
         <v>497</v>
       </c>
@@ -47597,7 +47600,7 @@
       </c>
       <c r="N492" s="5"/>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>498</v>
       </c>
@@ -47638,7 +47641,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>499</v>
       </c>
@@ -47679,7 +47682,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="495" spans="1:14">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>500</v>
       </c>
@@ -47720,7 +47723,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="496" spans="1:14">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496" s="5">
         <v>501</v>
       </c>
@@ -47762,7 +47765,7 @@
       </c>
       <c r="N496" s="5"/>
     </row>
-    <row r="497" spans="1:14">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>502</v>
       </c>
@@ -47803,7 +47806,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="498" spans="1:14">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498" s="5">
         <v>503</v>
       </c>
@@ -47845,7 +47848,7 @@
       </c>
       <c r="N498" s="5"/>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499" s="5">
         <v>504</v>
       </c>
@@ -47887,7 +47890,7 @@
       </c>
       <c r="N499" s="5"/>
     </row>
-    <row r="500" spans="1:14">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>505</v>
       </c>
@@ -47928,7 +47931,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="501" spans="1:14">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>506</v>
       </c>
@@ -47969,7 +47972,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="502" spans="1:14">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>507</v>
       </c>
@@ -48007,7 +48010,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="503" spans="1:14">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>508</v>
       </c>
@@ -48045,7 +48048,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="504" spans="1:14">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>509</v>
       </c>
@@ -48083,7 +48086,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="505" spans="1:14">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>510</v>
       </c>
@@ -48121,7 +48124,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="506" spans="1:14">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>511</v>
       </c>
@@ -48159,7 +48162,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="507" spans="1:14">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507" s="5">
         <v>512</v>
       </c>
@@ -48201,7 +48204,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508" s="5">
         <v>513</v>
       </c>
@@ -48243,7 +48246,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>514</v>
       </c>
@@ -48284,7 +48287,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="510" spans="1:14">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>515</v>
       </c>
@@ -48325,7 +48328,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="511" spans="1:14">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>516</v>
       </c>
@@ -48366,7 +48369,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="512" spans="1:14">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>517</v>
       </c>
@@ -48413,14 +48416,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -48684,22 +48685,58 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DE95047-1E93-4319-AEDC-4DFA7911D326}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96E32C67-4B3A-4CA1-AAAD-E7247368D478}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27665,11 +27665,20 @@
       </c>
     </row>
     <row r="515" spans="1:12">
+      <c r="A515">
+        <v>27100522</v>
+      </c>
       <c r="F515" t="s">
         <v>1418</v>
       </c>
       <c r="H515" t="s">
         <v>1220</v>
+      </c>
+      <c r="J515">
+        <v>2022</v>
+      </c>
+      <c r="K515">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E570E50B-DE9E-4404-900F-FF024E262669}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AFC6077-BF7A-41F0-A1F7-732B90D6DE41}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10452" uniqueCount="2231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10453" uniqueCount="2231">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27683,6 +27683,9 @@
       <c r="H515" t="s">
         <v>1220</v>
       </c>
+      <c r="I515" t="s">
+        <v>790</v>
+      </c>
       <c r="J515">
         <v>2022</v>
       </c>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A4BF04-8311-437B-9D4E-6EDDCF4C39BE}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2017EBF-63C1-43DD-AE1E-9C5A99102AC8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6743,6 +6743,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -6812,7 +6815,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6825,6 +6828,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27594,7 +27598,7 @@
       <c r="M512">
         <v>5</v>
       </c>
-      <c r="P512" s="7">
+      <c r="P512" s="8">
         <v>46175</v>
       </c>
     </row>
@@ -27632,7 +27636,7 @@
       <c r="L513">
         <v>6.9</v>
       </c>
-      <c r="P513" s="7">
+      <c r="P513" s="8">
         <v>46176</v>
       </c>
     </row>
@@ -27673,7 +27677,7 @@
       <c r="L514">
         <v>6.2</v>
       </c>
-      <c r="P514" s="7">
+      <c r="P514" s="8">
         <v>46177</v>
       </c>
     </row>
@@ -27705,7 +27709,7 @@
       <c r="K515">
         <v>75</v>
       </c>
-      <c r="P515" s="7">
+      <c r="P515" s="8">
         <v>46178</v>
       </c>
     </row>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2017EBF-63C1-43DD-AE1E-9C5A99102AC8}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0ED8BDA-42FB-4288-ADC4-675C0775774C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10453" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10454" uniqueCount="2232">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27691,6 +27691,9 @@
       <c r="D515" t="s">
         <v>1418</v>
       </c>
+      <c r="E515" t="s">
+        <v>80</v>
+      </c>
       <c r="F515" t="s">
         <v>1419</v>
       </c>
@@ -27708,6 +27711,9 @@
       </c>
       <c r="K515">
         <v>75</v>
+      </c>
+      <c r="L515">
+        <v>17.8</v>
       </c>
       <c r="P515" s="8">
         <v>46178</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0ED8BDA-42FB-4288-ADC4-675C0775774C}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{050DA6E4-69C7-41CE-9244-FF60ABF5C3F2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10454" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10455" uniqueCount="2232">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27685,6 +27685,9 @@
       <c r="A515">
         <v>27100522</v>
       </c>
+      <c r="B515" t="s">
+        <v>56</v>
+      </c>
       <c r="C515" t="s">
         <v>977</v>
       </c>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7142F1A-C0F9-4C6B-A3D3-5E8EA24A86A4}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{042E8A9C-17D0-427A-892B-CD593899D364}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10464" uniqueCount="2234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10477" uniqueCount="2234">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -20786,6 +20786,9 @@
       <c r="C337" t="s">
         <v>916</v>
       </c>
+      <c r="D337" t="s">
+        <v>923</v>
+      </c>
       <c r="E337" t="s">
         <v>934</v>
       </c>
@@ -20827,6 +20830,9 @@
       <c r="C338" t="s">
         <v>916</v>
       </c>
+      <c r="D338" t="s">
+        <v>923</v>
+      </c>
       <c r="E338" t="s">
         <v>934</v>
       </c>
@@ -20868,6 +20874,9 @@
       <c r="C339" t="s">
         <v>916</v>
       </c>
+      <c r="D339" t="s">
+        <v>923</v>
+      </c>
       <c r="E339" t="s">
         <v>934</v>
       </c>
@@ -20906,6 +20915,9 @@
       <c r="C340" t="s">
         <v>916</v>
       </c>
+      <c r="D340" t="s">
+        <v>923</v>
+      </c>
       <c r="E340" t="s">
         <v>934</v>
       </c>
@@ -20944,6 +20956,9 @@
       <c r="C341" t="s">
         <v>916</v>
       </c>
+      <c r="D341" t="s">
+        <v>923</v>
+      </c>
       <c r="E341" t="s">
         <v>934</v>
       </c>
@@ -20985,6 +21000,9 @@
       <c r="C342" t="s">
         <v>916</v>
       </c>
+      <c r="D342" t="s">
+        <v>923</v>
+      </c>
       <c r="E342" t="s">
         <v>934</v>
       </c>
@@ -21023,6 +21041,9 @@
       <c r="C343" t="s">
         <v>916</v>
       </c>
+      <c r="D343" t="s">
+        <v>923</v>
+      </c>
       <c r="E343" t="s">
         <v>934</v>
       </c>
@@ -21061,6 +21082,9 @@
       <c r="C344" t="s">
         <v>916</v>
       </c>
+      <c r="D344" t="s">
+        <v>923</v>
+      </c>
       <c r="E344" t="s">
         <v>934</v>
       </c>
@@ -21102,6 +21126,9 @@
       <c r="C345" t="s">
         <v>916</v>
       </c>
+      <c r="D345" t="s">
+        <v>923</v>
+      </c>
       <c r="E345" t="s">
         <v>934</v>
       </c>
@@ -21143,6 +21170,9 @@
       <c r="C346" t="s">
         <v>916</v>
       </c>
+      <c r="D346" t="s">
+        <v>923</v>
+      </c>
       <c r="E346" t="s">
         <v>934</v>
       </c>
@@ -21178,6 +21208,9 @@
       <c r="C347" t="s">
         <v>916</v>
       </c>
+      <c r="D347" t="s">
+        <v>923</v>
+      </c>
       <c r="E347" t="s">
         <v>934</v>
       </c>
@@ -21216,6 +21249,9 @@
       <c r="C348" t="s">
         <v>916</v>
       </c>
+      <c r="D348" t="s">
+        <v>923</v>
+      </c>
       <c r="E348" t="s">
         <v>934</v>
       </c>
@@ -21253,6 +21289,9 @@
       </c>
       <c r="C349" t="s">
         <v>916</v>
+      </c>
+      <c r="D349" t="s">
+        <v>923</v>
       </c>
       <c r="E349" t="s">
         <v>934</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D9F350C-9E5C-484F-ABF4-92B463634DC6}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28753623-7CDF-4A2C-BF31-C1F473BBA16B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22451,7 +22451,7 @@
         <v>979</v>
       </c>
       <c r="D377" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E377" t="s">
         <v>58</v>
@@ -22492,7 +22492,7 @@
         <v>979</v>
       </c>
       <c r="D378" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E378" t="s">
         <v>58</v>
@@ -22533,7 +22533,7 @@
         <v>979</v>
       </c>
       <c r="D379" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E379" t="s">
         <v>58</v>
@@ -22574,7 +22574,7 @@
         <v>979</v>
       </c>
       <c r="D380" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E380" t="s">
         <v>58</v>
@@ -22615,7 +22615,7 @@
         <v>979</v>
       </c>
       <c r="D381" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E381" t="s">
         <v>58</v>
@@ -22656,7 +22656,7 @@
         <v>979</v>
       </c>
       <c r="D382" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E382" t="s">
         <v>58</v>
@@ -22697,7 +22697,7 @@
         <v>979</v>
       </c>
       <c r="D383" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E383" t="s">
         <v>58</v>
@@ -22738,7 +22738,7 @@
         <v>979</v>
       </c>
       <c r="D384" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E384" t="s">
         <v>58</v>
@@ -22776,7 +22776,7 @@
         <v>979</v>
       </c>
       <c r="D385" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E385" t="s">
         <v>58</v>
@@ -22814,7 +22814,7 @@
         <v>979</v>
       </c>
       <c r="D386" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
@@ -22937,7 +22937,7 @@
         <v>979</v>
       </c>
       <c r="D389" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E389" t="s">
         <v>80</v>
@@ -23394,7 +23394,7 @@
         <v>979</v>
       </c>
       <c r="D400" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E400" t="s">
         <v>80</v>
@@ -23435,7 +23435,7 @@
         <v>979</v>
       </c>
       <c r="D401" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E401" t="s">
         <v>80</v>
@@ -23476,7 +23476,7 @@
         <v>979</v>
       </c>
       <c r="D402" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="E402" t="s">
         <v>80</v>
@@ -23517,7 +23517,7 @@
         <v>979</v>
       </c>
       <c r="D403" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E403" t="s">
         <v>80</v>
@@ -23555,7 +23555,7 @@
         <v>979</v>
       </c>
       <c r="D404" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E404" t="s">
         <v>80</v>
@@ -23596,7 +23596,7 @@
         <v>979</v>
       </c>
       <c r="D405" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E405" t="s">
         <v>80</v>
@@ -23637,7 +23637,7 @@
         <v>979</v>
       </c>
       <c r="D406" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E406" t="s">
         <v>80</v>
@@ -23678,7 +23678,7 @@
         <v>979</v>
       </c>
       <c r="D407" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E407" t="s">
         <v>80</v>
@@ -23719,7 +23719,7 @@
         <v>979</v>
       </c>
       <c r="D408" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E408" t="s">
         <v>80</v>
@@ -23763,7 +23763,7 @@
         <v>979</v>
       </c>
       <c r="D409" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E409" t="s">
         <v>80</v>
@@ -23804,7 +23804,7 @@
         <v>979</v>
       </c>
       <c r="D410" t="s">
-        <v>980</v>
+        <v>1055</v>
       </c>
       <c r="E410" t="s">
         <v>80</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F819ED09-7BAD-4094-8810-295EFCBEF4A7}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9562AED-EE1A-42C7-AE06-602F9927BFE0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10548" uniqueCount="2238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10549" uniqueCount="2238">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27652,6 +27652,9 @@
       <c r="C506" t="s">
         <v>1375</v>
       </c>
+      <c r="D506" t="s">
+        <v>1364</v>
+      </c>
       <c r="E506" t="s">
         <v>1375</v>
       </c>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9562AED-EE1A-42C7-AE06-602F9927BFE0}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE8A448-3057-4D06-A36F-4414C15D883F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3076,6 +3076,9 @@
     <t>16002825</t>
   </si>
   <si>
+    <t>les Magnums (150cl) et autres beaux flacons</t>
+  </si>
+  <si>
     <t>Cuvée Antique Chardonnay - MAGNUM</t>
   </si>
   <si>
@@ -4133,9 +4136,6 @@
   </si>
   <si>
     <t>252010NM</t>
-  </si>
-  <si>
-    <t>les Magnums (150cl) et autres beaux flacons</t>
   </si>
   <si>
     <t>Grande Réserve - MAGNUM</t>
@@ -21766,7 +21766,7 @@
         <v>981</v>
       </c>
       <c r="D360" t="s">
-        <v>982</v>
+        <v>1011</v>
       </c>
       <c r="E360" t="s">
         <v>58</v>
@@ -21775,7 +21775,7 @@
         <v>983</v>
       </c>
       <c r="G360" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H360" t="s">
         <v>1009</v>
@@ -21798,7 +21798,7 @@
     </row>
     <row r="361" spans="1:18">
       <c r="A361" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B361" t="s">
         <v>56</v>
@@ -21816,13 +21816,13 @@
         <v>983</v>
       </c>
       <c r="G361" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H361" t="s">
         <v>995</v>
       </c>
       <c r="I361" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J361" t="s">
         <v>94</v>
@@ -21842,7 +21842,7 @@
     </row>
     <row r="362" spans="1:18">
       <c r="A362" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B362" t="s">
         <v>56</v>
@@ -21851,19 +21851,19 @@
         <v>981</v>
       </c>
       <c r="D362" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E362" t="s">
         <v>58</v>
       </c>
       <c r="F362" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G362" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H362" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J362" t="s">
         <v>83</v>
@@ -21883,7 +21883,7 @@
     </row>
     <row r="363" spans="1:18">
       <c r="A363" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B363" t="s">
         <v>56</v>
@@ -21898,13 +21898,13 @@
         <v>58</v>
       </c>
       <c r="F363" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G363" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H363" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="I363" t="s">
         <v>792</v>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="364" spans="1:18">
       <c r="A364" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B364" t="s">
         <v>56</v>
@@ -21945,7 +21945,7 @@
         <v>983</v>
       </c>
       <c r="G364" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H364" t="s">
         <v>995</v>
@@ -21968,7 +21968,7 @@
     </row>
     <row r="365" spans="1:18">
       <c r="A365" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B365" t="s">
         <v>56</v>
@@ -21986,13 +21986,13 @@
         <v>983</v>
       </c>
       <c r="G365" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H365" t="s">
         <v>995</v>
       </c>
       <c r="I365" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J365" t="s">
         <v>94</v>
@@ -22012,7 +22012,7 @@
     </row>
     <row r="366" spans="1:18">
       <c r="A366" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B366" t="s">
         <v>56</v>
@@ -22030,7 +22030,7 @@
         <v>983</v>
       </c>
       <c r="G366" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H366" t="s">
         <v>615</v>
@@ -22053,7 +22053,7 @@
     </row>
     <row r="367" spans="1:18">
       <c r="A367" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B367" t="s">
         <v>56</v>
@@ -22068,13 +22068,13 @@
         <v>58</v>
       </c>
       <c r="F367" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G367" t="s">
         <v>160</v>
       </c>
       <c r="H367" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J367" t="s">
         <v>94</v>
@@ -22091,7 +22091,7 @@
     </row>
     <row r="368" spans="1:18">
       <c r="A368" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B368" t="s">
         <v>56</v>
@@ -22106,13 +22106,13 @@
         <v>58</v>
       </c>
       <c r="F368" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G368" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H368" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J368" t="s">
         <v>94</v>
@@ -22132,7 +22132,7 @@
     </row>
     <row r="369" spans="1:16">
       <c r="A369" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B369" t="s">
         <v>56</v>
@@ -22147,13 +22147,13 @@
         <v>58</v>
       </c>
       <c r="F369" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G369" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H369" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J369" t="s">
         <v>94</v>
@@ -22173,7 +22173,7 @@
     </row>
     <row r="370" spans="1:16">
       <c r="A370" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B370" t="s">
         <v>118</v>
@@ -22191,10 +22191,10 @@
         <v>59</v>
       </c>
       <c r="G370" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H370" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J370" t="s">
         <v>335</v>
@@ -22214,7 +22214,7 @@
     </row>
     <row r="371" spans="1:16">
       <c r="A371" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B371" t="s">
         <v>118</v>
@@ -22223,19 +22223,19 @@
         <v>981</v>
       </c>
       <c r="D371" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E371" t="s">
         <v>58</v>
       </c>
       <c r="F371" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G371" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H371" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J371" t="s">
         <v>83</v>
@@ -22255,7 +22255,7 @@
     </row>
     <row r="372" spans="1:16">
       <c r="A372" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B372" t="s">
         <v>118</v>
@@ -22273,10 +22273,10 @@
         <v>59</v>
       </c>
       <c r="G372" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H372" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J372" t="s">
         <v>335</v>
@@ -22296,7 +22296,7 @@
     </row>
     <row r="373" spans="1:16">
       <c r="A373" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B373" t="s">
         <v>118</v>
@@ -22305,19 +22305,19 @@
         <v>981</v>
       </c>
       <c r="D373" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E373" t="s">
         <v>58</v>
       </c>
       <c r="F373" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G373" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H373" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J373" t="s">
         <v>63</v>
@@ -22337,7 +22337,7 @@
     </row>
     <row r="374" spans="1:16">
       <c r="A374" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B374" t="s">
         <v>118</v>
@@ -22355,13 +22355,13 @@
         <v>59</v>
       </c>
       <c r="G374" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H374" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I374" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="J374" t="s">
         <v>94</v>
@@ -22381,7 +22381,7 @@
     </row>
     <row r="375" spans="1:16">
       <c r="A375" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B375" t="s">
         <v>118</v>
@@ -22390,19 +22390,19 @@
         <v>981</v>
       </c>
       <c r="D375" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E375" t="s">
         <v>58</v>
       </c>
       <c r="F375" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G375" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H375" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="J375" t="s">
         <v>94</v>
@@ -22422,7 +22422,7 @@
     </row>
     <row r="376" spans="1:16">
       <c r="A376" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B376" t="s">
         <v>118</v>
@@ -22431,19 +22431,19 @@
         <v>981</v>
       </c>
       <c r="D376" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E376" t="s">
         <v>58</v>
       </c>
       <c r="F376" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G376" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H376" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J376" t="s">
         <v>129</v>
@@ -22463,7 +22463,7 @@
     </row>
     <row r="377" spans="1:16">
       <c r="A377" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B377" t="s">
         <v>118</v>
@@ -22472,19 +22472,19 @@
         <v>981</v>
       </c>
       <c r="D377" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E377" t="s">
         <v>58</v>
       </c>
       <c r="F377" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G377" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H377" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J377" t="s">
         <v>102</v>
@@ -22504,7 +22504,7 @@
     </row>
     <row r="378" spans="1:16">
       <c r="A378" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B378" t="s">
         <v>118</v>
@@ -22513,19 +22513,19 @@
         <v>981</v>
       </c>
       <c r="D378" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E378" t="s">
         <v>58</v>
       </c>
       <c r="F378" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G378" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H378" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="J378" t="s">
         <v>335</v>
@@ -22545,7 +22545,7 @@
     </row>
     <row r="379" spans="1:16">
       <c r="A379" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B379" t="s">
         <v>118</v>
@@ -22554,19 +22554,19 @@
         <v>981</v>
       </c>
       <c r="D379" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E379" t="s">
         <v>58</v>
       </c>
       <c r="F379" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G379" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H379" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="J379" t="s">
         <v>335</v>
@@ -22586,7 +22586,7 @@
     </row>
     <row r="380" spans="1:16">
       <c r="A380" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B380" t="s">
         <v>118</v>
@@ -22595,19 +22595,19 @@
         <v>981</v>
       </c>
       <c r="D380" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E380" t="s">
         <v>58</v>
       </c>
       <c r="F380" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G380" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H380" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J380" t="s">
         <v>94</v>
@@ -22627,7 +22627,7 @@
     </row>
     <row r="381" spans="1:16">
       <c r="A381" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B381" t="s">
         <v>56</v>
@@ -22636,19 +22636,19 @@
         <v>981</v>
       </c>
       <c r="D381" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E381" t="s">
         <v>58</v>
       </c>
       <c r="F381" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G381" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H381" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="J381" t="s">
         <v>94</v>
@@ -22668,7 +22668,7 @@
     </row>
     <row r="382" spans="1:16">
       <c r="A382" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B382" t="s">
         <v>56</v>
@@ -22677,19 +22677,19 @@
         <v>981</v>
       </c>
       <c r="D382" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E382" t="s">
         <v>58</v>
       </c>
       <c r="F382" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G382" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H382" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J382" t="s">
         <v>94</v>
@@ -22709,7 +22709,7 @@
     </row>
     <row r="383" spans="1:16">
       <c r="A383" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B383" t="s">
         <v>56</v>
@@ -22718,19 +22718,19 @@
         <v>981</v>
       </c>
       <c r="D383" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E383" t="s">
         <v>58</v>
       </c>
       <c r="F383" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G383" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H383" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J383" t="s">
         <v>94</v>
@@ -22750,7 +22750,7 @@
     </row>
     <row r="384" spans="1:16">
       <c r="A384" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B384" t="s">
         <v>56</v>
@@ -22759,19 +22759,19 @@
         <v>981</v>
       </c>
       <c r="D384" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E384" t="s">
         <v>58</v>
       </c>
       <c r="F384" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G384" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H384" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J384" t="s">
         <v>94</v>
@@ -22788,7 +22788,7 @@
     </row>
     <row r="385" spans="1:16">
       <c r="A385" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B385" t="s">
         <v>56</v>
@@ -22797,19 +22797,19 @@
         <v>981</v>
       </c>
       <c r="D385" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E385" t="s">
         <v>58</v>
       </c>
       <c r="F385" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G385" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H385" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J385" t="s">
         <v>530</v>
@@ -22835,19 +22835,19 @@
         <v>981</v>
       </c>
       <c r="D386" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
       </c>
       <c r="F386" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="G386" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H386" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J386" t="s">
         <v>63</v>
@@ -22867,7 +22867,7 @@
     </row>
     <row r="387" spans="1:16">
       <c r="A387" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B387" t="s">
         <v>56</v>
@@ -22885,7 +22885,7 @@
         <v>983</v>
       </c>
       <c r="G387" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H387" t="s">
         <v>985</v>
@@ -22908,7 +22908,7 @@
     </row>
     <row r="388" spans="1:16">
       <c r="A388" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B388" t="s">
         <v>56</v>
@@ -22926,7 +22926,7 @@
         <v>983</v>
       </c>
       <c r="G388" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H388" t="s">
         <v>988</v>
@@ -22949,7 +22949,7 @@
     </row>
     <row r="389" spans="1:16">
       <c r="A389" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B389" t="s">
         <v>56</v>
@@ -22958,7 +22958,7 @@
         <v>981</v>
       </c>
       <c r="D389" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E389" t="s">
         <v>80</v>
@@ -22990,7 +22990,7 @@
     </row>
     <row r="390" spans="1:16">
       <c r="A390" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B390" t="s">
         <v>56</v>
@@ -23031,7 +23031,7 @@
     </row>
     <row r="391" spans="1:16">
       <c r="A391" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B391" t="s">
         <v>56</v>
@@ -23072,7 +23072,7 @@
     </row>
     <row r="392" spans="1:16">
       <c r="A392" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
@@ -23090,7 +23090,7 @@
         <v>983</v>
       </c>
       <c r="G392" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H392" t="s">
         <v>286</v>
@@ -23113,7 +23113,7 @@
     </row>
     <row r="393" spans="1:16">
       <c r="A393" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
@@ -23131,7 +23131,7 @@
         <v>983</v>
       </c>
       <c r="G393" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H393" t="s">
         <v>988</v>
@@ -23154,7 +23154,7 @@
     </row>
     <row r="394" spans="1:16">
       <c r="A394" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
@@ -23172,7 +23172,7 @@
         <v>59</v>
       </c>
       <c r="G394" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H394" t="s">
         <v>1004</v>
@@ -23195,7 +23195,7 @@
     </row>
     <row r="395" spans="1:16">
       <c r="A395" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
@@ -23213,7 +23213,7 @@
         <v>983</v>
       </c>
       <c r="G395" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H395" t="s">
         <v>995</v>
@@ -23236,7 +23236,7 @@
     </row>
     <row r="396" spans="1:16">
       <c r="A396" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
@@ -23254,10 +23254,10 @@
         <v>983</v>
       </c>
       <c r="G396" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H396" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J396" t="s">
         <v>83</v>
@@ -23277,7 +23277,7 @@
     </row>
     <row r="397" spans="1:16">
       <c r="A397" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
@@ -23295,7 +23295,7 @@
         <v>983</v>
       </c>
       <c r="G397" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H397" t="s">
         <v>985</v>
@@ -23321,7 +23321,7 @@
     </row>
     <row r="398" spans="1:16">
       <c r="A398" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
@@ -23339,13 +23339,13 @@
         <v>983</v>
       </c>
       <c r="G398" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H398" t="s">
         <v>995</v>
       </c>
       <c r="I398" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J398" t="s">
         <v>63</v>
@@ -23365,7 +23365,7 @@
     </row>
     <row r="399" spans="1:16">
       <c r="A399" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
@@ -23383,10 +23383,10 @@
         <v>59</v>
       </c>
       <c r="G399" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H399" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J399" t="s">
         <v>63</v>
@@ -23406,7 +23406,7 @@
     </row>
     <row r="400" spans="1:16">
       <c r="A400" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
@@ -23415,19 +23415,19 @@
         <v>981</v>
       </c>
       <c r="D400" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E400" t="s">
         <v>80</v>
       </c>
       <c r="F400" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G400" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H400" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J400" t="s">
         <v>63</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="401" spans="1:16">
       <c r="A401" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
@@ -23456,19 +23456,19 @@
         <v>981</v>
       </c>
       <c r="D401" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E401" t="s">
         <v>80</v>
       </c>
       <c r="F401" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G401" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H401" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J401" t="s">
         <v>83</v>
@@ -23488,7 +23488,7 @@
     </row>
     <row r="402" spans="1:16">
       <c r="A402" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B402" t="s">
         <v>56</v>
@@ -23497,19 +23497,19 @@
         <v>981</v>
       </c>
       <c r="D402" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E402" t="s">
         <v>80</v>
       </c>
       <c r="F402" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G402" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H402" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J402" t="s">
         <v>105</v>
@@ -23529,7 +23529,7 @@
     </row>
     <row r="403" spans="1:16">
       <c r="A403" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B403" t="s">
         <v>118</v>
@@ -23538,19 +23538,19 @@
         <v>981</v>
       </c>
       <c r="D403" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E403" t="s">
         <v>80</v>
       </c>
       <c r="F403" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G403" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H403" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="J403" t="s">
         <v>63</v>
@@ -23567,7 +23567,7 @@
     </row>
     <row r="404" spans="1:16">
       <c r="A404" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B404" t="s">
         <v>118</v>
@@ -23576,19 +23576,19 @@
         <v>981</v>
       </c>
       <c r="D404" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E404" t="s">
         <v>80</v>
       </c>
       <c r="F404" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G404" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H404" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J404" t="s">
         <v>124</v>
@@ -23608,7 +23608,7 @@
     </row>
     <row r="405" spans="1:16">
       <c r="A405" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B405" t="s">
         <v>118</v>
@@ -23617,19 +23617,19 @@
         <v>981</v>
       </c>
       <c r="D405" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E405" t="s">
         <v>80</v>
       </c>
       <c r="F405" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G405" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H405" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J405" t="s">
         <v>205</v>
@@ -23649,7 +23649,7 @@
     </row>
     <row r="406" spans="1:16">
       <c r="A406" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B406" t="s">
         <v>118</v>
@@ -23658,19 +23658,19 @@
         <v>981</v>
       </c>
       <c r="D406" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E406" t="s">
         <v>80</v>
       </c>
       <c r="F406" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G406" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H406" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="J406" t="s">
         <v>94</v>
@@ -23690,7 +23690,7 @@
     </row>
     <row r="407" spans="1:16">
       <c r="A407" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B407" t="s">
         <v>56</v>
@@ -23699,19 +23699,19 @@
         <v>981</v>
       </c>
       <c r="D407" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E407" t="s">
         <v>80</v>
       </c>
       <c r="F407" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G407" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H407" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="J407" t="s">
         <v>63</v>
@@ -23731,7 +23731,7 @@
     </row>
     <row r="408" spans="1:16">
       <c r="A408" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B408" t="s">
         <v>118</v>
@@ -23740,19 +23740,19 @@
         <v>981</v>
       </c>
       <c r="D408" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E408" t="s">
         <v>80</v>
       </c>
       <c r="F408" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G408" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H408" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="I408" t="s">
         <v>62</v>
@@ -23775,7 +23775,7 @@
     </row>
     <row r="409" spans="1:16">
       <c r="A409" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B409" t="s">
         <v>118</v>
@@ -23784,19 +23784,19 @@
         <v>981</v>
       </c>
       <c r="D409" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E409" t="s">
         <v>80</v>
       </c>
       <c r="F409" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G409" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H409" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="J409" t="s">
         <v>63</v>
@@ -23816,7 +23816,7 @@
     </row>
     <row r="410" spans="1:16">
       <c r="A410" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B410" t="s">
         <v>118</v>
@@ -23825,22 +23825,22 @@
         <v>981</v>
       </c>
       <c r="D410" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E410" t="s">
         <v>80</v>
       </c>
       <c r="F410" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G410" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H410" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I410" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="J410" t="s">
         <v>94</v>
@@ -23860,7 +23860,7 @@
     </row>
     <row r="411" spans="1:16">
       <c r="A411" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B411" t="s">
         <v>56</v>
@@ -23875,13 +23875,13 @@
         <v>80</v>
       </c>
       <c r="F411" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G411" t="s">
         <v>832</v>
       </c>
       <c r="H411" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="I411" t="s">
         <v>792</v>
@@ -23904,7 +23904,7 @@
     </row>
     <row r="412" spans="1:16">
       <c r="A412" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B412" t="s">
         <v>56</v>
@@ -23922,10 +23922,10 @@
         <v>983</v>
       </c>
       <c r="G412" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H412" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I412" t="s">
         <v>62</v>
@@ -23948,7 +23948,7 @@
     </row>
     <row r="413" spans="1:16">
       <c r="A413" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B413" t="s">
         <v>118</v>
@@ -23963,13 +23963,13 @@
         <v>80</v>
       </c>
       <c r="F413" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G413" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H413" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J413" t="s">
         <v>63</v>
@@ -23989,7 +23989,7 @@
     </row>
     <row r="414" spans="1:16">
       <c r="A414" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B414" t="s">
         <v>118</v>
@@ -24004,13 +24004,13 @@
         <v>80</v>
       </c>
       <c r="F414" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G414" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H414" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J414" t="s">
         <v>83</v>
@@ -24027,7 +24027,7 @@
     </row>
     <row r="415" spans="1:16">
       <c r="A415" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B415" t="s">
         <v>56</v>
@@ -24042,13 +24042,13 @@
         <v>80</v>
       </c>
       <c r="F415" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="G415" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H415" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="I415" t="s">
         <v>62</v>
@@ -24071,7 +24071,7 @@
     </row>
     <row r="416" spans="1:16">
       <c r="A416" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B416" t="s">
         <v>118</v>
@@ -24086,13 +24086,13 @@
         <v>80</v>
       </c>
       <c r="F416" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G416" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H416" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J416" t="s">
         <v>83</v>
@@ -24112,7 +24112,7 @@
     </row>
     <row r="417" spans="1:16">
       <c r="A417" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B417" t="s">
         <v>118</v>
@@ -24127,13 +24127,13 @@
         <v>80</v>
       </c>
       <c r="F417" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G417" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H417" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J417" t="s">
         <v>129</v>
@@ -24153,7 +24153,7 @@
     </row>
     <row r="418" spans="1:16">
       <c r="A418" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B418" t="s">
         <v>56</v>
@@ -24168,13 +24168,13 @@
         <v>80</v>
       </c>
       <c r="F418" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G418" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H418" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="J418" t="s">
         <v>83</v>
@@ -24194,7 +24194,7 @@
     </row>
     <row r="419" spans="1:16">
       <c r="A419" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B419" t="s">
         <v>56</v>
@@ -24209,13 +24209,13 @@
         <v>80</v>
       </c>
       <c r="F419" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G419" t="s">
         <v>160</v>
       </c>
       <c r="H419" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I419" t="s">
         <v>792</v>
@@ -24235,7 +24235,7 @@
     </row>
     <row r="420" spans="1:16">
       <c r="A420" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B420" t="s">
         <v>56</v>
@@ -24250,13 +24250,13 @@
         <v>80</v>
       </c>
       <c r="F420" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G420" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H420" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="J420" t="s">
         <v>124</v>
@@ -24276,7 +24276,7 @@
     </row>
     <row r="421" spans="1:16">
       <c r="A421" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B421" t="s">
         <v>56</v>
@@ -24291,13 +24291,13 @@
         <v>80</v>
       </c>
       <c r="F421" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G421" t="s">
         <v>160</v>
       </c>
       <c r="H421" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="I421" t="s">
         <v>792</v>
@@ -24317,7 +24317,7 @@
     </row>
     <row r="422" spans="1:16">
       <c r="A422" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B422" t="s">
         <v>56</v>
@@ -24332,10 +24332,10 @@
         <v>80</v>
       </c>
       <c r="F422" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G422" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H422" t="s">
         <v>1009</v>
@@ -24361,7 +24361,7 @@
     </row>
     <row r="423" spans="1:16">
       <c r="A423" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B423" t="s">
         <v>118</v>
@@ -24376,13 +24376,13 @@
         <v>80</v>
       </c>
       <c r="F423" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G423" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H423" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="J423" t="s">
         <v>94</v>
@@ -24417,13 +24417,13 @@
         <v>58</v>
       </c>
       <c r="F424" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G424" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H424" t="s">
         <v>1179</v>
-      </c>
-      <c r="H424" t="s">
-        <v>1178</v>
       </c>
       <c r="J424" t="s">
         <v>94</v>
@@ -24443,7 +24443,7 @@
     </row>
     <row r="425" spans="1:16">
       <c r="A425" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B425" t="s">
         <v>56</v>
@@ -24458,10 +24458,10 @@
         <v>80</v>
       </c>
       <c r="F425" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G425" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H425" t="s">
         <v>1009</v>
@@ -24487,7 +24487,7 @@
     </row>
     <row r="426" spans="1:16">
       <c r="A426" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B426" t="s">
         <v>118</v>
@@ -24502,13 +24502,13 @@
         <v>80</v>
       </c>
       <c r="F426" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G426" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H426" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="I426" t="s">
         <v>62</v>
@@ -24531,7 +24531,7 @@
     </row>
     <row r="427" spans="1:16">
       <c r="A427" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B427" t="s">
         <v>56</v>
@@ -24546,10 +24546,10 @@
         <v>80</v>
       </c>
       <c r="F427" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G427" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H427" t="s">
         <v>1009</v>
@@ -24575,7 +24575,7 @@
     </row>
     <row r="428" spans="1:16">
       <c r="A428" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B428" t="s">
         <v>118</v>
@@ -24590,13 +24590,13 @@
         <v>80</v>
       </c>
       <c r="F428" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G428" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H428" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="J428" t="s">
         <v>83</v>
@@ -24613,7 +24613,7 @@
     </row>
     <row r="429" spans="1:16">
       <c r="A429" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B429" t="s">
         <v>56</v>
@@ -24631,7 +24631,7 @@
         <v>59</v>
       </c>
       <c r="G429" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H429" t="s">
         <v>1009</v>
@@ -24657,7 +24657,7 @@
     </row>
     <row r="430" spans="1:16">
       <c r="A430" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B430" t="s">
         <v>118</v>
@@ -24672,10 +24672,10 @@
         <v>80</v>
       </c>
       <c r="F430" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H430" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="J430" t="s">
         <v>63</v>
@@ -24692,7 +24692,7 @@
     </row>
     <row r="431" spans="1:16">
       <c r="A431" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B431" t="s">
         <v>56</v>
@@ -24707,7 +24707,7 @@
         <v>80</v>
       </c>
       <c r="F431" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H431" t="s">
         <v>985</v>
@@ -24730,7 +24730,7 @@
     </row>
     <row r="432" spans="1:16">
       <c r="A432" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B432" t="s">
         <v>118</v>
@@ -24748,13 +24748,13 @@
         <v>59</v>
       </c>
       <c r="G432" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H432" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="J432" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="K432">
         <v>75</v>
@@ -24768,7 +24768,7 @@
     </row>
     <row r="433" spans="1:18">
       <c r="A433" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B433" t="s">
         <v>56</v>
@@ -24783,13 +24783,13 @@
         <v>80</v>
       </c>
       <c r="F433" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G433" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H433" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J433" t="s">
         <v>94</v>
@@ -24821,13 +24821,13 @@
         <v>80</v>
       </c>
       <c r="F434" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G434" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H434" t="s">
         <v>1204</v>
-      </c>
-      <c r="H434" t="s">
-        <v>1203</v>
       </c>
       <c r="J434" t="s">
         <v>63</v>
@@ -24847,7 +24847,7 @@
     </row>
     <row r="435" spans="1:18">
       <c r="A435" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B435" t="s">
         <v>56</v>
@@ -24862,13 +24862,13 @@
         <v>80</v>
       </c>
       <c r="F435" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G435" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H435" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J435" t="s">
         <v>83</v>
@@ -24888,7 +24888,7 @@
     </row>
     <row r="436" spans="1:18">
       <c r="A436" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B436" t="s">
         <v>56</v>
@@ -24903,16 +24903,16 @@
         <v>80</v>
       </c>
       <c r="F436" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G436" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H436" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="I436" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="J436" t="s">
         <v>63</v>
@@ -24932,7 +24932,7 @@
     </row>
     <row r="437" spans="1:18">
       <c r="A437" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B437" t="s">
         <v>118</v>
@@ -24947,13 +24947,13 @@
         <v>80</v>
       </c>
       <c r="F437" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G437" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H437" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="J437" t="s">
         <v>94</v>
@@ -24970,7 +24970,7 @@
     </row>
     <row r="438" spans="1:18">
       <c r="A438" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B438" t="s">
         <v>118</v>
@@ -24985,13 +24985,13 @@
         <v>80</v>
       </c>
       <c r="F438" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G438" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H438" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="J438" t="s">
         <v>94</v>
@@ -25011,7 +25011,7 @@
     </row>
     <row r="439" spans="1:18">
       <c r="A439" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B439" t="s">
         <v>56</v>
@@ -25026,13 +25026,13 @@
         <v>80</v>
       </c>
       <c r="F439" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G439" t="s">
         <v>160</v>
       </c>
       <c r="H439" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J439" t="s">
         <v>63</v>
@@ -25049,7 +25049,7 @@
     </row>
     <row r="440" spans="1:18">
       <c r="A440" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B440" t="s">
         <v>56</v>
@@ -25090,7 +25090,7 @@
     </row>
     <row r="441" spans="1:18">
       <c r="A441" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -25131,7 +25131,7 @@
     </row>
     <row r="442" spans="1:18">
       <c r="A442" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B442" t="s">
         <v>56</v>
@@ -25149,7 +25149,7 @@
         <v>983</v>
       </c>
       <c r="G442" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H442" t="s">
         <v>286</v>
@@ -25172,7 +25172,7 @@
     </row>
     <row r="443" spans="1:18">
       <c r="A443" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B443" t="s">
         <v>118</v>
@@ -25190,10 +25190,10 @@
         <v>983</v>
       </c>
       <c r="G443" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H443" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="J443" t="s">
         <v>335</v>
@@ -25213,7 +25213,7 @@
     </row>
     <row r="444" spans="1:18">
       <c r="A444" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B444" t="s">
         <v>56</v>
@@ -25231,7 +25231,7 @@
         <v>983</v>
       </c>
       <c r="G444" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H444" t="s">
         <v>985</v>
@@ -25254,7 +25254,7 @@
     </row>
     <row r="445" spans="1:18">
       <c r="A445" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B445" t="s">
         <v>56</v>
@@ -25272,7 +25272,7 @@
         <v>983</v>
       </c>
       <c r="G445" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H445" t="s">
         <v>988</v>
@@ -25295,28 +25295,28 @@
     </row>
     <row r="446" spans="1:18">
       <c r="A446" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B446" t="s">
         <v>56</v>
       </c>
       <c r="C446" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D446" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E446" t="s">
         <v>58</v>
       </c>
       <c r="F446" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G446" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H446" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J446" t="s">
         <v>335</v>
@@ -25336,28 +25336,28 @@
     </row>
     <row r="447" spans="1:18">
       <c r="A447" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B447" t="s">
         <v>56</v>
       </c>
       <c r="C447" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D447" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E447" t="s">
         <v>58</v>
       </c>
       <c r="F447" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G447" t="s">
         <v>109</v>
       </c>
       <c r="H447" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="J447" t="s">
         <v>335</v>
@@ -25380,28 +25380,28 @@
     </row>
     <row r="448" spans="1:18">
       <c r="A448" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B448" t="s">
         <v>56</v>
       </c>
       <c r="C448" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D448" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E448" t="s">
         <v>936</v>
       </c>
       <c r="F448" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G448" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H448" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J448" t="s">
         <v>94</v>
@@ -25421,28 +25421,28 @@
     </row>
     <row r="449" spans="1:16">
       <c r="A449" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B449" t="s">
         <v>56</v>
       </c>
       <c r="C449" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D449" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E449" t="s">
         <v>80</v>
       </c>
       <c r="F449" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="G449" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H449" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="J449" t="s">
         <v>83</v>
@@ -25462,28 +25462,28 @@
     </row>
     <row r="450" spans="1:16">
       <c r="A450" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B450" t="s">
         <v>56</v>
       </c>
       <c r="C450" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D450" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E450" t="s">
         <v>80</v>
       </c>
       <c r="F450" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G450" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H450" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="J450" t="s">
         <v>94</v>
@@ -25503,28 +25503,28 @@
     </row>
     <row r="451" spans="1:16">
       <c r="A451" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B451" t="s">
         <v>56</v>
       </c>
       <c r="C451" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D451" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E451" t="s">
         <v>80</v>
       </c>
       <c r="F451" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G451" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H451" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J451" t="s">
         <v>83</v>
@@ -25544,25 +25544,25 @@
     </row>
     <row r="452" spans="1:16">
       <c r="A452" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B452" t="s">
         <v>56</v>
       </c>
       <c r="C452" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D452" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E452" t="s">
         <v>80</v>
       </c>
       <c r="F452" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H452" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="J452" t="s">
         <v>94</v>
@@ -25582,28 +25582,28 @@
     </row>
     <row r="453" spans="1:16">
       <c r="A453" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B453" t="s">
         <v>56</v>
       </c>
       <c r="C453" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D453" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E453" t="s">
         <v>80</v>
       </c>
       <c r="F453" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="G453" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H453" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="I453" t="s">
         <v>62</v>
@@ -25626,28 +25626,28 @@
     </row>
     <row r="454" spans="1:16">
       <c r="A454" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B454" t="s">
         <v>56</v>
       </c>
       <c r="C454" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D454" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E454" t="s">
         <v>80</v>
       </c>
       <c r="F454" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G454" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H454" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="J454" t="s">
         <v>63</v>
@@ -25664,28 +25664,28 @@
     </row>
     <row r="455" spans="1:16">
       <c r="A455" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B455" t="s">
         <v>56</v>
       </c>
       <c r="C455" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D455" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E455" t="s">
         <v>80</v>
       </c>
       <c r="F455" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G455" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H455" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="J455" t="s">
         <v>83</v>
@@ -25705,28 +25705,28 @@
     </row>
     <row r="456" spans="1:16">
       <c r="A456" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B456" t="s">
         <v>118</v>
       </c>
       <c r="C456" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D456" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E456" t="s">
         <v>80</v>
       </c>
       <c r="F456" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G456" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H456" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J456" t="s">
         <v>105</v>
@@ -25746,31 +25746,31 @@
     </row>
     <row r="457" spans="1:16">
       <c r="A457" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B457" t="s">
         <v>118</v>
       </c>
       <c r="C457" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D457" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E457" t="s">
         <v>80</v>
       </c>
       <c r="F457" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G457" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H457" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J457" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="K457">
         <v>75</v>
@@ -25787,28 +25787,28 @@
     </row>
     <row r="458" spans="1:16">
       <c r="A458" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B458" t="s">
         <v>118</v>
       </c>
       <c r="C458" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D458" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E458" t="s">
         <v>80</v>
       </c>
       <c r="F458" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G458" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H458" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J458" t="s">
         <v>63</v>
@@ -25828,28 +25828,28 @@
     </row>
     <row r="459" spans="1:16">
       <c r="A459" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B459" t="s">
         <v>56</v>
       </c>
       <c r="C459" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D459" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E459" t="s">
         <v>58</v>
       </c>
       <c r="F459" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="G459" t="s">
         <v>740</v>
       </c>
       <c r="H459" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="J459" t="s">
         <v>94</v>
@@ -25869,28 +25869,28 @@
     </row>
     <row r="460" spans="1:16">
       <c r="A460" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B460" t="s">
         <v>56</v>
       </c>
       <c r="C460" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D460" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E460" t="s">
         <v>80</v>
       </c>
       <c r="F460" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G460" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H460" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J460" t="s">
         <v>105</v>
@@ -25910,28 +25910,28 @@
     </row>
     <row r="461" spans="1:16">
       <c r="A461" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B461" t="s">
         <v>56</v>
       </c>
       <c r="C461" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D461" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E461" t="s">
         <v>80</v>
       </c>
       <c r="F461" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G461" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H461" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J461" t="s">
         <v>105</v>
@@ -25951,28 +25951,28 @@
     </row>
     <row r="462" spans="1:16">
       <c r="A462" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B462" t="s">
         <v>56</v>
       </c>
       <c r="C462" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D462" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E462" t="s">
         <v>80</v>
       </c>
       <c r="F462" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G462" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H462" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J462" t="s">
         <v>105</v>
@@ -25992,28 +25992,28 @@
     </row>
     <row r="463" spans="1:16">
       <c r="A463" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B463" t="s">
         <v>56</v>
       </c>
       <c r="C463" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D463" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E463" t="s">
         <v>80</v>
       </c>
       <c r="F463" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G463" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H463" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J463" t="s">
         <v>129</v>
@@ -26033,28 +26033,28 @@
     </row>
     <row r="464" spans="1:16">
       <c r="A464" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B464" t="s">
         <v>56</v>
       </c>
       <c r="C464" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D464" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E464" t="s">
         <v>80</v>
       </c>
       <c r="F464" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G464" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H464" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J464" t="s">
         <v>129</v>
@@ -26074,28 +26074,28 @@
     </row>
     <row r="465" spans="1:16">
       <c r="A465" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B465" t="s">
         <v>56</v>
       </c>
       <c r="C465" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D465" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E465" t="s">
         <v>80</v>
       </c>
       <c r="F465" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G465" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H465" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J465" t="s">
         <v>124</v>
@@ -26115,28 +26115,28 @@
     </row>
     <row r="466" spans="1:16">
       <c r="A466" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B466" t="s">
         <v>56</v>
       </c>
       <c r="C466" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D466" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E466" t="s">
         <v>80</v>
       </c>
       <c r="F466" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G466" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H466" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J466" t="s">
         <v>105</v>
@@ -26156,28 +26156,28 @@
     </row>
     <row r="467" spans="1:16">
       <c r="A467" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B467" t="s">
         <v>56</v>
       </c>
       <c r="C467" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D467" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E467" t="s">
         <v>80</v>
       </c>
       <c r="F467" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G467" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H467" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J467" t="s">
         <v>105</v>
@@ -26197,28 +26197,28 @@
     </row>
     <row r="468" spans="1:16">
       <c r="A468" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B468" t="s">
         <v>56</v>
       </c>
       <c r="C468" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D468" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E468" t="s">
         <v>80</v>
       </c>
       <c r="F468" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G468" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H468" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J468" t="s">
         <v>105</v>
@@ -26238,28 +26238,28 @@
     </row>
     <row r="469" spans="1:16">
       <c r="A469" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B469" t="s">
         <v>56</v>
       </c>
       <c r="C469" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D469" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E469" t="s">
         <v>58</v>
       </c>
       <c r="F469" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G469" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H469" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J469" t="s">
         <v>83</v>
@@ -26279,28 +26279,28 @@
     </row>
     <row r="470" spans="1:16">
       <c r="A470" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B470" t="s">
         <v>56</v>
       </c>
       <c r="C470" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D470" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E470" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F470" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="G470" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H470" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J470" t="s">
         <v>586</v>
@@ -26320,22 +26320,22 @@
     </row>
     <row r="471" spans="1:16">
       <c r="A471" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B471" t="s">
         <v>56</v>
       </c>
       <c r="C471" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E471" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F471" t="s">
         <v>59</v>
       </c>
       <c r="G471" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H471" t="s">
         <v>1004</v>
@@ -26355,25 +26355,25 @@
     </row>
     <row r="472" spans="1:16">
       <c r="A472" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B472" t="s">
         <v>56</v>
       </c>
       <c r="C472" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E472" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F472" t="s">
         <v>59</v>
       </c>
       <c r="G472" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H472" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="J472" t="s">
         <v>586</v>
@@ -26390,25 +26390,25 @@
     </row>
     <row r="473" spans="1:16">
       <c r="A473" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B473" t="s">
         <v>56</v>
       </c>
       <c r="C473" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E473" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F473" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G473" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H473" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J473" t="s">
         <v>586</v>
@@ -26428,25 +26428,25 @@
     </row>
     <row r="474" spans="1:16">
       <c r="A474" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B474" t="s">
         <v>56</v>
       </c>
       <c r="C474" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E474" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F474" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G474" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H474" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="J474" t="s">
         <v>586</v>
@@ -26466,25 +26466,25 @@
     </row>
     <row r="475" spans="1:16">
       <c r="A475" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B475" t="s">
         <v>56</v>
       </c>
       <c r="C475" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E475" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F475" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G475" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H475" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="J475" t="s">
         <v>586</v>
@@ -26504,25 +26504,25 @@
     </row>
     <row r="476" spans="1:16">
       <c r="A476" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B476" t="s">
         <v>118</v>
       </c>
       <c r="C476" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E476" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F476" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G476" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H476" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="J476" t="s">
         <v>586</v>
@@ -26539,25 +26539,25 @@
     </row>
     <row r="477" spans="1:16">
       <c r="A477" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B477" t="s">
         <v>56</v>
       </c>
       <c r="C477" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E477" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F477" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G477" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H477" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="J477" t="s">
         <v>586</v>
@@ -26577,25 +26577,25 @@
     </row>
     <row r="478" spans="1:16">
       <c r="A478" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B478" t="s">
         <v>56</v>
       </c>
       <c r="C478" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E478" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F478" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G478" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H478" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="J478" t="s">
         <v>586</v>
@@ -26615,25 +26615,25 @@
     </row>
     <row r="479" spans="1:16">
       <c r="A479" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B479" t="s">
         <v>56</v>
       </c>
       <c r="C479" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E479" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F479" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G479" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H479" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J479" t="s">
         <v>586</v>
@@ -26653,25 +26653,25 @@
     </row>
     <row r="480" spans="1:16">
       <c r="A480" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B480" t="s">
         <v>56</v>
       </c>
       <c r="C480" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E480" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F480" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G480" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H480" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J480" t="s">
         <v>586</v>
@@ -26691,25 +26691,25 @@
     </row>
     <row r="481" spans="1:16">
       <c r="A481" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B481" t="s">
         <v>56</v>
       </c>
       <c r="C481" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E481" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F481" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G481" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H481" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="J481" t="s">
         <v>586</v>
@@ -26729,25 +26729,25 @@
     </row>
     <row r="482" spans="1:16">
       <c r="A482" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B482" t="s">
         <v>56</v>
       </c>
       <c r="C482" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E482" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F482" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G482" t="s">
         <v>931</v>
       </c>
       <c r="H482" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J482" t="s">
         <v>586</v>
@@ -26767,25 +26767,25 @@
     </row>
     <row r="483" spans="1:16">
       <c r="A483" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B483" t="s">
         <v>56</v>
       </c>
       <c r="C483" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E483" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F483" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G483" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H483" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J483" t="s">
         <v>586</v>
@@ -26805,25 +26805,25 @@
     </row>
     <row r="484" spans="1:16">
       <c r="A484" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B484" t="s">
         <v>56</v>
       </c>
       <c r="C484" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E484" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F484" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G484" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H484" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="J484" t="s">
         <v>586</v>
@@ -26843,25 +26843,25 @@
     </row>
     <row r="485" spans="1:16">
       <c r="A485" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B485" t="s">
         <v>56</v>
       </c>
       <c r="C485" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E485" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F485" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G485" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H485" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="J485" t="s">
         <v>586</v>
@@ -26881,25 +26881,25 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B486" t="s">
         <v>56</v>
       </c>
       <c r="C486" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E486" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F486" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G486" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H486" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="J486" t="s">
         <v>586</v>
@@ -26919,25 +26919,25 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B487" t="s">
         <v>56</v>
       </c>
       <c r="C487" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E487" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F487" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G487" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H487" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="J487" t="s">
         <v>586</v>
@@ -26957,25 +26957,25 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B488" t="s">
         <v>118</v>
       </c>
       <c r="C488" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E488" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F488" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G488" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H488" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J488" t="s">
         <v>586</v>
@@ -26995,25 +26995,25 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B489" t="s">
         <v>56</v>
       </c>
       <c r="C489" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E489" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F489" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G489" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H489" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J489" t="s">
         <v>586</v>
@@ -27033,25 +27033,25 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B490" t="s">
         <v>56</v>
       </c>
       <c r="C490" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E490" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F490" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G490" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H490" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J490" t="s">
         <v>586</v>
@@ -27071,25 +27071,25 @@
     </row>
     <row r="491" spans="1:16">
       <c r="A491" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B491" t="s">
         <v>56</v>
       </c>
       <c r="C491" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E491" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F491" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G491" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H491" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="J491" t="s">
         <v>586</v>
@@ -27109,25 +27109,25 @@
     </row>
     <row r="492" spans="1:16">
       <c r="A492" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B492" t="s">
         <v>56</v>
       </c>
       <c r="C492" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E492" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F492" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G492" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H492" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="J492" t="s">
         <v>586</v>
@@ -27147,25 +27147,25 @@
     </row>
     <row r="493" spans="1:16">
       <c r="A493" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B493" t="s">
         <v>56</v>
       </c>
       <c r="C493" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E493" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F493" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G493" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H493" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J493" t="s">
         <v>162</v>
@@ -27185,28 +27185,28 @@
     </row>
     <row r="494" spans="1:16">
       <c r="A494" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B494" t="s">
         <v>56</v>
       </c>
       <c r="C494" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E494" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F494" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G494" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H494" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="J494" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="K494">
         <v>75</v>
@@ -27223,28 +27223,28 @@
     </row>
     <row r="495" spans="1:16">
       <c r="A495" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B495" t="s">
         <v>56</v>
       </c>
       <c r="C495" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D495" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E495" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F495" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G495" t="s">
         <v>1365</v>
       </c>
       <c r="H495" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J495" t="s">
         <v>586</v>
@@ -27270,22 +27270,22 @@
         <v>56</v>
       </c>
       <c r="C496" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D496" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E496" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F496" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G496" t="s">
         <v>1367</v>
       </c>
       <c r="H496" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="J496" t="s">
         <v>586</v>
@@ -27311,22 +27311,22 @@
         <v>118</v>
       </c>
       <c r="C497" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D497" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E497" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F497" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G497" t="s">
         <v>1369</v>
       </c>
       <c r="H497" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J497" t="s">
         <v>586</v>
@@ -27352,22 +27352,22 @@
         <v>118</v>
       </c>
       <c r="C498" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D498" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E498" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F498" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G498" t="s">
         <v>1371</v>
       </c>
       <c r="H498" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J498" t="s">
         <v>586</v>
@@ -27393,22 +27393,22 @@
         <v>118</v>
       </c>
       <c r="C499" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D499" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E499" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F499" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G499" t="s">
         <v>1373</v>
       </c>
       <c r="H499" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="J499" t="s">
         <v>586</v>
@@ -27653,7 +27653,7 @@
         <v>1375</v>
       </c>
       <c r="D506" t="s">
-        <v>1364</v>
+        <v>1011</v>
       </c>
       <c r="E506" t="s">
         <v>1375</v>
@@ -27960,7 +27960,7 @@
         <v>59</v>
       </c>
       <c r="G514" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H514" t="s">
         <v>1424</v>
@@ -28004,7 +28004,7 @@
         <v>1426</v>
       </c>
       <c r="H515" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="I515" t="s">
         <v>792</v>
@@ -42605,7 +42605,7 @@
         <v>58</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D361" s="5" t="s">
         <v>1009</v>
@@ -42649,7 +42649,7 @@
         <v>58</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D362" s="5" t="s">
         <v>995</v>
@@ -42661,13 +42661,13 @@
         <v>1988</v>
       </c>
       <c r="G362" s="5" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H362" s="5" t="s">
         <v>1988</v>
       </c>
       <c r="I362" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J362" s="5" t="s">
         <v>1473</v>
@@ -42693,10 +42693,10 @@
         <v>58</v>
       </c>
       <c r="C363" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D363" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E363" t="s">
         <v>83</v>
@@ -42705,13 +42705,13 @@
         <v>1994</v>
       </c>
       <c r="G363" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H363" t="s">
         <v>1994</v>
       </c>
       <c r="I363" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J363" t="s">
         <v>1473</v>
@@ -42734,10 +42734,10 @@
         <v>58</v>
       </c>
       <c r="C364" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D364" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E364" t="s">
         <v>63</v>
@@ -42746,7 +42746,7 @@
         <v>1995</v>
       </c>
       <c r="G364" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H364" t="s">
         <v>1995</v>
@@ -42775,7 +42775,7 @@
         <v>58</v>
       </c>
       <c r="C365" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D365" t="s">
         <v>995</v>
@@ -42787,13 +42787,13 @@
         <v>1996</v>
       </c>
       <c r="G365" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H365" t="s">
         <v>1996</v>
       </c>
       <c r="I365" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="J365" t="s">
         <v>1473</v>
@@ -42816,7 +42816,7 @@
         <v>58</v>
       </c>
       <c r="C366" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D366" t="s">
         <v>995</v>
@@ -42828,13 +42828,13 @@
         <v>1997</v>
       </c>
       <c r="G366" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H366" t="s">
         <v>1997</v>
       </c>
       <c r="I366" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J366" t="s">
         <v>1473</v>
@@ -42857,7 +42857,7 @@
         <v>58</v>
       </c>
       <c r="C367" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D367" t="s">
         <v>615</v>
@@ -42869,13 +42869,13 @@
         <v>1998</v>
       </c>
       <c r="G367" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H367" t="s">
         <v>1998</v>
       </c>
       <c r="I367" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J367" t="s">
         <v>1473</v>
@@ -42901,13 +42901,13 @@
         <v>160</v>
       </c>
       <c r="D368" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E368" t="s">
         <v>94</v>
       </c>
       <c r="G368" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H368" t="s">
         <v>1999</v>
@@ -42936,10 +42936,10 @@
         <v>58</v>
       </c>
       <c r="C369" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D369" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E369" t="s">
         <v>94</v>
@@ -42948,13 +42948,13 @@
         <v>2001</v>
       </c>
       <c r="G369" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H369" t="s">
         <v>2001</v>
       </c>
       <c r="I369" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J369" t="s">
         <v>1473</v>
@@ -42977,10 +42977,10 @@
         <v>58</v>
       </c>
       <c r="C370" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D370" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E370" t="s">
         <v>94</v>
@@ -42989,13 +42989,13 @@
         <v>2002</v>
       </c>
       <c r="G370" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H370" t="s">
         <v>2002</v>
       </c>
       <c r="I370" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J370" t="s">
         <v>1473</v>
@@ -43018,10 +43018,10 @@
         <v>58</v>
       </c>
       <c r="C371" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D371" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E371" t="s">
         <v>335</v>
@@ -43030,7 +43030,7 @@
         <v>2003</v>
       </c>
       <c r="G371" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H371" t="s">
         <v>2003</v>
@@ -43059,10 +43059,10 @@
         <v>58</v>
       </c>
       <c r="C372" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D372" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E372" t="s">
         <v>83</v>
@@ -43071,7 +43071,7 @@
         <v>2005</v>
       </c>
       <c r="G372" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H372" t="s">
         <v>2005</v>
@@ -43100,10 +43100,10 @@
         <v>58</v>
       </c>
       <c r="C373" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D373" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E373" t="s">
         <v>335</v>
@@ -43112,13 +43112,13 @@
         <v>2007</v>
       </c>
       <c r="G373" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H373" t="s">
         <v>2007</v>
       </c>
       <c r="I373" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="J373" t="s">
         <v>1473</v>
@@ -43141,10 +43141,10 @@
         <v>58</v>
       </c>
       <c r="C374" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D374" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E374" t="s">
         <v>63</v>
@@ -43153,13 +43153,13 @@
         <v>2008</v>
       </c>
       <c r="G374" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H374" t="s">
         <v>2008</v>
       </c>
       <c r="I374" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J374" t="s">
         <v>1473</v>
@@ -43182,10 +43182,10 @@
         <v>58</v>
       </c>
       <c r="C375" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D375" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E375" t="s">
         <v>94</v>
@@ -43194,13 +43194,13 @@
         <v>2009</v>
       </c>
       <c r="G375" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H375" t="s">
         <v>2009</v>
       </c>
       <c r="I375" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J375" t="s">
         <v>1473</v>
@@ -43223,10 +43223,10 @@
         <v>58</v>
       </c>
       <c r="C376" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D376" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E376" t="s">
         <v>94</v>
@@ -43235,7 +43235,7 @@
         <v>2010</v>
       </c>
       <c r="G376" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H376" t="s">
         <v>2010</v>
@@ -43264,10 +43264,10 @@
         <v>58</v>
       </c>
       <c r="C377" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D377" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E377" t="s">
         <v>129</v>
@@ -43276,13 +43276,13 @@
         <v>2012</v>
       </c>
       <c r="G377" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H377" t="s">
         <v>2012</v>
       </c>
       <c r="I377" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="J377" t="s">
         <v>1473</v>
@@ -43305,10 +43305,10 @@
         <v>58</v>
       </c>
       <c r="C378" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D378" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E378" t="s">
         <v>102</v>
@@ -43317,13 +43317,13 @@
         <v>2013</v>
       </c>
       <c r="G378" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H378" t="s">
         <v>2013</v>
       </c>
       <c r="I378" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="J378" t="s">
         <v>1473</v>
@@ -43346,10 +43346,10 @@
         <v>58</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E379" s="5" t="s">
         <v>335</v>
@@ -43358,13 +43358,13 @@
         <v>2014</v>
       </c>
       <c r="G379" s="5" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H379" s="5" t="s">
         <v>2015</v>
       </c>
       <c r="I379" s="5" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J379" s="5" t="s">
         <v>1473</v>
@@ -43390,10 +43390,10 @@
         <v>58</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="E380" s="5" t="s">
         <v>335</v>
@@ -43402,7 +43402,7 @@
         <v>2014</v>
       </c>
       <c r="G380" s="5" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H380" s="5" t="s">
         <v>2016</v>
@@ -43434,10 +43434,10 @@
         <v>58</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E381" s="5" t="s">
         <v>94</v>
@@ -43446,13 +43446,13 @@
         <v>2014</v>
       </c>
       <c r="G381" s="5" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H381" s="5" t="s">
         <v>2014</v>
       </c>
       <c r="I381" s="5" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J381" s="5" t="s">
         <v>1473</v>
@@ -43478,10 +43478,10 @@
         <v>58</v>
       </c>
       <c r="C382" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D382" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E382" t="s">
         <v>94</v>
@@ -43490,7 +43490,7 @@
         <v>2018</v>
       </c>
       <c r="G382" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H382" t="s">
         <v>2018</v>
@@ -43519,10 +43519,10 @@
         <v>58</v>
       </c>
       <c r="C383" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D383" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E383" t="s">
         <v>94</v>
@@ -43531,7 +43531,7 @@
         <v>2020</v>
       </c>
       <c r="G383" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H383" t="s">
         <v>2020</v>
@@ -43560,10 +43560,10 @@
         <v>58</v>
       </c>
       <c r="C384" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D384" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E384" t="s">
         <v>94</v>
@@ -43572,7 +43572,7 @@
         <v>2022</v>
       </c>
       <c r="G384" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H384" t="s">
         <v>2022</v>
@@ -43601,16 +43601,16 @@
         <v>58</v>
       </c>
       <c r="C385" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D385" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E385" t="s">
         <v>94</v>
       </c>
       <c r="G385" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H385" t="s">
         <v>2024</v>
@@ -43639,22 +43639,22 @@
         <v>58</v>
       </c>
       <c r="C386" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D386" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E386" t="s">
         <v>530</v>
       </c>
       <c r="G386" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H386" t="s">
         <v>2026</v>
       </c>
       <c r="I386" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J386" t="s">
         <v>1473</v>
@@ -43677,10 +43677,10 @@
         <v>58</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D387" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E387" s="6" t="s">
         <v>63</v>
@@ -43709,7 +43709,7 @@
         <v>58</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D388" s="5" t="s">
         <v>985</v>
@@ -43721,7 +43721,7 @@
         <v>2029</v>
       </c>
       <c r="G388" s="5" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H388" s="5" t="s">
         <v>2030</v>
@@ -43751,7 +43751,7 @@
         <v>58</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D389" s="5" t="s">
         <v>988</v>
@@ -43763,7 +43763,7 @@
         <v>2033</v>
       </c>
       <c r="G389" s="5" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H389" s="5" t="s">
         <v>2034</v>
@@ -43805,7 +43805,7 @@
         <v>1978</v>
       </c>
       <c r="G390" s="5" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H390" s="5" t="s">
         <v>2037</v>
@@ -43847,7 +43847,7 @@
         <v>2039</v>
       </c>
       <c r="G391" s="5" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H391" s="5" t="s">
         <v>2040</v>
@@ -43889,7 +43889,7 @@
         <v>2042</v>
       </c>
       <c r="G392" s="5" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H392" s="5" t="s">
         <v>1975</v>
@@ -43919,7 +43919,7 @@
         <v>80</v>
       </c>
       <c r="C393" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D393" t="s">
         <v>286</v>
@@ -43931,7 +43931,7 @@
         <v>2044</v>
       </c>
       <c r="G393" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H393" t="s">
         <v>2044</v>
@@ -43960,7 +43960,7 @@
         <v>80</v>
       </c>
       <c r="C394" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D394" t="s">
         <v>988</v>
@@ -43972,7 +43972,7 @@
         <v>2046</v>
       </c>
       <c r="G394" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H394" t="s">
         <v>2046</v>
@@ -44001,7 +44001,7 @@
         <v>80</v>
       </c>
       <c r="C395" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D395" t="s">
         <v>1004</v>
@@ -44013,7 +44013,7 @@
         <v>2048</v>
       </c>
       <c r="G395" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H395" t="s">
         <v>2048</v>
@@ -44042,7 +44042,7 @@
         <v>80</v>
       </c>
       <c r="C396" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D396" t="s">
         <v>995</v>
@@ -44054,7 +44054,7 @@
         <v>2050</v>
       </c>
       <c r="G396" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H396" t="s">
         <v>2050</v>
@@ -44083,7 +44083,7 @@
         <v>80</v>
       </c>
       <c r="C397" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D397" t="s">
         <v>1006</v>
@@ -44095,7 +44095,7 @@
         <v>2052</v>
       </c>
       <c r="G397" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H397" t="s">
         <v>2052</v>
@@ -44124,7 +44124,7 @@
         <v>80</v>
       </c>
       <c r="C398" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D398" t="s">
         <v>985</v>
@@ -44136,7 +44136,7 @@
         <v>2054</v>
       </c>
       <c r="G398" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H398" t="s">
         <v>2054</v>
@@ -44165,7 +44165,7 @@
         <v>80</v>
       </c>
       <c r="C399" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D399" t="s">
         <v>995</v>
@@ -44177,7 +44177,7 @@
         <v>2056</v>
       </c>
       <c r="G399" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H399" t="s">
         <v>2056</v>
@@ -44206,10 +44206,10 @@
         <v>80</v>
       </c>
       <c r="C400" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D400" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E400" t="s">
         <v>63</v>
@@ -44218,7 +44218,7 @@
         <v>2058</v>
       </c>
       <c r="G400" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H400" t="s">
         <v>2058</v>
@@ -44247,10 +44247,10 @@
         <v>80</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E401" s="5" t="s">
         <v>63</v>
@@ -44259,7 +44259,7 @@
         <v>2060</v>
       </c>
       <c r="G401" s="5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H401" s="5" t="s">
         <v>2061</v>
@@ -44289,10 +44289,10 @@
         <v>80</v>
       </c>
       <c r="C402" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D402" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E402" t="s">
         <v>83</v>
@@ -44301,7 +44301,7 @@
         <v>2063</v>
       </c>
       <c r="G402" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H402" t="s">
         <v>2063</v>
@@ -44333,7 +44333,7 @@
         <v>2065</v>
       </c>
       <c r="D403" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E403" t="s">
         <v>105</v>
@@ -44342,7 +44342,7 @@
         <v>2066</v>
       </c>
       <c r="G403" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H403" t="s">
         <v>2066</v>
@@ -44371,22 +44371,22 @@
         <v>80</v>
       </c>
       <c r="C404" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D404" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="E404" t="s">
         <v>63</v>
       </c>
       <c r="G404" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H404" t="s">
         <v>2068</v>
       </c>
       <c r="I404" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="J404" t="s">
         <v>1485</v>
@@ -44409,10 +44409,10 @@
         <v>80</v>
       </c>
       <c r="C405" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D405" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E405" t="s">
         <v>124</v>
@@ -44421,13 +44421,13 @@
         <v>2069</v>
       </c>
       <c r="G405" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H405" t="s">
         <v>2069</v>
       </c>
       <c r="I405" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J405" t="s">
         <v>1485</v>
@@ -44450,10 +44450,10 @@
         <v>80</v>
       </c>
       <c r="C406" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D406" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E406" t="s">
         <v>205</v>
@@ -44462,13 +44462,13 @@
         <v>2070</v>
       </c>
       <c r="G406" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H406" t="s">
         <v>2070</v>
       </c>
       <c r="I406" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="J406" t="s">
         <v>1485</v>
@@ -44491,10 +44491,10 @@
         <v>80</v>
       </c>
       <c r="C407" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D407" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E407" t="s">
         <v>94</v>
@@ -44503,7 +44503,7 @@
         <v>2071</v>
       </c>
       <c r="G407" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H407" t="s">
         <v>2071</v>
@@ -44532,10 +44532,10 @@
         <v>80</v>
       </c>
       <c r="C408" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D408" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E408" t="s">
         <v>63</v>
@@ -44544,7 +44544,7 @@
         <v>2073</v>
       </c>
       <c r="G408" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H408" t="s">
         <v>2073</v>
@@ -44573,10 +44573,10 @@
         <v>80</v>
       </c>
       <c r="C409" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D409" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E409" t="s">
         <v>63</v>
@@ -44585,13 +44585,13 @@
         <v>2075</v>
       </c>
       <c r="G409" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H409" t="s">
         <v>2075</v>
       </c>
       <c r="I409" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="J409" t="s">
         <v>1485</v>
@@ -44614,10 +44614,10 @@
         <v>80</v>
       </c>
       <c r="C410" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D410" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E410" t="s">
         <v>63</v>
@@ -44626,13 +44626,13 @@
         <v>2076</v>
       </c>
       <c r="G410" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H410" t="s">
         <v>2076</v>
       </c>
       <c r="I410" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J410" t="s">
         <v>1485</v>
@@ -44655,10 +44655,10 @@
         <v>80</v>
       </c>
       <c r="C411" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D411" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E411" t="s">
         <v>94</v>
@@ -44667,13 +44667,13 @@
         <v>2077</v>
       </c>
       <c r="G411" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H411" t="s">
         <v>2077</v>
       </c>
       <c r="I411" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J411" t="s">
         <v>1485</v>
@@ -44699,7 +44699,7 @@
         <v>832</v>
       </c>
       <c r="D412" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E412" t="s">
         <v>94</v>
@@ -44708,7 +44708,7 @@
         <v>2078</v>
       </c>
       <c r="G412" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H412" t="s">
         <v>2078</v>
@@ -44737,10 +44737,10 @@
         <v>80</v>
       </c>
       <c r="C413" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D413" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E413" t="s">
         <v>83</v>
@@ -44749,13 +44749,13 @@
         <v>2079</v>
       </c>
       <c r="G413" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H413" t="s">
         <v>2079</v>
       </c>
       <c r="I413" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="J413" t="s">
         <v>1485</v>
@@ -44778,10 +44778,10 @@
         <v>80</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E414" s="5" t="s">
         <v>63</v>
@@ -44790,13 +44790,13 @@
         <v>2075</v>
       </c>
       <c r="G414" s="5" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H414" s="5" t="s">
         <v>2080</v>
       </c>
       <c r="I414" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J414" s="5" t="s">
         <v>1485</v>
@@ -44820,22 +44820,22 @@
         <v>80</v>
       </c>
       <c r="C415" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D415" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E415" t="s">
         <v>83</v>
       </c>
       <c r="G415" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H415" t="s">
         <v>2081</v>
       </c>
       <c r="I415" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="J415" t="s">
         <v>1485</v>
@@ -44858,10 +44858,10 @@
         <v>80</v>
       </c>
       <c r="C416" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D416" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E416" t="s">
         <v>63</v>
@@ -44870,13 +44870,13 @@
         <v>2082</v>
       </c>
       <c r="G416" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H416" t="s">
         <v>2082</v>
       </c>
       <c r="I416" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J416" t="s">
         <v>1485</v>
@@ -44899,10 +44899,10 @@
         <v>80</v>
       </c>
       <c r="C417" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D417" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E417" t="s">
         <v>83</v>
@@ -44911,13 +44911,13 @@
         <v>2083</v>
       </c>
       <c r="G417" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H417" t="s">
         <v>2083</v>
       </c>
       <c r="I417" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="J417" t="s">
         <v>1485</v>
@@ -44940,10 +44940,10 @@
         <v>80</v>
       </c>
       <c r="C418" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D418" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E418" t="s">
         <v>129</v>
@@ -44952,13 +44952,13 @@
         <v>2084</v>
       </c>
       <c r="G418" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H418" t="s">
         <v>2084</v>
       </c>
       <c r="I418" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="J418" t="s">
         <v>1485</v>
@@ -44981,10 +44981,10 @@
         <v>80</v>
       </c>
       <c r="C419" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D419" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E419" t="s">
         <v>83</v>
@@ -44993,13 +44993,13 @@
         <v>2085</v>
       </c>
       <c r="G419" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H419" t="s">
         <v>2085</v>
       </c>
       <c r="I419" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J419" t="s">
         <v>1485</v>
@@ -45025,13 +45025,13 @@
         <v>160</v>
       </c>
       <c r="D420" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E420" t="s">
         <v>83</v>
       </c>
       <c r="G420" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H420" t="s">
         <v>2086</v>
@@ -45060,10 +45060,10 @@
         <v>80</v>
       </c>
       <c r="C421" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D421" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E421" t="s">
         <v>124</v>
@@ -45072,7 +45072,7 @@
         <v>2088</v>
       </c>
       <c r="G421" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H421" t="s">
         <v>2088</v>
@@ -45104,13 +45104,13 @@
         <v>160</v>
       </c>
       <c r="D422" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E422" t="s">
         <v>83</v>
       </c>
       <c r="G422" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H422" t="s">
         <v>2090</v>
@@ -45139,7 +45139,7 @@
         <v>80</v>
       </c>
       <c r="C423" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D423" t="s">
         <v>1009</v>
@@ -45151,7 +45151,7 @@
         <v>2092</v>
       </c>
       <c r="G423" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H423" t="s">
         <v>2092</v>
@@ -45180,22 +45180,22 @@
         <v>80</v>
       </c>
       <c r="C424" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D424" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E424" t="s">
         <v>94</v>
       </c>
       <c r="G424" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H424" t="s">
         <v>2094</v>
       </c>
       <c r="I424" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="J424" t="s">
         <v>1485</v>
@@ -45221,10 +45221,10 @@
         <v>80</v>
       </c>
       <c r="C425" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D425" s="6" t="s">
         <v>1179</v>
-      </c>
-      <c r="D425" s="6" t="s">
-        <v>1178</v>
       </c>
       <c r="E425" s="6" t="s">
         <v>94</v>
@@ -45251,7 +45251,7 @@
         <v>80</v>
       </c>
       <c r="C426" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D426" t="s">
         <v>1009</v>
@@ -45263,13 +45263,13 @@
         <v>2097</v>
       </c>
       <c r="G426" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H426" t="s">
         <v>2097</v>
       </c>
       <c r="I426" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J426" t="s">
         <v>1485</v>
@@ -45292,22 +45292,22 @@
         <v>80</v>
       </c>
       <c r="C427" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D427" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E427" t="s">
         <v>63</v>
       </c>
       <c r="G427" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H427" t="s">
         <v>2098</v>
       </c>
       <c r="I427" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J427" t="s">
         <v>1485</v>
@@ -45330,7 +45330,7 @@
         <v>80</v>
       </c>
       <c r="C428" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D428" t="s">
         <v>1009</v>
@@ -45342,13 +45342,13 @@
         <v>2099</v>
       </c>
       <c r="G428" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H428" t="s">
         <v>2099</v>
       </c>
       <c r="I428" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="J428" t="s">
         <v>1485</v>
@@ -45371,22 +45371,22 @@
         <v>80</v>
       </c>
       <c r="C429" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D429" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E429" t="s">
         <v>83</v>
       </c>
       <c r="G429" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H429" t="s">
         <v>2100</v>
       </c>
       <c r="I429" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J429" t="s">
         <v>1485</v>
@@ -45409,7 +45409,7 @@
         <v>80</v>
       </c>
       <c r="C430" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D430" t="s">
         <v>1009</v>
@@ -45421,13 +45421,13 @@
         <v>2101</v>
       </c>
       <c r="G430" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H430" t="s">
         <v>2101</v>
       </c>
       <c r="I430" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J430" t="s">
         <v>1485</v>
@@ -45450,13 +45450,13 @@
         <v>80</v>
       </c>
       <c r="D431" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E431" t="s">
         <v>63</v>
       </c>
       <c r="G431" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H431" t="s">
         <v>2102</v>
@@ -45494,7 +45494,7 @@
         <v>2104</v>
       </c>
       <c r="G432" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H432" t="s">
         <v>2104</v>
@@ -45523,22 +45523,22 @@
         <v>80</v>
       </c>
       <c r="C433" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D433" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E433" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G433" t="s">
         <v>1197</v>
-      </c>
-      <c r="D433" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E433" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G433" t="s">
-        <v>1196</v>
       </c>
       <c r="H433" t="s">
         <v>2105</v>
       </c>
       <c r="I433" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="J433" t="s">
         <v>1485</v>
@@ -45561,10 +45561,10 @@
         <v>80</v>
       </c>
       <c r="C434" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D434" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E434" t="s">
         <v>94</v>
@@ -45573,7 +45573,7 @@
         <v>2106</v>
       </c>
       <c r="G434" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H434" t="s">
         <v>2106</v>
@@ -45602,10 +45602,10 @@
         <v>80</v>
       </c>
       <c r="C435" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D435" s="6" t="s">
         <v>1204</v>
-      </c>
-      <c r="D435" s="6" t="s">
-        <v>1203</v>
       </c>
       <c r="E435" s="6" t="s">
         <v>63</v>
@@ -45634,10 +45634,10 @@
         <v>80</v>
       </c>
       <c r="C436" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D436" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E436" t="s">
         <v>83</v>
@@ -45646,13 +45646,13 @@
         <v>2109</v>
       </c>
       <c r="G436" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H436" t="s">
         <v>2109</v>
       </c>
       <c r="I436" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J436" t="s">
         <v>1485</v>
@@ -45675,10 +45675,10 @@
         <v>80</v>
       </c>
       <c r="C437" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D437" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E437" t="s">
         <v>63</v>
@@ -45687,13 +45687,13 @@
         <v>2110</v>
       </c>
       <c r="G437" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H437" t="s">
         <v>2110</v>
       </c>
       <c r="I437" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="J437" t="s">
         <v>1485</v>
@@ -45716,22 +45716,22 @@
         <v>80</v>
       </c>
       <c r="C438" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D438" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="E438" t="s">
         <v>94</v>
       </c>
       <c r="G438" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H438" t="s">
         <v>2111</v>
       </c>
       <c r="I438" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="J438" t="s">
         <v>1485</v>
@@ -45754,10 +45754,10 @@
         <v>80</v>
       </c>
       <c r="C439" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="D439" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="E439" t="s">
         <v>94</v>
@@ -45766,7 +45766,7 @@
         <v>2112</v>
       </c>
       <c r="G439" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H439" t="s">
         <v>2112</v>
@@ -45798,13 +45798,13 @@
         <v>160</v>
       </c>
       <c r="D440" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E440" t="s">
         <v>63</v>
       </c>
       <c r="G440" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H440" t="s">
         <v>2114</v>
@@ -45845,7 +45845,7 @@
         <v>2039</v>
       </c>
       <c r="G441" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H441" t="s">
         <v>2039</v>
@@ -45886,7 +45886,7 @@
         <v>1975</v>
       </c>
       <c r="G442" s="5" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H442" s="5" t="s">
         <v>2042</v>
@@ -45916,7 +45916,7 @@
         <v>936</v>
       </c>
       <c r="C443" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="D443" t="s">
         <v>286</v>
@@ -45928,13 +45928,13 @@
         <v>2118</v>
       </c>
       <c r="G443" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H443" t="s">
         <v>2118</v>
       </c>
       <c r="I443" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="J443" t="s">
         <v>1946</v>
@@ -45957,10 +45957,10 @@
         <v>936</v>
       </c>
       <c r="C444" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D444" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E444" t="s">
         <v>335</v>
@@ -45969,13 +45969,13 @@
         <v>2119</v>
       </c>
       <c r="G444" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H444" t="s">
         <v>2119</v>
       </c>
       <c r="I444" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="J444" t="s">
         <v>1946</v>
@@ -45998,7 +45998,7 @@
         <v>936</v>
       </c>
       <c r="C445" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D445" t="s">
         <v>985</v>
@@ -46010,7 +46010,7 @@
         <v>2029</v>
       </c>
       <c r="G445" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H445" t="s">
         <v>2029</v>
@@ -46039,7 +46039,7 @@
         <v>936</v>
       </c>
       <c r="C446" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D446" t="s">
         <v>988</v>
@@ -46051,7 +46051,7 @@
         <v>2033</v>
       </c>
       <c r="G446" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H446" t="s">
         <v>2033</v>
@@ -46080,10 +46080,10 @@
         <v>58</v>
       </c>
       <c r="C447" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D447" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E447" t="s">
         <v>335</v>
@@ -46092,7 +46092,7 @@
         <v>2124</v>
       </c>
       <c r="G447" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H447" t="s">
         <v>2124</v>
@@ -46124,7 +46124,7 @@
         <v>109</v>
       </c>
       <c r="D448" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="E448" t="s">
         <v>335</v>
@@ -46133,7 +46133,7 @@
         <v>2126</v>
       </c>
       <c r="G448" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H448" t="s">
         <v>2126</v>
@@ -46162,10 +46162,10 @@
         <v>936</v>
       </c>
       <c r="C449" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D449" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E449" t="s">
         <v>94</v>
@@ -46174,13 +46174,13 @@
         <v>2127</v>
       </c>
       <c r="G449" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H449" t="s">
         <v>2127</v>
       </c>
       <c r="I449" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="J449" t="s">
         <v>1946</v>
@@ -46203,10 +46203,10 @@
         <v>80</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D450" s="5" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E450" s="5" t="s">
         <v>83</v>
@@ -46215,13 +46215,13 @@
         <v>2128</v>
       </c>
       <c r="G450" s="5" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H450" s="5" t="s">
         <v>2129</v>
       </c>
       <c r="I450" s="5" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="J450" s="5" t="s">
         <v>1485</v>
@@ -46245,10 +46245,10 @@
         <v>80</v>
       </c>
       <c r="C451" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D451" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E451" t="s">
         <v>94</v>
@@ -46257,7 +46257,7 @@
         <v>2130</v>
       </c>
       <c r="G451" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H451" t="s">
         <v>2130</v>
@@ -46286,10 +46286,10 @@
         <v>80</v>
       </c>
       <c r="C452" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D452" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E452" t="s">
         <v>83</v>
@@ -46298,7 +46298,7 @@
         <v>2132</v>
       </c>
       <c r="G452" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H452" t="s">
         <v>2132</v>
@@ -46327,7 +46327,7 @@
         <v>80</v>
       </c>
       <c r="D453" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E453" t="s">
         <v>94</v>
@@ -46336,13 +46336,13 @@
         <v>2134</v>
       </c>
       <c r="G453" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H453" t="s">
         <v>2134</v>
       </c>
       <c r="I453" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="J453" t="s">
         <v>1485</v>
@@ -46365,10 +46365,10 @@
         <v>80</v>
       </c>
       <c r="C454" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D454" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E454" t="s">
         <v>63</v>
@@ -46377,7 +46377,7 @@
         <v>2135</v>
       </c>
       <c r="G454" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H454" t="s">
         <v>2135</v>
@@ -46406,16 +46406,16 @@
         <v>80</v>
       </c>
       <c r="C455" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D455" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E455" t="s">
         <v>63</v>
       </c>
       <c r="G455" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H455" t="s">
         <v>2137</v>
@@ -46444,10 +46444,10 @@
         <v>80</v>
       </c>
       <c r="C456" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D456" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E456" t="s">
         <v>83</v>
@@ -46456,13 +46456,13 @@
         <v>2139</v>
       </c>
       <c r="G456" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H456" t="s">
         <v>2139</v>
       </c>
       <c r="I456" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="J456" t="s">
         <v>1485</v>
@@ -46485,10 +46485,10 @@
         <v>80</v>
       </c>
       <c r="C457" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D457" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E457" t="s">
         <v>105</v>
@@ -46497,13 +46497,13 @@
         <v>2140</v>
       </c>
       <c r="G457" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H457" t="s">
         <v>2140</v>
       </c>
       <c r="I457" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="J457" t="s">
         <v>1485</v>
@@ -46526,25 +46526,25 @@
         <v>80</v>
       </c>
       <c r="C458" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D458" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E458" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F458" t="s">
         <v>2141</v>
       </c>
       <c r="G458" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H458" t="s">
         <v>2141</v>
       </c>
       <c r="I458" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="J458" t="s">
         <v>1485</v>
@@ -46567,10 +46567,10 @@
         <v>80</v>
       </c>
       <c r="C459" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D459" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E459" t="s">
         <v>63</v>
@@ -46579,13 +46579,13 @@
         <v>2142</v>
       </c>
       <c r="G459" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H459" t="s">
         <v>2142</v>
       </c>
       <c r="I459" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="J459" t="s">
         <v>1485</v>
@@ -46611,7 +46611,7 @@
         <v>740</v>
       </c>
       <c r="D460" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E460" t="s">
         <v>94</v>
@@ -46620,7 +46620,7 @@
         <v>2143</v>
       </c>
       <c r="G460" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H460" t="s">
         <v>2143</v>
@@ -46649,10 +46649,10 @@
         <v>80</v>
       </c>
       <c r="C461" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D461" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E461" t="s">
         <v>105</v>
@@ -46661,13 +46661,13 @@
         <v>2145</v>
       </c>
       <c r="G461" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H461" t="s">
         <v>2145</v>
       </c>
       <c r="I461" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="J461" t="s">
         <v>1485</v>
@@ -46690,10 +46690,10 @@
         <v>80</v>
       </c>
       <c r="C462" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D462" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E462" t="s">
         <v>105</v>
@@ -46702,13 +46702,13 @@
         <v>2146</v>
       </c>
       <c r="G462" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H462" t="s">
         <v>2146</v>
       </c>
       <c r="I462" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="J462" t="s">
         <v>1485</v>
@@ -46731,10 +46731,10 @@
         <v>80</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E463" s="5" t="s">
         <v>105</v>
@@ -46743,7 +46743,7 @@
         <v>2147</v>
       </c>
       <c r="G463" s="5" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H463" s="5" t="s">
         <v>2148</v>
@@ -46775,10 +46775,10 @@
         <v>80</v>
       </c>
       <c r="C464" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D464" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E464" t="s">
         <v>129</v>
@@ -46787,13 +46787,13 @@
         <v>2150</v>
       </c>
       <c r="G464" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H464" t="s">
         <v>2150</v>
       </c>
       <c r="I464" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="J464" t="s">
         <v>1485</v>
@@ -46816,10 +46816,10 @@
         <v>80</v>
       </c>
       <c r="C465" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D465" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E465" t="s">
         <v>129</v>
@@ -46828,13 +46828,13 @@
         <v>2151</v>
       </c>
       <c r="G465" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H465" t="s">
         <v>2151</v>
       </c>
       <c r="I465" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="J465" t="s">
         <v>1485</v>
@@ -46857,10 +46857,10 @@
         <v>80</v>
       </c>
       <c r="C466" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D466" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E466" t="s">
         <v>124</v>
@@ -46869,13 +46869,13 @@
         <v>2152</v>
       </c>
       <c r="G466" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H466" t="s">
         <v>2152</v>
       </c>
       <c r="I466" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="J466" t="s">
         <v>1485</v>
@@ -46898,10 +46898,10 @@
         <v>80</v>
       </c>
       <c r="C467" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D467" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E467" t="s">
         <v>105</v>
@@ -46910,13 +46910,13 @@
         <v>2153</v>
       </c>
       <c r="G467" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H467" t="s">
         <v>2153</v>
       </c>
       <c r="I467" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="J467" t="s">
         <v>1485</v>
@@ -46939,10 +46939,10 @@
         <v>80</v>
       </c>
       <c r="C468" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D468" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E468" t="s">
         <v>105</v>
@@ -46951,13 +46951,13 @@
         <v>2154</v>
       </c>
       <c r="G468" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H468" t="s">
         <v>2154</v>
       </c>
       <c r="I468" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="J468" t="s">
         <v>1485</v>
@@ -46980,10 +46980,10 @@
         <v>80</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E469" s="5" t="s">
         <v>105</v>
@@ -46992,13 +46992,13 @@
         <v>2147</v>
       </c>
       <c r="G469" s="5" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H469" s="5" t="s">
         <v>2147</v>
       </c>
       <c r="I469" s="5" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="J469" s="5" t="s">
         <v>1485</v>
@@ -47024,10 +47024,10 @@
         <v>58</v>
       </c>
       <c r="C470" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D470" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E470" t="s">
         <v>83</v>
@@ -47036,13 +47036,13 @@
         <v>2155</v>
       </c>
       <c r="G470" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H470" t="s">
         <v>2155</v>
       </c>
       <c r="I470" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="J470" t="s">
         <v>1473</v>
@@ -47062,13 +47062,13 @@
         <v>476</v>
       </c>
       <c r="B471" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C471" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="D471" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E471" t="s">
         <v>586</v>
@@ -47077,7 +47077,7 @@
         <v>2156</v>
       </c>
       <c r="G471" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H471" t="s">
         <v>2156</v>
@@ -47103,10 +47103,10 @@
         <v>477</v>
       </c>
       <c r="B472" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C472" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D472" t="s">
         <v>1004</v>
@@ -47115,13 +47115,13 @@
         <v>586</v>
       </c>
       <c r="G472" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H472" t="s">
         <v>2159</v>
       </c>
       <c r="I472" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="J472" t="s">
         <v>2158</v>
@@ -47141,19 +47141,19 @@
         <v>478</v>
       </c>
       <c r="B473" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C473" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D473" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E473" t="s">
         <v>586</v>
       </c>
       <c r="G473" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H473" t="s">
         <v>2160</v>
@@ -47179,13 +47179,13 @@
         <v>479</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C474" s="5" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D474" s="5" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E474" s="5" t="s">
         <v>586</v>
@@ -47194,7 +47194,7 @@
         <v>2162</v>
       </c>
       <c r="G474" s="5" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H474" s="5" t="s">
         <v>2163</v>
@@ -47221,13 +47221,13 @@
         <v>480</v>
       </c>
       <c r="B475" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C475" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D475" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E475" t="s">
         <v>586</v>
@@ -47236,7 +47236,7 @@
         <v>2166</v>
       </c>
       <c r="G475" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H475" t="s">
         <v>2166</v>
@@ -47262,13 +47262,13 @@
         <v>481</v>
       </c>
       <c r="B476" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C476" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D476" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="E476" t="s">
         <v>586</v>
@@ -47277,7 +47277,7 @@
         <v>2168</v>
       </c>
       <c r="G476" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H476" t="s">
         <v>2168</v>
@@ -47303,13 +47303,13 @@
         <v>482</v>
       </c>
       <c r="B477" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C477" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D477" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E477" t="s">
         <v>586</v>
@@ -47318,7 +47318,7 @@
         <v>2170</v>
       </c>
       <c r="G477" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H477" t="s">
         <v>2170</v>
@@ -47344,13 +47344,13 @@
         <v>483</v>
       </c>
       <c r="B478" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C478" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D478" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="E478" t="s">
         <v>586</v>
@@ -47359,7 +47359,7 @@
         <v>2172</v>
       </c>
       <c r="G478" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H478" t="s">
         <v>2172</v>
@@ -47385,13 +47385,13 @@
         <v>484</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E479" s="5" t="s">
         <v>586</v>
@@ -47400,7 +47400,7 @@
         <v>2174</v>
       </c>
       <c r="G479" s="5" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H479" s="5" t="s">
         <v>2175</v>
@@ -47429,13 +47429,13 @@
         <v>485</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C480" s="5" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E480" s="5" t="s">
         <v>586</v>
@@ -47444,7 +47444,7 @@
         <v>2162</v>
       </c>
       <c r="G480" s="5" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H480" s="5" t="s">
         <v>2177</v>
@@ -47473,13 +47473,13 @@
         <v>486</v>
       </c>
       <c r="B481" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C481" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D481" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="E481" t="s">
         <v>586</v>
@@ -47488,7 +47488,7 @@
         <v>2179</v>
       </c>
       <c r="G481" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H481" t="s">
         <v>2179</v>
@@ -47514,13 +47514,13 @@
         <v>487</v>
       </c>
       <c r="B482" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C482" t="s">
         <v>931</v>
       </c>
       <c r="D482" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E482" t="s">
         <v>586</v>
@@ -47529,7 +47529,7 @@
         <v>2181</v>
       </c>
       <c r="G482" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H482" t="s">
         <v>2181</v>
@@ -47555,13 +47555,13 @@
         <v>488</v>
       </c>
       <c r="B483" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C483" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D483" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E483" t="s">
         <v>586</v>
@@ -47570,7 +47570,7 @@
         <v>2183</v>
       </c>
       <c r="G483" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H483" t="s">
         <v>2183</v>
@@ -47596,13 +47596,13 @@
         <v>489</v>
       </c>
       <c r="B484" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C484" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D484" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E484" t="s">
         <v>586</v>
@@ -47611,7 +47611,7 @@
         <v>2185</v>
       </c>
       <c r="G484" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H484" t="s">
         <v>2185</v>
@@ -47637,13 +47637,13 @@
         <v>490</v>
       </c>
       <c r="B485" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C485" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D485" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="E485" t="s">
         <v>586</v>
@@ -47652,7 +47652,7 @@
         <v>2187</v>
       </c>
       <c r="G485" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H485" t="s">
         <v>2187</v>
@@ -47678,13 +47678,13 @@
         <v>491</v>
       </c>
       <c r="B486" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C486" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D486" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="E486" t="s">
         <v>586</v>
@@ -47693,13 +47693,13 @@
         <v>2189</v>
       </c>
       <c r="G486" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H486" t="s">
         <v>2189</v>
       </c>
       <c r="I486" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J486" t="s">
         <v>2158</v>
@@ -47719,13 +47719,13 @@
         <v>492</v>
       </c>
       <c r="B487" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C487" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D487" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="E487" t="s">
         <v>586</v>
@@ -47734,13 +47734,13 @@
         <v>2190</v>
       </c>
       <c r="G487" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H487" t="s">
         <v>2190</v>
       </c>
       <c r="I487" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J487" t="s">
         <v>2158</v>
@@ -47760,13 +47760,13 @@
         <v>493</v>
       </c>
       <c r="B488" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C488" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D488" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E488" t="s">
         <v>586</v>
@@ -47775,13 +47775,13 @@
         <v>2191</v>
       </c>
       <c r="G488" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H488" t="s">
         <v>2191</v>
       </c>
       <c r="I488" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="J488" t="s">
         <v>2192</v>
@@ -47801,13 +47801,13 @@
         <v>494</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D489" s="5" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E489" s="5" t="s">
         <v>586</v>
@@ -47816,7 +47816,7 @@
         <v>2174</v>
       </c>
       <c r="G489" s="5" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H489" s="5" t="s">
         <v>2174</v>
@@ -47845,13 +47845,13 @@
         <v>495</v>
       </c>
       <c r="B490" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C490" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D490" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E490" t="s">
         <v>586</v>
@@ -47860,7 +47860,7 @@
         <v>2194</v>
       </c>
       <c r="G490" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H490" t="s">
         <v>2194</v>
@@ -47886,13 +47886,13 @@
         <v>496</v>
       </c>
       <c r="B491" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C491" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D491" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E491" t="s">
         <v>586</v>
@@ -47901,7 +47901,7 @@
         <v>2196</v>
       </c>
       <c r="G491" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H491" t="s">
         <v>2196</v>
@@ -47927,13 +47927,13 @@
         <v>497</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C492" s="5" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D492" s="5" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E492" s="5" t="s">
         <v>586</v>
@@ -47942,7 +47942,7 @@
         <v>2198</v>
       </c>
       <c r="G492" s="5" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H492" s="5" t="s">
         <v>2199</v>
@@ -47969,13 +47969,13 @@
         <v>498</v>
       </c>
       <c r="B493" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C493" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D493" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E493" t="s">
         <v>162</v>
@@ -47984,7 +47984,7 @@
         <v>2201</v>
       </c>
       <c r="G493" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H493" t="s">
         <v>2201</v>
@@ -48010,22 +48010,22 @@
         <v>499</v>
       </c>
       <c r="B494" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C494" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D494" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="E494" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F494" t="s">
         <v>2203</v>
       </c>
       <c r="G494" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H494" t="s">
         <v>2203</v>
@@ -48051,13 +48051,13 @@
         <v>500</v>
       </c>
       <c r="B495" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C495" t="s">
         <v>1365</v>
       </c>
       <c r="D495" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E495" t="s">
         <v>586</v>
@@ -48066,7 +48066,7 @@
         <v>2205</v>
       </c>
       <c r="G495" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H495" t="s">
         <v>2205</v>
@@ -48092,13 +48092,13 @@
         <v>501</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C496" s="5" t="s">
         <v>1367</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E496" s="5" t="s">
         <v>586</v>
@@ -48134,13 +48134,13 @@
         <v>502</v>
       </c>
       <c r="B497" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C497" t="s">
         <v>1369</v>
       </c>
       <c r="D497" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E497" t="s">
         <v>586</v>
@@ -48175,13 +48175,13 @@
         <v>503</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C498" s="5" t="s">
         <v>1371</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E498" s="5" t="s">
         <v>586</v>
@@ -48217,13 +48217,13 @@
         <v>504</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C499" s="5" t="s">
         <v>1373</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E499" s="5" t="s">
         <v>586</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7DBC9D0-1936-48F9-B538-0042F75F682D}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C86AFB-6064-0942-BFC0-E69E4CAC4EDC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10561" uniqueCount="2247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10560" uniqueCount="2248">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6782,6 +6782,9 @@
   </si>
   <si>
     <t>8805</t>
+  </si>
+  <si>
+    <t>BDRCHE24</t>
   </si>
 </sst>
 </file>
@@ -6789,9 +6792,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6860,7 +6863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6873,8 +6876,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7178,192 +7180,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A43"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -7376,19 +7378,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R515"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" customWidth="1"/>
+    <col min="11" max="11" width="6.5" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
@@ -7397,7 +7399,7 @@
     <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -7453,7 +7455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -7494,7 +7496,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -7532,9 +7534,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>2247</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -7557,8 +7559,8 @@
       <c r="I4" t="s">
         <v>62</v>
       </c>
-      <c r="J4" t="s">
-        <v>63</v>
+      <c r="J4">
+        <v>2024</v>
       </c>
       <c r="K4">
         <v>75</v>
@@ -7576,7 +7578,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -7617,7 +7619,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -7661,7 +7663,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -7705,7 +7707,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -7743,7 +7745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -7781,7 +7783,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -7822,7 +7824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -7863,7 +7865,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -7904,7 +7906,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -7948,7 +7950,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -7992,7 +7994,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -8030,7 +8032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>103</v>
       </c>
@@ -8071,7 +8073,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -8112,7 +8114,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>111</v>
       </c>
@@ -8153,7 +8155,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -8191,7 +8193,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -8229,7 +8231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -8267,7 +8269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -8305,7 +8307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>125</v>
       </c>
@@ -8346,7 +8348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -8384,7 +8386,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -8422,7 +8424,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -8460,7 +8462,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -8501,7 +8503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -8542,7 +8544,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -8583,7 +8585,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -8624,7 +8626,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>149</v>
       </c>
@@ -8665,7 +8667,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -8700,7 +8702,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -8741,7 +8743,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -8782,7 +8784,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -8820,7 +8822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>163</v>
       </c>
@@ -8858,7 +8860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>165</v>
       </c>
@@ -8899,7 +8901,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -8943,7 +8945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -8984,7 +8986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>176</v>
       </c>
@@ -9028,7 +9030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>181</v>
       </c>
@@ -9069,7 +9071,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>184</v>
       </c>
@@ -9107,7 +9109,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>188</v>
       </c>
@@ -9145,7 +9147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -9183,7 +9185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>193</v>
       </c>
@@ -9224,7 +9226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -9265,7 +9267,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -9303,7 +9305,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -9344,7 +9346,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -9382,7 +9384,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>208</v>
       </c>
@@ -9420,7 +9422,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>209</v>
       </c>
@@ -9458,7 +9460,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>213</v>
       </c>
@@ -9496,7 +9498,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>216</v>
       </c>
@@ -9540,7 +9542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -9578,7 +9580,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>222</v>
       </c>
@@ -9619,7 +9621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>224</v>
       </c>
@@ -9657,7 +9659,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>226</v>
       </c>
@@ -9698,7 +9700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>229</v>
       </c>
@@ -9733,7 +9735,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>230</v>
       </c>
@@ -9774,7 +9776,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>234</v>
       </c>
@@ -9812,7 +9814,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>236</v>
       </c>
@@ -9856,7 +9858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>240</v>
       </c>
@@ -9894,7 +9896,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>243</v>
       </c>
@@ -9932,7 +9934,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>246</v>
       </c>
@@ -9970,7 +9972,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>247</v>
       </c>
@@ -10008,7 +10010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>250</v>
       </c>
@@ -10046,7 +10048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>253</v>
       </c>
@@ -10084,7 +10086,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>256</v>
       </c>
@@ -10122,7 +10124,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>259</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>263</v>
       </c>
@@ -10207,7 +10209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>268</v>
       </c>
@@ -10248,7 +10250,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>271</v>
       </c>
@@ -10286,7 +10288,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>275</v>
       </c>
@@ -10324,7 +10326,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>279</v>
       </c>
@@ -10362,7 +10364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>281</v>
       </c>
@@ -10397,7 +10399,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>284</v>
       </c>
@@ -10435,7 +10437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>287</v>
       </c>
@@ -10476,7 +10478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>291</v>
       </c>
@@ -10514,7 +10516,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>293</v>
       </c>
@@ -10552,7 +10554,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>295</v>
       </c>
@@ -10590,7 +10592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>299</v>
       </c>
@@ -10628,7 +10630,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>303</v>
       </c>
@@ -10669,7 +10671,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>305</v>
       </c>
@@ -10707,7 +10709,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>307</v>
       </c>
@@ -10745,7 +10747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>310</v>
       </c>
@@ -10780,7 +10782,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>313</v>
       </c>
@@ -10818,7 +10820,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>318</v>
       </c>
@@ -10850,7 +10852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>321</v>
       </c>
@@ -10888,7 +10890,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>15401623</v>
       </c>
@@ -10923,7 +10925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>325</v>
       </c>
@@ -10964,7 +10966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>328</v>
       </c>
@@ -11005,7 +11007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>330</v>
       </c>
@@ -11046,7 +11048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>336</v>
       </c>
@@ -11087,7 +11089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>339</v>
       </c>
@@ -11128,7 +11130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>342</v>
       </c>
@@ -11172,7 +11174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>344</v>
       </c>
@@ -11213,7 +11215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>347</v>
       </c>
@@ -11254,7 +11256,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>348</v>
       </c>
@@ -11295,7 +11297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>25000124</v>
       </c>
@@ -11336,7 +11338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>354</v>
       </c>
@@ -11377,7 +11379,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>356</v>
       </c>
@@ -11418,7 +11420,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>358</v>
       </c>
@@ -11459,7 +11461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>361</v>
       </c>
@@ -11500,7 +11502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>364</v>
       </c>
@@ -11541,7 +11543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>365</v>
       </c>
@@ -11582,7 +11584,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>368</v>
       </c>
@@ -11620,7 +11622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>35800124</v>
       </c>
@@ -11655,7 +11657,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>35800224</v>
       </c>
@@ -11690,7 +11692,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>376</v>
       </c>
@@ -11728,7 +11730,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>377</v>
       </c>
@@ -11766,7 +11768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>379</v>
       </c>
@@ -11810,7 +11812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>383</v>
       </c>
@@ -11851,7 +11853,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>386</v>
       </c>
@@ -11895,7 +11897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>388</v>
       </c>
@@ -11933,7 +11935,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>390</v>
       </c>
@@ -11971,7 +11973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>393</v>
       </c>
@@ -12009,7 +12011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>394</v>
       </c>
@@ -12053,7 +12055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>398</v>
       </c>
@@ -12097,7 +12099,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>401</v>
       </c>
@@ -12132,7 +12134,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>405</v>
       </c>
@@ -12167,7 +12169,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>408</v>
       </c>
@@ -12208,7 +12210,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>410</v>
       </c>
@@ -12249,7 +12251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>412</v>
       </c>
@@ -12287,7 +12289,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>413</v>
       </c>
@@ -12325,7 +12327,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>416</v>
       </c>
@@ -12366,7 +12368,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>419</v>
       </c>
@@ -12407,7 +12409,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>423</v>
       </c>
@@ -12448,7 +12450,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>425</v>
       </c>
@@ -12489,7 +12491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>428</v>
       </c>
@@ -12530,7 +12532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>431</v>
       </c>
@@ -12571,7 +12573,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>436</v>
       </c>
@@ -12612,7 +12614,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>439</v>
       </c>
@@ -12653,7 +12655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>442</v>
       </c>
@@ -12697,7 +12699,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>445</v>
       </c>
@@ -12738,7 +12740,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>448</v>
       </c>
@@ -12776,7 +12778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>450</v>
       </c>
@@ -12817,7 +12819,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>452</v>
       </c>
@@ -12855,7 +12857,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>455</v>
       </c>
@@ -12896,7 +12898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>457</v>
       </c>
@@ -12937,7 +12939,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>458</v>
       </c>
@@ -12978,7 +12980,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>461</v>
       </c>
@@ -13019,7 +13021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>463</v>
       </c>
@@ -13060,7 +13062,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>466</v>
       </c>
@@ -13101,7 +13103,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>470</v>
       </c>
@@ -13145,7 +13147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>473</v>
       </c>
@@ -13186,7 +13188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>474</v>
       </c>
@@ -13224,7 +13226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>477</v>
       </c>
@@ -13265,7 +13267,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>480</v>
       </c>
@@ -13300,7 +13302,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>482</v>
       </c>
@@ -13335,7 +13337,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>483</v>
       </c>
@@ -13376,7 +13378,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>485</v>
       </c>
@@ -13420,7 +13422,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>488</v>
       </c>
@@ -13455,7 +13457,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>492</v>
       </c>
@@ -13496,7 +13498,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>496</v>
       </c>
@@ -13537,7 +13539,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>499</v>
       </c>
@@ -13578,7 +13580,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>502</v>
       </c>
@@ -13619,7 +13621,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>505</v>
       </c>
@@ -13660,7 +13662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>507</v>
       </c>
@@ -13701,7 +13703,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>510</v>
       </c>
@@ -13745,7 +13747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>514</v>
       </c>
@@ -13786,7 +13788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>515</v>
       </c>
@@ -13827,7 +13829,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>518</v>
       </c>
@@ -13868,7 +13870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>522</v>
       </c>
@@ -13909,7 +13911,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>525</v>
       </c>
@@ -13950,7 +13952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>528</v>
       </c>
@@ -13994,7 +13996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>531</v>
       </c>
@@ -14029,7 +14031,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>532</v>
       </c>
@@ -14064,7 +14066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>534</v>
       </c>
@@ -14102,7 +14104,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>535</v>
       </c>
@@ -14143,7 +14145,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>537</v>
       </c>
@@ -14184,7 +14186,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>540</v>
       </c>
@@ -14222,7 +14224,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>542</v>
       </c>
@@ -14263,7 +14265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>545</v>
       </c>
@@ -14298,7 +14300,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>547</v>
       </c>
@@ -14342,7 +14344,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>549</v>
       </c>
@@ -14383,7 +14385,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>552</v>
       </c>
@@ -14424,7 +14426,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>554</v>
       </c>
@@ -14465,7 +14467,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>555</v>
       </c>
@@ -14509,7 +14511,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>559</v>
       </c>
@@ -14550,7 +14552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>561</v>
       </c>
@@ -14594,7 +14596,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>25002122</v>
       </c>
@@ -14632,7 +14634,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>564</v>
       </c>
@@ -14673,7 +14675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>568</v>
       </c>
@@ -14714,7 +14716,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>570</v>
       </c>
@@ -14755,7 +14757,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>573</v>
       </c>
@@ -14796,7 +14798,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>577</v>
       </c>
@@ -14837,7 +14839,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>581</v>
       </c>
@@ -14878,7 +14880,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>583</v>
       </c>
@@ -14919,7 +14921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>587</v>
       </c>
@@ -14960,7 +14962,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>589</v>
       </c>
@@ -15001,7 +15003,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>591</v>
       </c>
@@ -15042,7 +15044,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>595</v>
       </c>
@@ -15083,7 +15085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>598</v>
       </c>
@@ -15121,7 +15123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>600</v>
       </c>
@@ -15159,7 +15161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>602</v>
       </c>
@@ -15203,7 +15205,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>604</v>
       </c>
@@ -15244,7 +15246,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>607</v>
       </c>
@@ -15288,7 +15290,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>610</v>
       </c>
@@ -15329,7 +15331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>613</v>
       </c>
@@ -15370,7 +15372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>616</v>
       </c>
@@ -15411,7 +15413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>618</v>
       </c>
@@ -15455,7 +15457,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>622</v>
       </c>
@@ -15496,7 +15498,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>624</v>
       </c>
@@ -15537,7 +15539,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>626</v>
       </c>
@@ -15581,7 +15583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>628</v>
       </c>
@@ -15622,7 +15624,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>629</v>
       </c>
@@ -15666,7 +15668,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>631</v>
       </c>
@@ -15707,7 +15709,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>633</v>
       </c>
@@ -15748,7 +15750,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>635</v>
       </c>
@@ -15789,7 +15791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>636</v>
       </c>
@@ -15830,7 +15832,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>637</v>
       </c>
@@ -15871,7 +15873,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>642</v>
       </c>
@@ -15912,7 +15914,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>644</v>
       </c>
@@ -15953,7 +15955,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>648</v>
       </c>
@@ -15994,7 +15996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>651</v>
       </c>
@@ -16035,7 +16037,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>654</v>
       </c>
@@ -16076,7 +16078,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>655</v>
       </c>
@@ -16117,7 +16119,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>658</v>
       </c>
@@ -16158,7 +16160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>661</v>
       </c>
@@ -16199,7 +16201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>662</v>
       </c>
@@ -16240,7 +16242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>663</v>
       </c>
@@ -16281,7 +16283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>665</v>
       </c>
@@ -16322,7 +16324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>669</v>
       </c>
@@ -16363,7 +16365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>671</v>
       </c>
@@ -16404,7 +16406,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>673</v>
       </c>
@@ -16445,7 +16447,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>676</v>
       </c>
@@ -16486,7 +16488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>678</v>
       </c>
@@ -16530,7 +16532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>681</v>
       </c>
@@ -16571,7 +16573,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>683</v>
       </c>
@@ -16612,7 +16614,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>685</v>
       </c>
@@ -16653,7 +16655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>688</v>
       </c>
@@ -16697,7 +16699,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>691</v>
       </c>
@@ -16738,7 +16740,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>693</v>
       </c>
@@ -16779,7 +16781,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>696</v>
       </c>
@@ -16820,7 +16822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>700</v>
       </c>
@@ -16861,7 +16863,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>702</v>
       </c>
@@ -16902,7 +16904,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>705</v>
       </c>
@@ -16943,7 +16945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>707</v>
       </c>
@@ -16984,7 +16986,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>710</v>
       </c>
@@ -17025,7 +17027,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>711</v>
       </c>
@@ -17069,7 +17071,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>712</v>
       </c>
@@ -17110,7 +17112,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>713</v>
       </c>
@@ -17154,7 +17156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>716</v>
       </c>
@@ -17195,7 +17197,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>718</v>
       </c>
@@ -17236,7 +17238,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>720</v>
       </c>
@@ -17277,7 +17279,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>722</v>
       </c>
@@ -17318,7 +17320,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>724</v>
       </c>
@@ -17359,7 +17361,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>726</v>
       </c>
@@ -17400,7 +17402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>728</v>
       </c>
@@ -17441,7 +17443,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>13800524</v>
       </c>
@@ -17482,7 +17484,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>730</v>
       </c>
@@ -17523,7 +17525,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>732</v>
       </c>
@@ -17564,7 +17566,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>734</v>
       </c>
@@ -17605,7 +17607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>735</v>
       </c>
@@ -17643,7 +17645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>739</v>
       </c>
@@ -17681,7 +17683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>10700325</v>
       </c>
@@ -17719,7 +17721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>744</v>
       </c>
@@ -17757,7 +17759,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>748</v>
       </c>
@@ -17798,7 +17800,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>751</v>
       </c>
@@ -17839,7 +17841,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>754</v>
       </c>
@@ -17880,7 +17882,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>758</v>
       </c>
@@ -17921,7 +17923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>762</v>
       </c>
@@ -17962,7 +17964,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>766</v>
       </c>
@@ -18003,7 +18005,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>771</v>
       </c>
@@ -18044,7 +18046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="265" spans="1:18">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>775</v>
       </c>
@@ -18088,7 +18090,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:18">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>778</v>
       </c>
@@ -18129,7 +18131,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="267" spans="1:18">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>782</v>
       </c>
@@ -18170,7 +18172,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="268" spans="1:18">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>785</v>
       </c>
@@ -18211,7 +18213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:18">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>790</v>
       </c>
@@ -18249,7 +18251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="270" spans="1:18">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>14700422</v>
       </c>
@@ -18290,7 +18292,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="271" spans="1:18">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>794</v>
       </c>
@@ -18328,7 +18330,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:18">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>796</v>
       </c>
@@ -18366,7 +18368,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="273" spans="1:18">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>799</v>
       </c>
@@ -18398,7 +18400,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>802</v>
       </c>
@@ -18436,7 +18438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>43800825</v>
       </c>
@@ -18477,7 +18479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>808</v>
       </c>
@@ -18515,7 +18517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>811</v>
       </c>
@@ -18550,7 +18552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="278" spans="1:18">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>813</v>
       </c>
@@ -18585,7 +18587,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>815</v>
       </c>
@@ -18623,7 +18625,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>818</v>
       </c>
@@ -18661,7 +18663,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:18">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>821</v>
       </c>
@@ -18696,7 +18698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>824</v>
       </c>
@@ -18734,7 +18736,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>826</v>
       </c>
@@ -18775,7 +18777,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>828</v>
       </c>
@@ -18810,7 +18812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>829</v>
       </c>
@@ -18848,7 +18850,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>831</v>
       </c>
@@ -18886,7 +18888,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>833</v>
       </c>
@@ -18924,7 +18926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>835</v>
       </c>
@@ -18965,7 +18967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>838</v>
       </c>
@@ -19006,7 +19008,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>842</v>
       </c>
@@ -19044,7 +19046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>845</v>
       </c>
@@ -19082,7 +19084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>847</v>
       </c>
@@ -19123,7 +19125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>849</v>
       </c>
@@ -19164,7 +19166,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>851</v>
       </c>
@@ -19205,7 +19207,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>853</v>
       </c>
@@ -19243,7 +19245,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>854</v>
       </c>
@@ -19284,7 +19286,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>855</v>
       </c>
@@ -19322,7 +19324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>858</v>
       </c>
@@ -19360,7 +19362,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>860</v>
       </c>
@@ -19398,7 +19400,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>862</v>
       </c>
@@ -19433,7 +19435,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>863</v>
       </c>
@@ -19474,7 +19476,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>865</v>
       </c>
@@ -19512,7 +19514,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>10701525</v>
       </c>
@@ -19550,7 +19552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>872</v>
       </c>
@@ -19588,7 +19590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>875</v>
       </c>
@@ -19629,7 +19631,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>877</v>
       </c>
@@ -19670,7 +19672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>879</v>
       </c>
@@ -19708,7 +19710,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>883</v>
       </c>
@@ -19749,7 +19751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>886</v>
       </c>
@@ -19787,7 +19789,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>887</v>
       </c>
@@ -19825,7 +19827,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>890</v>
       </c>
@@ -19866,7 +19868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>893</v>
       </c>
@@ -19898,7 +19900,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>895</v>
       </c>
@@ -19933,7 +19935,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>897</v>
       </c>
@@ -19974,7 +19976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>899</v>
       </c>
@@ -20015,7 +20017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>901</v>
       </c>
@@ -20047,7 +20049,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>903</v>
       </c>
@@ -20082,7 +20084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>904</v>
       </c>
@@ -20120,7 +20122,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>905</v>
       </c>
@@ -20158,7 +20160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>906</v>
       </c>
@@ -20196,7 +20198,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="321" spans="1:18">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>907</v>
       </c>
@@ -20234,7 +20236,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="322" spans="1:18">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>909</v>
       </c>
@@ -20275,7 +20277,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="323" spans="1:18">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>910</v>
       </c>
@@ -20310,7 +20312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:18">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>911</v>
       </c>
@@ -20351,7 +20353,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:18">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>913</v>
       </c>
@@ -20392,7 +20394,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="326" spans="1:18">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>917</v>
       </c>
@@ -20436,7 +20438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:18">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>924</v>
       </c>
@@ -20471,7 +20473,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:18">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>928</v>
       </c>
@@ -20515,7 +20517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="329" spans="1:18">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>929</v>
       </c>
@@ -20559,7 +20561,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:18">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>933</v>
       </c>
@@ -20594,7 +20596,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="331" spans="1:18">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>935</v>
       </c>
@@ -20629,7 +20631,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="332" spans="1:18">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>938</v>
       </c>
@@ -20667,7 +20669,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="333" spans="1:18">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>940</v>
       </c>
@@ -20711,7 +20713,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="334" spans="1:18">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>941</v>
       </c>
@@ -20746,7 +20748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="335" spans="1:18">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>944</v>
       </c>
@@ -20784,7 +20786,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="336" spans="1:18">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>948</v>
       </c>
@@ -20822,7 +20824,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>951</v>
       </c>
@@ -20866,7 +20868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>955</v>
       </c>
@@ -20910,7 +20912,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>957</v>
       </c>
@@ -20951,7 +20953,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>960</v>
       </c>
@@ -20992,7 +20994,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>962</v>
       </c>
@@ -21036,7 +21038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>965</v>
       </c>
@@ -21077,7 +21079,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>967</v>
       </c>
@@ -21118,7 +21120,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>969</v>
       </c>
@@ -21162,7 +21164,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>971</v>
       </c>
@@ -21206,7 +21208,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>974</v>
       </c>
@@ -21244,7 +21246,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>976</v>
       </c>
@@ -21285,7 +21287,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>977</v>
       </c>
@@ -21326,7 +21328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>978</v>
       </c>
@@ -21370,7 +21372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>980</v>
       </c>
@@ -21411,7 +21413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>986</v>
       </c>
@@ -21452,7 +21454,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>989</v>
       </c>
@@ -21493,7 +21495,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="353" spans="1:18">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>993</v>
       </c>
@@ -21534,7 +21536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" spans="1:18">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>996</v>
       </c>
@@ -21575,7 +21577,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:18">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>998</v>
       </c>
@@ -21616,7 +21618,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:18">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>1000</v>
       </c>
@@ -21657,7 +21659,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:18">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>1002</v>
       </c>
@@ -21698,7 +21700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:18">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>1005</v>
       </c>
@@ -21742,7 +21744,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="359" spans="1:18">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1007</v>
       </c>
@@ -21783,7 +21785,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:18">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>1010</v>
       </c>
@@ -21824,7 +21826,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="361" spans="1:18">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1013</v>
       </c>
@@ -21868,7 +21870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:18">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>1016</v>
       </c>
@@ -21909,7 +21911,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:18">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>1021</v>
       </c>
@@ -21953,7 +21955,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="364" spans="1:18">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1025</v>
       </c>
@@ -21994,7 +21996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="365" spans="1:18">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1027</v>
       </c>
@@ -22038,7 +22040,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:18">
+    <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1029</v>
       </c>
@@ -22079,7 +22081,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="367" spans="1:18">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1031</v>
       </c>
@@ -22117,7 +22119,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:18">
+    <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1034</v>
       </c>
@@ -22158,7 +22160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1038</v>
       </c>
@@ -22199,7 +22201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1041</v>
       </c>
@@ -22240,7 +22242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1044</v>
       </c>
@@ -22281,7 +22283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1047</v>
       </c>
@@ -22322,7 +22324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1050</v>
       </c>
@@ -22363,7 +22365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1053</v>
       </c>
@@ -22407,7 +22409,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1057</v>
       </c>
@@ -22448,7 +22450,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1061</v>
       </c>
@@ -22489,7 +22491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1063</v>
       </c>
@@ -22530,7 +22532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1066</v>
       </c>
@@ -22571,7 +22573,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>1070</v>
       </c>
@@ -22612,7 +22614,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1073</v>
       </c>
@@ -22653,7 +22655,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1075</v>
       </c>
@@ -22694,7 +22696,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1078</v>
       </c>
@@ -22735,7 +22737,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>1080</v>
       </c>
@@ -22776,7 +22778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>1082</v>
       </c>
@@ -22814,7 +22816,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1086</v>
       </c>
@@ -22852,7 +22854,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>53800623</v>
       </c>
@@ -22893,7 +22895,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1091</v>
       </c>
@@ -22934,7 +22936,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>1093</v>
       </c>
@@ -22975,7 +22977,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1095</v>
       </c>
@@ -23016,7 +23018,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>1096</v>
       </c>
@@ -23057,7 +23059,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>1097</v>
       </c>
@@ -23098,7 +23100,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1098</v>
       </c>
@@ -23139,7 +23141,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1100</v>
       </c>
@@ -23180,7 +23182,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1102</v>
       </c>
@@ -23221,7 +23223,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>1104</v>
       </c>
@@ -23262,7 +23264,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>1106</v>
       </c>
@@ -23303,7 +23305,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>1109</v>
       </c>
@@ -23347,7 +23349,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>1111</v>
       </c>
@@ -23391,7 +23393,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>1113</v>
       </c>
@@ -23432,7 +23434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>1115</v>
       </c>
@@ -23473,7 +23475,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1118</v>
       </c>
@@ -23514,7 +23516,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>1122</v>
       </c>
@@ -23555,7 +23557,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>1124</v>
       </c>
@@ -23593,7 +23595,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>1127</v>
       </c>
@@ -23634,7 +23636,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>1129</v>
       </c>
@@ -23675,7 +23677,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>1132</v>
       </c>
@@ -23716,7 +23718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1135</v>
       </c>
@@ -23757,7 +23759,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1137</v>
       </c>
@@ -23801,7 +23803,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1139</v>
       </c>
@@ -23842,7 +23844,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1141</v>
       </c>
@@ -23886,7 +23888,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1143</v>
       </c>
@@ -23930,7 +23932,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1145</v>
       </c>
@@ -23974,7 +23976,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1148</v>
       </c>
@@ -24015,7 +24017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1152</v>
       </c>
@@ -24053,7 +24055,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>1154</v>
       </c>
@@ -24097,7 +24099,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1158</v>
       </c>
@@ -24138,7 +24140,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1161</v>
       </c>
@@ -24179,7 +24181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>1163</v>
       </c>
@@ -24220,7 +24222,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1166</v>
       </c>
@@ -24261,7 +24263,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>1169</v>
       </c>
@@ -24302,7 +24304,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>1171</v>
       </c>
@@ -24343,7 +24345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>1174</v>
       </c>
@@ -24387,7 +24389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1177</v>
       </c>
@@ -24428,7 +24430,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>16003124</v>
       </c>
@@ -24469,7 +24471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>1181</v>
       </c>
@@ -24513,7 +24515,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1183</v>
       </c>
@@ -24557,7 +24559,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>1185</v>
       </c>
@@ -24601,7 +24603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1187</v>
       </c>
@@ -24639,7 +24641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>1190</v>
       </c>
@@ -24683,7 +24685,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1192</v>
       </c>
@@ -24718,7 +24720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1195</v>
       </c>
@@ -24756,7 +24758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>1197</v>
       </c>
@@ -24794,7 +24796,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="433" spans="1:18">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1201</v>
       </c>
@@ -24835,7 +24837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="434" spans="1:18">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B434" t="s">
         <v>118</v>
       </c>
@@ -24873,7 +24875,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="435" spans="1:18">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1206</v>
       </c>
@@ -24914,7 +24916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="436" spans="1:18">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>1208</v>
       </c>
@@ -24958,7 +24960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="437" spans="1:18">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1212</v>
       </c>
@@ -24996,7 +24998,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="438" spans="1:18">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>1215</v>
       </c>
@@ -25037,7 +25039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="439" spans="1:18">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>1218</v>
       </c>
@@ -25075,7 +25077,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="440" spans="1:18">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>1219</v>
       </c>
@@ -25116,7 +25118,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="441" spans="1:18">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>1220</v>
       </c>
@@ -25157,7 +25159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="442" spans="1:18">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>1221</v>
       </c>
@@ -25198,7 +25200,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="443" spans="1:18">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>1223</v>
       </c>
@@ -25239,7 +25241,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="444" spans="1:18">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1226</v>
       </c>
@@ -25280,7 +25282,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="445" spans="1:18">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1227</v>
       </c>
@@ -25321,7 +25323,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="446" spans="1:18">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1229</v>
       </c>
@@ -25362,7 +25364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="447" spans="1:18">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>1235</v>
       </c>
@@ -25406,7 +25408,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="448" spans="1:18">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1238</v>
       </c>
@@ -25447,7 +25449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="449" spans="1:16">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1240</v>
       </c>
@@ -25488,7 +25490,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="450" spans="1:16">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1244</v>
       </c>
@@ -25529,7 +25531,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="451" spans="1:16">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1248</v>
       </c>
@@ -25570,7 +25572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="452" spans="1:16">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1250</v>
       </c>
@@ -25608,7 +25610,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="453" spans="1:16">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1253</v>
       </c>
@@ -25652,7 +25654,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="454" spans="1:16">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1257</v>
       </c>
@@ -25690,7 +25692,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="455" spans="1:16">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1262</v>
       </c>
@@ -25731,7 +25733,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="456" spans="1:16">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1265</v>
       </c>
@@ -25772,7 +25774,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="457" spans="1:16">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1268</v>
       </c>
@@ -25813,7 +25815,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="458" spans="1:16">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>1270</v>
       </c>
@@ -25854,7 +25856,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="459" spans="1:16">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>1273</v>
       </c>
@@ -25895,7 +25897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="460" spans="1:16">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>1276</v>
       </c>
@@ -25936,7 +25938,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="461" spans="1:16">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1281</v>
       </c>
@@ -25977,7 +25979,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="462" spans="1:16">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>1283</v>
       </c>
@@ -26018,7 +26020,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="463" spans="1:16">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>1285</v>
       </c>
@@ -26059,7 +26061,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="464" spans="1:16">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>1286</v>
       </c>
@@ -26100,7 +26102,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="465" spans="1:16">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>1288</v>
       </c>
@@ -26141,7 +26143,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="466" spans="1:16">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1290</v>
       </c>
@@ -26182,7 +26184,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="467" spans="1:16">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1292</v>
       </c>
@@ -26223,7 +26225,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="468" spans="1:16">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>1294</v>
       </c>
@@ -26264,7 +26266,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="469" spans="1:16">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>1296</v>
       </c>
@@ -26305,7 +26307,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="470" spans="1:16">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1298</v>
       </c>
@@ -26346,7 +26348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="471" spans="1:16">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>1302</v>
       </c>
@@ -26381,7 +26383,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="472" spans="1:16">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>1304</v>
       </c>
@@ -26416,7 +26418,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="473" spans="1:16">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>1307</v>
       </c>
@@ -26454,7 +26456,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="474" spans="1:16">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>1311</v>
       </c>
@@ -26492,7 +26494,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="475" spans="1:16">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>1314</v>
       </c>
@@ -26530,7 +26532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="476" spans="1:16">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1317</v>
       </c>
@@ -26565,7 +26567,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="477" spans="1:16">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1320</v>
       </c>
@@ -26603,7 +26605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="478" spans="1:16">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1323</v>
       </c>
@@ -26641,7 +26643,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="479" spans="1:16">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1326</v>
       </c>
@@ -26679,7 +26681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="480" spans="1:16">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1329</v>
       </c>
@@ -26717,7 +26719,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="481" spans="1:16">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1331</v>
       </c>
@@ -26755,7 +26757,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="482" spans="1:16">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1333</v>
       </c>
@@ -26793,7 +26795,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="483" spans="1:16">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1334</v>
       </c>
@@ -26831,7 +26833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="484" spans="1:16">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>1337</v>
       </c>
@@ -26869,7 +26871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="485" spans="1:16">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1340</v>
       </c>
@@ -26907,7 +26909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="486" spans="1:16">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>1343</v>
       </c>
@@ -26945,7 +26947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="487" spans="1:16">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>1345</v>
       </c>
@@ -26983,7 +26985,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="488" spans="1:16">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>1348</v>
       </c>
@@ -27021,7 +27023,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="489" spans="1:16">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>1350</v>
       </c>
@@ -27059,7 +27061,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="490" spans="1:16">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>1352</v>
       </c>
@@ -27097,7 +27099,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="491" spans="1:16">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1354</v>
       </c>
@@ -27135,7 +27137,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="492" spans="1:16">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>1357</v>
       </c>
@@ -27173,7 +27175,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="493" spans="1:16">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>1360</v>
       </c>
@@ -27211,7 +27213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="494" spans="1:16">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1362</v>
       </c>
@@ -27249,7 +27251,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="495" spans="1:16">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1364</v>
       </c>
@@ -27290,7 +27292,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="496" spans="1:16">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1366</v>
       </c>
@@ -27331,7 +27333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="497" spans="1:16">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1368</v>
       </c>
@@ -27372,7 +27374,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="498" spans="1:16">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1370</v>
       </c>
@@ -27413,7 +27415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="499" spans="1:16">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1372</v>
       </c>
@@ -27454,7 +27456,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="500" spans="1:16">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1374</v>
       </c>
@@ -27492,7 +27494,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="501" spans="1:16">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1380</v>
       </c>
@@ -27530,7 +27532,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="502" spans="1:16">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>1382</v>
       </c>
@@ -27565,7 +27567,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="503" spans="1:16">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>1386</v>
       </c>
@@ -27600,7 +27602,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="504" spans="1:16">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>1390</v>
       </c>
@@ -27635,7 +27637,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="505" spans="1:16">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>1393</v>
       </c>
@@ -27670,7 +27672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" spans="1:16">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>1397</v>
       </c>
@@ -27708,7 +27710,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="507" spans="1:16">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>1400</v>
       </c>
@@ -27743,7 +27745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="508" spans="1:16">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>1404</v>
       </c>
@@ -27778,7 +27780,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="509" spans="1:16">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>1407</v>
       </c>
@@ -27816,7 +27818,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:16">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>1410</v>
       </c>
@@ -27854,7 +27856,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="511" spans="1:16">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>1414</v>
       </c>
@@ -27892,7 +27894,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="512" spans="1:16">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>1419</v>
       </c>
@@ -27930,7 +27932,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="513" spans="1:16">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>43902124</v>
       </c>
@@ -27968,7 +27970,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="514" spans="1:16">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>24003025</v>
       </c>
@@ -28009,7 +28011,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="515" spans="1:16">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>27100522</v>
       </c>
@@ -28058,9 +28060,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1427</v>
       </c>
@@ -28135,17 +28137,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1449</v>
       </c>
@@ -28162,7 +28164,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1454</v>
       </c>
@@ -28176,8 +28178,8 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1458</v>
       </c>
       <c r="B3" t="s">
@@ -28190,8 +28192,8 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>1462</v>
       </c>
       <c r="B4" t="s">
@@ -28203,9 +28205,6 @@
       <c r="E4" t="s">
         <v>1461</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28215,14 +28214,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1463</v>
       </c>
@@ -28233,7 +28232,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1466</v>
       </c>
@@ -28252,7 +28251,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N512"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -28270,7 +28269,7 @@
     <col min="14" max="14" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30">
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1469</v>
       </c>
@@ -28314,7 +28313,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -28355,7 +28354,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -28399,7 +28398,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -28440,7 +28439,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -28481,7 +28480,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>6</v>
       </c>
@@ -28525,7 +28524,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -28566,7 +28565,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8</v>
       </c>
@@ -28607,7 +28606,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9</v>
       </c>
@@ -28648,7 +28647,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10</v>
       </c>
@@ -28689,7 +28688,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>11</v>
       </c>
@@ -28730,7 +28729,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>12</v>
       </c>
@@ -28771,7 +28770,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>13</v>
       </c>
@@ -28812,7 +28811,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>14</v>
       </c>
@@ -28853,7 +28852,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>15</v>
       </c>
@@ -28894,7 +28893,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>16</v>
       </c>
@@ -28935,7 +28934,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>17</v>
       </c>
@@ -28976,7 +28975,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>18</v>
       </c>
@@ -29017,7 +29016,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>19</v>
       </c>
@@ -29058,7 +29057,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>20</v>
       </c>
@@ -29099,7 +29098,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>21</v>
       </c>
@@ -29140,7 +29139,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>22</v>
       </c>
@@ -29181,7 +29180,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>23</v>
       </c>
@@ -29222,7 +29221,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>24</v>
       </c>
@@ -29263,7 +29262,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>25</v>
       </c>
@@ -29304,7 +29303,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>26</v>
       </c>
@@ -29345,7 +29344,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>27</v>
       </c>
@@ -29386,7 +29385,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>28</v>
       </c>
@@ -29427,7 +29426,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>29</v>
       </c>
@@ -29468,7 +29467,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>30</v>
       </c>
@@ -29509,7 +29508,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>31</v>
       </c>
@@ -29550,7 +29549,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32</v>
       </c>
@@ -29585,7 +29584,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>33</v>
       </c>
@@ -29626,7 +29625,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34</v>
       </c>
@@ -29667,7 +29666,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>35</v>
       </c>
@@ -29705,7 +29704,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>36</v>
       </c>
@@ -29743,7 +29742,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>37</v>
       </c>
@@ -29784,7 +29783,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
@@ -29825,7 +29824,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>39</v>
       </c>
@@ -29866,7 +29865,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40</v>
       </c>
@@ -29907,7 +29906,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41</v>
       </c>
@@ -29945,7 +29944,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>42</v>
       </c>
@@ -29983,7 +29982,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>43</v>
       </c>
@@ -30021,7 +30020,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>44</v>
       </c>
@@ -30059,7 +30058,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>45</v>
       </c>
@@ -30100,7 +30099,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>46</v>
       </c>
@@ -30141,7 +30140,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>47</v>
       </c>
@@ -30179,7 +30178,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>48</v>
       </c>
@@ -30217,7 +30216,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>49</v>
       </c>
@@ -30255,7 +30254,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>50</v>
       </c>
@@ -30293,7 +30292,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>51</v>
       </c>
@@ -30331,7 +30330,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>52</v>
       </c>
@@ -30369,7 +30368,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>53</v>
       </c>
@@ -30410,7 +30409,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>54</v>
       </c>
@@ -30448,7 +30447,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>55</v>
       </c>
@@ -30486,7 +30485,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>56</v>
       </c>
@@ -30524,7 +30523,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>57</v>
       </c>
@@ -30565,7 +30564,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>58</v>
       </c>
@@ -30600,7 +30599,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>59</v>
       </c>
@@ -30641,7 +30640,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>60</v>
       </c>
@@ -30679,7 +30678,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>61</v>
       </c>
@@ -30720,7 +30719,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>62</v>
       </c>
@@ -30758,7 +30757,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>63</v>
       </c>
@@ -30796,7 +30795,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>64</v>
       </c>
@@ -30834,7 +30833,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>65</v>
       </c>
@@ -30872,7 +30871,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>66</v>
       </c>
@@ -30910,7 +30909,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>67</v>
       </c>
@@ -30948,7 +30947,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>68</v>
       </c>
@@ -30986,7 +30985,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>69</v>
       </c>
@@ -31027,7 +31026,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>70</v>
       </c>
@@ -31065,7 +31064,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>71</v>
       </c>
@@ -31106,7 +31105,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>72</v>
       </c>
@@ -31147,7 +31146,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>73</v>
       </c>
@@ -31188,7 +31187,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>74</v>
       </c>
@@ -31229,7 +31228,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>75</v>
       </c>
@@ -31267,7 +31266,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>76</v>
       </c>
@@ -31308,7 +31307,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>77</v>
       </c>
@@ -31349,7 +31348,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>78</v>
       </c>
@@ -31390,7 +31389,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>79</v>
       </c>
@@ -31431,7 +31430,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>80</v>
       </c>
@@ -31469,7 +31468,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>81</v>
       </c>
@@ -31510,7 +31509,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>82</v>
       </c>
@@ -31551,7 +31550,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>83</v>
       </c>
@@ -31592,7 +31591,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>84</v>
       </c>
@@ -31633,7 +31632,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>85</v>
       </c>
@@ -31671,7 +31670,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>86</v>
       </c>
@@ -31712,7 +31711,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>87</v>
       </c>
@@ -31747,7 +31746,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>88</v>
       </c>
@@ -31788,7 +31787,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -31816,7 +31815,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>90</v>
       </c>
@@ -31857,7 +31856,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>91</v>
       </c>
@@ -31895,7 +31894,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>92</v>
       </c>
@@ -31936,7 +31935,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>93</v>
       </c>
@@ -31977,7 +31976,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>94</v>
       </c>
@@ -32018,7 +32017,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>95</v>
       </c>
@@ -32059,7 +32058,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>96</v>
       </c>
@@ -32100,7 +32099,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>97</v>
       </c>
@@ -32141,7 +32140,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>98</v>
       </c>
@@ -32182,7 +32181,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -32214,7 +32213,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -32255,7 +32254,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -32296,7 +32295,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -32337,7 +32336,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -32378,7 +32377,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>104</v>
       </c>
@@ -32419,7 +32418,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>105</v>
       </c>
@@ -32460,7 +32459,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>106</v>
       </c>
@@ -32498,7 +32497,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -32526,7 +32525,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -32554,7 +32553,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>109</v>
       </c>
@@ -32592,7 +32591,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>110</v>
       </c>
@@ -32630,7 +32629,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>111</v>
       </c>
@@ -32671,7 +32670,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>112</v>
       </c>
@@ -32712,7 +32711,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>113</v>
       </c>
@@ -32753,7 +32752,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>114</v>
       </c>
@@ -32793,7 +32792,7 @@
       </c>
       <c r="N114" s="5"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>115</v>
       </c>
@@ -32831,7 +32830,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>116</v>
       </c>
@@ -32869,7 +32868,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>117</v>
       </c>
@@ -32910,7 +32909,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>118</v>
       </c>
@@ -32951,7 +32950,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>119</v>
       </c>
@@ -32986,7 +32985,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>120</v>
       </c>
@@ -33021,7 +33020,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>121</v>
       </c>
@@ -33062,7 +33061,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>122</v>
       </c>
@@ -33100,7 +33099,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>123</v>
       </c>
@@ -33135,7 +33134,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>124</v>
       </c>
@@ -33173,7 +33172,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>125</v>
       </c>
@@ -33214,7 +33213,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>126</v>
       </c>
@@ -33255,7 +33254,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>127</v>
       </c>
@@ -33296,7 +33295,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>128</v>
       </c>
@@ -33337,7 +33336,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>129</v>
       </c>
@@ -33378,7 +33377,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>130</v>
       </c>
@@ -33419,7 +33418,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>131</v>
       </c>
@@ -33460,7 +33459,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>132</v>
       </c>
@@ -33501,7 +33500,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>133</v>
       </c>
@@ -33542,7 +33541,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>134</v>
       </c>
@@ -33583,7 +33582,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>135</v>
       </c>
@@ -33621,7 +33620,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>136</v>
       </c>
@@ -33662,7 +33661,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>137</v>
       </c>
@@ -33700,7 +33699,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>138</v>
       </c>
@@ -33741,7 +33740,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>139</v>
       </c>
@@ -33782,7 +33781,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>140</v>
       </c>
@@ -33823,7 +33822,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>141</v>
       </c>
@@ -33864,7 +33863,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>142</v>
       </c>
@@ -33905,7 +33904,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>143</v>
       </c>
@@ -33943,7 +33942,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>144</v>
       </c>
@@ -33984,7 +33983,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>145</v>
       </c>
@@ -34022,7 +34021,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>146</v>
       </c>
@@ -34064,7 +34063,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>147</v>
       </c>
@@ -34108,7 +34107,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>148</v>
       </c>
@@ -34143,7 +34142,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>149</v>
       </c>
@@ -34178,7 +34177,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>150</v>
       </c>
@@ -34219,7 +34218,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>151</v>
       </c>
@@ -34260,7 +34259,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>152</v>
       </c>
@@ -34295,7 +34294,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>153</v>
       </c>
@@ -34336,7 +34335,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>154</v>
       </c>
@@ -34377,7 +34376,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>155</v>
       </c>
@@ -34418,7 +34417,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>156</v>
       </c>
@@ -34456,7 +34455,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>157</v>
       </c>
@@ -34497,7 +34496,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>158</v>
       </c>
@@ -34538,7 +34537,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>159</v>
       </c>
@@ -34579,7 +34578,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>160</v>
       </c>
@@ -34620,7 +34619,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>161</v>
       </c>
@@ -34662,7 +34661,7 @@
       </c>
       <c r="N161" s="5"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>162</v>
       </c>
@@ -34703,7 +34702,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>163</v>
       </c>
@@ -34744,7 +34743,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>164</v>
       </c>
@@ -34785,7 +34784,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>165</v>
       </c>
@@ -34826,7 +34825,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>166</v>
       </c>
@@ -34861,7 +34860,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>167</v>
       </c>
@@ -34896,7 +34895,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>168</v>
       </c>
@@ -34934,7 +34933,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>169</v>
       </c>
@@ -34975,7 +34974,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>170</v>
       </c>
@@ -35016,7 +35015,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>171</v>
       </c>
@@ -35054,7 +35053,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>172</v>
       </c>
@@ -35095,7 +35094,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>173</v>
       </c>
@@ -35130,7 +35129,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>174</v>
       </c>
@@ -35171,7 +35170,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>175</v>
       </c>
@@ -35212,7 +35211,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>176</v>
       </c>
@@ -35253,7 +35252,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>177</v>
       </c>
@@ -35294,7 +35293,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>178</v>
       </c>
@@ -35335,7 +35334,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>179</v>
       </c>
@@ -35376,7 +35375,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>180</v>
       </c>
@@ -35417,7 +35416,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -35447,7 +35446,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>182</v>
       </c>
@@ -35491,7 +35490,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>183</v>
       </c>
@@ -35535,7 +35534,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>184</v>
       </c>
@@ -35576,7 +35575,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>185</v>
       </c>
@@ -35617,7 +35616,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>186</v>
       </c>
@@ -35658,7 +35657,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>187</v>
       </c>
@@ -35699,7 +35698,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>188</v>
       </c>
@@ -35740,7 +35739,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>189</v>
       </c>
@@ -35781,7 +35780,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>190</v>
       </c>
@@ -35822,7 +35821,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>191</v>
       </c>
@@ -35863,7 +35862,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>192</v>
       </c>
@@ -35904,7 +35903,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>193</v>
       </c>
@@ -35942,7 +35941,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>194</v>
       </c>
@@ -35980,7 +35979,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>195</v>
       </c>
@@ -36021,7 +36020,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>196</v>
       </c>
@@ -36063,7 +36062,7 @@
       </c>
       <c r="N196" s="5"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>197</v>
       </c>
@@ -36104,7 +36103,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>198</v>
       </c>
@@ -36145,7 +36144,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>199</v>
       </c>
@@ -36186,7 +36185,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>200</v>
       </c>
@@ -36227,7 +36226,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>201</v>
       </c>
@@ -36268,7 +36267,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>202</v>
       </c>
@@ -36309,7 +36308,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>203</v>
       </c>
@@ -36349,7 +36348,7 @@
       </c>
       <c r="N203" s="5"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>204</v>
       </c>
@@ -36391,7 +36390,7 @@
       </c>
       <c r="N204" s="5"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>205</v>
       </c>
@@ -36432,7 +36431,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>206</v>
       </c>
@@ -36473,7 +36472,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>207</v>
       </c>
@@ -36514,7 +36513,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>208</v>
       </c>
@@ -36555,7 +36554,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>209</v>
       </c>
@@ -36593,7 +36592,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>210</v>
       </c>
@@ -36634,7 +36633,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>211</v>
       </c>
@@ -36675,7 +36674,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>212</v>
       </c>
@@ -36716,7 +36715,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>213</v>
       </c>
@@ -36757,7 +36756,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>214</v>
       </c>
@@ -36795,7 +36794,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>215</v>
       </c>
@@ -36837,7 +36836,7 @@
       </c>
       <c r="N215" s="5"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>216</v>
       </c>
@@ -36878,7 +36877,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>217</v>
       </c>
@@ -36916,7 +36915,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -36948,7 +36947,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>219</v>
       </c>
@@ -36989,7 +36988,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>220</v>
       </c>
@@ -37027,7 +37026,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>221</v>
       </c>
@@ -37068,7 +37067,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>222</v>
       </c>
@@ -37109,7 +37108,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>223</v>
       </c>
@@ -37150,7 +37149,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>224</v>
       </c>
@@ -37191,7 +37190,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>225</v>
       </c>
@@ -37232,7 +37231,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>226</v>
       </c>
@@ -37273,7 +37272,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>227</v>
       </c>
@@ -37314,7 +37313,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>228</v>
       </c>
@@ -37356,7 +37355,7 @@
       </c>
       <c r="N228" s="5"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>229</v>
       </c>
@@ -37397,7 +37396,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>230</v>
       </c>
@@ -37438,7 +37437,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>231</v>
       </c>
@@ -37479,7 +37478,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>232</v>
       </c>
@@ -37520,7 +37519,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>233</v>
       </c>
@@ -37561,7 +37560,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>234</v>
       </c>
@@ -37602,7 +37601,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>235</v>
       </c>
@@ -37643,7 +37642,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>236</v>
       </c>
@@ -37685,7 +37684,7 @@
       </c>
       <c r="N236" s="5"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>237</v>
       </c>
@@ -37726,7 +37725,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>238</v>
       </c>
@@ -37764,7 +37763,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>239</v>
       </c>
@@ -37805,7 +37804,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>240</v>
       </c>
@@ -37846,7 +37845,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>241</v>
       </c>
@@ -37888,7 +37887,7 @@
       </c>
       <c r="N241" s="5"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>242</v>
       </c>
@@ -37930,7 +37929,7 @@
       </c>
       <c r="N242" s="5"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>243</v>
       </c>
@@ -37971,7 +37970,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>244</v>
       </c>
@@ -38012,7 +38011,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>245</v>
       </c>
@@ -38053,7 +38052,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>246</v>
       </c>
@@ -38094,7 +38093,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>247</v>
       </c>
@@ -38132,7 +38131,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>248</v>
       </c>
@@ -38173,7 +38172,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>249</v>
       </c>
@@ -38214,7 +38213,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>250</v>
       </c>
@@ -38258,7 +38257,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -38288,7 +38287,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>252</v>
       </c>
@@ -38329,7 +38328,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>253</v>
       </c>
@@ -38370,7 +38369,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>254</v>
       </c>
@@ -38411,7 +38410,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>255</v>
       </c>
@@ -38452,7 +38451,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>256</v>
       </c>
@@ -38493,7 +38492,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>257</v>
       </c>
@@ -38535,7 +38534,7 @@
       </c>
       <c r="N257" s="5"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>258</v>
       </c>
@@ -38576,7 +38575,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>259</v>
       </c>
@@ -38618,7 +38617,7 @@
       </c>
       <c r="N259" s="5"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>260</v>
       </c>
@@ -38659,7 +38658,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>261</v>
       </c>
@@ -38700,7 +38699,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>262</v>
       </c>
@@ -38741,7 +38740,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>263</v>
       </c>
@@ -38782,7 +38781,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>264</v>
       </c>
@@ -38823,7 +38822,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>265</v>
       </c>
@@ -38864,7 +38863,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>266</v>
       </c>
@@ -38905,7 +38904,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>267</v>
       </c>
@@ -38946,7 +38945,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>268</v>
       </c>
@@ -38987,7 +38986,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>269</v>
       </c>
@@ -39028,7 +39027,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>270</v>
       </c>
@@ -39066,7 +39065,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -39098,7 +39097,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>272</v>
       </c>
@@ -39136,7 +39135,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>273</v>
       </c>
@@ -39174,7 +39173,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>274</v>
       </c>
@@ -39209,7 +39208,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>275</v>
       </c>
@@ -39250,7 +39249,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>276</v>
       </c>
@@ -39291,7 +39290,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>277</v>
       </c>
@@ -39332,7 +39331,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>278</v>
       </c>
@@ -39370,7 +39369,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>279</v>
       </c>
@@ -39408,7 +39407,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>280</v>
       </c>
@@ -39449,7 +39448,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>281</v>
       </c>
@@ -39490,7 +39489,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>282</v>
       </c>
@@ -39530,7 +39529,7 @@
       </c>
       <c r="N282" s="5"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>283</v>
       </c>
@@ -39571,7 +39570,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>284</v>
       </c>
@@ -39613,7 +39612,7 @@
       </c>
       <c r="N284" s="5"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>285</v>
       </c>
@@ -39651,7 +39650,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>286</v>
       </c>
@@ -39692,7 +39691,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>287</v>
       </c>
@@ -39733,7 +39732,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>288</v>
       </c>
@@ -39774,7 +39773,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>289</v>
       </c>
@@ -39815,7 +39814,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>290</v>
       </c>
@@ -39856,7 +39855,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>291</v>
       </c>
@@ -39897,7 +39896,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>292</v>
       </c>
@@ -39938,7 +39937,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>293</v>
       </c>
@@ -39979,7 +39978,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>294</v>
       </c>
@@ -40020,7 +40019,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>295</v>
       </c>
@@ -40061,7 +40060,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>296</v>
       </c>
@@ -40099,7 +40098,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>297</v>
       </c>
@@ -40140,7 +40139,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>298</v>
       </c>
@@ -40178,7 +40177,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>299</v>
       </c>
@@ -40219,7 +40218,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>300</v>
       </c>
@@ -40260,7 +40259,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>301</v>
       </c>
@@ -40298,7 +40297,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>302</v>
       </c>
@@ -40339,7 +40338,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>303</v>
       </c>
@@ -40380,7 +40379,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>304</v>
       </c>
@@ -40421,7 +40420,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>305</v>
       </c>
@@ -40462,7 +40461,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>306</v>
       </c>
@@ -40503,7 +40502,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>307</v>
       </c>
@@ -40544,7 +40543,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>308</v>
       </c>
@@ -40585,7 +40584,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>309</v>
       </c>
@@ -40626,7 +40625,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>310</v>
       </c>
@@ -40667,7 +40666,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>311</v>
       </c>
@@ -40708,7 +40707,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>312</v>
       </c>
@@ -40749,7 +40748,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>313</v>
       </c>
@@ -40784,7 +40783,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>314</v>
       </c>
@@ -40822,7 +40821,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>315</v>
       </c>
@@ -40863,7 +40862,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>316</v>
       </c>
@@ -40904,7 +40903,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>317</v>
       </c>
@@ -40939,7 +40938,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>318</v>
       </c>
@@ -40977,7 +40976,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>319</v>
       </c>
@@ -41018,7 +41017,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>320</v>
       </c>
@@ -41056,7 +41055,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>321</v>
       </c>
@@ -41097,7 +41096,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>322</v>
       </c>
@@ -41138,7 +41137,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>323</v>
       </c>
@@ -41179,7 +41178,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>324</v>
       </c>
@@ -41217,7 +41216,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>325</v>
       </c>
@@ -41258,7 +41257,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>326</v>
       </c>
@@ -41299,7 +41298,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>327</v>
       </c>
@@ -41341,7 +41340,7 @@
       </c>
       <c r="N327" s="5"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>331</v>
       </c>
@@ -41376,7 +41375,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>332</v>
       </c>
@@ -41417,7 +41416,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>335</v>
       </c>
@@ -41458,7 +41457,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>336</v>
       </c>
@@ -41493,7 +41492,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>337</v>
       </c>
@@ -41528,7 +41527,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>338</v>
       </c>
@@ -41566,7 +41565,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>339</v>
       </c>
@@ -41607,7 +41606,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>340</v>
       </c>
@@ -41645,7 +41644,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>341</v>
       </c>
@@ -41686,7 +41685,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>342</v>
       </c>
@@ -41727,7 +41726,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>343</v>
       </c>
@@ -41768,7 +41767,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>344</v>
       </c>
@@ -41809,7 +41808,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>345</v>
       </c>
@@ -41850,7 +41849,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>346</v>
       </c>
@@ -41888,7 +41887,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>347</v>
       </c>
@@ -41929,7 +41928,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>348</v>
       </c>
@@ -41970,7 +41969,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>349</v>
       </c>
@@ -42011,7 +42010,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>350</v>
       </c>
@@ -42052,7 +42051,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>351</v>
       </c>
@@ -42093,7 +42092,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>352</v>
       </c>
@@ -42131,7 +42130,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="5">
         <v>353</v>
       </c>
@@ -42173,7 +42172,7 @@
       </c>
       <c r="N348" s="5"/>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>354</v>
       </c>
@@ -42211,7 +42210,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>355</v>
       </c>
@@ -42252,7 +42251,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="5">
         <v>356</v>
       </c>
@@ -42294,7 +42293,7 @@
       </c>
       <c r="N351" s="5"/>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="5">
         <v>357</v>
       </c>
@@ -42336,7 +42335,7 @@
       </c>
       <c r="N352" s="5"/>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>358</v>
       </c>
@@ -42378,7 +42377,7 @@
       </c>
       <c r="N353" s="5"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>359</v>
       </c>
@@ -42419,7 +42418,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>360</v>
       </c>
@@ -42460,7 +42459,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>361</v>
       </c>
@@ -42501,7 +42500,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>362</v>
       </c>
@@ -42542,7 +42541,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>363</v>
       </c>
@@ -42583,7 +42582,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359" s="5">
         <v>364</v>
       </c>
@@ -42627,7 +42626,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360" s="5">
         <v>365</v>
       </c>
@@ -42671,7 +42670,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" s="5">
         <v>366</v>
       </c>
@@ -42715,7 +42714,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" s="5">
         <v>367</v>
       </c>
@@ -42759,7 +42758,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>368</v>
       </c>
@@ -42800,7 +42799,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>369</v>
       </c>
@@ -42841,7 +42840,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>370</v>
       </c>
@@ -42882,7 +42881,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>371</v>
       </c>
@@ -42923,7 +42922,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>372</v>
       </c>
@@ -42964,7 +42963,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>373</v>
       </c>
@@ -43002,7 +43001,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>374</v>
       </c>
@@ -43043,7 +43042,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>375</v>
       </c>
@@ -43084,7 +43083,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>376</v>
       </c>
@@ -43125,7 +43124,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>377</v>
       </c>
@@ -43166,7 +43165,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>378</v>
       </c>
@@ -43207,7 +43206,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>379</v>
       </c>
@@ -43248,7 +43247,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>380</v>
       </c>
@@ -43289,7 +43288,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>381</v>
       </c>
@@ -43330,7 +43329,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>382</v>
       </c>
@@ -43371,7 +43370,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>383</v>
       </c>
@@ -43412,7 +43411,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" s="5">
         <v>384</v>
       </c>
@@ -43456,7 +43455,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" s="5">
         <v>385</v>
       </c>
@@ -43500,7 +43499,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" s="5">
         <v>386</v>
       </c>
@@ -43544,7 +43543,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>387</v>
       </c>
@@ -43585,7 +43584,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>388</v>
       </c>
@@ -43626,7 +43625,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>389</v>
       </c>
@@ -43667,7 +43666,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>390</v>
       </c>
@@ -43705,7 +43704,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>391</v>
       </c>
@@ -43743,7 +43742,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" s="6">
         <v>392</v>
       </c>
@@ -43775,7 +43774,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" s="5">
         <v>393</v>
       </c>
@@ -43817,7 +43816,7 @@
       </c>
       <c r="N388" s="5"/>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" s="5">
         <v>394</v>
       </c>
@@ -43859,7 +43858,7 @@
       </c>
       <c r="N389" s="5"/>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" s="5">
         <v>395</v>
       </c>
@@ -43901,7 +43900,7 @@
       </c>
       <c r="N390" s="5"/>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" s="5">
         <v>396</v>
       </c>
@@ -43943,7 +43942,7 @@
       </c>
       <c r="N391" s="5"/>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" s="5">
         <v>397</v>
       </c>
@@ -43985,7 +43984,7 @@
       </c>
       <c r="N392" s="5"/>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>398</v>
       </c>
@@ -44026,7 +44025,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>399</v>
       </c>
@@ -44067,7 +44066,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>400</v>
       </c>
@@ -44108,7 +44107,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>401</v>
       </c>
@@ -44149,7 +44148,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>402</v>
       </c>
@@ -44190,7 +44189,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>403</v>
       </c>
@@ -44231,7 +44230,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>404</v>
       </c>
@@ -44272,7 +44271,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>405</v>
       </c>
@@ -44313,7 +44312,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401" s="5">
         <v>406</v>
       </c>
@@ -44355,7 +44354,7 @@
       </c>
       <c r="N401" s="5"/>
     </row>
-    <row r="402" spans="1:14">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>407</v>
       </c>
@@ -44396,7 +44395,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="403" spans="1:14">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>408</v>
       </c>
@@ -44437,7 +44436,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="404" spans="1:14">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>409</v>
       </c>
@@ -44475,7 +44474,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="405" spans="1:14">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>410</v>
       </c>
@@ -44516,7 +44515,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="406" spans="1:14">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>411</v>
       </c>
@@ -44557,7 +44556,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="407" spans="1:14">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>412</v>
       </c>
@@ -44598,7 +44597,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="408" spans="1:14">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>413</v>
       </c>
@@ -44639,7 +44638,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="409" spans="1:14">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>414</v>
       </c>
@@ -44680,7 +44679,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="410" spans="1:14">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>415</v>
       </c>
@@ -44721,7 +44720,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="411" spans="1:14">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>416</v>
       </c>
@@ -44762,7 +44761,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="412" spans="1:14">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>417</v>
       </c>
@@ -44803,7 +44802,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="413" spans="1:14">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>418</v>
       </c>
@@ -44844,7 +44843,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="414" spans="1:14">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414" s="5">
         <v>419</v>
       </c>
@@ -44886,7 +44885,7 @@
       </c>
       <c r="N414" s="5"/>
     </row>
-    <row r="415" spans="1:14">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>420</v>
       </c>
@@ -44924,7 +44923,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="416" spans="1:14">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>421</v>
       </c>
@@ -44965,7 +44964,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>422</v>
       </c>
@@ -45006,7 +45005,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>423</v>
       </c>
@@ -45047,7 +45046,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>424</v>
       </c>
@@ -45088,7 +45087,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="420" spans="1:14">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>425</v>
       </c>
@@ -45126,7 +45125,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="421" spans="1:14">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>426</v>
       </c>
@@ -45167,7 +45166,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>427</v>
       </c>
@@ -45205,7 +45204,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>428</v>
       </c>
@@ -45246,7 +45245,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>429</v>
       </c>
@@ -45287,7 +45286,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="425" spans="1:14">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425" s="6">
         <v>430</v>
       </c>
@@ -45317,7 +45316,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="426" spans="1:14">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>431</v>
       </c>
@@ -45358,7 +45357,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>432</v>
       </c>
@@ -45396,7 +45395,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="428" spans="1:14">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>433</v>
       </c>
@@ -45437,7 +45436,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="429" spans="1:14">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>434</v>
       </c>
@@ -45475,7 +45474,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="430" spans="1:14">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>435</v>
       </c>
@@ -45516,7 +45515,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>436</v>
       </c>
@@ -45551,7 +45550,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>437</v>
       </c>
@@ -45589,7 +45588,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>438</v>
       </c>
@@ -45627,7 +45626,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>439</v>
       </c>
@@ -45668,7 +45667,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435" s="6">
         <v>440</v>
       </c>
@@ -45700,7 +45699,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>441</v>
       </c>
@@ -45741,7 +45740,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>442</v>
       </c>
@@ -45782,7 +45781,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="438" spans="1:14">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>443</v>
       </c>
@@ -45820,7 +45819,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="439" spans="1:14">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>444</v>
       </c>
@@ -45861,7 +45860,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="440" spans="1:14">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>445</v>
       </c>
@@ -45899,7 +45898,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>446</v>
       </c>
@@ -45940,7 +45939,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442" s="5">
         <v>447</v>
       </c>
@@ -45982,7 +45981,7 @@
       </c>
       <c r="N442" s="5"/>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>448</v>
       </c>
@@ -46023,7 +46022,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>449</v>
       </c>
@@ -46064,7 +46063,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>450</v>
       </c>
@@ -46105,7 +46104,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>451</v>
       </c>
@@ -46146,7 +46145,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>452</v>
       </c>
@@ -46187,7 +46186,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>453</v>
       </c>
@@ -46228,7 +46227,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="449" spans="1:14">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>454</v>
       </c>
@@ -46269,7 +46268,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="450" spans="1:14">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450" s="5">
         <v>455</v>
       </c>
@@ -46311,7 +46310,7 @@
       </c>
       <c r="N450" s="5"/>
     </row>
-    <row r="451" spans="1:14">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>456</v>
       </c>
@@ -46352,7 +46351,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="452" spans="1:14">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>457</v>
       </c>
@@ -46393,7 +46392,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="453" spans="1:14">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>458</v>
       </c>
@@ -46431,7 +46430,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="454" spans="1:14">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>459</v>
       </c>
@@ -46472,7 +46471,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="455" spans="1:14">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>460</v>
       </c>
@@ -46510,7 +46509,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="456" spans="1:14">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>461</v>
       </c>
@@ -46551,7 +46550,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="457" spans="1:14">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>462</v>
       </c>
@@ -46592,7 +46591,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="458" spans="1:14">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>463</v>
       </c>
@@ -46633,7 +46632,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="459" spans="1:14">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>464</v>
       </c>
@@ -46674,7 +46673,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="460" spans="1:14">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>465</v>
       </c>
@@ -46715,7 +46714,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="461" spans="1:14">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>466</v>
       </c>
@@ -46756,7 +46755,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="462" spans="1:14">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>467</v>
       </c>
@@ -46797,7 +46796,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="463" spans="1:14">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A463" s="5">
         <v>468</v>
       </c>
@@ -46841,7 +46840,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="464" spans="1:14">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>469</v>
       </c>
@@ -46882,7 +46881,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="465" spans="1:14">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>470</v>
       </c>
@@ -46923,7 +46922,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="466" spans="1:14">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>471</v>
       </c>
@@ -46964,7 +46963,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="467" spans="1:14">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>472</v>
       </c>
@@ -47005,7 +47004,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="468" spans="1:14">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>473</v>
       </c>
@@ -47046,7 +47045,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="469" spans="1:14">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469" s="5">
         <v>474</v>
       </c>
@@ -47090,7 +47089,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="470" spans="1:14">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>475</v>
       </c>
@@ -47131,7 +47130,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="471" spans="1:14">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>476</v>
       </c>
@@ -47172,7 +47171,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="472" spans="1:14">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>477</v>
       </c>
@@ -47210,7 +47209,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="473" spans="1:14">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>478</v>
       </c>
@@ -47248,7 +47247,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="474" spans="1:14">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>479</v>
       </c>
@@ -47290,7 +47289,7 @@
       </c>
       <c r="N474" s="5"/>
     </row>
-    <row r="475" spans="1:14">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>480</v>
       </c>
@@ -47331,7 +47330,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="476" spans="1:14">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>481</v>
       </c>
@@ -47372,7 +47371,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="477" spans="1:14">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>482</v>
       </c>
@@ -47413,7 +47412,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="478" spans="1:14">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>483</v>
       </c>
@@ -47454,7 +47453,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="479" spans="1:14">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>484</v>
       </c>
@@ -47498,7 +47497,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="480" spans="1:14">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480" s="5">
         <v>485</v>
       </c>
@@ -47542,7 +47541,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>486</v>
       </c>
@@ -47583,7 +47582,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>487</v>
       </c>
@@ -47624,7 +47623,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>488</v>
       </c>
@@ -47665,7 +47664,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>489</v>
       </c>
@@ -47706,7 +47705,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="485" spans="1:14">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>490</v>
       </c>
@@ -47747,7 +47746,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="486" spans="1:14">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>491</v>
       </c>
@@ -47788,7 +47787,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="487" spans="1:14">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>492</v>
       </c>
@@ -47829,7 +47828,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="488" spans="1:14">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>493</v>
       </c>
@@ -47870,7 +47869,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="489" spans="1:14">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489" s="5">
         <v>494</v>
       </c>
@@ -47914,7 +47913,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="490" spans="1:14">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>495</v>
       </c>
@@ -47955,7 +47954,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="491" spans="1:14">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>496</v>
       </c>
@@ -47996,7 +47995,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492" s="5">
         <v>497</v>
       </c>
@@ -48038,7 +48037,7 @@
       </c>
       <c r="N492" s="5"/>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>498</v>
       </c>
@@ -48079,7 +48078,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>499</v>
       </c>
@@ -48120,7 +48119,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="495" spans="1:14">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>500</v>
       </c>
@@ -48161,7 +48160,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="496" spans="1:14">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496" s="5">
         <v>501</v>
       </c>
@@ -48203,7 +48202,7 @@
       </c>
       <c r="N496" s="5"/>
     </row>
-    <row r="497" spans="1:14">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>502</v>
       </c>
@@ -48244,7 +48243,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="498" spans="1:14">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498" s="5">
         <v>503</v>
       </c>
@@ -48286,7 +48285,7 @@
       </c>
       <c r="N498" s="5"/>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499" s="5">
         <v>504</v>
       </c>
@@ -48328,7 +48327,7 @@
       </c>
       <c r="N499" s="5"/>
     </row>
-    <row r="500" spans="1:14">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>505</v>
       </c>
@@ -48369,7 +48368,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="501" spans="1:14">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>506</v>
       </c>
@@ -48410,7 +48409,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="502" spans="1:14">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>507</v>
       </c>
@@ -48448,7 +48447,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="503" spans="1:14">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>508</v>
       </c>
@@ -48486,7 +48485,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="504" spans="1:14">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>509</v>
       </c>
@@ -48524,7 +48523,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="505" spans="1:14">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>510</v>
       </c>
@@ -48562,7 +48561,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="506" spans="1:14">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>511</v>
       </c>
@@ -48600,7 +48599,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="507" spans="1:14">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507" s="5">
         <v>512</v>
       </c>
@@ -48642,7 +48641,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508" s="5">
         <v>513</v>
       </c>
@@ -48684,7 +48683,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>514</v>
       </c>
@@ -48725,7 +48724,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="510" spans="1:14">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>515</v>
       </c>
@@ -48766,7 +48765,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="511" spans="1:14">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>516</v>
       </c>
@@ -48807,7 +48806,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="512" spans="1:14">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>517</v>
       </c>
@@ -48854,14 +48853,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49125,22 +49122,58 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C86AFB-6064-0942-BFC0-E69E4CAC4EDC}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E379BD54-B3E4-3449-B919-CE2360CCF216}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10560" uniqueCount="2248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10559" uniqueCount="2248">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27235,8 +27235,8 @@
       <c r="H494" t="s">
         <v>1342</v>
       </c>
-      <c r="J494" t="s">
-        <v>1200</v>
+      <c r="J494">
+        <v>2017</v>
       </c>
       <c r="K494">
         <v>75</v>
@@ -48853,15 +48853,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49121,6 +49112,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -49133,14 +49133,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49160,20 +49152,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAE9C5AF-E583-4B95-949E-B429E9C4F666}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B60B63D-1202-4B11-BC0A-6F56B2C7201F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15861,7 +15861,7 @@
         <v>75</v>
       </c>
       <c r="L211">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="P211" s="7">
         <v>46181</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B60B63D-1202-4B11-BC0A-6F56B2C7201F}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{365549B2-4DE3-4645-ACB6-25A3C35E4E39}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6792,7 +6792,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -6875,8 +6875,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7394,7 +7396,8 @@
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="16" width="12" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12" style="8" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
@@ -7445,7 +7448,7 @@
       <c r="O1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="7" t="s">
         <v>52</v>
       </c>
       <c r="Q1" s="2" t="s">
@@ -7492,7 +7495,7 @@
       <c r="M2">
         <v>191</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7530,7 +7533,7 @@
       <c r="M3">
         <v>7</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7571,7 +7574,7 @@
       <c r="M4">
         <v>564</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R4" t="s">
@@ -7615,7 +7618,7 @@
       <c r="M5">
         <v>411</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7656,7 +7659,7 @@
       <c r="M6">
         <v>7</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R6" t="s">
@@ -7700,7 +7703,7 @@
       <c r="M7">
         <v>10</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R7" t="s">
@@ -7741,7 +7744,7 @@
       <c r="M8">
         <v>153</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7779,7 +7782,7 @@
       <c r="M9">
         <v>381</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7820,7 +7823,7 @@
       <c r="M10">
         <v>13</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7861,7 +7864,7 @@
       <c r="M11">
         <v>29</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7902,7 +7905,7 @@
       <c r="M12">
         <v>37</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7943,7 +7946,7 @@
       <c r="M13">
         <v>13</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R13" t="s">
@@ -7987,7 +7990,7 @@
       <c r="M14">
         <v>5</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R14" t="s">
@@ -8028,7 +8031,7 @@
       <c r="M15">
         <v>33</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8066,7 +8069,7 @@
       <c r="M16">
         <v>6</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R16" t="s">
@@ -8107,7 +8110,7 @@
       <c r="M17">
         <v>110</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P17" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R17" t="s">
@@ -8148,7 +8151,7 @@
       <c r="M18">
         <v>30</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R18" t="s">
@@ -8189,7 +8192,7 @@
       <c r="M19">
         <v>37</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8227,7 +8230,7 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8265,7 +8268,7 @@
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8303,7 +8306,7 @@
       <c r="M22">
         <v>233</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P22" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8344,7 +8347,7 @@
       <c r="M23">
         <v>93</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P23" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8382,7 +8385,7 @@
       <c r="M24">
         <v>45</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8420,7 +8423,7 @@
       <c r="M25">
         <v>60</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8458,7 +8461,7 @@
       <c r="M26">
         <v>35</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P26" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8499,7 +8502,7 @@
       <c r="M27">
         <v>43</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P27" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8540,7 +8543,7 @@
       <c r="M28">
         <v>164</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P28" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8581,7 +8584,7 @@
       <c r="M29">
         <v>72</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8622,7 +8625,7 @@
       <c r="M30">
         <v>596</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8663,7 +8666,7 @@
       <c r="M31">
         <v>881</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8698,7 +8701,7 @@
       <c r="L32">
         <v>5.25</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8739,7 +8742,7 @@
       <c r="M33">
         <v>497</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P33" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8780,7 +8783,7 @@
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P34" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8818,7 +8821,7 @@
       <c r="L35">
         <v>16.649999999999999</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P35" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8856,7 +8859,7 @@
       <c r="M36">
         <v>117</v>
       </c>
-      <c r="P36" t="s">
+      <c r="P36" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8897,7 +8900,7 @@
       <c r="M37">
         <v>27</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8941,7 +8944,7 @@
       <c r="M38">
         <v>102</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P38" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -8982,7 +8985,7 @@
       <c r="M39">
         <v>63</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P39" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9026,7 +9029,7 @@
       <c r="M40">
         <v>126</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9067,7 +9070,7 @@
       <c r="M41">
         <v>216</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9105,7 +9108,7 @@
       <c r="M42">
         <v>72</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9143,7 +9146,7 @@
       <c r="M43">
         <v>248</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9181,7 +9184,7 @@
       <c r="M44">
         <v>138</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9222,7 +9225,7 @@
       <c r="M45">
         <v>332</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9263,7 +9266,7 @@
       <c r="M46">
         <v>346</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9301,7 +9304,7 @@
       <c r="M47">
         <v>180</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9342,7 +9345,7 @@
       <c r="M48">
         <v>257</v>
       </c>
-      <c r="P48" t="s">
+      <c r="P48" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9380,7 +9383,7 @@
       <c r="M49">
         <v>48</v>
       </c>
-      <c r="P49" t="s">
+      <c r="P49" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9418,7 +9421,7 @@
       <c r="M50">
         <v>15</v>
       </c>
-      <c r="P50" t="s">
+      <c r="P50" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9456,7 +9459,7 @@
       <c r="M51">
         <v>92</v>
       </c>
-      <c r="P51" t="s">
+      <c r="P51" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9494,7 +9497,7 @@
       <c r="M52">
         <v>9</v>
       </c>
-      <c r="P52" t="s">
+      <c r="P52" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9538,7 +9541,7 @@
       <c r="M53">
         <v>902</v>
       </c>
-      <c r="P53" t="s">
+      <c r="P53" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9576,7 +9579,7 @@
       <c r="M54">
         <v>87</v>
       </c>
-      <c r="P54" t="s">
+      <c r="P54" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9617,7 +9620,7 @@
       <c r="M55">
         <v>46</v>
       </c>
-      <c r="P55" t="s">
+      <c r="P55" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9655,7 +9658,7 @@
       <c r="M56">
         <v>45</v>
       </c>
-      <c r="P56" t="s">
+      <c r="P56" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9696,7 +9699,7 @@
       <c r="M57">
         <v>0</v>
       </c>
-      <c r="P57" t="s">
+      <c r="P57" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9731,7 +9734,7 @@
       <c r="L58">
         <v>31</v>
       </c>
-      <c r="P58" t="s">
+      <c r="P58" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9772,7 +9775,7 @@
       <c r="M59">
         <v>165</v>
       </c>
-      <c r="P59" t="s">
+      <c r="P59" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9810,7 +9813,7 @@
       <c r="M60">
         <v>162</v>
       </c>
-      <c r="P60" t="s">
+      <c r="P60" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9854,7 +9857,7 @@
       <c r="M61">
         <v>0</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P61" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9892,7 +9895,7 @@
       <c r="M62">
         <v>702</v>
       </c>
-      <c r="P62" t="s">
+      <c r="P62" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9930,7 +9933,7 @@
       <c r="M63">
         <v>12</v>
       </c>
-      <c r="P63" t="s">
+      <c r="P63" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9968,7 +9971,7 @@
       <c r="M64">
         <v>36</v>
       </c>
-      <c r="P64" t="s">
+      <c r="P64" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10006,7 +10009,7 @@
       <c r="M65">
         <v>69</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P65" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10044,7 +10047,7 @@
       <c r="M66">
         <v>0</v>
       </c>
-      <c r="P66" t="s">
+      <c r="P66" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10082,7 +10085,7 @@
       <c r="M67">
         <v>213</v>
       </c>
-      <c r="P67" t="s">
+      <c r="P67" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10120,7 +10123,7 @@
       <c r="M68">
         <v>57</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10161,7 +10164,7 @@
       <c r="M69">
         <v>102</v>
       </c>
-      <c r="P69" t="s">
+      <c r="P69" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10205,7 +10208,7 @@
       <c r="M70">
         <v>0</v>
       </c>
-      <c r="P70" t="s">
+      <c r="P70" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10246,7 +10249,7 @@
       <c r="M71">
         <v>15</v>
       </c>
-      <c r="P71" t="s">
+      <c r="P71" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10284,7 +10287,7 @@
       <c r="M72">
         <v>210</v>
       </c>
-      <c r="P72" t="s">
+      <c r="P72" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10322,7 +10325,7 @@
       <c r="M73">
         <v>114</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P73" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10360,7 +10363,7 @@
       <c r="M74">
         <v>264</v>
       </c>
-      <c r="P74" t="s">
+      <c r="P74" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10395,7 +10398,7 @@
       <c r="M75">
         <v>828</v>
       </c>
-      <c r="P75" t="s">
+      <c r="P75" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10433,7 +10436,7 @@
       <c r="M76">
         <v>6122</v>
       </c>
-      <c r="P76" t="s">
+      <c r="P76" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10474,7 +10477,7 @@
       <c r="M77">
         <v>726</v>
       </c>
-      <c r="P77" t="s">
+      <c r="P77" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10512,7 +10515,7 @@
       <c r="M78">
         <v>310</v>
       </c>
-      <c r="P78" t="s">
+      <c r="P78" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10550,7 +10553,7 @@
       <c r="M79">
         <v>81</v>
       </c>
-      <c r="P79" t="s">
+      <c r="P79" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10588,7 +10591,7 @@
       <c r="L80">
         <v>8</v>
       </c>
-      <c r="P80" t="s">
+      <c r="P80" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10626,7 +10629,7 @@
       <c r="M81">
         <v>237</v>
       </c>
-      <c r="P81" t="s">
+      <c r="P81" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10667,7 +10670,7 @@
       <c r="M82">
         <v>581</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P82" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10705,7 +10708,7 @@
       <c r="M83">
         <v>9</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10743,7 +10746,7 @@
       <c r="M84">
         <v>6</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10778,7 +10781,7 @@
       <c r="M85">
         <v>6</v>
       </c>
-      <c r="P85" t="s">
+      <c r="P85" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10816,7 +10819,7 @@
       <c r="M86">
         <v>902</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10848,7 +10851,7 @@
       <c r="L87">
         <v>13.85</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P87" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10886,7 +10889,7 @@
       <c r="M88">
         <v>780</v>
       </c>
-      <c r="P88" t="s">
+      <c r="P88" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10921,7 +10924,7 @@
       <c r="M89">
         <v>342</v>
       </c>
-      <c r="P89" t="s">
+      <c r="P89" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10962,7 +10965,7 @@
       <c r="M90">
         <v>342</v>
       </c>
-      <c r="P90" t="s">
+      <c r="P90" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11003,7 +11006,7 @@
       <c r="M91">
         <v>342</v>
       </c>
-      <c r="P91" t="s">
+      <c r="P91" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11044,7 +11047,7 @@
       <c r="M92">
         <v>66</v>
       </c>
-      <c r="P92" t="s">
+      <c r="P92" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11085,7 +11088,7 @@
       <c r="M93">
         <v>12</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11126,7 +11129,7 @@
       <c r="M94">
         <v>108</v>
       </c>
-      <c r="P94" t="s">
+      <c r="P94" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11170,7 +11173,7 @@
       <c r="M95">
         <v>856</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P95" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11211,7 +11214,7 @@
       <c r="M96">
         <v>132</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P96" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11252,7 +11255,7 @@
       <c r="M97">
         <v>120</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P97" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11293,7 +11296,7 @@
       <c r="M98">
         <v>187</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P98" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11334,7 +11337,7 @@
       <c r="M99">
         <v>36</v>
       </c>
-      <c r="P99" t="s">
+      <c r="P99" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11375,7 +11378,7 @@
       <c r="M100">
         <v>0</v>
       </c>
-      <c r="P100" t="s">
+      <c r="P100" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11416,7 +11419,7 @@
       <c r="M101">
         <v>156</v>
       </c>
-      <c r="P101" t="s">
+      <c r="P101" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11457,7 +11460,7 @@
       <c r="M102">
         <v>28</v>
       </c>
-      <c r="P102" t="s">
+      <c r="P102" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11498,7 +11501,7 @@
       <c r="M103">
         <v>206</v>
       </c>
-      <c r="P103" t="s">
+      <c r="P103" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11539,7 +11542,7 @@
       <c r="M104">
         <v>63</v>
       </c>
-      <c r="P104" t="s">
+      <c r="P104" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11580,7 +11583,7 @@
       <c r="M105">
         <v>78</v>
       </c>
-      <c r="P105" t="s">
+      <c r="P105" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11618,7 +11621,7 @@
       <c r="M106">
         <v>36</v>
       </c>
-      <c r="P106" t="s">
+      <c r="P106" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11653,7 +11656,7 @@
       <c r="L107">
         <v>10.65</v>
       </c>
-      <c r="P107" t="s">
+      <c r="P107" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11688,7 +11691,7 @@
       <c r="L108">
         <v>11.95</v>
       </c>
-      <c r="P108" t="s">
+      <c r="P108" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11726,7 +11729,7 @@
       <c r="M109">
         <v>152</v>
       </c>
-      <c r="P109" t="s">
+      <c r="P109" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11764,7 +11767,7 @@
       <c r="M110">
         <v>108</v>
       </c>
-      <c r="P110" t="s">
+      <c r="P110" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11808,7 +11811,7 @@
       <c r="M111">
         <v>0</v>
       </c>
-      <c r="P111" t="s">
+      <c r="P111" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11849,7 +11852,7 @@
       <c r="M112">
         <v>138</v>
       </c>
-      <c r="P112" t="s">
+      <c r="P112" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11893,7 +11896,7 @@
       <c r="M113">
         <v>0</v>
       </c>
-      <c r="P113" t="s">
+      <c r="P113" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11931,7 +11934,7 @@
       <c r="M114">
         <v>87</v>
       </c>
-      <c r="P114" t="s">
+      <c r="P114" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -11969,7 +11972,7 @@
       <c r="M115">
         <v>0</v>
       </c>
-      <c r="P115" t="s">
+      <c r="P115" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12007,7 +12010,7 @@
       <c r="M116">
         <v>36</v>
       </c>
-      <c r="P116" t="s">
+      <c r="P116" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12051,7 +12054,7 @@
       <c r="M117">
         <v>0</v>
       </c>
-      <c r="P117" t="s">
+      <c r="P117" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12095,7 +12098,7 @@
       <c r="M118">
         <v>0</v>
       </c>
-      <c r="P118" t="s">
+      <c r="P118" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12130,7 +12133,7 @@
       <c r="L119">
         <v>12.5</v>
       </c>
-      <c r="P119" t="s">
+      <c r="P119" s="8" t="s">
         <v>404</v>
       </c>
     </row>
@@ -12165,7 +12168,7 @@
       <c r="L120">
         <v>14.9</v>
       </c>
-      <c r="P120" t="s">
+      <c r="P120" s="8" t="s">
         <v>407</v>
       </c>
     </row>
@@ -12206,7 +12209,7 @@
       <c r="M121">
         <v>68</v>
       </c>
-      <c r="P121" t="s">
+      <c r="P121" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12247,7 +12250,7 @@
       <c r="M122">
         <v>68</v>
       </c>
-      <c r="P122" t="s">
+      <c r="P122" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12285,7 +12288,7 @@
       <c r="M123">
         <v>68</v>
       </c>
-      <c r="P123" t="s">
+      <c r="P123" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12323,7 +12326,7 @@
       <c r="M124">
         <v>137</v>
       </c>
-      <c r="P124" t="s">
+      <c r="P124" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12364,7 +12367,7 @@
       <c r="M125">
         <v>539</v>
       </c>
-      <c r="P125" t="s">
+      <c r="P125" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12405,7 +12408,7 @@
       <c r="M126">
         <v>9</v>
       </c>
-      <c r="P126" t="s">
+      <c r="P126" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12446,7 +12449,7 @@
       <c r="M127">
         <v>87</v>
       </c>
-      <c r="P127" t="s">
+      <c r="P127" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12487,7 +12490,7 @@
       <c r="M128">
         <v>0</v>
       </c>
-      <c r="P128" t="s">
+      <c r="P128" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12528,7 +12531,7 @@
       <c r="M129">
         <v>603</v>
       </c>
-      <c r="P129" t="s">
+      <c r="P129" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12569,7 +12572,7 @@
       <c r="M130">
         <v>174</v>
       </c>
-      <c r="P130" t="s">
+      <c r="P130" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12610,7 +12613,7 @@
       <c r="M131">
         <v>3</v>
       </c>
-      <c r="P131" t="s">
+      <c r="P131" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12651,7 +12654,7 @@
       <c r="M132">
         <v>15</v>
       </c>
-      <c r="P132" t="s">
+      <c r="P132" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12695,7 +12698,7 @@
       <c r="M133">
         <v>677</v>
       </c>
-      <c r="P133" t="s">
+      <c r="P133" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12736,7 +12739,7 @@
       <c r="M134">
         <v>3</v>
       </c>
-      <c r="P134" t="s">
+      <c r="P134" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12774,7 +12777,7 @@
       <c r="M135">
         <v>15</v>
       </c>
-      <c r="P135" t="s">
+      <c r="P135" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12815,7 +12818,7 @@
       <c r="M136">
         <v>51</v>
       </c>
-      <c r="P136" t="s">
+      <c r="P136" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12853,7 +12856,7 @@
       <c r="M137">
         <v>0</v>
       </c>
-      <c r="P137" t="s">
+      <c r="P137" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12894,7 +12897,7 @@
       <c r="M138">
         <v>9</v>
       </c>
-      <c r="P138" t="s">
+      <c r="P138" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12935,7 +12938,7 @@
       <c r="M139">
         <v>3</v>
       </c>
-      <c r="P139" t="s">
+      <c r="P139" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12976,7 +12979,7 @@
       <c r="M140">
         <v>69</v>
       </c>
-      <c r="P140" t="s">
+      <c r="P140" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13017,7 +13020,7 @@
       <c r="M141">
         <v>135</v>
       </c>
-      <c r="P141" t="s">
+      <c r="P141" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13058,7 +13061,7 @@
       <c r="M142">
         <v>305</v>
       </c>
-      <c r="P142" t="s">
+      <c r="P142" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13102,7 +13105,7 @@
       <c r="M143">
         <v>1282</v>
       </c>
-      <c r="P143" t="s">
+      <c r="P143" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13143,7 +13146,7 @@
       <c r="M144">
         <v>377</v>
       </c>
-      <c r="P144" t="s">
+      <c r="P144" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13181,7 +13184,7 @@
       <c r="M145">
         <v>9</v>
       </c>
-      <c r="P145" t="s">
+      <c r="P145" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13222,7 +13225,7 @@
       <c r="M146">
         <v>9</v>
       </c>
-      <c r="P146" t="s">
+      <c r="P146" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13257,7 +13260,7 @@
       <c r="L147">
         <v>45.2</v>
       </c>
-      <c r="P147" t="s">
+      <c r="P147" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13292,7 +13295,7 @@
       <c r="L148">
         <v>60.5</v>
       </c>
-      <c r="P148" t="s">
+      <c r="P148" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13333,7 +13336,7 @@
       <c r="M149">
         <v>9</v>
       </c>
-      <c r="P149" t="s">
+      <c r="P149" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13377,7 +13380,7 @@
       <c r="M150">
         <v>19</v>
       </c>
-      <c r="P150" t="s">
+      <c r="P150" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13412,7 +13415,7 @@
       <c r="L151">
         <v>17.2</v>
       </c>
-      <c r="P151" t="s">
+      <c r="P151" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13453,7 +13456,7 @@
       <c r="M152">
         <v>3</v>
       </c>
-      <c r="P152" t="s">
+      <c r="P152" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13494,7 +13497,7 @@
       <c r="M153">
         <v>1</v>
       </c>
-      <c r="P153" t="s">
+      <c r="P153" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13535,7 +13538,7 @@
       <c r="M154">
         <v>116</v>
       </c>
-      <c r="P154" t="s">
+      <c r="P154" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13576,7 +13579,7 @@
       <c r="M155">
         <v>116</v>
       </c>
-      <c r="P155" t="s">
+      <c r="P155" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13617,7 +13620,7 @@
       <c r="M156">
         <v>3</v>
       </c>
-      <c r="P156" t="s">
+      <c r="P156" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13658,7 +13661,7 @@
       <c r="M157">
         <v>38</v>
       </c>
-      <c r="P157" t="s">
+      <c r="P157" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13702,7 +13705,7 @@
       <c r="M158">
         <v>102</v>
       </c>
-      <c r="P158" t="s">
+      <c r="P158" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13743,7 +13746,7 @@
       <c r="M159">
         <v>6</v>
       </c>
-      <c r="P159" t="s">
+      <c r="P159" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13784,7 +13787,7 @@
       <c r="M160">
         <v>0</v>
       </c>
-      <c r="P160" t="s">
+      <c r="P160" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13825,7 +13828,7 @@
       <c r="M161">
         <v>6</v>
       </c>
-      <c r="P161" t="s">
+      <c r="P161" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13866,7 +13869,7 @@
       <c r="M162">
         <v>3</v>
       </c>
-      <c r="P162" t="s">
+      <c r="P162" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13907,7 +13910,7 @@
       <c r="M163">
         <v>378</v>
       </c>
-      <c r="P163" t="s">
+      <c r="P163" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13951,7 +13954,7 @@
       <c r="M164">
         <v>462</v>
       </c>
-      <c r="P164" t="s">
+      <c r="P164" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -13986,7 +13989,7 @@
       <c r="L165">
         <v>16.7</v>
       </c>
-      <c r="P165" t="s">
+      <c r="P165" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14021,7 +14024,7 @@
       <c r="L166">
         <v>19</v>
       </c>
-      <c r="P166" t="s">
+      <c r="P166" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14059,7 +14062,7 @@
       <c r="M167">
         <v>474</v>
       </c>
-      <c r="P167" t="s">
+      <c r="P167" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14100,7 +14103,7 @@
       <c r="M168">
         <v>0</v>
       </c>
-      <c r="P168" t="s">
+      <c r="P168" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14141,7 +14144,7 @@
       <c r="M169">
         <v>6</v>
       </c>
-      <c r="P169" t="s">
+      <c r="P169" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14179,7 +14182,7 @@
       <c r="M170">
         <v>51</v>
       </c>
-      <c r="P170" t="s">
+      <c r="P170" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14220,7 +14223,7 @@
       <c r="M171">
         <v>17</v>
       </c>
-      <c r="P171" t="s">
+      <c r="P171" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14255,7 +14258,7 @@
       <c r="L172">
         <v>26</v>
       </c>
-      <c r="P172" t="s">
+      <c r="P172" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14299,7 +14302,7 @@
       <c r="M173">
         <v>84</v>
       </c>
-      <c r="P173" t="s">
+      <c r="P173" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14340,7 +14343,7 @@
       <c r="M174">
         <v>67</v>
       </c>
-      <c r="P174" t="s">
+      <c r="P174" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14381,7 +14384,7 @@
       <c r="M175">
         <v>3</v>
       </c>
-      <c r="P175" t="s">
+      <c r="P175" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14422,7 +14425,7 @@
       <c r="M176">
         <v>0</v>
       </c>
-      <c r="P176" t="s">
+      <c r="P176" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14466,7 +14469,7 @@
       <c r="M177">
         <v>149</v>
       </c>
-      <c r="P177" t="s">
+      <c r="P177" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14507,7 +14510,7 @@
       <c r="M178">
         <v>6</v>
       </c>
-      <c r="P178" t="s">
+      <c r="P178" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14551,7 +14554,7 @@
       <c r="M179">
         <v>95</v>
       </c>
-      <c r="P179" t="s">
+      <c r="P179" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14589,7 +14592,7 @@
       <c r="M180">
         <v>18</v>
       </c>
-      <c r="P180" t="s">
+      <c r="P180" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14630,7 +14633,7 @@
       <c r="M181">
         <v>811</v>
       </c>
-      <c r="P181" t="s">
+      <c r="P181" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14671,7 +14674,7 @@
       <c r="M182">
         <v>811</v>
       </c>
-      <c r="P182" t="s">
+      <c r="P182" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14712,7 +14715,7 @@
       <c r="M183">
         <v>292</v>
       </c>
-      <c r="P183" t="s">
+      <c r="P183" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14753,7 +14756,7 @@
       <c r="M184">
         <v>432</v>
       </c>
-      <c r="P184" t="s">
+      <c r="P184" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14794,7 +14797,7 @@
       <c r="M185">
         <v>9</v>
       </c>
-      <c r="P185" t="s">
+      <c r="P185" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14835,7 +14838,7 @@
       <c r="M186">
         <v>18</v>
       </c>
-      <c r="P186" t="s">
+      <c r="P186" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14876,7 +14879,7 @@
       <c r="M187">
         <v>145</v>
       </c>
-      <c r="P187" t="s">
+      <c r="P187" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14917,7 +14920,7 @@
       <c r="M188">
         <v>24</v>
       </c>
-      <c r="P188" t="s">
+      <c r="P188" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14958,7 +14961,7 @@
       <c r="M189">
         <v>0</v>
       </c>
-      <c r="P189" t="s">
+      <c r="P189" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -14999,7 +15002,7 @@
       <c r="M190">
         <v>87</v>
       </c>
-      <c r="P190" t="s">
+      <c r="P190" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15040,7 +15043,7 @@
       <c r="M191">
         <v>944</v>
       </c>
-      <c r="P191" t="s">
+      <c r="P191" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15078,7 +15081,7 @@
       <c r="M192">
         <v>561</v>
       </c>
-      <c r="P192" t="s">
+      <c r="P192" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15116,7 +15119,7 @@
       <c r="M193">
         <v>1399</v>
       </c>
-      <c r="P193" t="s">
+      <c r="P193" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15160,7 +15163,7 @@
       <c r="M194">
         <v>1599</v>
       </c>
-      <c r="P194" t="s">
+      <c r="P194" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15201,7 +15204,7 @@
       <c r="M195">
         <v>0</v>
       </c>
-      <c r="P195" t="s">
+      <c r="P195" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15245,7 +15248,7 @@
       <c r="M196">
         <v>85</v>
       </c>
-      <c r="P196" t="s">
+      <c r="P196" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15286,7 +15289,7 @@
       <c r="M197">
         <v>75</v>
       </c>
-      <c r="P197" t="s">
+      <c r="P197" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15327,7 +15330,7 @@
       <c r="M198">
         <v>96</v>
       </c>
-      <c r="P198" t="s">
+      <c r="P198" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15406,7 +15409,7 @@
       <c r="M200">
         <v>60</v>
       </c>
-      <c r="P200" t="s">
+      <c r="P200" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15450,7 +15453,7 @@
       <c r="M201">
         <v>246</v>
       </c>
-      <c r="P201" t="s">
+      <c r="P201" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15491,7 +15494,7 @@
       <c r="M202">
         <v>6</v>
       </c>
-      <c r="P202" t="s">
+      <c r="P202" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15532,7 +15535,7 @@
       <c r="M203">
         <v>145</v>
       </c>
-      <c r="P203" t="s">
+      <c r="P203" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15576,7 +15579,7 @@
       <c r="M204">
         <v>70</v>
       </c>
-      <c r="P204" t="s">
+      <c r="P204" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15617,7 +15620,7 @@
       <c r="M205">
         <v>53</v>
       </c>
-      <c r="P205" t="s">
+      <c r="P205" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15661,7 +15664,7 @@
       <c r="M206">
         <v>81</v>
       </c>
-      <c r="P206" t="s">
+      <c r="P206" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15702,7 +15705,7 @@
       <c r="M207">
         <v>66</v>
       </c>
-      <c r="P207" t="s">
+      <c r="P207" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15743,7 +15746,7 @@
       <c r="M208">
         <v>196</v>
       </c>
-      <c r="P208" t="s">
+      <c r="P208" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15784,7 +15787,7 @@
       <c r="M209">
         <v>145</v>
       </c>
-      <c r="P209" t="s">
+      <c r="P209" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15825,7 +15828,7 @@
       <c r="M210">
         <v>9</v>
       </c>
-      <c r="P210" t="s">
+      <c r="P210" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15863,7 +15866,7 @@
       <c r="L211">
         <v>6.6</v>
       </c>
-      <c r="P211" s="7">
+      <c r="P211" s="8">
         <v>46181</v>
       </c>
     </row>
@@ -15904,7 +15907,7 @@
       <c r="M212">
         <v>120</v>
       </c>
-      <c r="P212" t="s">
+      <c r="P212" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15945,7 +15948,7 @@
       <c r="M213">
         <v>21</v>
       </c>
-      <c r="P213" t="s">
+      <c r="P213" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -15986,7 +15989,7 @@
       <c r="M214">
         <v>356</v>
       </c>
-      <c r="P214" t="s">
+      <c r="P214" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16027,7 +16030,7 @@
       <c r="M215">
         <v>93</v>
       </c>
-      <c r="P215" t="s">
+      <c r="P215" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16068,7 +16071,7 @@
       <c r="M216">
         <v>93</v>
       </c>
-      <c r="P216" t="s">
+      <c r="P216" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16109,7 +16112,7 @@
       <c r="M217">
         <v>87</v>
       </c>
-      <c r="P217" t="s">
+      <c r="P217" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16150,7 +16153,7 @@
       <c r="M218">
         <v>60</v>
       </c>
-      <c r="P218" t="s">
+      <c r="P218" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16191,7 +16194,7 @@
       <c r="M219">
         <v>2</v>
       </c>
-      <c r="P219" t="s">
+      <c r="P219" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16232,7 +16235,7 @@
       <c r="M220">
         <v>85</v>
       </c>
-      <c r="P220" t="s">
+      <c r="P220" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16273,7 +16276,7 @@
       <c r="M221">
         <v>216</v>
       </c>
-      <c r="P221" t="s">
+      <c r="P221" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16314,7 +16317,7 @@
       <c r="M222">
         <v>22</v>
       </c>
-      <c r="P222" t="s">
+      <c r="P222" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16355,7 +16358,7 @@
       <c r="M223">
         <v>42</v>
       </c>
-      <c r="P223" t="s">
+      <c r="P223" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16396,7 +16399,7 @@
       <c r="M224">
         <v>6</v>
       </c>
-      <c r="P224" t="s">
+      <c r="P224" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16437,7 +16440,7 @@
       <c r="M225">
         <v>6</v>
       </c>
-      <c r="P225" t="s">
+      <c r="P225" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16478,7 +16481,7 @@
       <c r="M226">
         <v>24</v>
       </c>
-      <c r="P226" t="s">
+      <c r="P226" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16519,7 +16522,7 @@
       <c r="M227">
         <v>65</v>
       </c>
-      <c r="P227" t="s">
+      <c r="P227" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16563,7 +16566,7 @@
       <c r="M228">
         <v>228</v>
       </c>
-      <c r="P228" t="s">
+      <c r="P228" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16604,7 +16607,7 @@
       <c r="M229">
         <v>146</v>
       </c>
-      <c r="P229" t="s">
+      <c r="P229" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16645,7 +16648,7 @@
       <c r="M230">
         <v>0</v>
       </c>
-      <c r="P230" t="s">
+      <c r="P230" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16686,7 +16689,7 @@
       <c r="M231">
         <v>12</v>
       </c>
-      <c r="P231" t="s">
+      <c r="P231" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16730,7 +16733,7 @@
       <c r="M232">
         <v>219</v>
       </c>
-      <c r="P232" t="s">
+      <c r="P232" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16771,7 +16774,7 @@
       <c r="M233">
         <v>47</v>
       </c>
-      <c r="P233" t="s">
+      <c r="P233" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16812,7 +16815,7 @@
       <c r="M234">
         <v>232</v>
       </c>
-      <c r="P234" t="s">
+      <c r="P234" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16853,7 +16856,7 @@
       <c r="M235">
         <v>18</v>
       </c>
-      <c r="P235" t="s">
+      <c r="P235" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16894,7 +16897,7 @@
       <c r="M236">
         <v>54</v>
       </c>
-      <c r="P236" t="s">
+      <c r="P236" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16935,7 +16938,7 @@
       <c r="M237">
         <v>138</v>
       </c>
-      <c r="P237" t="s">
+      <c r="P237" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -16976,7 +16979,7 @@
       <c r="M238">
         <v>138</v>
       </c>
-      <c r="P238" t="s">
+      <c r="P238" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17017,7 +17020,7 @@
       <c r="M239">
         <v>6</v>
       </c>
-      <c r="P239" t="s">
+      <c r="P239" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17058,7 +17061,7 @@
       <c r="M240">
         <v>0</v>
       </c>
-      <c r="P240" t="s">
+      <c r="P240" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17102,7 +17105,7 @@
       <c r="M241">
         <v>219</v>
       </c>
-      <c r="P241" t="s">
+      <c r="P241" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17143,7 +17146,7 @@
       <c r="M242">
         <v>47</v>
       </c>
-      <c r="P242" t="s">
+      <c r="P242" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17187,7 +17190,7 @@
       <c r="M243">
         <v>120</v>
       </c>
-      <c r="P243" t="s">
+      <c r="P243" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17228,7 +17231,7 @@
       <c r="M244">
         <v>81</v>
       </c>
-      <c r="P244" t="s">
+      <c r="P244" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17269,7 +17272,7 @@
       <c r="M245">
         <v>36</v>
       </c>
-      <c r="P245" t="s">
+      <c r="P245" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17310,7 +17313,7 @@
       <c r="M246">
         <v>59</v>
       </c>
-      <c r="P246" t="s">
+      <c r="P246" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17351,7 +17354,7 @@
       <c r="M247">
         <v>118</v>
       </c>
-      <c r="P247" t="s">
+      <c r="P247" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17392,7 +17395,7 @@
       <c r="M248">
         <v>0</v>
       </c>
-      <c r="P248" t="s">
+      <c r="P248" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17433,7 +17436,7 @@
       <c r="M249">
         <v>427</v>
       </c>
-      <c r="P249" t="s">
+      <c r="P249" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17474,7 +17477,7 @@
       <c r="M250">
         <v>24</v>
       </c>
-      <c r="P250" t="s">
+      <c r="P250" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17515,7 +17518,7 @@
       <c r="M251">
         <v>24</v>
       </c>
-      <c r="P251" t="s">
+      <c r="P251" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17556,7 +17559,7 @@
       <c r="M252">
         <v>24</v>
       </c>
-      <c r="P252" t="s">
+      <c r="P252" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17597,7 +17600,7 @@
       <c r="M253">
         <v>84</v>
       </c>
-      <c r="P253" t="s">
+      <c r="P253" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17638,7 +17641,7 @@
       <c r="M254">
         <v>186</v>
       </c>
-      <c r="P254" t="s">
+      <c r="P254" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17676,7 +17679,7 @@
       <c r="M255">
         <v>363</v>
       </c>
-      <c r="P255" t="s">
+      <c r="P255" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17714,7 +17717,7 @@
       <c r="M256">
         <v>186</v>
       </c>
-      <c r="P256" t="s">
+      <c r="P256" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17752,7 +17755,7 @@
       <c r="M257">
         <v>442</v>
       </c>
-      <c r="P257" t="s">
+      <c r="P257" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17790,7 +17793,7 @@
       <c r="M258">
         <v>671</v>
       </c>
-      <c r="P258" t="s">
+      <c r="P258" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17831,7 +17834,7 @@
       <c r="M259">
         <v>33</v>
       </c>
-      <c r="P259" t="s">
+      <c r="P259" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17872,7 +17875,7 @@
       <c r="M260">
         <v>111</v>
       </c>
-      <c r="P260" t="s">
+      <c r="P260" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17913,7 +17916,7 @@
       <c r="M261">
         <v>174</v>
       </c>
-      <c r="P261" t="s">
+      <c r="P261" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17954,7 +17957,7 @@
       <c r="M262">
         <v>1180</v>
       </c>
-      <c r="P262" t="s">
+      <c r="P262" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -17995,7 +17998,7 @@
       <c r="M263">
         <v>78</v>
       </c>
-      <c r="P263" t="s">
+      <c r="P263" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18036,7 +18039,7 @@
       <c r="M264">
         <v>0</v>
       </c>
-      <c r="P264" t="s">
+      <c r="P264" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18077,7 +18080,7 @@
       <c r="M265">
         <v>6</v>
       </c>
-      <c r="P265" t="s">
+      <c r="P265" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18118,7 +18121,7 @@
       <c r="M266">
         <v>296</v>
       </c>
-      <c r="P266" t="s">
+      <c r="P266" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R266" t="s">
@@ -18162,7 +18165,7 @@
       <c r="M267">
         <v>165</v>
       </c>
-      <c r="P267" t="s">
+      <c r="P267" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18203,7 +18206,7 @@
       <c r="M268">
         <v>0</v>
       </c>
-      <c r="P268" t="s">
+      <c r="P268" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18244,7 +18247,7 @@
       <c r="M269">
         <v>1159</v>
       </c>
-      <c r="P269" t="s">
+      <c r="P269" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18282,7 +18285,7 @@
       <c r="M270">
         <v>30</v>
       </c>
-      <c r="P270" t="s">
+      <c r="P270" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18323,7 +18326,7 @@
       <c r="M271">
         <v>3</v>
       </c>
-      <c r="P271" t="s">
+      <c r="P271" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18361,7 +18364,7 @@
       <c r="M272">
         <v>0</v>
       </c>
-      <c r="P272" t="s">
+      <c r="P272" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18399,7 +18402,7 @@
       <c r="L273">
         <v>33.9</v>
       </c>
-      <c r="P273" t="s">
+      <c r="P273" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18431,7 +18434,7 @@
       <c r="L274">
         <v>8.9</v>
       </c>
-      <c r="P274" t="s">
+      <c r="P274" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18469,7 +18472,7 @@
       <c r="M275">
         <v>24</v>
       </c>
-      <c r="P275" t="s">
+      <c r="P275" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18510,7 +18513,7 @@
       <c r="M276">
         <v>120</v>
       </c>
-      <c r="P276" t="s">
+      <c r="P276" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18548,7 +18551,7 @@
       <c r="M277">
         <v>528</v>
       </c>
-      <c r="P277" t="s">
+      <c r="P277" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18583,7 +18586,7 @@
       <c r="M278">
         <v>9</v>
       </c>
-      <c r="P278" t="s">
+      <c r="P278" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18618,7 +18621,7 @@
       <c r="M279">
         <v>9</v>
       </c>
-      <c r="P279" t="s">
+      <c r="P279" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18656,7 +18659,7 @@
       <c r="M280">
         <v>393</v>
       </c>
-      <c r="P280" t="s">
+      <c r="P280" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18694,7 +18697,7 @@
       <c r="M281">
         <v>0</v>
       </c>
-      <c r="P281" t="s">
+      <c r="P281" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18729,7 +18732,7 @@
       <c r="M282">
         <v>299</v>
       </c>
-      <c r="P282" t="s">
+      <c r="P282" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18767,7 +18770,7 @@
       <c r="M283">
         <v>76</v>
       </c>
-      <c r="P283" t="s">
+      <c r="P283" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18805,7 +18808,7 @@
       <c r="M284">
         <v>442</v>
       </c>
-      <c r="P284" t="s">
+      <c r="P284" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R284" t="s">
@@ -18843,7 +18846,7 @@
       <c r="M285">
         <v>1181</v>
       </c>
-      <c r="P285" t="s">
+      <c r="P285" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18881,7 +18884,7 @@
       <c r="M286">
         <v>12</v>
       </c>
-      <c r="P286" t="s">
+      <c r="P286" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18919,7 +18922,7 @@
       <c r="M287">
         <v>169</v>
       </c>
-      <c r="P287" t="s">
+      <c r="P287" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18957,7 +18960,7 @@
       <c r="M288">
         <v>63</v>
       </c>
-      <c r="P288" t="s">
+      <c r="P288" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -18998,7 +19001,7 @@
       <c r="M289">
         <v>31</v>
       </c>
-      <c r="P289" t="s">
+      <c r="P289" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19039,7 +19042,7 @@
       <c r="M290">
         <v>219</v>
       </c>
-      <c r="P290" t="s">
+      <c r="P290" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19077,7 +19080,7 @@
       <c r="M291">
         <v>38</v>
       </c>
-      <c r="P291" t="s">
+      <c r="P291" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19115,7 +19118,7 @@
       <c r="M292">
         <v>0</v>
       </c>
-      <c r="P292" t="s">
+      <c r="P292" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19156,7 +19159,7 @@
       <c r="M293">
         <v>0</v>
       </c>
-      <c r="P293" t="s">
+      <c r="P293" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19197,7 +19200,7 @@
       <c r="M294">
         <v>0</v>
       </c>
-      <c r="P294" t="s">
+      <c r="P294" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19238,7 +19241,7 @@
       <c r="M295">
         <v>940</v>
       </c>
-      <c r="P295" t="s">
+      <c r="P295" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19276,7 +19279,7 @@
       <c r="M296">
         <v>66</v>
       </c>
-      <c r="P296" t="s">
+      <c r="P296" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19317,7 +19320,7 @@
       <c r="M297">
         <v>0</v>
       </c>
-      <c r="P297" t="s">
+      <c r="P297" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19355,7 +19358,7 @@
       <c r="M298">
         <v>180</v>
       </c>
-      <c r="P298" t="s">
+      <c r="P298" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19393,7 +19396,7 @@
       <c r="M299">
         <v>0</v>
       </c>
-      <c r="P299" t="s">
+      <c r="P299" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19431,7 +19434,7 @@
       <c r="M300">
         <v>3</v>
       </c>
-      <c r="P300" t="s">
+      <c r="P300" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19466,7 +19469,7 @@
       <c r="M301">
         <v>6</v>
       </c>
-      <c r="P301" t="s">
+      <c r="P301" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19507,7 +19510,7 @@
       <c r="M302">
         <v>35</v>
       </c>
-      <c r="P302" t="s">
+      <c r="P302" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19545,7 +19548,7 @@
       <c r="M303">
         <v>787</v>
       </c>
-      <c r="P303" t="s">
+      <c r="P303" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19583,7 +19586,7 @@
       <c r="M304">
         <v>787</v>
       </c>
-      <c r="P304" t="s">
+      <c r="P304" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19621,7 +19624,7 @@
       <c r="M305">
         <v>12</v>
       </c>
-      <c r="P305" t="s">
+      <c r="P305" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19662,7 +19665,7 @@
       <c r="M306">
         <v>274</v>
       </c>
-      <c r="P306" t="s">
+      <c r="P306" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19703,7 +19706,7 @@
       <c r="M307">
         <v>21</v>
       </c>
-      <c r="P307" t="s">
+      <c r="P307" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19741,7 +19744,7 @@
       <c r="M308">
         <v>99</v>
       </c>
-      <c r="P308" t="s">
+      <c r="P308" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19782,7 +19785,7 @@
       <c r="M309">
         <v>12</v>
       </c>
-      <c r="P309" t="s">
+      <c r="P309" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19820,7 +19823,7 @@
       <c r="M310">
         <v>102</v>
       </c>
-      <c r="P310" t="s">
+      <c r="P310" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19858,7 +19861,7 @@
       <c r="M311">
         <v>327</v>
       </c>
-      <c r="P311" t="s">
+      <c r="P311" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19899,7 +19902,7 @@
       <c r="M312">
         <v>120</v>
       </c>
-      <c r="P312" t="s">
+      <c r="P312" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19931,7 +19934,7 @@
       <c r="L313">
         <v>15</v>
       </c>
-      <c r="P313" t="s">
+      <c r="P313" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -19966,7 +19969,7 @@
       <c r="M314">
         <v>54</v>
       </c>
-      <c r="P314" t="s">
+      <c r="P314" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20007,7 +20010,7 @@
       <c r="M315">
         <v>27</v>
       </c>
-      <c r="P315" t="s">
+      <c r="P315" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20048,7 +20051,7 @@
       <c r="M316">
         <v>0</v>
       </c>
-      <c r="P316" t="s">
+      <c r="P316" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20080,7 +20083,7 @@
       <c r="L317">
         <v>8.3000000000000007</v>
       </c>
-      <c r="P317" t="s">
+      <c r="P317" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20115,7 +20118,7 @@
       <c r="M318">
         <v>231</v>
       </c>
-      <c r="P318" t="s">
+      <c r="P318" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20153,7 +20156,7 @@
       <c r="M319">
         <v>12</v>
       </c>
-      <c r="P319" t="s">
+      <c r="P319" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20191,7 +20194,7 @@
       <c r="M320">
         <v>63</v>
       </c>
-      <c r="P320" t="s">
+      <c r="P320" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20229,7 +20232,7 @@
       <c r="M321">
         <v>0</v>
       </c>
-      <c r="P321" t="s">
+      <c r="P321" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20267,7 +20270,7 @@
       <c r="M322">
         <v>263</v>
       </c>
-      <c r="P322" t="s">
+      <c r="P322" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20305,7 +20308,7 @@
       <c r="M323">
         <v>102</v>
       </c>
-      <c r="P323" t="s">
+      <c r="P323" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R323" t="s">
@@ -20343,7 +20346,7 @@
       <c r="M324">
         <v>456</v>
       </c>
-      <c r="P324" t="s">
+      <c r="P324" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20384,7 +20387,7 @@
       <c r="M325">
         <v>12</v>
       </c>
-      <c r="P325" t="s">
+      <c r="P325" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20425,7 +20428,7 @@
       <c r="M326">
         <v>12</v>
       </c>
-      <c r="P326" t="s">
+      <c r="P326" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20469,7 +20472,7 @@
       <c r="M327">
         <v>10955</v>
       </c>
-      <c r="P327" t="s">
+      <c r="P327" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20504,7 +20507,7 @@
       <c r="L328">
         <v>17.3</v>
       </c>
-      <c r="P328" t="s">
+      <c r="P328" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20548,7 +20551,7 @@
       <c r="M329">
         <v>390</v>
       </c>
-      <c r="P329" t="s">
+      <c r="P329" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20592,7 +20595,7 @@
       <c r="M330">
         <v>97</v>
       </c>
-      <c r="P330" t="s">
+      <c r="P330" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20627,7 +20630,7 @@
       <c r="L331">
         <v>18.850000000000001</v>
       </c>
-      <c r="P331" t="s">
+      <c r="P331" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20662,7 +20665,7 @@
       <c r="L332">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P332" t="s">
+      <c r="P332" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20700,7 +20703,7 @@
       <c r="M333">
         <v>0</v>
       </c>
-      <c r="P333" t="s">
+      <c r="P333" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20744,7 +20747,7 @@
       <c r="M334">
         <v>10955</v>
       </c>
-      <c r="P334" t="s">
+      <c r="P334" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20779,7 +20782,7 @@
       <c r="M335">
         <v>324</v>
       </c>
-      <c r="P335" t="s">
+      <c r="P335" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20817,7 +20820,7 @@
       <c r="M336">
         <v>483</v>
       </c>
-      <c r="P336" t="s">
+      <c r="P336" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20855,7 +20858,7 @@
       <c r="M337">
         <v>0</v>
       </c>
-      <c r="P337" t="s">
+      <c r="P337" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20899,7 +20902,7 @@
       <c r="M338">
         <v>501</v>
       </c>
-      <c r="P338" t="s">
+      <c r="P338" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20943,7 +20946,7 @@
       <c r="M339">
         <v>741</v>
       </c>
-      <c r="P339" t="s">
+      <c r="P339" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20984,7 +20987,7 @@
       <c r="M340">
         <v>648</v>
       </c>
-      <c r="P340" t="s">
+      <c r="P340" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21025,7 +21028,7 @@
       <c r="M341">
         <v>574</v>
       </c>
-      <c r="P341" t="s">
+      <c r="P341" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21069,7 +21072,7 @@
       <c r="M342">
         <v>66</v>
       </c>
-      <c r="P342" t="s">
+      <c r="P342" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21110,7 +21113,7 @@
       <c r="M343">
         <v>253</v>
       </c>
-      <c r="P343" t="s">
+      <c r="P343" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21151,7 +21154,7 @@
       <c r="M344">
         <v>575</v>
       </c>
-      <c r="P344" t="s">
+      <c r="P344" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21195,7 +21198,7 @@
       <c r="M345">
         <v>12</v>
       </c>
-      <c r="P345" t="s">
+      <c r="P345" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21239,7 +21242,7 @@
       <c r="M346">
         <v>341</v>
       </c>
-      <c r="P346" t="s">
+      <c r="P346" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21277,7 +21280,7 @@
       <c r="M347">
         <v>394</v>
       </c>
-      <c r="P347" t="s">
+      <c r="P347" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21318,7 +21321,7 @@
       <c r="M348">
         <v>281</v>
       </c>
-      <c r="P348" t="s">
+      <c r="P348" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21359,7 +21362,7 @@
       <c r="M349">
         <v>27</v>
       </c>
-      <c r="P349" t="s">
+      <c r="P349" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21403,7 +21406,7 @@
       <c r="M350">
         <v>0</v>
       </c>
-      <c r="P350" t="s">
+      <c r="P350" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21444,7 +21447,7 @@
       <c r="M351">
         <v>60</v>
       </c>
-      <c r="P351" t="s">
+      <c r="P351" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21485,7 +21488,7 @@
       <c r="M352">
         <v>368</v>
       </c>
-      <c r="P352" t="s">
+      <c r="P352" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21526,7 +21529,7 @@
       <c r="M353">
         <v>152</v>
       </c>
-      <c r="P353" t="s">
+      <c r="P353" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21567,7 +21570,7 @@
       <c r="M354">
         <v>693</v>
       </c>
-      <c r="P354" t="s">
+      <c r="P354" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21608,7 +21611,7 @@
       <c r="M355">
         <v>363</v>
       </c>
-      <c r="P355" t="s">
+      <c r="P355" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21649,7 +21652,7 @@
       <c r="M356">
         <v>1425</v>
       </c>
-      <c r="P356" t="s">
+      <c r="P356" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21690,7 +21693,7 @@
       <c r="M357">
         <v>84</v>
       </c>
-      <c r="P357" t="s">
+      <c r="P357" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21731,7 +21734,7 @@
       <c r="M358">
         <v>42</v>
       </c>
-      <c r="P358" t="s">
+      <c r="P358" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21772,7 +21775,7 @@
       <c r="M359">
         <v>165</v>
       </c>
-      <c r="P359" t="s">
+      <c r="P359" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R359" t="s">
@@ -21816,7 +21819,7 @@
       <c r="M360">
         <v>3214</v>
       </c>
-      <c r="P360" t="s">
+      <c r="P360" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21857,7 +21860,7 @@
       <c r="M361">
         <v>0</v>
       </c>
-      <c r="P361" t="s">
+      <c r="P361" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21901,7 +21904,7 @@
       <c r="M362">
         <v>165</v>
       </c>
-      <c r="P362" t="s">
+      <c r="P362" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21942,7 +21945,7 @@
       <c r="M363">
         <v>24</v>
       </c>
-      <c r="P363" t="s">
+      <c r="P363" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -21986,7 +21989,7 @@
       <c r="M364">
         <v>182</v>
       </c>
-      <c r="P364" t="s">
+      <c r="P364" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22027,7 +22030,7 @@
       <c r="M365">
         <v>357</v>
       </c>
-      <c r="P365" t="s">
+      <c r="P365" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22071,7 +22074,7 @@
       <c r="M366">
         <v>474</v>
       </c>
-      <c r="P366" t="s">
+      <c r="P366" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22112,7 +22115,7 @@
       <c r="M367">
         <v>321</v>
       </c>
-      <c r="P367" t="s">
+      <c r="P367" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22150,7 +22153,7 @@
       <c r="L368">
         <v>37</v>
       </c>
-      <c r="P368" t="s">
+      <c r="P368" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22191,7 +22194,7 @@
       <c r="M369">
         <v>351</v>
       </c>
-      <c r="P369" t="s">
+      <c r="P369" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22232,7 +22235,7 @@
       <c r="M370">
         <v>14790</v>
       </c>
-      <c r="P370" t="s">
+      <c r="P370" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22273,7 +22276,7 @@
       <c r="M371">
         <v>0</v>
       </c>
-      <c r="P371" t="s">
+      <c r="P371" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22355,7 +22358,7 @@
       <c r="M373">
         <v>0</v>
       </c>
-      <c r="P373" t="s">
+      <c r="P373" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22396,7 +22399,7 @@
       <c r="M374">
         <v>0</v>
       </c>
-      <c r="P374" t="s">
+      <c r="P374" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22437,7 +22440,7 @@
       <c r="M375">
         <v>0</v>
       </c>
-      <c r="P375" t="s">
+      <c r="P375" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22481,7 +22484,7 @@
       <c r="M376">
         <v>6</v>
       </c>
-      <c r="P376" t="s">
+      <c r="P376" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22522,7 +22525,7 @@
       <c r="M377">
         <v>0</v>
       </c>
-      <c r="P377" t="s">
+      <c r="P377" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22563,7 +22566,7 @@
       <c r="M378">
         <v>0</v>
       </c>
-      <c r="P378" t="s">
+      <c r="P378" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22604,7 +22607,7 @@
       <c r="M379">
         <v>0</v>
       </c>
-      <c r="P379" t="s">
+      <c r="P379" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22645,7 +22648,7 @@
       <c r="M380">
         <v>0</v>
       </c>
-      <c r="P380" t="s">
+      <c r="P380" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22686,7 +22689,7 @@
       <c r="M381">
         <v>0</v>
       </c>
-      <c r="P381" t="s">
+      <c r="P381" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22727,7 +22730,7 @@
       <c r="M382">
         <v>0</v>
       </c>
-      <c r="P382" t="s">
+      <c r="P382" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22768,7 +22771,7 @@
       <c r="M383">
         <v>37</v>
       </c>
-      <c r="P383" t="s">
+      <c r="P383" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22809,7 +22812,7 @@
       <c r="M384">
         <v>539</v>
       </c>
-      <c r="P384" t="s">
+      <c r="P384" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22850,7 +22853,7 @@
       <c r="M385">
         <v>264</v>
       </c>
-      <c r="P385" t="s">
+      <c r="P385" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22888,7 +22891,7 @@
       <c r="L386">
         <v>7.1</v>
       </c>
-      <c r="P386" t="s">
+      <c r="P386" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22926,7 +22929,7 @@
       <c r="L387">
         <v>8.1999999999999993</v>
       </c>
-      <c r="P387" t="s">
+      <c r="P387" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -22967,7 +22970,7 @@
       <c r="M388">
         <v>0</v>
       </c>
-      <c r="P388" t="s">
+      <c r="P388" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23008,7 +23011,7 @@
       <c r="M389">
         <v>113</v>
       </c>
-      <c r="P389" t="s">
+      <c r="P389" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23049,7 +23052,7 @@
       <c r="M390">
         <v>71</v>
       </c>
-      <c r="P390" t="s">
+      <c r="P390" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23090,7 +23093,7 @@
       <c r="M391">
         <v>152</v>
       </c>
-      <c r="P391" t="s">
+      <c r="P391" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23131,7 +23134,7 @@
       <c r="M392">
         <v>324</v>
       </c>
-      <c r="P392" t="s">
+      <c r="P392" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23172,7 +23175,7 @@
       <c r="M393">
         <v>99</v>
       </c>
-      <c r="P393" t="s">
+      <c r="P393" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23213,7 +23216,7 @@
       <c r="M394">
         <v>915</v>
       </c>
-      <c r="P394" t="s">
+      <c r="P394" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23254,7 +23257,7 @@
       <c r="M395">
         <v>219</v>
       </c>
-      <c r="P395" t="s">
+      <c r="P395" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23295,7 +23298,7 @@
       <c r="M396">
         <v>96</v>
       </c>
-      <c r="P396" t="s">
+      <c r="P396" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23336,7 +23339,7 @@
       <c r="M397">
         <v>219</v>
       </c>
-      <c r="P397" t="s">
+      <c r="P397" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23377,7 +23380,7 @@
       <c r="M398">
         <v>27</v>
       </c>
-      <c r="P398" t="s">
+      <c r="P398" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23421,7 +23424,7 @@
       <c r="M399">
         <v>303</v>
       </c>
-      <c r="P399" t="s">
+      <c r="P399" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23465,7 +23468,7 @@
       <c r="M400">
         <v>187</v>
       </c>
-      <c r="P400" t="s">
+      <c r="P400" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23506,7 +23509,7 @@
       <c r="M401">
         <v>340</v>
       </c>
-      <c r="P401" t="s">
+      <c r="P401" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23547,7 +23550,7 @@
       <c r="M402">
         <v>46</v>
       </c>
-      <c r="P402" t="s">
+      <c r="P402" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23588,7 +23591,7 @@
       <c r="M403">
         <v>78</v>
       </c>
-      <c r="P403" t="s">
+      <c r="P403" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23629,7 +23632,7 @@
       <c r="M404">
         <v>36</v>
       </c>
-      <c r="P404" t="s">
+      <c r="P404" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23667,7 +23670,7 @@
       <c r="L405">
         <v>11.4</v>
       </c>
-      <c r="P405" t="s">
+      <c r="P405" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23708,7 +23711,7 @@
       <c r="M406">
         <v>0</v>
       </c>
-      <c r="P406" t="s">
+      <c r="P406" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23749,7 +23752,7 @@
       <c r="M407">
         <v>0</v>
       </c>
-      <c r="P407" t="s">
+      <c r="P407" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23790,7 +23793,7 @@
       <c r="M408">
         <v>0</v>
       </c>
-      <c r="P408" t="s">
+      <c r="P408" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23831,7 +23834,7 @@
       <c r="M409">
         <v>177</v>
       </c>
-      <c r="P409" t="s">
+      <c r="P409" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23875,7 +23878,7 @@
       <c r="M410">
         <v>0</v>
       </c>
-      <c r="P410" t="s">
+      <c r="P410" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23916,7 +23919,7 @@
       <c r="M411">
         <v>0</v>
       </c>
-      <c r="P411" t="s">
+      <c r="P411" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -23960,7 +23963,7 @@
       <c r="M412">
         <v>0</v>
       </c>
-      <c r="P412" t="s">
+      <c r="P412" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24004,7 +24007,7 @@
       <c r="M413">
         <v>42</v>
       </c>
-      <c r="P413" t="s">
+      <c r="P413" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24048,7 +24051,7 @@
       <c r="M414">
         <v>65</v>
       </c>
-      <c r="P414" t="s">
+      <c r="P414" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24089,7 +24092,7 @@
       <c r="M415">
         <v>0</v>
       </c>
-      <c r="P415" t="s">
+      <c r="P415" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24127,7 +24130,7 @@
       <c r="L416">
         <v>31</v>
       </c>
-      <c r="P416" t="s">
+      <c r="P416" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24171,7 +24174,7 @@
       <c r="M417">
         <v>270.39999999999998</v>
       </c>
-      <c r="P417" t="s">
+      <c r="P417" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24212,7 +24215,7 @@
       <c r="M418">
         <v>18</v>
       </c>
-      <c r="P418" t="s">
+      <c r="P418" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24253,7 +24256,7 @@
       <c r="M419">
         <v>6</v>
       </c>
-      <c r="P419" t="s">
+      <c r="P419" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24294,7 +24297,7 @@
       <c r="M420">
         <v>49</v>
       </c>
-      <c r="P420" t="s">
+      <c r="P420" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24335,7 +24338,7 @@
       <c r="L421">
         <v>17.8</v>
       </c>
-      <c r="P421" t="s">
+      <c r="P421" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24376,7 +24379,7 @@
       <c r="M422">
         <v>53</v>
       </c>
-      <c r="P422" t="s">
+      <c r="P422" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24417,7 +24420,7 @@
       <c r="L423">
         <v>22.3</v>
       </c>
-      <c r="P423" t="s">
+      <c r="P423" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24461,7 +24464,7 @@
       <c r="M424">
         <v>42</v>
       </c>
-      <c r="P424" t="s">
+      <c r="P424" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24502,7 +24505,7 @@
       <c r="M425">
         <v>171</v>
       </c>
-      <c r="P425" t="s">
+      <c r="P425" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24543,7 +24546,7 @@
       <c r="M426">
         <v>171</v>
       </c>
-      <c r="P426" t="s">
+      <c r="P426" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24587,7 +24590,7 @@
       <c r="M427">
         <v>12</v>
       </c>
-      <c r="P427" t="s">
+      <c r="P427" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24631,7 +24634,7 @@
       <c r="M428">
         <v>171</v>
       </c>
-      <c r="P428" t="s">
+      <c r="P428" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24675,7 +24678,7 @@
       <c r="M429">
         <v>171</v>
       </c>
-      <c r="P429" t="s">
+      <c r="P429" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24713,7 +24716,7 @@
       <c r="L430">
         <v>18.3</v>
       </c>
-      <c r="P430" t="s">
+      <c r="P430" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24757,7 +24760,7 @@
       <c r="M431">
         <v>12</v>
       </c>
-      <c r="P431" t="s">
+      <c r="P431" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24792,7 +24795,7 @@
       <c r="L432">
         <v>31.7</v>
       </c>
-      <c r="P432" t="s">
+      <c r="P432" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24830,7 +24833,7 @@
       <c r="M433">
         <v>30</v>
       </c>
-      <c r="P433" t="s">
+      <c r="P433" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24909,7 +24912,7 @@
       <c r="L435">
         <v>95</v>
       </c>
-      <c r="P435" t="s">
+      <c r="P435" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24950,7 +24953,7 @@
       <c r="M436">
         <v>2215</v>
       </c>
-      <c r="P436" t="s">
+      <c r="P436" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -24988,7 +24991,7 @@
       <c r="M437">
         <v>2215</v>
       </c>
-      <c r="P437" t="s">
+      <c r="P437" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25029,7 +25032,7 @@
       <c r="M438">
         <v>279</v>
       </c>
-      <c r="P438" t="s">
+      <c r="P438" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25073,7 +25076,7 @@
       <c r="M439">
         <v>205</v>
       </c>
-      <c r="P439" t="s">
+      <c r="P439" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25111,7 +25114,7 @@
       <c r="L440">
         <v>14.5</v>
       </c>
-      <c r="P440" t="s">
+      <c r="P440" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25152,7 +25155,7 @@
       <c r="M441">
         <v>0</v>
       </c>
-      <c r="P441" t="s">
+      <c r="P441" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25190,7 +25193,7 @@
       <c r="L442">
         <v>37</v>
       </c>
-      <c r="P442" t="s">
+      <c r="P442" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25231,7 +25234,7 @@
       <c r="M443">
         <v>324</v>
       </c>
-      <c r="P443" t="s">
+      <c r="P443" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25272,7 +25275,7 @@
       <c r="M444">
         <v>368</v>
       </c>
-      <c r="P444" t="s">
+      <c r="P444" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25313,7 +25316,7 @@
       <c r="M445">
         <v>969</v>
       </c>
-      <c r="P445" t="s">
+      <c r="P445" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25354,7 +25357,7 @@
       <c r="M446">
         <v>0</v>
       </c>
-      <c r="P446" t="s">
+      <c r="P446" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25395,7 +25398,7 @@
       <c r="M447">
         <v>113</v>
       </c>
-      <c r="P447" t="s">
+      <c r="P447" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25436,7 +25439,7 @@
       <c r="M448">
         <v>71</v>
       </c>
-      <c r="P448" t="s">
+      <c r="P448" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25477,7 +25480,7 @@
       <c r="M449">
         <v>240</v>
       </c>
-      <c r="P449" t="s">
+      <c r="P449" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25518,7 +25521,7 @@
       <c r="M450">
         <v>66</v>
       </c>
-      <c r="P450" t="s">
+      <c r="P450" s="8" t="s">
         <v>64</v>
       </c>
       <c r="R450" t="s">
@@ -25562,7 +25565,7 @@
       <c r="M451">
         <v>549</v>
       </c>
-      <c r="P451" t="s">
+      <c r="P451" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25603,7 +25606,7 @@
       <c r="M452">
         <v>3</v>
       </c>
-      <c r="P452" t="s">
+      <c r="P452" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25644,7 +25647,7 @@
       <c r="M453">
         <v>288</v>
       </c>
-      <c r="P453" t="s">
+      <c r="P453" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25685,7 +25688,7 @@
       <c r="M454">
         <v>54</v>
       </c>
-      <c r="P454" t="s">
+      <c r="P454" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25723,7 +25726,7 @@
       <c r="M455">
         <v>666</v>
       </c>
-      <c r="P455" t="s">
+      <c r="P455" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25767,7 +25770,7 @@
       <c r="M456">
         <v>318</v>
       </c>
-      <c r="P456" t="s">
+      <c r="P456" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25805,7 +25808,7 @@
       <c r="L457">
         <v>4.95</v>
       </c>
-      <c r="P457" t="s">
+      <c r="P457" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25846,7 +25849,7 @@
       <c r="M458">
         <v>133</v>
       </c>
-      <c r="P458" t="s">
+      <c r="P458" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25887,7 +25890,7 @@
       <c r="M459">
         <v>0</v>
       </c>
-      <c r="P459" t="s">
+      <c r="P459" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25928,7 +25931,7 @@
       <c r="M460">
         <v>0</v>
       </c>
-      <c r="P460" t="s">
+      <c r="P460" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -25969,7 +25972,7 @@
       <c r="M461">
         <v>0</v>
       </c>
-      <c r="P461" t="s">
+      <c r="P461" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26010,7 +26013,7 @@
       <c r="M462">
         <v>1327</v>
       </c>
-      <c r="P462" t="s">
+      <c r="P462" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26051,7 +26054,7 @@
       <c r="M463">
         <v>6</v>
       </c>
-      <c r="P463" t="s">
+      <c r="P463" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26092,7 +26095,7 @@
       <c r="M464">
         <v>30</v>
       </c>
-      <c r="P464" t="s">
+      <c r="P464" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26133,7 +26136,7 @@
       <c r="M465">
         <v>36</v>
       </c>
-      <c r="P465" t="s">
+      <c r="P465" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26174,7 +26177,7 @@
       <c r="M466">
         <v>18</v>
       </c>
-      <c r="P466" t="s">
+      <c r="P466" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26215,7 +26218,7 @@
       <c r="M467">
         <v>662</v>
       </c>
-      <c r="P467" t="s">
+      <c r="P467" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26256,7 +26259,7 @@
       <c r="M468">
         <v>64</v>
       </c>
-      <c r="P468" t="s">
+      <c r="P468" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26297,7 +26300,7 @@
       <c r="M469">
         <v>0</v>
       </c>
-      <c r="P469" t="s">
+      <c r="P469" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26338,7 +26341,7 @@
       <c r="M470">
         <v>36</v>
       </c>
-      <c r="P470" t="s">
+      <c r="P470" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26379,7 +26382,7 @@
       <c r="M471">
         <v>36</v>
       </c>
-      <c r="P471" t="s">
+      <c r="P471" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26420,7 +26423,7 @@
       <c r="M472">
         <v>55</v>
       </c>
-      <c r="P472" t="s">
+      <c r="P472" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26461,7 +26464,7 @@
       <c r="M473">
         <v>4411</v>
       </c>
-      <c r="P473" t="s">
+      <c r="P473" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26496,7 +26499,7 @@
       <c r="L474">
         <v>6.2</v>
       </c>
-      <c r="P474" t="s">
+      <c r="P474" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26531,7 +26534,7 @@
       <c r="L475">
         <v>8.99</v>
       </c>
-      <c r="P475" t="s">
+      <c r="P475" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26569,7 +26572,7 @@
       <c r="M476">
         <v>5</v>
       </c>
-      <c r="P476" t="s">
+      <c r="P476" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26607,7 +26610,7 @@
       <c r="M477">
         <v>6532</v>
       </c>
-      <c r="P477" t="s">
+      <c r="P477" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26645,7 +26648,7 @@
       <c r="M478">
         <v>418</v>
       </c>
-      <c r="P478" t="s">
+      <c r="P478" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26680,7 +26683,7 @@
       <c r="L479">
         <v>23.9</v>
       </c>
-      <c r="P479" t="s">
+      <c r="P479" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26718,7 +26721,7 @@
       <c r="M480">
         <v>34</v>
       </c>
-      <c r="P480" t="s">
+      <c r="P480" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26756,7 +26759,7 @@
       <c r="M481">
         <v>995</v>
       </c>
-      <c r="P481" t="s">
+      <c r="P481" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26794,7 +26797,7 @@
       <c r="M482">
         <v>31</v>
       </c>
-      <c r="P482" t="s">
+      <c r="P482" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26832,7 +26835,7 @@
       <c r="M483">
         <v>5</v>
       </c>
-      <c r="P483" t="s">
+      <c r="P483" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26870,7 +26873,7 @@
       <c r="M484">
         <v>60</v>
       </c>
-      <c r="P484" t="s">
+      <c r="P484" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26908,7 +26911,7 @@
       <c r="M485">
         <v>417</v>
       </c>
-      <c r="P485" t="s">
+      <c r="P485" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26946,7 +26949,7 @@
       <c r="M486">
         <v>777</v>
       </c>
-      <c r="P486" t="s">
+      <c r="P486" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -26984,7 +26987,7 @@
       <c r="M487">
         <v>428</v>
       </c>
-      <c r="P487" t="s">
+      <c r="P487" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27022,7 +27025,7 @@
       <c r="M488">
         <v>0</v>
       </c>
-      <c r="P488" t="s">
+      <c r="P488" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27060,7 +27063,7 @@
       <c r="M489">
         <v>36</v>
       </c>
-      <c r="P489" t="s">
+      <c r="P489" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27098,7 +27101,7 @@
       <c r="M490">
         <v>0</v>
       </c>
-      <c r="P490" t="s">
+      <c r="P490" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27136,7 +27139,7 @@
       <c r="M491">
         <v>0</v>
       </c>
-      <c r="P491" t="s">
+      <c r="P491" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27174,7 +27177,7 @@
       <c r="M492">
         <v>31</v>
       </c>
-      <c r="P492" t="s">
+      <c r="P492" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27212,7 +27215,7 @@
       <c r="M493">
         <v>41</v>
       </c>
-      <c r="P493" t="s">
+      <c r="P493" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27250,7 +27253,7 @@
       <c r="M494">
         <v>0</v>
       </c>
-      <c r="P494" t="s">
+      <c r="P494" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27288,7 +27291,7 @@
       <c r="M495">
         <v>0</v>
       </c>
-      <c r="P495" t="s">
+      <c r="P495" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27326,7 +27329,7 @@
       <c r="M496">
         <v>3</v>
       </c>
-      <c r="P496" t="s">
+      <c r="P496" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27364,7 +27367,7 @@
       <c r="M497">
         <v>23</v>
       </c>
-      <c r="P497" t="s">
+      <c r="P497" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27405,7 +27408,7 @@
       <c r="M498">
         <v>3</v>
       </c>
-      <c r="P498" t="s">
+      <c r="P498" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27446,7 +27449,7 @@
       <c r="M499">
         <v>31</v>
       </c>
-      <c r="P499" t="s">
+      <c r="P499" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27487,7 +27490,7 @@
       <c r="M500">
         <v>5</v>
       </c>
-      <c r="P500" t="s">
+      <c r="P500" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27528,7 +27531,7 @@
       <c r="M501">
         <v>5</v>
       </c>
-      <c r="P501" t="s">
+      <c r="P501" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27569,7 +27572,7 @@
       <c r="M502">
         <v>5</v>
       </c>
-      <c r="P502" t="s">
+      <c r="P502" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27607,7 +27610,7 @@
       <c r="M503">
         <v>6</v>
       </c>
-      <c r="P503" t="s">
+      <c r="P503" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27645,7 +27648,7 @@
       <c r="M504">
         <v>6</v>
       </c>
-      <c r="P504" t="s">
+      <c r="P504" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27680,7 +27683,7 @@
       <c r="L505">
         <v>14.85</v>
       </c>
-      <c r="P505" t="s">
+      <c r="P505" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27715,7 +27718,7 @@
       <c r="L506">
         <v>38.1</v>
       </c>
-      <c r="P506" t="s">
+      <c r="P506" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27750,7 +27753,7 @@
       <c r="L507">
         <v>35.5</v>
       </c>
-      <c r="P507" t="s">
+      <c r="P507" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27785,7 +27788,7 @@
       <c r="L508">
         <v>16.149999999999999</v>
       </c>
-      <c r="P508" t="s">
+      <c r="P508" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27823,7 +27826,7 @@
       <c r="L509">
         <v>112</v>
       </c>
-      <c r="P509" t="s">
+      <c r="P509" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27858,7 +27861,7 @@
       <c r="M510">
         <v>45</v>
       </c>
-      <c r="P510" t="s">
+      <c r="P510" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27893,7 +27896,7 @@
       <c r="M511">
         <v>45</v>
       </c>
-      <c r="P511" t="s">
+      <c r="P511" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27931,7 +27934,7 @@
       <c r="M512">
         <v>68</v>
       </c>
-      <c r="P512" t="s">
+      <c r="P512" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -27969,7 +27972,7 @@
       <c r="M513">
         <v>155</v>
       </c>
-      <c r="P513" t="s">
+      <c r="P513" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -28007,7 +28010,7 @@
       <c r="M514">
         <v>7</v>
       </c>
-      <c r="P514" s="7" t="s">
+      <c r="P514" s="8" t="s">
         <v>64</v>
       </c>
     </row>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{365549B2-4DE3-4645-ACB6-25A3C35E4E39}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A634FBAB-BECA-4EC5-B244-27205190BAEF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10556" uniqueCount="2248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10555" uniqueCount="2248">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -235,16 +235,16 @@
     <t>2023</t>
   </si>
   <si>
+    <t>BALCHA23</t>
+  </si>
+  <si>
+    <t>Ile de France IGP</t>
+  </si>
+  <si>
+    <t>Bal du Roi - Chardonnay</t>
+  </si>
+  <si>
     <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>BALCHA23</t>
-  </si>
-  <si>
-    <t>Ile de France IGP</t>
-  </si>
-  <si>
-    <t>Bal du Roi - Chardonnay</t>
   </si>
   <si>
     <t>BDRCHE24</t>
@@ -6791,9 +6791,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy;@"/>
-  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -6875,10 +6872,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7495,13 +7492,13 @@
       <c r="M2">
         <v>191</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>64</v>
+      <c r="P2" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -7513,10 +7510,10 @@
         <v>58</v>
       </c>
       <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
         <v>66</v>
-      </c>
-      <c r="G3" t="s">
-        <v>67</v>
       </c>
       <c r="H3" t="s">
         <v>61</v>
@@ -7534,7 +7531,7 @@
         <v>7</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7551,7 +7548,7 @@
         <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>69</v>
@@ -7575,7 +7572,7 @@
         <v>564</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R4" t="s">
         <v>71</v>
@@ -7595,7 +7592,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
         <v>73</v>
@@ -7619,7 +7616,7 @@
         <v>411</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7636,7 +7633,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
@@ -7660,7 +7657,7 @@
         <v>7</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R6" t="s">
         <v>71</v>
@@ -7680,7 +7677,7 @@
         <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
         <v>78</v>
@@ -7704,7 +7701,7 @@
         <v>10</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R7" t="s">
         <v>71</v>
@@ -7724,7 +7721,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>81</v>
@@ -7745,7 +7742,7 @@
         <v>153</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -7762,7 +7759,7 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>85</v>
@@ -7783,7 +7780,7 @@
         <v>381</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -7800,7 +7797,7 @@
         <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>88</v>
@@ -7824,7 +7821,7 @@
         <v>13</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7841,7 +7838,7 @@
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>91</v>
@@ -7865,7 +7862,7 @@
         <v>29</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7882,7 +7879,7 @@
         <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
         <v>93</v>
@@ -7906,7 +7903,7 @@
         <v>37</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7923,7 +7920,7 @@
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
         <v>96</v>
@@ -7947,7 +7944,7 @@
         <v>13</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R13" t="s">
         <v>71</v>
@@ -7967,7 +7964,7 @@
         <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
         <v>98</v>
@@ -7991,7 +7988,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R14" t="s">
         <v>71</v>
@@ -8032,7 +8029,7 @@
         <v>33</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -8070,7 +8067,7 @@
         <v>6</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R16" t="s">
         <v>71</v>
@@ -8111,7 +8108,7 @@
         <v>110</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R17" t="s">
         <v>71</v>
@@ -8152,7 +8149,7 @@
         <v>30</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R18" t="s">
         <v>71</v>
@@ -8193,7 +8190,7 @@
         <v>37</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -8231,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -8269,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -8307,7 +8304,7 @@
         <v>233</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -8348,7 +8345,7 @@
         <v>93</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -8386,7 +8383,7 @@
         <v>45</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -8424,7 +8421,7 @@
         <v>60</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -8462,7 +8459,7 @@
         <v>35</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -8503,7 +8500,7 @@
         <v>43</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -8544,7 +8541,7 @@
         <v>164</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -8585,7 +8582,7 @@
         <v>72</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -8626,7 +8623,7 @@
         <v>596</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -8667,7 +8664,7 @@
         <v>881</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -8702,7 +8699,7 @@
         <v>5.25</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -8743,7 +8740,7 @@
         <v>497</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -8784,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -8822,7 +8819,7 @@
         <v>16.649999999999999</v>
       </c>
       <c r="P35" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -8860,7 +8857,7 @@
         <v>117</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -8901,7 +8898,7 @@
         <v>27</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -8945,7 +8942,7 @@
         <v>102</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -8986,7 +8983,7 @@
         <v>63</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -9030,7 +9027,7 @@
         <v>126</v>
       </c>
       <c r="P40" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -9071,7 +9068,7 @@
         <v>216</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -9109,7 +9106,7 @@
         <v>72</v>
       </c>
       <c r="P42" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -9147,7 +9144,7 @@
         <v>248</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -9185,7 +9182,7 @@
         <v>138</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -9226,7 +9223,7 @@
         <v>332</v>
       </c>
       <c r="P45" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -9267,7 +9264,7 @@
         <v>346</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -9305,7 +9302,7 @@
         <v>180</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -9346,7 +9343,7 @@
         <v>257</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -9384,7 +9381,7 @@
         <v>48</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -9422,7 +9419,7 @@
         <v>15</v>
       </c>
       <c r="P50" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -9460,7 +9457,7 @@
         <v>92</v>
       </c>
       <c r="P51" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -9498,7 +9495,7 @@
         <v>9</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -9542,7 +9539,7 @@
         <v>902</v>
       </c>
       <c r="P53" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -9580,7 +9577,7 @@
         <v>87</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -9621,7 +9618,7 @@
         <v>46</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -9659,7 +9656,7 @@
         <v>45</v>
       </c>
       <c r="P56" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -9700,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -9735,7 +9732,7 @@
         <v>31</v>
       </c>
       <c r="P58" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -9776,7 +9773,7 @@
         <v>165</v>
       </c>
       <c r="P59" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -9814,7 +9811,7 @@
         <v>162</v>
       </c>
       <c r="P60" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -9858,7 +9855,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -9896,7 +9893,7 @@
         <v>702</v>
       </c>
       <c r="P62" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -9934,7 +9931,7 @@
         <v>12</v>
       </c>
       <c r="P63" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -9972,7 +9969,7 @@
         <v>36</v>
       </c>
       <c r="P64" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -10010,7 +10007,7 @@
         <v>69</v>
       </c>
       <c r="P65" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -10048,7 +10045,7 @@
         <v>0</v>
       </c>
       <c r="P66" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -10086,7 +10083,7 @@
         <v>213</v>
       </c>
       <c r="P67" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -10124,7 +10121,7 @@
         <v>57</v>
       </c>
       <c r="P68" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -10165,7 +10162,7 @@
         <v>102</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -10209,7 +10206,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -10250,7 +10247,7 @@
         <v>15</v>
       </c>
       <c r="P71" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -10288,7 +10285,7 @@
         <v>210</v>
       </c>
       <c r="P72" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -10326,7 +10323,7 @@
         <v>114</v>
       </c>
       <c r="P73" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -10364,7 +10361,7 @@
         <v>264</v>
       </c>
       <c r="P74" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -10399,7 +10396,7 @@
         <v>828</v>
       </c>
       <c r="P75" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -10437,7 +10434,7 @@
         <v>6122</v>
       </c>
       <c r="P76" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -10478,7 +10475,7 @@
         <v>726</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -10516,7 +10513,7 @@
         <v>310</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -10554,7 +10551,7 @@
         <v>81</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -10592,7 +10589,7 @@
         <v>8</v>
       </c>
       <c r="P80" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -10630,7 +10627,7 @@
         <v>237</v>
       </c>
       <c r="P81" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -10671,7 +10668,7 @@
         <v>581</v>
       </c>
       <c r="P82" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -10709,7 +10706,7 @@
         <v>9</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -10747,7 +10744,7 @@
         <v>6</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -10782,7 +10779,7 @@
         <v>6</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -10820,7 +10817,7 @@
         <v>902</v>
       </c>
       <c r="P86" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -10852,7 +10849,7 @@
         <v>13.85</v>
       </c>
       <c r="P87" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -10890,7 +10887,7 @@
         <v>780</v>
       </c>
       <c r="P88" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -10925,7 +10922,7 @@
         <v>342</v>
       </c>
       <c r="P89" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -10966,7 +10963,7 @@
         <v>342</v>
       </c>
       <c r="P90" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -11007,7 +11004,7 @@
         <v>342</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -11048,7 +11045,7 @@
         <v>66</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -11089,7 +11086,7 @@
         <v>12</v>
       </c>
       <c r="P93" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -11130,7 +11127,7 @@
         <v>108</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -11174,7 +11171,7 @@
         <v>856</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -11215,7 +11212,7 @@
         <v>132</v>
       </c>
       <c r="P96" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -11256,7 +11253,7 @@
         <v>120</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -11297,7 +11294,7 @@
         <v>187</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -11338,7 +11335,7 @@
         <v>36</v>
       </c>
       <c r="P99" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -11379,7 +11376,7 @@
         <v>0</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -11420,7 +11417,7 @@
         <v>156</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -11461,7 +11458,7 @@
         <v>28</v>
       </c>
       <c r="P102" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -11502,7 +11499,7 @@
         <v>206</v>
       </c>
       <c r="P103" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -11543,7 +11540,7 @@
         <v>63</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -11584,7 +11581,7 @@
         <v>78</v>
       </c>
       <c r="P105" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -11622,7 +11619,7 @@
         <v>36</v>
       </c>
       <c r="P106" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -11657,7 +11654,7 @@
         <v>10.65</v>
       </c>
       <c r="P107" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -11692,7 +11689,7 @@
         <v>11.95</v>
       </c>
       <c r="P108" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -11730,7 +11727,7 @@
         <v>152</v>
       </c>
       <c r="P109" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -11768,7 +11765,7 @@
         <v>108</v>
       </c>
       <c r="P110" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -11812,7 +11809,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -11853,7 +11850,7 @@
         <v>138</v>
       </c>
       <c r="P112" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -11897,7 +11894,7 @@
         <v>0</v>
       </c>
       <c r="P113" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -11935,7 +11932,7 @@
         <v>87</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -11973,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -12011,7 +12008,7 @@
         <v>36</v>
       </c>
       <c r="P116" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -12055,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="P117" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -12099,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -12210,7 +12207,7 @@
         <v>68</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -12251,7 +12248,7 @@
         <v>68</v>
       </c>
       <c r="P122" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -12289,7 +12286,7 @@
         <v>68</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -12327,7 +12324,7 @@
         <v>137</v>
       </c>
       <c r="P124" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -12368,7 +12365,7 @@
         <v>539</v>
       </c>
       <c r="P125" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -12409,7 +12406,7 @@
         <v>9</v>
       </c>
       <c r="P126" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -12450,7 +12447,7 @@
         <v>87</v>
       </c>
       <c r="P127" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -12491,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="P128" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -12532,7 +12529,7 @@
         <v>603</v>
       </c>
       <c r="P129" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -12573,7 +12570,7 @@
         <v>174</v>
       </c>
       <c r="P130" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -12614,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -12655,7 +12652,7 @@
         <v>15</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -12699,7 +12696,7 @@
         <v>677</v>
       </c>
       <c r="P133" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -12740,7 +12737,7 @@
         <v>3</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -12778,7 +12775,7 @@
         <v>15</v>
       </c>
       <c r="P135" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -12819,7 +12816,7 @@
         <v>51</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -12857,7 +12854,7 @@
         <v>0</v>
       </c>
       <c r="P137" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -12898,7 +12895,7 @@
         <v>9</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -12939,7 +12936,7 @@
         <v>3</v>
       </c>
       <c r="P139" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -12980,7 +12977,7 @@
         <v>69</v>
       </c>
       <c r="P140" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -13021,7 +13018,7 @@
         <v>135</v>
       </c>
       <c r="P141" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -13062,7 +13059,7 @@
         <v>305</v>
       </c>
       <c r="P142" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -13106,7 +13103,7 @@
         <v>1282</v>
       </c>
       <c r="P143" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -13147,7 +13144,7 @@
         <v>377</v>
       </c>
       <c r="P144" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -13185,7 +13182,7 @@
         <v>9</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -13226,7 +13223,7 @@
         <v>9</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -13261,7 +13258,7 @@
         <v>45.2</v>
       </c>
       <c r="P147" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -13296,7 +13293,7 @@
         <v>60.5</v>
       </c>
       <c r="P148" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -13337,7 +13334,7 @@
         <v>9</v>
       </c>
       <c r="P149" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -13381,7 +13378,7 @@
         <v>19</v>
       </c>
       <c r="P150" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -13416,7 +13413,7 @@
         <v>17.2</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -13457,7 +13454,7 @@
         <v>3</v>
       </c>
       <c r="P152" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -13498,7 +13495,7 @@
         <v>1</v>
       </c>
       <c r="P153" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -13539,7 +13536,7 @@
         <v>116</v>
       </c>
       <c r="P154" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -13580,7 +13577,7 @@
         <v>116</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -13621,7 +13618,7 @@
         <v>3</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -13662,7 +13659,7 @@
         <v>38</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -13706,7 +13703,7 @@
         <v>102</v>
       </c>
       <c r="P158" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -13747,7 +13744,7 @@
         <v>6</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -13788,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="P160" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -13829,7 +13826,7 @@
         <v>6</v>
       </c>
       <c r="P161" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -13870,7 +13867,7 @@
         <v>3</v>
       </c>
       <c r="P162" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -13911,7 +13908,7 @@
         <v>378</v>
       </c>
       <c r="P163" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -13955,7 +13952,7 @@
         <v>462</v>
       </c>
       <c r="P164" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -13990,7 +13987,7 @@
         <v>16.7</v>
       </c>
       <c r="P165" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -14025,7 +14022,7 @@
         <v>19</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -14063,7 +14060,7 @@
         <v>474</v>
       </c>
       <c r="P167" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -14104,7 +14101,7 @@
         <v>0</v>
       </c>
       <c r="P168" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -14145,7 +14142,7 @@
         <v>6</v>
       </c>
       <c r="P169" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -14183,7 +14180,7 @@
         <v>51</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -14224,7 +14221,7 @@
         <v>17</v>
       </c>
       <c r="P171" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -14259,7 +14256,7 @@
         <v>26</v>
       </c>
       <c r="P172" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -14303,7 +14300,7 @@
         <v>84</v>
       </c>
       <c r="P173" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -14344,7 +14341,7 @@
         <v>67</v>
       </c>
       <c r="P174" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -14385,7 +14382,7 @@
         <v>3</v>
       </c>
       <c r="P175" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -14426,7 +14423,7 @@
         <v>0</v>
       </c>
       <c r="P176" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -14470,7 +14467,7 @@
         <v>149</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -14511,7 +14508,7 @@
         <v>6</v>
       </c>
       <c r="P178" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -14555,7 +14552,7 @@
         <v>95</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -14593,7 +14590,7 @@
         <v>18</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -14634,7 +14631,7 @@
         <v>811</v>
       </c>
       <c r="P181" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -14675,7 +14672,7 @@
         <v>811</v>
       </c>
       <c r="P182" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -14716,7 +14713,7 @@
         <v>292</v>
       </c>
       <c r="P183" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -14757,7 +14754,7 @@
         <v>432</v>
       </c>
       <c r="P184" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -14798,7 +14795,7 @@
         <v>9</v>
       </c>
       <c r="P185" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -14839,7 +14836,7 @@
         <v>18</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -14880,7 +14877,7 @@
         <v>145</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -14921,7 +14918,7 @@
         <v>24</v>
       </c>
       <c r="P188" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -14962,7 +14959,7 @@
         <v>0</v>
       </c>
       <c r="P189" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -15003,7 +15000,7 @@
         <v>87</v>
       </c>
       <c r="P190" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -15044,7 +15041,7 @@
         <v>944</v>
       </c>
       <c r="P191" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -15082,7 +15079,7 @@
         <v>561</v>
       </c>
       <c r="P192" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -15120,7 +15117,7 @@
         <v>1399</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -15164,7 +15161,7 @@
         <v>1599</v>
       </c>
       <c r="P194" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -15205,7 +15202,7 @@
         <v>0</v>
       </c>
       <c r="P195" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -15249,7 +15246,7 @@
         <v>85</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -15290,7 +15287,7 @@
         <v>75</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -15331,7 +15328,7 @@
         <v>96</v>
       </c>
       <c r="P198" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -15410,7 +15407,7 @@
         <v>60</v>
       </c>
       <c r="P200" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -15454,7 +15451,7 @@
         <v>246</v>
       </c>
       <c r="P201" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -15495,7 +15492,7 @@
         <v>6</v>
       </c>
       <c r="P202" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -15536,7 +15533,7 @@
         <v>145</v>
       </c>
       <c r="P203" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -15580,7 +15577,7 @@
         <v>70</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -15621,7 +15618,7 @@
         <v>53</v>
       </c>
       <c r="P205" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -15665,7 +15662,7 @@
         <v>81</v>
       </c>
       <c r="P206" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -15706,7 +15703,7 @@
         <v>66</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -15747,7 +15744,7 @@
         <v>196</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -15788,7 +15785,7 @@
         <v>145</v>
       </c>
       <c r="P209" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -15829,7 +15826,7 @@
         <v>9</v>
       </c>
       <c r="P210" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -15908,7 +15905,7 @@
         <v>120</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -15949,7 +15946,7 @@
         <v>21</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -15990,7 +15987,7 @@
         <v>356</v>
       </c>
       <c r="P214" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -16031,7 +16028,7 @@
         <v>93</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -16072,7 +16069,7 @@
         <v>93</v>
       </c>
       <c r="P216" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16113,7 +16110,7 @@
         <v>87</v>
       </c>
       <c r="P217" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -16154,7 +16151,7 @@
         <v>60</v>
       </c>
       <c r="P218" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -16195,7 +16192,7 @@
         <v>2</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -16236,7 +16233,7 @@
         <v>85</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -16277,7 +16274,7 @@
         <v>216</v>
       </c>
       <c r="P221" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -16318,7 +16315,7 @@
         <v>22</v>
       </c>
       <c r="P222" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -16359,7 +16356,7 @@
         <v>42</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -16400,7 +16397,7 @@
         <v>6</v>
       </c>
       <c r="P224" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -16441,7 +16438,7 @@
         <v>6</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -16482,7 +16479,7 @@
         <v>24</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -16523,7 +16520,7 @@
         <v>65</v>
       </c>
       <c r="P227" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -16567,7 +16564,7 @@
         <v>228</v>
       </c>
       <c r="P228" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -16608,7 +16605,7 @@
         <v>146</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -16649,7 +16646,7 @@
         <v>0</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -16690,7 +16687,7 @@
         <v>12</v>
       </c>
       <c r="P231" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -16734,7 +16731,7 @@
         <v>219</v>
       </c>
       <c r="P232" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -16775,7 +16772,7 @@
         <v>47</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -16816,7 +16813,7 @@
         <v>232</v>
       </c>
       <c r="P234" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -16857,7 +16854,7 @@
         <v>18</v>
       </c>
       <c r="P235" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -16898,7 +16895,7 @@
         <v>54</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -16939,7 +16936,7 @@
         <v>138</v>
       </c>
       <c r="P237" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -16980,7 +16977,7 @@
         <v>138</v>
       </c>
       <c r="P238" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -17021,7 +17018,7 @@
         <v>6</v>
       </c>
       <c r="P239" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -17062,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="P240" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -17106,7 +17103,7 @@
         <v>219</v>
       </c>
       <c r="P241" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -17147,7 +17144,7 @@
         <v>47</v>
       </c>
       <c r="P242" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -17191,7 +17188,7 @@
         <v>120</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -17232,7 +17229,7 @@
         <v>81</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -17273,7 +17270,7 @@
         <v>36</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -17314,7 +17311,7 @@
         <v>59</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -17355,7 +17352,7 @@
         <v>118</v>
       </c>
       <c r="P247" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -17396,7 +17393,7 @@
         <v>0</v>
       </c>
       <c r="P248" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -17437,7 +17434,7 @@
         <v>427</v>
       </c>
       <c r="P249" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -17478,7 +17475,7 @@
         <v>24</v>
       </c>
       <c r="P250" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -17519,7 +17516,7 @@
         <v>24</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -17560,7 +17557,7 @@
         <v>24</v>
       </c>
       <c r="P252" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -17601,7 +17598,7 @@
         <v>84</v>
       </c>
       <c r="P253" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -17642,7 +17639,7 @@
         <v>186</v>
       </c>
       <c r="P254" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -17680,7 +17677,7 @@
         <v>363</v>
       </c>
       <c r="P255" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -17718,7 +17715,7 @@
         <v>186</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="257" spans="1:18">
@@ -17756,7 +17753,7 @@
         <v>442</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="258" spans="1:18">
@@ -17794,7 +17791,7 @@
         <v>671</v>
       </c>
       <c r="P258" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="259" spans="1:18">
@@ -17835,7 +17832,7 @@
         <v>33</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="260" spans="1:18">
@@ -17876,7 +17873,7 @@
         <v>111</v>
       </c>
       <c r="P260" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="261" spans="1:18">
@@ -17917,7 +17914,7 @@
         <v>174</v>
       </c>
       <c r="P261" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="262" spans="1:18">
@@ -17958,7 +17955,7 @@
         <v>1180</v>
       </c>
       <c r="P262" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -17999,7 +17996,7 @@
         <v>78</v>
       </c>
       <c r="P263" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -18040,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -18081,7 +18078,7 @@
         <v>6</v>
       </c>
       <c r="P265" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -18122,7 +18119,7 @@
         <v>296</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R266" t="s">
         <v>71</v>
@@ -18166,7 +18163,7 @@
         <v>165</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -18207,7 +18204,7 @@
         <v>0</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -18248,7 +18245,7 @@
         <v>1159</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -18286,7 +18283,7 @@
         <v>30</v>
       </c>
       <c r="P270" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -18327,7 +18324,7 @@
         <v>3</v>
       </c>
       <c r="P271" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -18365,7 +18362,7 @@
         <v>0</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="273" spans="1:18">
@@ -18403,7 +18400,7 @@
         <v>33.9</v>
       </c>
       <c r="P273" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="274" spans="1:18">
@@ -18435,7 +18432,7 @@
         <v>8.9</v>
       </c>
       <c r="P274" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="275" spans="1:18">
@@ -18473,7 +18470,7 @@
         <v>24</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="276" spans="1:18">
@@ -18514,7 +18511,7 @@
         <v>120</v>
       </c>
       <c r="P276" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="277" spans="1:18">
@@ -18552,7 +18549,7 @@
         <v>528</v>
       </c>
       <c r="P277" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="278" spans="1:18">
@@ -18587,7 +18584,7 @@
         <v>9</v>
       </c>
       <c r="P278" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="279" spans="1:18">
@@ -18622,7 +18619,7 @@
         <v>9</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="280" spans="1:18">
@@ -18660,7 +18657,7 @@
         <v>393</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="281" spans="1:18">
@@ -18698,7 +18695,7 @@
         <v>0</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="282" spans="1:18">
@@ -18733,7 +18730,7 @@
         <v>299</v>
       </c>
       <c r="P282" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="283" spans="1:18">
@@ -18771,7 +18768,7 @@
         <v>76</v>
       </c>
       <c r="P283" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="284" spans="1:18">
@@ -18809,7 +18806,7 @@
         <v>442</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R284" t="s">
         <v>71</v>
@@ -18847,7 +18844,7 @@
         <v>1181</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="286" spans="1:18">
@@ -18885,7 +18882,7 @@
         <v>12</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="287" spans="1:18">
@@ -18923,7 +18920,7 @@
         <v>169</v>
       </c>
       <c r="P287" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="288" spans="1:18">
@@ -18961,7 +18958,7 @@
         <v>63</v>
       </c>
       <c r="P288" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -19002,7 +18999,7 @@
         <v>31</v>
       </c>
       <c r="P289" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -19043,7 +19040,7 @@
         <v>219</v>
       </c>
       <c r="P290" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -19081,7 +19078,7 @@
         <v>38</v>
       </c>
       <c r="P291" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -19119,7 +19116,7 @@
         <v>0</v>
       </c>
       <c r="P292" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -19160,7 +19157,7 @@
         <v>0</v>
       </c>
       <c r="P293" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -19201,7 +19198,7 @@
         <v>0</v>
       </c>
       <c r="P294" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -19242,7 +19239,7 @@
         <v>940</v>
       </c>
       <c r="P295" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -19280,7 +19277,7 @@
         <v>66</v>
       </c>
       <c r="P296" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -19321,7 +19318,7 @@
         <v>0</v>
       </c>
       <c r="P297" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -19359,7 +19356,7 @@
         <v>180</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -19397,7 +19394,7 @@
         <v>0</v>
       </c>
       <c r="P299" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -19435,7 +19432,7 @@
         <v>3</v>
       </c>
       <c r="P300" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -19470,7 +19467,7 @@
         <v>6</v>
       </c>
       <c r="P301" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -19511,7 +19508,7 @@
         <v>35</v>
       </c>
       <c r="P302" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -19549,7 +19546,7 @@
         <v>787</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -19587,7 +19584,7 @@
         <v>787</v>
       </c>
       <c r="P304" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -19625,7 +19622,7 @@
         <v>12</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19666,7 +19663,7 @@
         <v>274</v>
       </c>
       <c r="P306" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -19707,7 +19704,7 @@
         <v>21</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -19745,7 +19742,7 @@
         <v>99</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -19786,7 +19783,7 @@
         <v>12</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19824,7 +19821,7 @@
         <v>102</v>
       </c>
       <c r="P310" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -19862,7 +19859,7 @@
         <v>327</v>
       </c>
       <c r="P311" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -19903,7 +19900,7 @@
         <v>120</v>
       </c>
       <c r="P312" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -19935,7 +19932,7 @@
         <v>15</v>
       </c>
       <c r="P313" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -19970,7 +19967,7 @@
         <v>54</v>
       </c>
       <c r="P314" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -20011,7 +20008,7 @@
         <v>27</v>
       </c>
       <c r="P315" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -20052,7 +20049,7 @@
         <v>0</v>
       </c>
       <c r="P316" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -20084,7 +20081,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="P317" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -20119,7 +20116,7 @@
         <v>231</v>
       </c>
       <c r="P318" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -20157,7 +20154,7 @@
         <v>12</v>
       </c>
       <c r="P319" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -20195,7 +20192,7 @@
         <v>63</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -20233,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="P321" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -20271,7 +20268,7 @@
         <v>263</v>
       </c>
       <c r="P322" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -20309,7 +20306,7 @@
         <v>102</v>
       </c>
       <c r="P323" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R323" t="s">
         <v>71</v>
@@ -20347,7 +20344,7 @@
         <v>456</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -20388,7 +20385,7 @@
         <v>12</v>
       </c>
       <c r="P325" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -20429,7 +20426,7 @@
         <v>12</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -20473,7 +20470,7 @@
         <v>10955</v>
       </c>
       <c r="P327" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -20508,7 +20505,7 @@
         <v>17.3</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -20552,7 +20549,7 @@
         <v>390</v>
       </c>
       <c r="P329" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -20596,7 +20593,7 @@
         <v>97</v>
       </c>
       <c r="P330" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -20631,7 +20628,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="P331" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -20666,7 +20663,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="P332" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -20704,7 +20701,7 @@
         <v>0</v>
       </c>
       <c r="P333" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -20748,7 +20745,7 @@
         <v>10955</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -20783,7 +20780,7 @@
         <v>324</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20821,7 +20818,7 @@
         <v>483</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -20859,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="P337" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -20903,7 +20900,7 @@
         <v>501</v>
       </c>
       <c r="P338" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -20947,7 +20944,7 @@
         <v>741</v>
       </c>
       <c r="P339" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -20988,7 +20985,7 @@
         <v>648</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -21029,7 +21026,7 @@
         <v>574</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -21073,7 +21070,7 @@
         <v>66</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -21114,7 +21111,7 @@
         <v>253</v>
       </c>
       <c r="P343" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -21155,7 +21152,7 @@
         <v>575</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -21199,7 +21196,7 @@
         <v>12</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21243,7 +21240,7 @@
         <v>341</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -21281,7 +21278,7 @@
         <v>394</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -21322,7 +21319,7 @@
         <v>281</v>
       </c>
       <c r="P348" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -21363,7 +21360,7 @@
         <v>27</v>
       </c>
       <c r="P349" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -21407,7 +21404,7 @@
         <v>0</v>
       </c>
       <c r="P350" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -21448,7 +21445,7 @@
         <v>60</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -21489,7 +21486,7 @@
         <v>368</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="353" spans="1:18">
@@ -21530,7 +21527,7 @@
         <v>152</v>
       </c>
       <c r="P353" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="354" spans="1:18">
@@ -21571,7 +21568,7 @@
         <v>693</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="355" spans="1:18">
@@ -21612,7 +21609,7 @@
         <v>363</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="356" spans="1:18">
@@ -21653,7 +21650,7 @@
         <v>1425</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="357" spans="1:18">
@@ -21694,7 +21691,7 @@
         <v>84</v>
       </c>
       <c r="P357" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="358" spans="1:18">
@@ -21735,7 +21732,7 @@
         <v>42</v>
       </c>
       <c r="P358" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="359" spans="1:18">
@@ -21776,7 +21773,7 @@
         <v>165</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R359" t="s">
         <v>71</v>
@@ -21820,7 +21817,7 @@
         <v>3214</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="361" spans="1:18">
@@ -21861,7 +21858,7 @@
         <v>0</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="362" spans="1:18">
@@ -21905,7 +21902,7 @@
         <v>165</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="363" spans="1:18">
@@ -21946,7 +21943,7 @@
         <v>24</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="364" spans="1:18">
@@ -21990,7 +21987,7 @@
         <v>182</v>
       </c>
       <c r="P364" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="365" spans="1:18">
@@ -22031,7 +22028,7 @@
         <v>357</v>
       </c>
       <c r="P365" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="366" spans="1:18">
@@ -22075,7 +22072,7 @@
         <v>474</v>
       </c>
       <c r="P366" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="367" spans="1:18">
@@ -22116,7 +22113,7 @@
         <v>321</v>
       </c>
       <c r="P367" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="368" spans="1:18">
@@ -22154,7 +22151,7 @@
         <v>37</v>
       </c>
       <c r="P368" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -22195,7 +22192,7 @@
         <v>351</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22236,7 +22233,7 @@
         <v>14790</v>
       </c>
       <c r="P370" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -22277,7 +22274,7 @@
         <v>0</v>
       </c>
       <c r="P371" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -22359,7 +22356,7 @@
         <v>0</v>
       </c>
       <c r="P373" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -22400,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="P374" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -22441,7 +22438,7 @@
         <v>0</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -22485,7 +22482,7 @@
         <v>6</v>
       </c>
       <c r="P376" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -22526,7 +22523,7 @@
         <v>0</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -22567,7 +22564,7 @@
         <v>0</v>
       </c>
       <c r="P378" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -22608,7 +22605,7 @@
         <v>0</v>
       </c>
       <c r="P379" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -22649,7 +22646,7 @@
         <v>0</v>
       </c>
       <c r="P380" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -22690,7 +22687,7 @@
         <v>0</v>
       </c>
       <c r="P381" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -22731,7 +22728,7 @@
         <v>0</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22772,7 +22769,7 @@
         <v>37</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -22813,7 +22810,7 @@
         <v>539</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -22854,7 +22851,7 @@
         <v>264</v>
       </c>
       <c r="P385" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -22892,7 +22889,7 @@
         <v>7.1</v>
       </c>
       <c r="P386" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -22930,7 +22927,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="P387" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -22971,7 +22968,7 @@
         <v>0</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -23012,7 +23009,7 @@
         <v>113</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -23053,7 +23050,7 @@
         <v>71</v>
       </c>
       <c r="P390" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -23094,7 +23091,7 @@
         <v>152</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -23135,7 +23132,7 @@
         <v>324</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -23176,7 +23173,7 @@
         <v>99</v>
       </c>
       <c r="P393" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -23217,7 +23214,7 @@
         <v>915</v>
       </c>
       <c r="P394" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -23258,7 +23255,7 @@
         <v>219</v>
       </c>
       <c r="P395" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -23299,7 +23296,7 @@
         <v>96</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -23340,7 +23337,7 @@
         <v>219</v>
       </c>
       <c r="P397" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -23381,7 +23378,7 @@
         <v>27</v>
       </c>
       <c r="P398" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -23425,7 +23422,7 @@
         <v>303</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -23469,7 +23466,7 @@
         <v>187</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -23510,7 +23507,7 @@
         <v>340</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -23551,7 +23548,7 @@
         <v>46</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -23592,7 +23589,7 @@
         <v>78</v>
       </c>
       <c r="P403" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -23633,7 +23630,7 @@
         <v>36</v>
       </c>
       <c r="P404" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -23671,7 +23668,7 @@
         <v>11.4</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -23712,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -23753,7 +23750,7 @@
         <v>0</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -23794,7 +23791,7 @@
         <v>0</v>
       </c>
       <c r="P408" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -23835,7 +23832,7 @@
         <v>177</v>
       </c>
       <c r="P409" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23879,7 +23876,7 @@
         <v>0</v>
       </c>
       <c r="P410" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23920,7 +23917,7 @@
         <v>0</v>
       </c>
       <c r="P411" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23964,7 +23961,7 @@
         <v>0</v>
       </c>
       <c r="P412" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -24008,7 +24005,7 @@
         <v>42</v>
       </c>
       <c r="P413" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -24052,7 +24049,7 @@
         <v>65</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -24093,7 +24090,7 @@
         <v>0</v>
       </c>
       <c r="P415" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -24131,7 +24128,7 @@
         <v>31</v>
       </c>
       <c r="P416" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -24175,7 +24172,7 @@
         <v>270.39999999999998</v>
       </c>
       <c r="P417" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -24216,7 +24213,7 @@
         <v>18</v>
       </c>
       <c r="P418" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -24257,7 +24254,7 @@
         <v>6</v>
       </c>
       <c r="P419" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -24298,7 +24295,7 @@
         <v>49</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -24339,7 +24336,7 @@
         <v>17.8</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -24380,7 +24377,7 @@
         <v>53</v>
       </c>
       <c r="P422" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -24421,7 +24418,7 @@
         <v>22.3</v>
       </c>
       <c r="P423" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -24465,7 +24462,7 @@
         <v>42</v>
       </c>
       <c r="P424" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -24506,7 +24503,7 @@
         <v>171</v>
       </c>
       <c r="P425" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -24547,7 +24544,7 @@
         <v>171</v>
       </c>
       <c r="P426" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -24591,7 +24588,7 @@
         <v>12</v>
       </c>
       <c r="P427" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -24635,7 +24632,7 @@
         <v>171</v>
       </c>
       <c r="P428" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -24679,7 +24676,7 @@
         <v>171</v>
       </c>
       <c r="P429" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24717,7 +24714,7 @@
         <v>18.3</v>
       </c>
       <c r="P430" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24761,7 +24758,7 @@
         <v>12</v>
       </c>
       <c r="P431" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24796,7 +24793,7 @@
         <v>31.7</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24834,7 +24831,7 @@
         <v>30</v>
       </c>
       <c r="P433" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24913,7 +24910,7 @@
         <v>95</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24954,7 +24951,7 @@
         <v>2215</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24992,7 +24989,7 @@
         <v>2215</v>
       </c>
       <c r="P437" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -25033,7 +25030,7 @@
         <v>279</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -25077,7 +25074,7 @@
         <v>205</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -25115,7 +25112,7 @@
         <v>14.5</v>
       </c>
       <c r="P440" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -25156,7 +25153,7 @@
         <v>0</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -25194,7 +25191,7 @@
         <v>37</v>
       </c>
       <c r="P442" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -25235,7 +25232,7 @@
         <v>324</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -25276,7 +25273,7 @@
         <v>368</v>
       </c>
       <c r="P444" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -25317,7 +25314,7 @@
         <v>969</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -25358,7 +25355,7 @@
         <v>0</v>
       </c>
       <c r="P446" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -25399,7 +25396,7 @@
         <v>113</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -25440,7 +25437,7 @@
         <v>71</v>
       </c>
       <c r="P448" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="449" spans="1:18">
@@ -25481,7 +25478,7 @@
         <v>240</v>
       </c>
       <c r="P449" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="450" spans="1:18">
@@ -25522,7 +25519,7 @@
         <v>66</v>
       </c>
       <c r="P450" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R450" t="s">
         <v>71</v>
@@ -25566,7 +25563,7 @@
         <v>549</v>
       </c>
       <c r="P451" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="452" spans="1:18">
@@ -25607,7 +25604,7 @@
         <v>3</v>
       </c>
       <c r="P452" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="453" spans="1:18">
@@ -25648,7 +25645,7 @@
         <v>288</v>
       </c>
       <c r="P453" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="454" spans="1:18">
@@ -25689,7 +25686,7 @@
         <v>54</v>
       </c>
       <c r="P454" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="455" spans="1:18">
@@ -25727,7 +25724,7 @@
         <v>666</v>
       </c>
       <c r="P455" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="456" spans="1:18">
@@ -25771,7 +25768,7 @@
         <v>318</v>
       </c>
       <c r="P456" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="457" spans="1:18">
@@ -25809,7 +25806,7 @@
         <v>4.95</v>
       </c>
       <c r="P457" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="458" spans="1:18">
@@ -25850,7 +25847,7 @@
         <v>133</v>
       </c>
       <c r="P458" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="459" spans="1:18">
@@ -25891,7 +25888,7 @@
         <v>0</v>
       </c>
       <c r="P459" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="460" spans="1:18">
@@ -25932,7 +25929,7 @@
         <v>0</v>
       </c>
       <c r="P460" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="461" spans="1:18">
@@ -25973,7 +25970,7 @@
         <v>0</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="462" spans="1:18">
@@ -26014,7 +26011,7 @@
         <v>1327</v>
       </c>
       <c r="P462" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="463" spans="1:18">
@@ -26055,7 +26052,7 @@
         <v>6</v>
       </c>
       <c r="P463" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="464" spans="1:18">
@@ -26096,7 +26093,7 @@
         <v>30</v>
       </c>
       <c r="P464" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -26137,7 +26134,7 @@
         <v>36</v>
       </c>
       <c r="P465" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -26178,7 +26175,7 @@
         <v>18</v>
       </c>
       <c r="P466" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -26219,7 +26216,7 @@
         <v>662</v>
       </c>
       <c r="P467" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -26260,7 +26257,7 @@
         <v>64</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -26301,7 +26298,7 @@
         <v>0</v>
       </c>
       <c r="P469" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26342,7 +26339,7 @@
         <v>36</v>
       </c>
       <c r="P470" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26383,7 +26380,7 @@
         <v>36</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -26424,7 +26421,7 @@
         <v>55</v>
       </c>
       <c r="P472" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -26465,7 +26462,7 @@
         <v>4411</v>
       </c>
       <c r="P473" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26500,7 +26497,7 @@
         <v>6.2</v>
       </c>
       <c r="P474" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26535,7 +26532,7 @@
         <v>8.99</v>
       </c>
       <c r="P475" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26573,7 +26570,7 @@
         <v>5</v>
       </c>
       <c r="P476" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26611,7 +26608,7 @@
         <v>6532</v>
       </c>
       <c r="P477" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26649,7 +26646,7 @@
         <v>418</v>
       </c>
       <c r="P478" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26684,7 +26681,7 @@
         <v>23.9</v>
       </c>
       <c r="P479" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26722,7 +26719,7 @@
         <v>34</v>
       </c>
       <c r="P480" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26760,7 +26757,7 @@
         <v>995</v>
       </c>
       <c r="P481" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26798,7 +26795,7 @@
         <v>31</v>
       </c>
       <c r="P482" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26836,7 +26833,7 @@
         <v>5</v>
       </c>
       <c r="P483" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26874,7 +26871,7 @@
         <v>60</v>
       </c>
       <c r="P484" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26912,7 +26909,7 @@
         <v>417</v>
       </c>
       <c r="P485" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26950,7 +26947,7 @@
         <v>777</v>
       </c>
       <c r="P486" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26988,7 +26985,7 @@
         <v>428</v>
       </c>
       <c r="P487" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -27026,7 +27023,7 @@
         <v>0</v>
       </c>
       <c r="P488" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27064,7 +27061,7 @@
         <v>36</v>
       </c>
       <c r="P489" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -27102,7 +27099,7 @@
         <v>0</v>
       </c>
       <c r="P490" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -27140,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="P491" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -27178,7 +27175,7 @@
         <v>31</v>
       </c>
       <c r="P492" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27216,7 +27213,7 @@
         <v>41</v>
       </c>
       <c r="P493" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27254,7 +27251,7 @@
         <v>0</v>
       </c>
       <c r="P494" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27292,7 +27289,7 @@
         <v>0</v>
       </c>
       <c r="P495" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27330,7 +27327,7 @@
         <v>3</v>
       </c>
       <c r="P496" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27368,7 +27365,7 @@
         <v>23</v>
       </c>
       <c r="P497" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27409,7 +27406,7 @@
         <v>3</v>
       </c>
       <c r="P498" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27450,7 +27447,7 @@
         <v>31</v>
       </c>
       <c r="P499" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27491,7 +27488,7 @@
         <v>5</v>
       </c>
       <c r="P500" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27532,7 +27529,7 @@
         <v>5</v>
       </c>
       <c r="P501" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27573,7 +27570,7 @@
         <v>5</v>
       </c>
       <c r="P502" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27611,7 +27608,7 @@
         <v>6</v>
       </c>
       <c r="P503" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27649,7 +27646,7 @@
         <v>6</v>
       </c>
       <c r="P504" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27684,7 +27681,7 @@
         <v>14.85</v>
       </c>
       <c r="P505" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27719,7 +27716,7 @@
         <v>38.1</v>
       </c>
       <c r="P506" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27754,7 +27751,7 @@
         <v>35.5</v>
       </c>
       <c r="P507" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27789,7 +27786,7 @@
         <v>16.149999999999999</v>
       </c>
       <c r="P508" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27827,7 +27824,7 @@
         <v>112</v>
       </c>
       <c r="P509" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27862,7 +27859,7 @@
         <v>45</v>
       </c>
       <c r="P510" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27897,7 +27894,7 @@
         <v>45</v>
       </c>
       <c r="P511" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27935,7 +27932,7 @@
         <v>68</v>
       </c>
       <c r="P512" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27973,7 +27970,7 @@
         <v>155</v>
       </c>
       <c r="P513" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28011,7 +28008,7 @@
         <v>7</v>
       </c>
       <c r="P514" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28362,7 +28359,7 @@
         <v>58</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>61</v>
@@ -28374,13 +28371,13 @@
         <v>1483</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>1484</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>1480</v>
@@ -49113,6 +49110,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
@@ -49123,23 +49129,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC8EC0E4-369C-458D-9531-282432A8BA3E}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90C957E-6483-40C7-8474-E983589994D6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10359" uniqueCount="2246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10347" uniqueCount="2246">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -1888,91 +1888,91 @@
     <t>Cuvée Maclura</t>
   </si>
   <si>
+    <t>28400523</t>
+  </si>
+  <si>
+    <t>Côtes du Rhône Villages</t>
+  </si>
+  <si>
+    <t>La Petite Bellane</t>
+  </si>
+  <si>
+    <t>Clos Bellane</t>
+  </si>
+  <si>
+    <t>46300522</t>
+  </si>
+  <si>
+    <t>Cuvée Setier</t>
+  </si>
+  <si>
+    <t>28400223</t>
+  </si>
+  <si>
+    <t>Côtes du Rhône Valreas</t>
+  </si>
+  <si>
+    <t>28400322</t>
+  </si>
+  <si>
+    <t>Les Echalas</t>
+  </si>
+  <si>
+    <t>31902023</t>
+  </si>
+  <si>
+    <t>15001824</t>
+  </si>
+  <si>
+    <t>Dne.Paul Jaboulet Aîné</t>
+  </si>
+  <si>
+    <t>46300324</t>
+  </si>
+  <si>
+    <t>Cuvée Lône</t>
+  </si>
+  <si>
+    <t>13800123</t>
+  </si>
+  <si>
+    <t>La Truffière</t>
+  </si>
+  <si>
+    <t>28400123</t>
+  </si>
+  <si>
+    <t>28400423</t>
+  </si>
+  <si>
+    <t>Méridional</t>
+  </si>
+  <si>
+    <t>Ventoux</t>
+  </si>
+  <si>
+    <t>Saint Pétrarque</t>
+  </si>
+  <si>
+    <t>Gabriel Meffre</t>
+  </si>
+  <si>
+    <t>50000120</t>
+  </si>
+  <si>
+    <t>Vox</t>
+  </si>
+  <si>
+    <t>Via Caritatis</t>
+  </si>
+  <si>
+    <t>12300123</t>
+  </si>
+  <si>
+    <t>Orca</t>
+  </si>
+  <si>
     <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>28400523</t>
-  </si>
-  <si>
-    <t>Côtes du Rhône Villages</t>
-  </si>
-  <si>
-    <t>La Petite Bellane</t>
-  </si>
-  <si>
-    <t>Clos Bellane</t>
-  </si>
-  <si>
-    <t>46300522</t>
-  </si>
-  <si>
-    <t>Cuvée Setier</t>
-  </si>
-  <si>
-    <t>28400223</t>
-  </si>
-  <si>
-    <t>Côtes du Rhône Valreas</t>
-  </si>
-  <si>
-    <t>28400322</t>
-  </si>
-  <si>
-    <t>Les Echalas</t>
-  </si>
-  <si>
-    <t>31902023</t>
-  </si>
-  <si>
-    <t>15001824</t>
-  </si>
-  <si>
-    <t>Dne.Paul Jaboulet Aîné</t>
-  </si>
-  <si>
-    <t>46300324</t>
-  </si>
-  <si>
-    <t>Cuvée Lône</t>
-  </si>
-  <si>
-    <t>13800123</t>
-  </si>
-  <si>
-    <t>La Truffière</t>
-  </si>
-  <si>
-    <t>28400123</t>
-  </si>
-  <si>
-    <t>28400423</t>
-  </si>
-  <si>
-    <t>Méridional</t>
-  </si>
-  <si>
-    <t>Ventoux</t>
-  </si>
-  <si>
-    <t>Saint Pétrarque</t>
-  </si>
-  <si>
-    <t>Gabriel Meffre</t>
-  </si>
-  <si>
-    <t>50000120</t>
-  </si>
-  <si>
-    <t>Vox</t>
-  </si>
-  <si>
-    <t>Via Caritatis</t>
-  </si>
-  <si>
-    <t>12300123</t>
-  </si>
-  <si>
-    <t>Orca</t>
   </si>
   <si>
     <t>31900521</t>
@@ -15400,13 +15400,13 @@
       <c r="M200">
         <v>60</v>
       </c>
-      <c r="P200" s="8" t="s">
-        <v>615</v>
+      <c r="P200" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="201" spans="1:16">
       <c r="A201" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B201" t="s">
         <v>56</v>
@@ -15421,13 +15421,13 @@
         <v>79</v>
       </c>
       <c r="F201" t="s">
+        <v>616</v>
+      </c>
+      <c r="G201" t="s">
         <v>617</v>
       </c>
-      <c r="G201" t="s">
+      <c r="H201" t="s">
         <v>618</v>
-      </c>
-      <c r="H201" t="s">
-        <v>619</v>
       </c>
       <c r="I201" t="s">
         <v>62</v>
@@ -15444,13 +15444,13 @@
       <c r="M201">
         <v>246</v>
       </c>
-      <c r="P201" s="8" t="s">
-        <v>615</v>
+      <c r="P201" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="202" spans="1:16">
       <c r="A202" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B202" t="s">
         <v>56</v>
@@ -15465,10 +15465,10 @@
         <v>79</v>
       </c>
       <c r="F202" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G202" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H202" t="s">
         <v>579</v>
@@ -15485,13 +15485,13 @@
       <c r="M202">
         <v>6</v>
       </c>
-      <c r="P202" s="8" t="s">
-        <v>615</v>
+      <c r="P202" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="203" spans="1:16">
       <c r="A203" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B203" t="s">
         <v>56</v>
@@ -15506,10 +15506,10 @@
         <v>79</v>
       </c>
       <c r="F203" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H203" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I203" t="s">
         <v>62</v>
@@ -15526,13 +15526,13 @@
       <c r="M203">
         <v>145</v>
       </c>
-      <c r="P203" s="8" t="s">
-        <v>615</v>
+      <c r="P203" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="204" spans="1:16">
       <c r="A204" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B204" t="s">
         <v>56</v>
@@ -15547,13 +15547,13 @@
         <v>79</v>
       </c>
       <c r="F204" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G204" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H204" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I204" t="s">
         <v>62</v>
@@ -15570,13 +15570,13 @@
       <c r="M204">
         <v>70</v>
       </c>
-      <c r="P204" s="8" t="s">
-        <v>615</v>
+      <c r="P204" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="205" spans="1:16">
       <c r="A205" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B205" t="s">
         <v>56</v>
@@ -15611,13 +15611,13 @@
       <c r="M205">
         <v>53</v>
       </c>
-      <c r="P205" s="8" t="s">
-        <v>615</v>
+      <c r="P205" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="206" spans="1:16">
       <c r="A206" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B206" t="s">
         <v>56</v>
@@ -15638,7 +15638,7 @@
         <v>602</v>
       </c>
       <c r="H206" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I206" t="s">
         <v>62</v>
@@ -15655,13 +15655,13 @@
       <c r="M206">
         <v>81</v>
       </c>
-      <c r="P206" s="8" t="s">
-        <v>615</v>
+      <c r="P206" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="207" spans="1:16">
       <c r="A207" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B207" t="s">
         <v>56</v>
@@ -15679,7 +15679,7 @@
         <v>590</v>
       </c>
       <c r="G207" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H207" t="s">
         <v>579</v>
@@ -15696,13 +15696,13 @@
       <c r="M207">
         <v>66</v>
       </c>
-      <c r="P207" s="8" t="s">
-        <v>615</v>
+      <c r="P207" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="208" spans="1:16">
       <c r="A208" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B208" t="s">
         <v>56</v>
@@ -15720,7 +15720,7 @@
         <v>590</v>
       </c>
       <c r="G208" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H208" t="s">
         <v>606</v>
@@ -15737,13 +15737,13 @@
       <c r="M208">
         <v>196</v>
       </c>
-      <c r="P208" s="8" t="s">
-        <v>615</v>
+      <c r="P208" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="209" spans="1:16">
       <c r="A209" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B209" t="s">
         <v>56</v>
@@ -15758,10 +15758,10 @@
         <v>58</v>
       </c>
       <c r="F209" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H209" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I209" t="s">
         <v>62</v>
@@ -15778,13 +15778,13 @@
       <c r="M209">
         <v>145</v>
       </c>
-      <c r="P209" s="8" t="s">
-        <v>615</v>
+      <c r="P209" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="210" spans="1:16">
       <c r="A210" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B210" t="s">
         <v>56</v>
@@ -15799,13 +15799,13 @@
         <v>58</v>
       </c>
       <c r="F210" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G210" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H210" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J210" t="s">
         <v>63</v>
@@ -15819,8 +15819,8 @@
       <c r="M210">
         <v>9</v>
       </c>
-      <c r="P210" s="8" t="s">
-        <v>615</v>
+      <c r="P210" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -15834,19 +15834,19 @@
         <v>559</v>
       </c>
       <c r="D211" t="s">
+        <v>634</v>
+      </c>
+      <c r="E211" t="s">
+        <v>79</v>
+      </c>
+      <c r="F211" t="s">
         <v>635</v>
       </c>
-      <c r="E211" t="s">
-        <v>79</v>
-      </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>636</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>637</v>
-      </c>
-      <c r="H211" t="s">
-        <v>638</v>
       </c>
       <c r="J211">
         <v>2025</v>
@@ -15863,7 +15863,7 @@
     </row>
     <row r="212" spans="1:16">
       <c r="A212" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B212" t="s">
         <v>56</v>
@@ -15872,19 +15872,19 @@
         <v>559</v>
       </c>
       <c r="D212" t="s">
+        <v>634</v>
+      </c>
+      <c r="E212" t="s">
+        <v>79</v>
+      </c>
+      <c r="F212" t="s">
         <v>635</v>
       </c>
-      <c r="E212" t="s">
-        <v>79</v>
-      </c>
-      <c r="F212" t="s">
-        <v>636</v>
-      </c>
       <c r="G212" t="s">
+        <v>639</v>
+      </c>
+      <c r="H212" t="s">
         <v>640</v>
-      </c>
-      <c r="H212" t="s">
-        <v>641</v>
       </c>
       <c r="J212" t="s">
         <v>104</v>
@@ -15898,13 +15898,13 @@
       <c r="M212">
         <v>120</v>
       </c>
-      <c r="P212" s="8" t="s">
-        <v>615</v>
+      <c r="P212" s="8">
+        <v>46155</v>
       </c>
     </row>
     <row r="213" spans="1:16">
       <c r="A213" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B213" t="s">
         <v>56</v>
@@ -15913,16 +15913,16 @@
         <v>559</v>
       </c>
       <c r="D213" t="s">
+        <v>634</v>
+      </c>
+      <c r="E213" t="s">
+        <v>79</v>
+      </c>
+      <c r="F213" t="s">
         <v>635</v>
       </c>
-      <c r="E213" t="s">
-        <v>79</v>
-      </c>
-      <c r="F213" t="s">
-        <v>636</v>
-      </c>
       <c r="G213" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H213" t="s">
         <v>570</v>
@@ -15940,7 +15940,7 @@
         <v>21</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -15954,7 +15954,7 @@
         <v>559</v>
       </c>
       <c r="D214" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E214" t="s">
         <v>79</v>
@@ -15966,7 +15966,7 @@
         <v>646</v>
       </c>
       <c r="H214" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J214" t="s">
         <v>128</v>
@@ -15981,7 +15981,7 @@
         <v>356</v>
       </c>
       <c r="P214" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -15995,7 +15995,7 @@
         <v>559</v>
       </c>
       <c r="D215" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E215" t="s">
         <v>79</v>
@@ -16022,7 +16022,7 @@
         <v>93</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -16036,7 +16036,7 @@
         <v>559</v>
       </c>
       <c r="D216" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E216" t="s">
         <v>79</v>
@@ -16063,7 +16063,7 @@
         <v>93</v>
       </c>
       <c r="P216" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -16077,19 +16077,19 @@
         <v>559</v>
       </c>
       <c r="D217" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E217" t="s">
         <v>58</v>
       </c>
       <c r="F217" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G217" t="s">
+        <v>639</v>
+      </c>
+      <c r="H217" t="s">
         <v>640</v>
-      </c>
-      <c r="H217" t="s">
-        <v>641</v>
       </c>
       <c r="J217" t="s">
         <v>93</v>
@@ -16104,7 +16104,7 @@
         <v>87</v>
       </c>
       <c r="P217" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -16118,7 +16118,7 @@
         <v>559</v>
       </c>
       <c r="D218" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E218" t="s">
         <v>58</v>
@@ -16145,7 +16145,7 @@
         <v>60</v>
       </c>
       <c r="P218" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -16159,7 +16159,7 @@
         <v>559</v>
       </c>
       <c r="D219" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E219" t="s">
         <v>58</v>
@@ -16186,7 +16186,7 @@
         <v>2</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -16200,7 +16200,7 @@
         <v>559</v>
       </c>
       <c r="D220" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E220" t="s">
         <v>79</v>
@@ -16227,7 +16227,7 @@
         <v>85</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -16241,7 +16241,7 @@
         <v>559</v>
       </c>
       <c r="D221" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E221" t="s">
         <v>79</v>
@@ -16268,7 +16268,7 @@
         <v>216</v>
       </c>
       <c r="P221" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -16282,7 +16282,7 @@
         <v>559</v>
       </c>
       <c r="D222" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E222" t="s">
         <v>79</v>
@@ -16309,7 +16309,7 @@
         <v>22</v>
       </c>
       <c r="P222" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -16350,7 +16350,7 @@
         <v>42</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -16391,7 +16391,7 @@
         <v>6</v>
       </c>
       <c r="P224" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -16432,7 +16432,7 @@
         <v>6</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -16473,7 +16473,7 @@
         <v>24</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -16499,7 +16499,7 @@
         <v>675</v>
       </c>
       <c r="H227" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J227" t="s">
         <v>123</v>
@@ -16514,7 +16514,7 @@
         <v>65</v>
       </c>
       <c r="P227" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -16558,7 +16558,7 @@
         <v>228</v>
       </c>
       <c r="P228" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -16584,7 +16584,7 @@
         <v>680</v>
       </c>
       <c r="H229" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J229" t="s">
         <v>63</v>
@@ -16599,7 +16599,7 @@
         <v>146</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -16640,7 +16640,7 @@
         <v>0</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -16681,7 +16681,7 @@
         <v>12</v>
       </c>
       <c r="P231" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -16725,7 +16725,7 @@
         <v>219</v>
       </c>
       <c r="P232" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -16766,7 +16766,7 @@
         <v>47</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -16807,7 +16807,7 @@
         <v>232</v>
       </c>
       <c r="P234" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -16848,7 +16848,7 @@
         <v>18</v>
       </c>
       <c r="P235" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -16889,7 +16889,7 @@
         <v>54</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -16930,7 +16930,7 @@
         <v>138</v>
       </c>
       <c r="P237" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -16971,7 +16971,7 @@
         <v>138</v>
       </c>
       <c r="P238" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -17012,7 +17012,7 @@
         <v>6</v>
       </c>
       <c r="P239" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -17053,7 +17053,7 @@
         <v>0</v>
       </c>
       <c r="P240" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -17097,7 +17097,7 @@
         <v>219</v>
       </c>
       <c r="P241" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -17138,7 +17138,7 @@
         <v>47</v>
       </c>
       <c r="P242" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -17182,7 +17182,7 @@
         <v>120</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -17208,7 +17208,7 @@
         <v>715</v>
       </c>
       <c r="H244" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J244" t="s">
         <v>63</v>
@@ -17223,7 +17223,7 @@
         <v>81</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -17264,7 +17264,7 @@
         <v>36</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -17305,7 +17305,7 @@
         <v>59</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -17346,7 +17346,7 @@
         <v>118</v>
       </c>
       <c r="P247" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -17387,7 +17387,7 @@
         <v>0</v>
       </c>
       <c r="P248" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -17428,7 +17428,7 @@
         <v>427</v>
       </c>
       <c r="P249" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -17469,7 +17469,7 @@
         <v>24</v>
       </c>
       <c r="P250" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -17510,7 +17510,7 @@
         <v>24</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -17551,7 +17551,7 @@
         <v>24</v>
       </c>
       <c r="P252" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -17592,7 +17592,7 @@
         <v>84</v>
       </c>
       <c r="P253" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -17618,7 +17618,7 @@
         <v>675</v>
       </c>
       <c r="H254" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J254" t="s">
         <v>63</v>
@@ -17633,7 +17633,7 @@
         <v>186</v>
       </c>
       <c r="P254" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -17671,7 +17671,7 @@
         <v>363</v>
       </c>
       <c r="P255" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -17709,7 +17709,7 @@
         <v>186</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="257" spans="1:18">
@@ -17747,7 +17747,7 @@
         <v>442</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="258" spans="1:18">
@@ -17785,7 +17785,7 @@
         <v>671</v>
       </c>
       <c r="P258" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="259" spans="1:18">
@@ -17826,7 +17826,7 @@
         <v>33</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="260" spans="1:18">
@@ -17867,7 +17867,7 @@
         <v>111</v>
       </c>
       <c r="P260" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="261" spans="1:18">
@@ -17908,7 +17908,7 @@
         <v>174</v>
       </c>
       <c r="P261" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="262" spans="1:18">
@@ -17949,7 +17949,7 @@
         <v>1180</v>
       </c>
       <c r="P262" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -17990,7 +17990,7 @@
         <v>78</v>
       </c>
       <c r="P263" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -18031,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -18072,7 +18072,7 @@
         <v>6</v>
       </c>
       <c r="P265" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -18113,7 +18113,7 @@
         <v>296</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="R266" t="s">
         <v>70</v>
@@ -18157,7 +18157,7 @@
         <v>165</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -18198,7 +18198,7 @@
         <v>0</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -18239,7 +18239,7 @@
         <v>1159</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -18277,7 +18277,7 @@
         <v>30</v>
       </c>
       <c r="P270" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -18318,7 +18318,7 @@
         <v>3</v>
       </c>
       <c r="P271" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -18356,7 +18356,7 @@
         <v>0</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="273" spans="1:18">
@@ -18394,7 +18394,7 @@
         <v>33.9</v>
       </c>
       <c r="P273" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="274" spans="1:18">
@@ -18426,7 +18426,7 @@
         <v>8.9</v>
       </c>
       <c r="P274" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="275" spans="1:18">
@@ -18464,7 +18464,7 @@
         <v>24</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="276" spans="1:18">
@@ -18505,7 +18505,7 @@
         <v>120</v>
       </c>
       <c r="P276" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="277" spans="1:18">
@@ -18543,7 +18543,7 @@
         <v>528</v>
       </c>
       <c r="P277" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="278" spans="1:18">
@@ -18578,7 +18578,7 @@
         <v>9</v>
       </c>
       <c r="P278" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="279" spans="1:18">
@@ -18613,7 +18613,7 @@
         <v>9</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="280" spans="1:18">
@@ -18651,7 +18651,7 @@
         <v>393</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="281" spans="1:18">
@@ -18689,7 +18689,7 @@
         <v>0</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="282" spans="1:18">
@@ -18724,7 +18724,7 @@
         <v>299</v>
       </c>
       <c r="P282" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="283" spans="1:18">
@@ -18762,7 +18762,7 @@
         <v>76</v>
       </c>
       <c r="P283" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="284" spans="1:18">
@@ -18800,7 +18800,7 @@
         <v>442</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="R284" t="s">
         <v>70</v>
@@ -18838,7 +18838,7 @@
         <v>1181</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="286" spans="1:18">
@@ -18876,7 +18876,7 @@
         <v>12</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="287" spans="1:18">
@@ -18914,7 +18914,7 @@
         <v>169</v>
       </c>
       <c r="P287" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="288" spans="1:18">
@@ -18952,7 +18952,7 @@
         <v>63</v>
       </c>
       <c r="P288" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -18993,7 +18993,7 @@
         <v>31</v>
       </c>
       <c r="P289" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -19034,7 +19034,7 @@
         <v>219</v>
       </c>
       <c r="P290" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -19072,7 +19072,7 @@
         <v>38</v>
       </c>
       <c r="P291" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="P292" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -19151,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="P293" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -19192,7 +19192,7 @@
         <v>0</v>
       </c>
       <c r="P294" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -19233,7 +19233,7 @@
         <v>940</v>
       </c>
       <c r="P295" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -19271,7 +19271,7 @@
         <v>66</v>
       </c>
       <c r="P296" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -19312,7 +19312,7 @@
         <v>0</v>
       </c>
       <c r="P297" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -19350,7 +19350,7 @@
         <v>180</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -19388,7 +19388,7 @@
         <v>0</v>
       </c>
       <c r="P299" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -19426,7 +19426,7 @@
         <v>3</v>
       </c>
       <c r="P300" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -19461,7 +19461,7 @@
         <v>6</v>
       </c>
       <c r="P301" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -19502,7 +19502,7 @@
         <v>35</v>
       </c>
       <c r="P302" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -19540,7 +19540,7 @@
         <v>787</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -19578,7 +19578,7 @@
         <v>787</v>
       </c>
       <c r="P304" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -19616,7 +19616,7 @@
         <v>12</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -19657,7 +19657,7 @@
         <v>274</v>
       </c>
       <c r="P306" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -19698,7 +19698,7 @@
         <v>21</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -19736,7 +19736,7 @@
         <v>99</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -19777,7 +19777,7 @@
         <v>12</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -19815,7 +19815,7 @@
         <v>102</v>
       </c>
       <c r="P310" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -19853,7 +19853,7 @@
         <v>327</v>
       </c>
       <c r="P311" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -19894,7 +19894,7 @@
         <v>120</v>
       </c>
       <c r="P312" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -19926,7 +19926,7 @@
         <v>15</v>
       </c>
       <c r="P313" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -19961,7 +19961,7 @@
         <v>54</v>
       </c>
       <c r="P314" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -20002,7 +20002,7 @@
         <v>27</v>
       </c>
       <c r="P315" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -20043,7 +20043,7 @@
         <v>0</v>
       </c>
       <c r="P316" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -20075,7 +20075,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="P317" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -20110,7 +20110,7 @@
         <v>231</v>
       </c>
       <c r="P318" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -20148,7 +20148,7 @@
         <v>12</v>
       </c>
       <c r="P319" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -20186,7 +20186,7 @@
         <v>63</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -20224,7 +20224,7 @@
         <v>0</v>
       </c>
       <c r="P321" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -20262,7 +20262,7 @@
         <v>263</v>
       </c>
       <c r="P322" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -20300,7 +20300,7 @@
         <v>102</v>
       </c>
       <c r="P323" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="R323" t="s">
         <v>70</v>
@@ -20338,7 +20338,7 @@
         <v>456</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -20379,7 +20379,7 @@
         <v>12</v>
       </c>
       <c r="P325" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -20420,7 +20420,7 @@
         <v>12</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -20464,7 +20464,7 @@
         <v>10955</v>
       </c>
       <c r="P327" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -20499,7 +20499,7 @@
         <v>17.3</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -20543,7 +20543,7 @@
         <v>390</v>
       </c>
       <c r="P329" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -20587,7 +20587,7 @@
         <v>97</v>
       </c>
       <c r="P330" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -20622,7 +20622,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="P331" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -20657,7 +20657,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="P332" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -20695,7 +20695,7 @@
         <v>0</v>
       </c>
       <c r="P333" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -20739,7 +20739,7 @@
         <v>10955</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -20774,7 +20774,7 @@
         <v>324</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -20812,7 +20812,7 @@
         <v>483</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -20850,7 +20850,7 @@
         <v>0</v>
       </c>
       <c r="P337" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -20894,7 +20894,7 @@
         <v>501</v>
       </c>
       <c r="P338" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -20938,7 +20938,7 @@
         <v>741</v>
       </c>
       <c r="P339" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -20979,7 +20979,7 @@
         <v>648</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -21020,7 +21020,7 @@
         <v>574</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -21064,7 +21064,7 @@
         <v>66</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -21105,7 +21105,7 @@
         <v>253</v>
       </c>
       <c r="P343" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -21146,7 +21146,7 @@
         <v>575</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -21190,7 +21190,7 @@
         <v>12</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -21234,7 +21234,7 @@
         <v>341</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -21272,7 +21272,7 @@
         <v>394</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -21313,7 +21313,7 @@
         <v>281</v>
       </c>
       <c r="P348" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -21354,7 +21354,7 @@
         <v>27</v>
       </c>
       <c r="P349" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -21398,7 +21398,7 @@
         <v>0</v>
       </c>
       <c r="P350" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -21439,7 +21439,7 @@
         <v>60</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -21480,7 +21480,7 @@
         <v>368</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="353" spans="1:18">
@@ -21521,7 +21521,7 @@
         <v>152</v>
       </c>
       <c r="P353" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="354" spans="1:18">
@@ -21562,7 +21562,7 @@
         <v>693</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="355" spans="1:18">
@@ -21603,7 +21603,7 @@
         <v>363</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="356" spans="1:18">
@@ -21644,7 +21644,7 @@
         <v>1425</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="357" spans="1:18">
@@ -21685,7 +21685,7 @@
         <v>84</v>
       </c>
       <c r="P357" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="358" spans="1:18">
@@ -21726,7 +21726,7 @@
         <v>42</v>
       </c>
       <c r="P358" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="359" spans="1:18">
@@ -21767,7 +21767,7 @@
         <v>165</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="R359" t="s">
         <v>70</v>
@@ -21811,7 +21811,7 @@
         <v>3214</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="361" spans="1:18">
@@ -21852,7 +21852,7 @@
         <v>0</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="362" spans="1:18">
@@ -21896,7 +21896,7 @@
         <v>165</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="363" spans="1:18">
@@ -21937,7 +21937,7 @@
         <v>24</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="364" spans="1:18">
@@ -21981,7 +21981,7 @@
         <v>182</v>
       </c>
       <c r="P364" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="365" spans="1:18">
@@ -22022,7 +22022,7 @@
         <v>357</v>
       </c>
       <c r="P365" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="366" spans="1:18">
@@ -22066,7 +22066,7 @@
         <v>474</v>
       </c>
       <c r="P366" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="367" spans="1:18">
@@ -22107,7 +22107,7 @@
         <v>321</v>
       </c>
       <c r="P367" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="368" spans="1:18">
@@ -22145,7 +22145,7 @@
         <v>37</v>
       </c>
       <c r="P368" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -22186,7 +22186,7 @@
         <v>351</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -22227,7 +22227,7 @@
         <v>14790</v>
       </c>
       <c r="P370" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -22268,7 +22268,7 @@
         <v>0</v>
       </c>
       <c r="P371" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -22350,7 +22350,7 @@
         <v>0</v>
       </c>
       <c r="P373" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -22391,7 +22391,7 @@
         <v>0</v>
       </c>
       <c r="P374" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -22432,7 +22432,7 @@
         <v>0</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -22476,7 +22476,7 @@
         <v>6</v>
       </c>
       <c r="P376" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -22517,7 +22517,7 @@
         <v>0</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -22558,7 +22558,7 @@
         <v>0</v>
       </c>
       <c r="P378" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -22599,7 +22599,7 @@
         <v>0</v>
       </c>
       <c r="P379" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -22640,7 +22640,7 @@
         <v>0</v>
       </c>
       <c r="P380" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -22681,7 +22681,7 @@
         <v>0</v>
       </c>
       <c r="P381" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -22722,7 +22722,7 @@
         <v>0</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -22763,7 +22763,7 @@
         <v>37</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -22804,7 +22804,7 @@
         <v>539</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -22845,7 +22845,7 @@
         <v>264</v>
       </c>
       <c r="P385" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -22883,7 +22883,7 @@
         <v>7.1</v>
       </c>
       <c r="P386" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -22921,7 +22921,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="P387" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -22962,7 +22962,7 @@
         <v>0</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -23003,7 +23003,7 @@
         <v>113</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -23044,7 +23044,7 @@
         <v>71</v>
       </c>
       <c r="P390" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -23085,7 +23085,7 @@
         <v>152</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -23126,7 +23126,7 @@
         <v>324</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -23167,7 +23167,7 @@
         <v>99</v>
       </c>
       <c r="P393" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -23208,7 +23208,7 @@
         <v>915</v>
       </c>
       <c r="P394" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -23249,7 +23249,7 @@
         <v>219</v>
       </c>
       <c r="P395" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -23290,7 +23290,7 @@
         <v>96</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -23331,7 +23331,7 @@
         <v>219</v>
       </c>
       <c r="P397" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -23372,7 +23372,7 @@
         <v>27</v>
       </c>
       <c r="P398" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -23416,7 +23416,7 @@
         <v>303</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -23460,7 +23460,7 @@
         <v>187</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -23501,7 +23501,7 @@
         <v>340</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -23542,7 +23542,7 @@
         <v>46</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -23583,7 +23583,7 @@
         <v>78</v>
       </c>
       <c r="P403" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -23624,7 +23624,7 @@
         <v>36</v>
       </c>
       <c r="P404" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -23662,7 +23662,7 @@
         <v>11.4</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -23703,7 +23703,7 @@
         <v>0</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -23744,7 +23744,7 @@
         <v>0</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -23785,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="P408" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -23826,7 +23826,7 @@
         <v>177</v>
       </c>
       <c r="P409" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -23870,7 +23870,7 @@
         <v>0</v>
       </c>
       <c r="P410" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23911,7 +23911,7 @@
         <v>0</v>
       </c>
       <c r="P411" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23955,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="P412" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23999,7 +23999,7 @@
         <v>42</v>
       </c>
       <c r="P413" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -24043,7 +24043,7 @@
         <v>65</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -24084,7 +24084,7 @@
         <v>0</v>
       </c>
       <c r="P415" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -24122,7 +24122,7 @@
         <v>31</v>
       </c>
       <c r="P416" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -24166,7 +24166,7 @@
         <v>270.39999999999998</v>
       </c>
       <c r="P417" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -24207,7 +24207,7 @@
         <v>18</v>
       </c>
       <c r="P418" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -24248,7 +24248,7 @@
         <v>6</v>
       </c>
       <c r="P419" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -24289,7 +24289,7 @@
         <v>49</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -24330,7 +24330,7 @@
         <v>17.8</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -24371,7 +24371,7 @@
         <v>53</v>
       </c>
       <c r="P422" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -24412,7 +24412,7 @@
         <v>22.3</v>
       </c>
       <c r="P423" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -24456,7 +24456,7 @@
         <v>42</v>
       </c>
       <c r="P424" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -24497,7 +24497,7 @@
         <v>171</v>
       </c>
       <c r="P425" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -24538,7 +24538,7 @@
         <v>171</v>
       </c>
       <c r="P426" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -24582,7 +24582,7 @@
         <v>12</v>
       </c>
       <c r="P427" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -24626,7 +24626,7 @@
         <v>171</v>
       </c>
       <c r="P428" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -24670,7 +24670,7 @@
         <v>171</v>
       </c>
       <c r="P429" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -24708,7 +24708,7 @@
         <v>18.3</v>
       </c>
       <c r="P430" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -24752,7 +24752,7 @@
         <v>12</v>
       </c>
       <c r="P431" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24787,7 +24787,7 @@
         <v>31.7</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24825,7 +24825,7 @@
         <v>30</v>
       </c>
       <c r="P433" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24904,7 +24904,7 @@
         <v>95</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24945,7 +24945,7 @@
         <v>2215</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24983,7 +24983,7 @@
         <v>2215</v>
       </c>
       <c r="P437" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -25024,7 +25024,7 @@
         <v>279</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -25068,7 +25068,7 @@
         <v>205</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -25106,7 +25106,7 @@
         <v>14.5</v>
       </c>
       <c r="P440" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -25147,7 +25147,7 @@
         <v>0</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -25185,7 +25185,7 @@
         <v>37</v>
       </c>
       <c r="P442" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -25226,7 +25226,7 @@
         <v>324</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -25267,7 +25267,7 @@
         <v>368</v>
       </c>
       <c r="P444" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -25308,7 +25308,7 @@
         <v>969</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -25349,7 +25349,7 @@
         <v>0</v>
       </c>
       <c r="P446" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -25390,7 +25390,7 @@
         <v>113</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -25431,7 +25431,7 @@
         <v>71</v>
       </c>
       <c r="P448" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="449" spans="1:18">
@@ -25472,7 +25472,7 @@
         <v>240</v>
       </c>
       <c r="P449" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="450" spans="1:18">
@@ -25513,7 +25513,7 @@
         <v>66</v>
       </c>
       <c r="P450" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="R450" t="s">
         <v>70</v>
@@ -25557,7 +25557,7 @@
         <v>549</v>
       </c>
       <c r="P451" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="452" spans="1:18">
@@ -25598,7 +25598,7 @@
         <v>3</v>
       </c>
       <c r="P452" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="453" spans="1:18">
@@ -25639,7 +25639,7 @@
         <v>288</v>
       </c>
       <c r="P453" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="454" spans="1:18">
@@ -25680,7 +25680,7 @@
         <v>54</v>
       </c>
       <c r="P454" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="455" spans="1:18">
@@ -25718,7 +25718,7 @@
         <v>666</v>
       </c>
       <c r="P455" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="456" spans="1:18">
@@ -25762,7 +25762,7 @@
         <v>318</v>
       </c>
       <c r="P456" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="457" spans="1:18">
@@ -25800,7 +25800,7 @@
         <v>4.95</v>
       </c>
       <c r="P457" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="458" spans="1:18">
@@ -25841,7 +25841,7 @@
         <v>133</v>
       </c>
       <c r="P458" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="459" spans="1:18">
@@ -25882,7 +25882,7 @@
         <v>0</v>
       </c>
       <c r="P459" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="460" spans="1:18">
@@ -25923,7 +25923,7 @@
         <v>0</v>
       </c>
       <c r="P460" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="461" spans="1:18">
@@ -25964,7 +25964,7 @@
         <v>0</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="462" spans="1:18">
@@ -26005,7 +26005,7 @@
         <v>1327</v>
       </c>
       <c r="P462" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="463" spans="1:18">
@@ -26046,7 +26046,7 @@
         <v>6</v>
       </c>
       <c r="P463" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="464" spans="1:18">
@@ -26087,7 +26087,7 @@
         <v>30</v>
       </c>
       <c r="P464" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -26128,7 +26128,7 @@
         <v>36</v>
       </c>
       <c r="P465" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -26169,7 +26169,7 @@
         <v>18</v>
       </c>
       <c r="P466" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -26210,7 +26210,7 @@
         <v>662</v>
       </c>
       <c r="P467" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -26251,7 +26251,7 @@
         <v>64</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -26292,7 +26292,7 @@
         <v>0</v>
       </c>
       <c r="P469" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -26333,7 +26333,7 @@
         <v>36</v>
       </c>
       <c r="P470" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -26374,7 +26374,7 @@
         <v>36</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -26415,7 +26415,7 @@
         <v>55</v>
       </c>
       <c r="P472" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -26456,7 +26456,7 @@
         <v>4411</v>
       </c>
       <c r="P473" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26491,7 +26491,7 @@
         <v>6.2</v>
       </c>
       <c r="P474" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26526,7 +26526,7 @@
         <v>8.99</v>
       </c>
       <c r="P475" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26564,7 +26564,7 @@
         <v>5</v>
       </c>
       <c r="P476" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26602,7 +26602,7 @@
         <v>6532</v>
       </c>
       <c r="P477" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26640,7 +26640,7 @@
         <v>418</v>
       </c>
       <c r="P478" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26675,7 +26675,7 @@
         <v>23.9</v>
       </c>
       <c r="P479" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26713,7 +26713,7 @@
         <v>34</v>
       </c>
       <c r="P480" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26751,7 +26751,7 @@
         <v>995</v>
       </c>
       <c r="P481" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26789,7 +26789,7 @@
         <v>31</v>
       </c>
       <c r="P482" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26827,7 +26827,7 @@
         <v>5</v>
       </c>
       <c r="P483" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26865,7 +26865,7 @@
         <v>60</v>
       </c>
       <c r="P484" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26903,7 +26903,7 @@
         <v>417</v>
       </c>
       <c r="P485" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26941,7 +26941,7 @@
         <v>777</v>
       </c>
       <c r="P486" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26979,7 +26979,7 @@
         <v>428</v>
       </c>
       <c r="P487" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -27017,7 +27017,7 @@
         <v>0</v>
       </c>
       <c r="P488" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -27055,7 +27055,7 @@
         <v>36</v>
       </c>
       <c r="P489" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -27093,7 +27093,7 @@
         <v>0</v>
       </c>
       <c r="P490" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -27131,7 +27131,7 @@
         <v>0</v>
       </c>
       <c r="P491" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -27169,7 +27169,7 @@
         <v>31</v>
       </c>
       <c r="P492" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27207,7 +27207,7 @@
         <v>41</v>
       </c>
       <c r="P493" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27245,7 +27245,7 @@
         <v>0</v>
       </c>
       <c r="P494" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27283,7 +27283,7 @@
         <v>0</v>
       </c>
       <c r="P495" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27321,7 +27321,7 @@
         <v>3</v>
       </c>
       <c r="P496" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27359,7 +27359,7 @@
         <v>23</v>
       </c>
       <c r="P497" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27400,7 +27400,7 @@
         <v>3</v>
       </c>
       <c r="P498" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27441,7 +27441,7 @@
         <v>31</v>
       </c>
       <c r="P499" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27482,7 +27482,7 @@
         <v>5</v>
       </c>
       <c r="P500" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27523,7 +27523,7 @@
         <v>5</v>
       </c>
       <c r="P501" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27564,7 +27564,7 @@
         <v>5</v>
       </c>
       <c r="P502" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27602,7 +27602,7 @@
         <v>6</v>
       </c>
       <c r="P503" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27640,7 +27640,7 @@
         <v>6</v>
       </c>
       <c r="P504" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27675,7 +27675,7 @@
         <v>14.85</v>
       </c>
       <c r="P505" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27710,7 +27710,7 @@
         <v>38.1</v>
       </c>
       <c r="P506" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27745,7 +27745,7 @@
         <v>35.5</v>
       </c>
       <c r="P507" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27780,7 +27780,7 @@
         <v>16.149999999999999</v>
       </c>
       <c r="P508" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27818,7 +27818,7 @@
         <v>112</v>
       </c>
       <c r="P509" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27853,7 +27853,7 @@
         <v>45</v>
       </c>
       <c r="P510" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27888,7 +27888,7 @@
         <v>45</v>
       </c>
       <c r="P511" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27926,7 +27926,7 @@
         <v>68</v>
       </c>
       <c r="P512" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27964,7 +27964,7 @@
         <v>155</v>
       </c>
       <c r="P513" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28002,7 +28002,7 @@
         <v>7</v>
       </c>
       <c r="P514" s="8" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -36225,10 +36225,10 @@
         <v>79</v>
       </c>
       <c r="C201" t="s">
+        <v>617</v>
+      </c>
+      <c r="D201" t="s">
         <v>618</v>
-      </c>
-      <c r="D201" t="s">
-        <v>619</v>
       </c>
       <c r="E201" t="s">
         <v>63</v>
@@ -36237,7 +36237,7 @@
         <v>1756</v>
       </c>
       <c r="G201" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H201" t="s">
         <v>1756</v>
@@ -36266,7 +36266,7 @@
         <v>79</v>
       </c>
       <c r="C202" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D202" t="s">
         <v>579</v>
@@ -36278,13 +36278,13 @@
         <v>1758</v>
       </c>
       <c r="G202" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H202" t="s">
         <v>1758</v>
       </c>
       <c r="I202" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J202" t="s">
         <v>1491</v>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="C203" s="5"/>
       <c r="D203" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>63</v>
@@ -36317,7 +36317,7 @@
         <v>1759</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H203" s="5" t="s">
         <v>1760</v>
@@ -36347,10 +36347,10 @@
         <v>79</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>82</v>
@@ -36359,7 +36359,7 @@
         <v>1762</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H204" s="5" t="s">
         <v>1763</v>
@@ -36401,7 +36401,7 @@
         <v>1765</v>
       </c>
       <c r="G205" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H205" t="s">
         <v>1765</v>
@@ -36433,7 +36433,7 @@
         <v>602</v>
       </c>
       <c r="D206" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E206" t="s">
         <v>93</v>
@@ -36442,7 +36442,7 @@
         <v>1767</v>
       </c>
       <c r="G206" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H206" t="s">
         <v>1767</v>
@@ -36471,7 +36471,7 @@
         <v>58</v>
       </c>
       <c r="C207" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D207" t="s">
         <v>579</v>
@@ -36483,13 +36483,13 @@
         <v>1769</v>
       </c>
       <c r="G207" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H207" t="s">
         <v>1769</v>
       </c>
       <c r="I207" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J207" t="s">
         <v>1478</v>
@@ -36512,7 +36512,7 @@
         <v>58</v>
       </c>
       <c r="C208" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D208" t="s">
         <v>606</v>
@@ -36524,13 +36524,13 @@
         <v>1770</v>
       </c>
       <c r="G208" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H208" t="s">
         <v>1770</v>
       </c>
       <c r="I208" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J208" t="s">
         <v>1478</v>
@@ -36553,7 +36553,7 @@
         <v>58</v>
       </c>
       <c r="D209" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E209" t="s">
         <v>63</v>
@@ -36562,7 +36562,7 @@
         <v>1759</v>
       </c>
       <c r="G209" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H209" t="s">
         <v>1759</v>
@@ -36591,10 +36591,10 @@
         <v>58</v>
       </c>
       <c r="C210" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D210" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E210" t="s">
         <v>63</v>
@@ -36603,7 +36603,7 @@
         <v>1772</v>
       </c>
       <c r="G210" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H210" t="s">
         <v>1772</v>
@@ -36632,10 +36632,10 @@
         <v>79</v>
       </c>
       <c r="C211" t="s">
+        <v>639</v>
+      </c>
+      <c r="D211" t="s">
         <v>640</v>
-      </c>
-      <c r="D211" t="s">
-        <v>641</v>
       </c>
       <c r="E211" t="s">
         <v>104</v>
@@ -36644,7 +36644,7 @@
         <v>1774</v>
       </c>
       <c r="G211" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H211" t="s">
         <v>1774</v>
@@ -36673,7 +36673,7 @@
         <v>79</v>
       </c>
       <c r="C212" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D212" t="s">
         <v>570</v>
@@ -36685,13 +36685,13 @@
         <v>1776</v>
       </c>
       <c r="G212" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H212" t="s">
         <v>1776</v>
       </c>
       <c r="I212" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J212" t="s">
         <v>1491</v>
@@ -36717,7 +36717,7 @@
         <v>646</v>
       </c>
       <c r="D213" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E213" t="s">
         <v>128</v>
@@ -36835,10 +36835,10 @@
         <v>58</v>
       </c>
       <c r="C216" t="s">
+        <v>639</v>
+      </c>
+      <c r="D216" t="s">
         <v>640</v>
-      </c>
-      <c r="D216" t="s">
-        <v>641</v>
       </c>
       <c r="E216" t="s">
         <v>93</v>
@@ -37274,7 +37274,7 @@
         <v>675</v>
       </c>
       <c r="D227" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E227" t="s">
         <v>123</v>
@@ -37357,7 +37357,7 @@
         <v>680</v>
       </c>
       <c r="D229" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E229" t="s">
         <v>63</v>
@@ -37972,7 +37972,7 @@
         <v>715</v>
       </c>
       <c r="D244" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E244" t="s">
         <v>63</v>
@@ -38371,7 +38371,7 @@
         <v>675</v>
       </c>
       <c r="D254" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E254" t="s">
         <v>63</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9680EF-598B-4B60-95E8-5A424899EAED}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2DF6C7-42D4-4D56-B4F9-8969D99D2052}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -48855,15 +48855,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="860f336250d6f7d113c3b43983ff209d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f4eda2c29f4341f43b2cc38e2775c30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -49123,14 +49114,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2293BB-1BB0-48A0-A955-B37D029329BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2DF6C7-42D4-4D56-B4F9-8969D99D2052}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40A283E2-58A1-47F2-8CB8-4657369BF7E2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
     <sheet name="Tarif" sheetId="2" r:id="rId2"/>
-    <sheet name="Sponsors" sheetId="3" r:id="rId3"/>
-    <sheet name="OffresEnCours" sheetId="4" r:id="rId4"/>
-    <sheet name="Edito" sheetId="5" r:id="rId5"/>
-    <sheet name="MAJ_Codes" sheetId="6" r:id="rId6"/>
+    <sheet name="Feuil1" sheetId="7" r:id="rId3"/>
+    <sheet name="Sponsors" sheetId="3" r:id="rId4"/>
+    <sheet name="OffresEnCours" sheetId="4" r:id="rId5"/>
+    <sheet name="Edito" sheetId="5" r:id="rId6"/>
+    <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -28049,6 +28050,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5BE8D6-DCE4-4E26-AF96-1ED564232314}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -28126,7 +28136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -28202,7 +28212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -28239,7 +28249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N512"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58AAB42D-F6C7-4628-BD8F-8599CC03E5D2}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA49BAC-5983-4DBB-9AED-F320EB230283}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28335,10 +28335,12 @@
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="46.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="45.75">
@@ -28379,7 +28381,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="121.5">
+    <row r="2" spans="1:12" ht="27">
       <c r="A2" s="11" t="s">
         <v>1428</v>
       </c>
@@ -28417,7 +28419,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="121.5">
+    <row r="3" spans="1:12" ht="27">
       <c r="A3" s="11" t="s">
         <v>1428</v>
       </c>
@@ -28455,7 +28457,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="121.5">
+    <row r="4" spans="1:12" ht="27">
       <c r="A4" s="11" t="s">
         <v>1428</v>
       </c>
@@ -28493,7 +28495,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="161.25">
+    <row r="5" spans="1:12" ht="40.5">
       <c r="A5" s="11" t="s">
         <v>1428</v>
       </c>
@@ -28531,7 +28533,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="121.5">
+    <row r="6" spans="1:12" ht="27">
       <c r="A6" s="11" t="s">
         <v>1428</v>
       </c>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFA49BAC-5983-4DBB-9AED-F320EB230283}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DD9862-0C47-43C2-A1D5-16FF16D30461}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28332,7 +28332,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5BE8D6-DCE4-4E26-AF96-1ED564232314}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -28495,7 +28495,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="40.5">
+    <row r="5" spans="1:12" ht="27">
       <c r="A5" s="11" t="s">
         <v>1428</v>
       </c>
@@ -28655,122 +28655,136 @@
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+    <row r="13" spans="1:12" ht="15.75">
+      <c r="A13" s="20" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="A15" s="22" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
+      <c r="A16" s="21" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
+      <c r="A17" s="21" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
+      <c r="A18" s="21" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75">
-      <c r="A20" s="20" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="A19" s="21" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="21" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="21"/>
+      <c r="A21" s="21" t="s">
+        <v>1449</v>
+      </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -28784,25 +28798,23 @@
       <c r="L21" s="21"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="22" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="A22" s="21" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="21" t="s">
-        <v>1444</v>
-      </c>
+      <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
@@ -28816,24 +28828,24 @@
       <c r="L23" s="21"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="21" t="s">
-        <v>1445</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
+      <c r="A24" s="22" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="21" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -28849,7 +28861,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="21" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -28864,9 +28876,7 @@
       <c r="L26" s="21"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="21" t="s">
-        <v>1448</v>
-      </c>
+      <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
@@ -28880,24 +28890,24 @@
       <c r="L27" s="21"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="21" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="A28" s="23" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="21" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -28912,7 +28922,9 @@
       <c r="L29" s="21"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="21"/>
+      <c r="A30" s="21" t="s">
+        <v>1456</v>
+      </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -28926,25 +28938,23 @@
       <c r="L30" s="21"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="22" t="s">
-        <v>1451</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="A31" s="21" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="21" t="s">
-        <v>1452</v>
-      </c>
+      <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
@@ -28958,23 +28968,25 @@
       <c r="L32" s="21"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="21" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="A33" s="23" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="21"/>
+      <c r="A34" s="21" t="s">
+        <v>1459</v>
+      </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -28987,140 +28999,30 @@
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
     </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="23" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="21" t="s">
-        <v>1455</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="21" t="s">
-        <v>1456</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="21" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="23" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="21" t="s">
-        <v>1459</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-    </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A31:L31"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A25:L25"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DD9862-0C47-43C2-A1D5-16FF16D30461}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9179C040-F26C-455E-839C-331424417B8E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
     <sheet name="Tarif" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil1" sheetId="7" r:id="rId3"/>
+    <sheet name="Destockages" sheetId="7" r:id="rId3"/>
     <sheet name="Sponsors" sheetId="3" r:id="rId4"/>
     <sheet name="OffresEnCours" sheetId="4" r:id="rId5"/>
     <sheet name="Edito" sheetId="5" r:id="rId6"/>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E036FE-2A9B-6E45-B99D-402532BFE5CE}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BBEE6F3-5FA5-9E40-AA6D-505704653E6D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10106" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10104" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7148,10 +7148,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12007,8 +12007,8 @@
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>376</v>
+      <c r="A110">
+        <v>27202325</v>
       </c>
       <c r="B110" t="s">
         <v>56</v>
@@ -12028,8 +12028,8 @@
       <c r="H110" t="s">
         <v>377</v>
       </c>
-      <c r="J110" t="s">
-        <v>374</v>
+      <c r="J110">
+        <v>2025</v>
       </c>
       <c r="K110">
         <v>75</v>
@@ -28656,351 +28656,361 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1442</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1443</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1444</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1445</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1446</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1447</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1449</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1450</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1451</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1453</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1454</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1455</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1456</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1457</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1458</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1459</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -29013,16 +29023,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49824,12 +49824,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50093,20 +50095,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -50132,19 +50142,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BBEE6F3-5FA5-9E40-AA6D-505704653E6D}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{616C16E1-2626-6D4D-A5D1-DD03A143D457}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10104" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -14232,8 +14232,8 @@
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>525</v>
+      <c r="A165">
+        <v>12100124</v>
       </c>
       <c r="B165" t="s">
         <v>56</v>
@@ -14253,8 +14253,8 @@
       <c r="H165" t="s">
         <v>485</v>
       </c>
-      <c r="J165" t="s">
-        <v>63</v>
+      <c r="J165">
+        <v>2024</v>
       </c>
       <c r="K165">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{616C16E1-2626-6D4D-A5D1-DD03A143D457}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{354527CE-3F46-B144-9D88-A5DBC0F9D358}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10100" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -13257,8 +13257,8 @@
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>458</v>
+      <c r="A141">
+        <v>35900524</v>
       </c>
       <c r="B141" t="s">
         <v>56</v>
@@ -13275,8 +13275,8 @@
       <c r="F141" t="s">
         <v>437</v>
       </c>
-      <c r="G141" t="s">
-        <v>459</v>
+      <c r="G141">
+        <v>2024</v>
       </c>
       <c r="H141" t="s">
         <v>432</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B397E097-27E4-4E1D-B6E0-1FB4DA626461}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E23866C-9342-403B-8221-05632FE38A02}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -29001,6 +29001,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -29013,16 +29023,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29041,6 +29041,8 @@
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -50115,6 +50117,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
@@ -50127,23 +50138,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E23866C-9342-403B-8221-05632FE38A02}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDB65371-6642-4D93-8097-EC19546DE717}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDB65371-6642-4D93-8097-EC19546DE717}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128C6C5B-E421-4D05-B512-AFCE0439CE04}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -20971,7 +20971,7 @@
         <v>75</v>
       </c>
       <c r="L333">
-        <v>4.9000000000000004</v>
+        <v>5.05</v>
       </c>
       <c r="M333">
         <v>0</v>
@@ -29001,16 +29001,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -29023,6 +29013,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49836,6 +49836,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50116,15 +50125,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -50139,11 +50139,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128C6C5B-E421-4D05-B512-AFCE0439CE04}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC973C8-8ABE-45B4-A7E0-4056B826442A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10100" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10099" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -15509,8 +15509,8 @@
       <c r="I196" t="s">
         <v>62</v>
       </c>
-      <c r="J196" t="s">
-        <v>93</v>
+      <c r="J196">
+        <v>2025</v>
       </c>
       <c r="K196">
         <v>75</v>
@@ -29001,6 +29001,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -29013,16 +29023,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49845,6 +49845,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50125,27 +50138,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC973C8-8ABE-45B4-A7E0-4056B826442A}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{898ED804-8878-458C-86DB-D03C118BEB08}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,9 @@
     <sheet name="Edito" sheetId="5" r:id="rId6"/>
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$515</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28326,6 +28329,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R515" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29001,16 +29005,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -29023,6 +29017,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49836,28 +49840,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50138,8 +50120,30 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50147,5 +50151,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3469FA-FB74-FF4C-AE50-D93D5587BEE4}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88323A3-1A6B-A54D-9407-BB37778FEBA1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10088" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10087" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -12079,8 +12079,8 @@
       <c r="I111" t="s">
         <v>380</v>
       </c>
-      <c r="J111" t="s">
-        <v>82</v>
+      <c r="J111">
+        <v>2023</v>
       </c>
       <c r="K111">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88323A3-1A6B-A54D-9407-BB37778FEBA1}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE515FC-7504-D44C-9843-CB542635263E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10087" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10086" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -12164,8 +12164,8 @@
       <c r="I113" t="s">
         <v>380</v>
       </c>
-      <c r="J113" t="s">
-        <v>82</v>
+      <c r="J113">
+        <v>2023</v>
       </c>
       <c r="K113">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE515FC-7504-D44C-9843-CB542635263E}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0100FF-BF58-ED4C-9C62-08CFE4B19937}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10086" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10085" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -20898,8 +20898,8 @@
       <c r="H331" t="s">
         <v>929</v>
       </c>
-      <c r="J331" t="s">
-        <v>93</v>
+      <c r="J331">
+        <v>2025</v>
       </c>
       <c r="K331">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0100FF-BF58-ED4C-9C62-08CFE4B19937}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CAB2FD-EC72-9C48-8429-BD28D79CB2A4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$513</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10085" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10074" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7151,10 +7151,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7170,10 +7170,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7659,7 +7655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R514"/>
+  <dimension ref="A1:R513"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -21592,8 +21588,8 @@
       <c r="I348" t="s">
         <v>62</v>
       </c>
-      <c r="J348" t="s">
-        <v>93</v>
+      <c r="J348">
+        <v>2025</v>
       </c>
       <c r="K348">
         <v>75</v>
@@ -21610,31 +21606,28 @@
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B349" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C349" t="s">
-        <v>910</v>
+        <v>973</v>
       </c>
       <c r="D349" t="s">
-        <v>917</v>
+        <v>974</v>
       </c>
       <c r="E349" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F349" t="s">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G349" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="H349" t="s">
-        <v>965</v>
-      </c>
-      <c r="I349" t="s">
-        <v>62</v>
+        <v>977</v>
       </c>
       <c r="J349" t="s">
         <v>334</v>
@@ -21643,10 +21636,10 @@
         <v>75</v>
       </c>
       <c r="L349">
-        <v>14.5</v>
+        <v>3.8</v>
       </c>
       <c r="M349">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P349" s="8">
         <v>46155</v>
@@ -21654,7 +21647,7 @@
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B350" t="s">
         <v>56</v>
@@ -21672,22 +21665,22 @@
         <v>975</v>
       </c>
       <c r="G350" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="H350" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J350" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K350">
         <v>75</v>
       </c>
       <c r="L350">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M350">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="P350" s="8">
         <v>46155</v>
@@ -21695,7 +21688,7 @@
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B351" t="s">
         <v>56</v>
@@ -21710,25 +21703,25 @@
         <v>58</v>
       </c>
       <c r="F351" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G351" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="H351" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="J351" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K351">
         <v>75</v>
       </c>
       <c r="L351">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="M351">
-        <v>368</v>
+        <v>152</v>
       </c>
       <c r="P351" s="8">
         <v>46155</v>
@@ -21736,7 +21729,7 @@
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B352" t="s">
         <v>56</v>
@@ -21751,25 +21744,25 @@
         <v>58</v>
       </c>
       <c r="F352" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G352" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="H352" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="J352" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K352">
         <v>75</v>
       </c>
       <c r="L352">
-        <v>4.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M352">
-        <v>152</v>
+        <v>693</v>
       </c>
       <c r="P352" s="8">
         <v>46155</v>
@@ -21777,7 +21770,7 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B353" t="s">
         <v>56</v>
@@ -21795,10 +21788,10 @@
         <v>975</v>
       </c>
       <c r="G353" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="H353" t="s">
-        <v>987</v>
+        <v>285</v>
       </c>
       <c r="J353" t="s">
         <v>93</v>
@@ -21807,10 +21800,10 @@
         <v>75</v>
       </c>
       <c r="L353">
-        <v>5.0999999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="M353">
-        <v>693</v>
+        <v>363</v>
       </c>
       <c r="P353" s="8">
         <v>46155</v>
@@ -21818,7 +21811,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B354" t="s">
         <v>56</v>
@@ -21836,7 +21829,7 @@
         <v>975</v>
       </c>
       <c r="G354" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="H354" t="s">
         <v>285</v>
@@ -21848,10 +21841,10 @@
         <v>75</v>
       </c>
       <c r="L354">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="M354">
-        <v>363</v>
+        <v>1425</v>
       </c>
       <c r="P354" s="8">
         <v>46155</v>
@@ -21859,7 +21852,7 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B355" t="s">
         <v>56</v>
@@ -21877,22 +21870,22 @@
         <v>975</v>
       </c>
       <c r="G355" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H355" t="s">
-        <v>285</v>
+        <v>987</v>
       </c>
       <c r="J355" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K355">
         <v>75</v>
       </c>
       <c r="L355">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="M355">
-        <v>1425</v>
+        <v>84</v>
       </c>
       <c r="P355" s="8">
         <v>46155</v>
@@ -21900,7 +21893,7 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B356" t="s">
         <v>56</v>
@@ -21915,13 +21908,13 @@
         <v>58</v>
       </c>
       <c r="F356" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G356" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="H356" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="J356" t="s">
         <v>334</v>
@@ -21930,10 +21923,10 @@
         <v>75</v>
       </c>
       <c r="L356">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="M356">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="P356" s="8">
         <v>46155</v>
@@ -21941,7 +21934,7 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="B357" t="s">
         <v>56</v>
@@ -21956,16 +21949,16 @@
         <v>58</v>
       </c>
       <c r="F357" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G357" t="s">
-        <v>995</v>
+        <v>108</v>
       </c>
       <c r="H357" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="J357" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K357">
         <v>75</v>
@@ -21974,15 +21967,18 @@
         <v>5.7</v>
       </c>
       <c r="M357">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="P357" s="8">
         <v>46155</v>
+      </c>
+      <c r="R357" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B358" t="s">
         <v>56</v>
@@ -22000,42 +21996,39 @@
         <v>975</v>
       </c>
       <c r="G358" t="s">
-        <v>108</v>
+        <v>1000</v>
       </c>
       <c r="H358" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="J358" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K358">
         <v>75</v>
       </c>
       <c r="L358">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="M358">
-        <v>165</v>
+        <v>3214</v>
       </c>
       <c r="P358" s="8">
         <v>46155</v>
-      </c>
-      <c r="R358" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B359" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C359" t="s">
         <v>973</v>
       </c>
       <c r="D359" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="E359" t="s">
         <v>58</v>
@@ -22044,7 +22037,7 @@
         <v>975</v>
       </c>
       <c r="G359" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="H359" t="s">
         <v>1001</v>
@@ -22053,13 +22046,13 @@
         <v>334</v>
       </c>
       <c r="K359">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L359">
-        <v>5.85</v>
+        <v>12.9</v>
       </c>
       <c r="M359">
-        <v>3214</v>
+        <v>0</v>
       </c>
       <c r="P359" s="8">
         <v>46155</v>
@@ -22067,16 +22060,16 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B360" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C360" t="s">
         <v>973</v>
       </c>
       <c r="D360" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E360" t="s">
         <v>58</v>
@@ -22085,22 +22078,25 @@
         <v>975</v>
       </c>
       <c r="G360" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="H360" t="s">
-        <v>1001</v>
+        <v>987</v>
+      </c>
+      <c r="I360" t="s">
+        <v>1007</v>
       </c>
       <c r="J360" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K360">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L360">
-        <v>12.9</v>
+        <v>6.05</v>
       </c>
       <c r="M360">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="P360" s="8">
         <v>46155</v>
@@ -22108,7 +22104,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B361" t="s">
         <v>56</v>
@@ -22117,34 +22113,31 @@
         <v>973</v>
       </c>
       <c r="D361" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E361" t="s">
         <v>58</v>
       </c>
       <c r="F361" t="s">
-        <v>975</v>
+        <v>1010</v>
       </c>
       <c r="G361" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="H361" t="s">
-        <v>987</v>
-      </c>
-      <c r="I361" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="J361" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K361">
         <v>75</v>
       </c>
       <c r="L361">
-        <v>6.05</v>
+        <v>14.5</v>
       </c>
       <c r="M361">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="P361" s="8">
         <v>46155</v>
@@ -22152,7 +22145,7 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="B362" t="s">
         <v>56</v>
@@ -22161,31 +22154,34 @@
         <v>973</v>
       </c>
       <c r="D362" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E362" t="s">
         <v>58</v>
       </c>
       <c r="F362" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="G362" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="H362" t="s">
-        <v>1012</v>
+        <v>1016</v>
+      </c>
+      <c r="I362" t="s">
+        <v>784</v>
       </c>
       <c r="J362" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K362">
         <v>75</v>
       </c>
       <c r="L362">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="M362">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="P362" s="8">
         <v>46155</v>
@@ -22193,7 +22189,7 @@
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B363" t="s">
         <v>56</v>
@@ -22208,28 +22204,25 @@
         <v>58</v>
       </c>
       <c r="F363" t="s">
-        <v>1014</v>
+        <v>975</v>
       </c>
       <c r="G363" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="H363" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I363" t="s">
-        <v>784</v>
+        <v>987</v>
       </c>
       <c r="J363" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K363">
         <v>75</v>
       </c>
       <c r="L363">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="M363">
-        <v>182</v>
+        <v>357</v>
       </c>
       <c r="P363" s="8">
         <v>46155</v>
@@ -22237,7 +22230,7 @@
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B364" t="s">
         <v>56</v>
@@ -22255,22 +22248,25 @@
         <v>975</v>
       </c>
       <c r="G364" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="H364" t="s">
         <v>987</v>
       </c>
+      <c r="I364" t="s">
+        <v>1007</v>
+      </c>
       <c r="J364" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K364">
         <v>75</v>
       </c>
       <c r="L364">
-        <v>5.4</v>
+        <v>6.05</v>
       </c>
       <c r="M364">
-        <v>357</v>
+        <v>474</v>
       </c>
       <c r="P364" s="8">
         <v>46155</v>
@@ -22278,7 +22274,7 @@
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B365" t="s">
         <v>56</v>
@@ -22296,25 +22292,22 @@
         <v>975</v>
       </c>
       <c r="G365" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="H365" t="s">
-        <v>987</v>
-      </c>
-      <c r="I365" t="s">
-        <v>1007</v>
+        <v>605</v>
       </c>
       <c r="J365" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K365">
         <v>75</v>
       </c>
       <c r="L365">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="M365">
-        <v>474</v>
+        <v>321</v>
       </c>
       <c r="P365" s="8">
         <v>46155</v>
@@ -22322,7 +22315,7 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B366" t="s">
         <v>56</v>
@@ -22337,25 +22330,22 @@
         <v>58</v>
       </c>
       <c r="F366" t="s">
-        <v>975</v>
+        <v>1024</v>
       </c>
       <c r="G366" t="s">
-        <v>1022</v>
+        <v>159</v>
       </c>
       <c r="H366" t="s">
-        <v>605</v>
+        <v>1025</v>
       </c>
       <c r="J366" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K366">
         <v>75</v>
       </c>
       <c r="L366">
-        <v>6.4</v>
-      </c>
-      <c r="M366">
-        <v>321</v>
+        <v>37</v>
       </c>
       <c r="P366" s="8">
         <v>46155</v>
@@ -22363,7 +22353,7 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B367" t="s">
         <v>56</v>
@@ -22378,13 +22368,13 @@
         <v>58</v>
       </c>
       <c r="F367" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="G367" t="s">
-        <v>159</v>
+        <v>1028</v>
       </c>
       <c r="H367" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="J367" t="s">
         <v>93</v>
@@ -22393,7 +22383,10 @@
         <v>75</v>
       </c>
       <c r="L367">
-        <v>37</v>
+        <v>3.95</v>
+      </c>
+      <c r="M367">
+        <v>351</v>
       </c>
       <c r="P367" s="8">
         <v>46155</v>
@@ -22401,7 +22394,7 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B368" t="s">
         <v>56</v>
@@ -22419,10 +22412,10 @@
         <v>1027</v>
       </c>
       <c r="G368" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="H368" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="J368" t="s">
         <v>93</v>
@@ -22431,10 +22424,10 @@
         <v>75</v>
       </c>
       <c r="L368">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="M368">
-        <v>351</v>
+        <v>14790</v>
       </c>
       <c r="P368" s="8">
         <v>46155</v>
@@ -22442,10 +22435,10 @@
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B369" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C369" t="s">
         <v>973</v>
@@ -22457,33 +22450,33 @@
         <v>58</v>
       </c>
       <c r="F369" t="s">
-        <v>1027</v>
+        <v>59</v>
       </c>
       <c r="G369" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="H369" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="J369" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K369">
         <v>75</v>
       </c>
       <c r="L369">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="M369">
-        <v>14790</v>
+        <v>0</v>
       </c>
       <c r="P369" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A370" t="s">
-        <v>1033</v>
+      <c r="A370">
+        <v>24003025</v>
       </c>
       <c r="B370" t="s">
         <v>117</v>
@@ -22492,7 +22485,7 @@
         <v>973</v>
       </c>
       <c r="D370" t="s">
-        <v>974</v>
+        <v>1036</v>
       </c>
       <c r="E370" t="s">
         <v>58</v>
@@ -22501,13 +22494,16 @@
         <v>59</v>
       </c>
       <c r="G370" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="H370" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J370" t="s">
-        <v>334</v>
+        <v>1038</v>
+      </c>
+      <c r="I370" t="s">
+        <v>62</v>
+      </c>
+      <c r="J370">
+        <v>2025</v>
       </c>
       <c r="K370">
         <v>75</v>
@@ -22515,16 +22511,13 @@
       <c r="L370">
         <v>6.2</v>
       </c>
-      <c r="M370">
-        <v>0</v>
-      </c>
       <c r="P370" s="8">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A371">
-        <v>24003025</v>
+      <c r="A371" t="s">
+        <v>1039</v>
       </c>
       <c r="B371" t="s">
         <v>117</v>
@@ -22533,39 +22526,39 @@
         <v>973</v>
       </c>
       <c r="D371" t="s">
-        <v>1036</v>
+        <v>1009</v>
       </c>
       <c r="E371" t="s">
         <v>58</v>
       </c>
       <c r="F371" t="s">
-        <v>59</v>
+        <v>1040</v>
       </c>
       <c r="G371" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="H371" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I371" t="s">
-        <v>62</v>
-      </c>
-      <c r="J371">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J371" t="s">
+        <v>82</v>
       </c>
       <c r="K371">
         <v>75</v>
       </c>
       <c r="L371">
-        <v>6.2</v>
+        <v>7.55</v>
+      </c>
+      <c r="M371">
+        <v>0</v>
       </c>
       <c r="P371" s="8">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B372" t="s">
         <v>117</v>
@@ -22574,28 +22567,28 @@
         <v>973</v>
       </c>
       <c r="D372" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E372" t="s">
         <v>58</v>
       </c>
       <c r="F372" t="s">
-        <v>1040</v>
+        <v>59</v>
       </c>
       <c r="G372" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="H372" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="J372" t="s">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="K372">
         <v>75</v>
       </c>
       <c r="L372">
-        <v>7.55</v>
+        <v>10.5</v>
       </c>
       <c r="M372">
         <v>0</v>
@@ -22606,7 +22599,7 @@
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B373" t="s">
         <v>117</v>
@@ -22615,28 +22608,28 @@
         <v>973</v>
       </c>
       <c r="D373" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E373" t="s">
         <v>58</v>
       </c>
       <c r="F373" t="s">
-        <v>59</v>
+        <v>1046</v>
       </c>
       <c r="G373" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="H373" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="J373" t="s">
-        <v>334</v>
+        <v>63</v>
       </c>
       <c r="K373">
         <v>75</v>
       </c>
       <c r="L373">
-        <v>10.5</v>
+        <v>10.65</v>
       </c>
       <c r="M373">
         <v>0</v>
@@ -22647,7 +22640,7 @@
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B374" t="s">
         <v>117</v>
@@ -22656,31 +22649,34 @@
         <v>973</v>
       </c>
       <c r="D374" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E374" t="s">
         <v>58</v>
       </c>
       <c r="F374" t="s">
-        <v>1046</v>
+        <v>59</v>
       </c>
       <c r="G374" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="H374" t="s">
-        <v>1035</v>
+        <v>1050</v>
+      </c>
+      <c r="I374" t="s">
+        <v>1051</v>
       </c>
       <c r="J374" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K374">
         <v>75</v>
       </c>
       <c r="L374">
-        <v>10.65</v>
+        <v>11.5</v>
       </c>
       <c r="M374">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P374" s="8">
         <v>46155</v>
@@ -22688,7 +22684,7 @@
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B375" t="s">
         <v>117</v>
@@ -22697,23 +22693,20 @@
         <v>973</v>
       </c>
       <c r="D375" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E375" t="s">
         <v>58</v>
       </c>
       <c r="F375" t="s">
-        <v>59</v>
+        <v>1054</v>
       </c>
       <c r="G375" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="H375" t="s">
         <v>1050</v>
       </c>
-      <c r="I375" t="s">
-        <v>1051</v>
-      </c>
       <c r="J375" t="s">
         <v>93</v>
       </c>
@@ -22721,10 +22714,10 @@
         <v>75</v>
       </c>
       <c r="L375">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="M375">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P375" s="8">
         <v>46155</v>
@@ -22732,7 +22725,7 @@
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B376" t="s">
         <v>117</v>
@@ -22741,28 +22734,28 @@
         <v>973</v>
       </c>
       <c r="D376" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E376" t="s">
         <v>58</v>
       </c>
       <c r="F376" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="G376" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="H376" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="J376" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="K376">
         <v>75</v>
       </c>
       <c r="L376">
-        <v>12.2</v>
+        <v>13.95</v>
       </c>
       <c r="M376">
         <v>0</v>
@@ -22773,7 +22766,7 @@
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B377" t="s">
         <v>117</v>
@@ -22782,28 +22775,28 @@
         <v>973</v>
       </c>
       <c r="D377" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E377" t="s">
         <v>58</v>
       </c>
       <c r="F377" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="G377" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="H377" t="s">
-        <v>1035</v>
+        <v>1060</v>
       </c>
       <c r="J377" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="K377">
         <v>75</v>
       </c>
       <c r="L377">
-        <v>13.95</v>
+        <v>14.8</v>
       </c>
       <c r="M377">
         <v>0</v>
@@ -22814,7 +22807,7 @@
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B378" t="s">
         <v>117</v>
@@ -22829,22 +22822,22 @@
         <v>58</v>
       </c>
       <c r="F378" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="G378" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="H378" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="J378" t="s">
-        <v>101</v>
+        <v>334</v>
       </c>
       <c r="K378">
         <v>75</v>
       </c>
       <c r="L378">
-        <v>14.8</v>
+        <v>6.5</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -22855,7 +22848,7 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="B379" t="s">
         <v>117</v>
@@ -22873,10 +22866,10 @@
         <v>1062</v>
       </c>
       <c r="G379" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="H379" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="J379" t="s">
         <v>334</v>
@@ -22885,7 +22878,7 @@
         <v>75</v>
       </c>
       <c r="L379">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="M379">
         <v>0</v>
@@ -22896,7 +22889,7 @@
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B380" t="s">
         <v>117</v>
@@ -22914,19 +22907,19 @@
         <v>1062</v>
       </c>
       <c r="G380" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="H380" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="J380" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K380">
         <v>75</v>
       </c>
       <c r="L380">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="M380">
         <v>0</v>
@@ -22937,10 +22930,10 @@
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B381" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C381" t="s">
         <v>973</v>
@@ -22955,10 +22948,10 @@
         <v>1062</v>
       </c>
       <c r="G381" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="H381" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="J381" t="s">
         <v>93</v>
@@ -22967,10 +22960,10 @@
         <v>75</v>
       </c>
       <c r="L381">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="M381">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P381" s="8">
         <v>46155</v>
@@ -22978,7 +22971,7 @@
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B382" t="s">
         <v>56</v>
@@ -22987,19 +22980,19 @@
         <v>973</v>
       </c>
       <c r="D382" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E382" t="s">
         <v>58</v>
       </c>
       <c r="F382" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
       <c r="G382" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="H382" t="s">
-        <v>1072</v>
+        <v>1012</v>
       </c>
       <c r="J382" t="s">
         <v>93</v>
@@ -23008,10 +23001,10 @@
         <v>75</v>
       </c>
       <c r="L382">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="M382">
-        <v>37</v>
+        <v>539</v>
       </c>
       <c r="P382" s="8">
         <v>46155</v>
@@ -23019,7 +23012,7 @@
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B383" t="s">
         <v>56</v>
@@ -23037,10 +23030,10 @@
         <v>1027</v>
       </c>
       <c r="G383" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="H383" t="s">
-        <v>1012</v>
+        <v>1032</v>
       </c>
       <c r="J383" t="s">
         <v>93</v>
@@ -23049,10 +23042,10 @@
         <v>75</v>
       </c>
       <c r="L383">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="M383">
-        <v>539</v>
+        <v>264</v>
       </c>
       <c r="P383" s="8">
         <v>46155</v>
@@ -23060,7 +23053,7 @@
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B384" t="s">
         <v>56</v>
@@ -23075,13 +23068,13 @@
         <v>58</v>
       </c>
       <c r="F384" t="s">
-        <v>1027</v>
+        <v>1078</v>
       </c>
       <c r="G384" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="H384" t="s">
-        <v>1032</v>
+        <v>1080</v>
       </c>
       <c r="J384" t="s">
         <v>93</v>
@@ -23090,10 +23083,7 @@
         <v>75</v>
       </c>
       <c r="L384">
-        <v>6.95</v>
-      </c>
-      <c r="M384">
-        <v>264</v>
+        <v>7.1</v>
       </c>
       <c r="P384" s="8">
         <v>46155</v>
@@ -23101,7 +23091,7 @@
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B385" t="s">
         <v>56</v>
@@ -23116,101 +23106,104 @@
         <v>58</v>
       </c>
       <c r="F385" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="G385" t="s">
         <v>1079</v>
       </c>
       <c r="H385" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="J385" t="s">
-        <v>93</v>
+        <v>521</v>
       </c>
       <c r="K385">
         <v>75</v>
       </c>
       <c r="L385">
-        <v>7.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P385" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A386" t="s">
-        <v>1081</v>
+      <c r="A386">
+        <v>53800623</v>
       </c>
       <c r="B386" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C386" t="s">
         <v>973</v>
       </c>
       <c r="D386" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
       </c>
       <c r="F386" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="G386" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="H386" t="s">
-        <v>1083</v>
+        <v>1060</v>
       </c>
       <c r="J386" t="s">
-        <v>521</v>
+        <v>63</v>
       </c>
       <c r="K386">
         <v>75</v>
       </c>
       <c r="L386">
-        <v>8.1999999999999993</v>
+        <v>11</v>
+      </c>
+      <c r="M386">
+        <v>0</v>
       </c>
       <c r="P386" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A387">
-        <v>53800623</v>
+      <c r="A387" t="s">
+        <v>1086</v>
       </c>
       <c r="B387" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C387" t="s">
         <v>973</v>
       </c>
       <c r="D387" t="s">
-        <v>1053</v>
+        <v>974</v>
       </c>
       <c r="E387" t="s">
         <v>58</v>
       </c>
       <c r="F387" t="s">
-        <v>1084</v>
+        <v>975</v>
       </c>
       <c r="G387" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="H387" t="s">
-        <v>1060</v>
+        <v>977</v>
       </c>
       <c r="J387" t="s">
-        <v>63</v>
+        <v>576</v>
       </c>
       <c r="K387">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="L387">
-        <v>11</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M387">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="P387" s="8">
         <v>46155</v>
@@ -23218,7 +23211,7 @@
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B388" t="s">
         <v>56</v>
@@ -23236,22 +23229,22 @@
         <v>975</v>
       </c>
       <c r="G388" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="H388" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J388" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K388">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L388">
-        <v>16.399999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="M388">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="P388" s="8">
         <v>46155</v>
@@ -23259,7 +23252,7 @@
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B389" t="s">
         <v>56</v>
@@ -23268,31 +23261,31 @@
         <v>973</v>
       </c>
       <c r="D389" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E389" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F389" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G389" t="s">
-        <v>1089</v>
+        <v>983</v>
       </c>
       <c r="H389" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="J389" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K389">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="L389">
-        <v>25.5</v>
+        <v>4.8</v>
       </c>
       <c r="M389">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="P389" s="8">
         <v>46155</v>
@@ -23300,7 +23293,7 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B390" t="s">
         <v>56</v>
@@ -23309,31 +23302,31 @@
         <v>973</v>
       </c>
       <c r="D390" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E390" t="s">
         <v>79</v>
       </c>
       <c r="F390" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G390" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="H390" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="J390" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K390">
         <v>75</v>
       </c>
       <c r="L390">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="M390">
-        <v>152</v>
+        <v>324</v>
       </c>
       <c r="P390" s="8">
         <v>46155</v>
@@ -23341,7 +23334,7 @@
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B391" t="s">
         <v>56</v>
@@ -23359,22 +23352,22 @@
         <v>975</v>
       </c>
       <c r="G391" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="H391" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J391" t="s">
-        <v>93</v>
+        <v>316</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M391">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="P391" s="8">
         <v>46155</v>
@@ -23382,7 +23375,7 @@
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
@@ -23400,22 +23393,22 @@
         <v>975</v>
       </c>
       <c r="G392" t="s">
-        <v>979</v>
+        <v>1094</v>
       </c>
       <c r="H392" t="s">
-        <v>980</v>
+        <v>285</v>
       </c>
       <c r="J392" t="s">
-        <v>316</v>
+        <v>93</v>
       </c>
       <c r="K392">
         <v>75</v>
       </c>
       <c r="L392">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M392">
-        <v>99</v>
+        <v>915</v>
       </c>
       <c r="P392" s="8">
         <v>46155</v>
@@ -23423,7 +23416,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
@@ -23441,10 +23434,10 @@
         <v>975</v>
       </c>
       <c r="G393" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="H393" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J393" t="s">
         <v>93</v>
@@ -23453,10 +23446,10 @@
         <v>75</v>
       </c>
       <c r="L393">
-        <v>4.0999999999999996</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M393">
-        <v>915</v>
+        <v>219</v>
       </c>
       <c r="P393" s="8">
         <v>46155</v>
@@ -23464,7 +23457,7 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
@@ -23479,25 +23472,25 @@
         <v>79</v>
       </c>
       <c r="F394" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G394" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="H394" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="J394" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>4.8499999999999996</v>
+        <v>5.7</v>
       </c>
       <c r="M394">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P394" s="8">
         <v>46155</v>
@@ -23505,7 +23498,7 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
@@ -23520,25 +23513,25 @@
         <v>79</v>
       </c>
       <c r="F395" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G395" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="H395" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="J395" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="M395">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P395" s="8">
         <v>46155</v>
@@ -23546,7 +23539,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
@@ -23564,22 +23557,22 @@
         <v>975</v>
       </c>
       <c r="G396" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="H396" t="s">
-        <v>987</v>
+        <v>1103</v>
       </c>
       <c r="J396" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="M396">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="P396" s="8">
         <v>46155</v>
@@ -23587,7 +23580,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
@@ -23605,22 +23598,25 @@
         <v>975</v>
       </c>
       <c r="G397" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="H397" t="s">
-        <v>1103</v>
+        <v>977</v>
+      </c>
+      <c r="I397" t="s">
+        <v>289</v>
       </c>
       <c r="J397" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M397">
-        <v>27</v>
+        <v>303</v>
       </c>
       <c r="P397" s="8">
         <v>46155</v>
@@ -23628,7 +23624,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
@@ -23646,13 +23642,13 @@
         <v>975</v>
       </c>
       <c r="G398" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="H398" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="I398" t="s">
-        <v>289</v>
+        <v>1007</v>
       </c>
       <c r="J398" t="s">
         <v>63</v>
@@ -23661,10 +23657,10 @@
         <v>75</v>
       </c>
       <c r="L398">
-        <v>5.4</v>
+        <v>6.05</v>
       </c>
       <c r="M398">
-        <v>303</v>
+        <v>187</v>
       </c>
       <c r="P398" s="8">
         <v>46155</v>
@@ -23672,7 +23668,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
@@ -23687,16 +23683,13 @@
         <v>79</v>
       </c>
       <c r="F399" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G399" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="H399" t="s">
-        <v>987</v>
-      </c>
-      <c r="I399" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="J399" t="s">
         <v>63</v>
@@ -23705,10 +23698,10 @@
         <v>75</v>
       </c>
       <c r="L399">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="M399">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="P399" s="8">
         <v>46155</v>
@@ -23716,7 +23709,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
@@ -23725,19 +23718,19 @@
         <v>973</v>
       </c>
       <c r="D400" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E400" t="s">
         <v>79</v>
       </c>
       <c r="F400" t="s">
-        <v>59</v>
+        <v>1111</v>
       </c>
       <c r="G400" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H400" t="s">
-        <v>1012</v>
+        <v>1080</v>
       </c>
       <c r="J400" t="s">
         <v>63</v>
@@ -23746,10 +23739,10 @@
         <v>75</v>
       </c>
       <c r="L400">
-        <v>6.35</v>
+        <v>6.15</v>
       </c>
       <c r="M400">
-        <v>340</v>
+        <v>46</v>
       </c>
       <c r="P400" s="8">
         <v>46155</v>
@@ -23757,7 +23750,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
@@ -23772,25 +23765,25 @@
         <v>79</v>
       </c>
       <c r="F401" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="G401" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="H401" t="s">
-        <v>1080</v>
+        <v>1116</v>
       </c>
       <c r="J401" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>6.15</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M401">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="P401" s="8">
         <v>46155</v>
@@ -23798,7 +23791,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B402" t="s">
         <v>56</v>
@@ -23816,22 +23809,22 @@
         <v>1114</v>
       </c>
       <c r="G402" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="H402" t="s">
         <v>1116</v>
       </c>
       <c r="J402" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>9.8000000000000007</v>
+        <v>18.2</v>
       </c>
       <c r="M402">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="P402" s="8">
         <v>46155</v>
@@ -23839,40 +23832,37 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B403" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C403" t="s">
         <v>973</v>
       </c>
       <c r="D403" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E403" t="s">
         <v>79</v>
       </c>
       <c r="F403" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="G403" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="H403" t="s">
-        <v>1116</v>
+        <v>1067</v>
       </c>
       <c r="J403" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>18.2</v>
-      </c>
-      <c r="M403">
-        <v>36</v>
+        <v>11.4</v>
       </c>
       <c r="P403" s="8">
         <v>46155</v>
@@ -23880,7 +23870,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B404" t="s">
         <v>117</v>
@@ -23895,22 +23885,25 @@
         <v>79</v>
       </c>
       <c r="F404" t="s">
-        <v>1120</v>
+        <v>1054</v>
       </c>
       <c r="G404" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="H404" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="J404" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>11.4</v>
+        <v>12.5</v>
+      </c>
+      <c r="M404">
+        <v>0</v>
       </c>
       <c r="P404" s="8">
         <v>46155</v>
@@ -23918,7 +23911,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B405" t="s">
         <v>117</v>
@@ -23933,22 +23926,22 @@
         <v>79</v>
       </c>
       <c r="F405" t="s">
-        <v>1054</v>
+        <v>1125</v>
       </c>
       <c r="G405" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="H405" t="s">
         <v>1060</v>
       </c>
       <c r="J405" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="M405">
         <v>0</v>
@@ -23959,7 +23952,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B406" t="s">
         <v>117</v>
@@ -23977,19 +23970,19 @@
         <v>1125</v>
       </c>
       <c r="G406" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="H406" t="s">
-        <v>1060</v>
+        <v>1129</v>
       </c>
       <c r="J406" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M406">
         <v>0</v>
@@ -24000,10 +23993,10 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B407" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C407" t="s">
         <v>973</v>
@@ -24015,25 +24008,25 @@
         <v>79</v>
       </c>
       <c r="F407" t="s">
-        <v>1125</v>
+        <v>1062</v>
       </c>
       <c r="G407" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="H407" t="s">
-        <v>1129</v>
+        <v>1072</v>
       </c>
       <c r="J407" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>17</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M407">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P407" s="8">
         <v>46155</v>
@@ -24041,10 +24034,10 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B408" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C408" t="s">
         <v>973</v>
@@ -24059,10 +24052,13 @@
         <v>1062</v>
       </c>
       <c r="G408" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="H408" t="s">
-        <v>1072</v>
+        <v>1060</v>
+      </c>
+      <c r="I408" t="s">
+        <v>62</v>
       </c>
       <c r="J408" t="s">
         <v>63</v>
@@ -24071,10 +24067,10 @@
         <v>75</v>
       </c>
       <c r="L408">
-        <v>4.8499999999999996</v>
+        <v>9.9</v>
       </c>
       <c r="M408">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P408" s="8">
         <v>46155</v>
@@ -24082,7 +24078,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B409" t="s">
         <v>117</v>
@@ -24100,13 +24096,10 @@
         <v>1062</v>
       </c>
       <c r="G409" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="H409" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I409" t="s">
-        <v>62</v>
+        <v>1050</v>
       </c>
       <c r="J409" t="s">
         <v>63</v>
@@ -24115,7 +24108,7 @@
         <v>75</v>
       </c>
       <c r="L409">
-        <v>9.9</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24126,7 +24119,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B410" t="s">
         <v>117</v>
@@ -24144,19 +24137,22 @@
         <v>1062</v>
       </c>
       <c r="G410" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="H410" t="s">
         <v>1050</v>
       </c>
+      <c r="I410" t="s">
+        <v>1051</v>
+      </c>
       <c r="J410" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K410">
         <v>75</v>
       </c>
       <c r="L410">
-        <v>9.9499999999999993</v>
+        <v>11.5</v>
       </c>
       <c r="M410">
         <v>0</v>
@@ -24167,31 +24163,31 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B411" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C411" t="s">
         <v>973</v>
       </c>
       <c r="D411" t="s">
-        <v>1053</v>
+        <v>974</v>
       </c>
       <c r="E411" t="s">
         <v>79</v>
       </c>
       <c r="F411" t="s">
-        <v>1062</v>
+        <v>1139</v>
       </c>
       <c r="G411" t="s">
-        <v>1137</v>
+        <v>824</v>
       </c>
       <c r="H411" t="s">
-        <v>1050</v>
+        <v>1016</v>
       </c>
       <c r="I411" t="s">
-        <v>1051</v>
+        <v>784</v>
       </c>
       <c r="J411" t="s">
         <v>93</v>
@@ -24200,10 +24196,10 @@
         <v>75</v>
       </c>
       <c r="L411">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="M411">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P411" s="8">
         <v>46155</v>
@@ -24211,7 +24207,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B412" t="s">
         <v>56</v>
@@ -24226,28 +24222,28 @@
         <v>79</v>
       </c>
       <c r="F412" t="s">
-        <v>1139</v>
+        <v>975</v>
       </c>
       <c r="G412" t="s">
-        <v>824</v>
+        <v>1141</v>
       </c>
       <c r="H412" t="s">
-        <v>1016</v>
+        <v>1142</v>
       </c>
       <c r="I412" t="s">
-        <v>784</v>
+        <v>62</v>
       </c>
       <c r="J412" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="M412">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="P412" s="8">
         <v>46155</v>
@@ -24255,10 +24251,10 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B413" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C413" t="s">
         <v>973</v>
@@ -24270,28 +24266,25 @@
         <v>79</v>
       </c>
       <c r="F413" t="s">
-        <v>975</v>
+        <v>1144</v>
       </c>
       <c r="G413" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="H413" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I413" t="s">
-        <v>62</v>
+        <v>1146</v>
       </c>
       <c r="J413" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>16.3</v>
+        <v>9.4</v>
       </c>
       <c r="M413">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="P413" s="8">
         <v>46155</v>
@@ -24299,7 +24292,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B414" t="s">
         <v>117</v>
@@ -24317,22 +24310,19 @@
         <v>1144</v>
       </c>
       <c r="G414" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="H414" t="s">
         <v>1146</v>
       </c>
       <c r="J414" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>9.4</v>
-      </c>
-      <c r="M414">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P414" s="8">
         <v>46155</v>
@@ -24340,10 +24330,10 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B415" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C415" t="s">
         <v>973</v>
@@ -24355,22 +24345,28 @@
         <v>79</v>
       </c>
       <c r="F415" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="G415" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="H415" t="s">
-        <v>1146</v>
+        <v>1152</v>
+      </c>
+      <c r="I415" t="s">
+        <v>62</v>
       </c>
       <c r="J415" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>31</v>
+        <v>7.6</v>
+      </c>
+      <c r="M415">
+        <v>270.39999999999998</v>
       </c>
       <c r="P415" s="8">
         <v>46155</v>
@@ -24378,10 +24374,10 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B416" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C416" t="s">
         <v>973</v>
@@ -24393,28 +24389,25 @@
         <v>79</v>
       </c>
       <c r="F416" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="G416" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="H416" t="s">
-        <v>1152</v>
-      </c>
-      <c r="I416" t="s">
-        <v>62</v>
+        <v>1044</v>
       </c>
       <c r="J416" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="M416">
-        <v>270.39999999999998</v>
+        <v>18</v>
       </c>
       <c r="P416" s="8">
         <v>46155</v>
@@ -24422,7 +24415,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B417" t="s">
         <v>117</v>
@@ -24440,22 +24433,22 @@
         <v>1154</v>
       </c>
       <c r="G417" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="H417" t="s">
         <v>1044</v>
       </c>
       <c r="J417" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>6.9</v>
+        <v>8.25</v>
       </c>
       <c r="M417">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="P417" s="8">
         <v>46155</v>
@@ -24463,10 +24456,10 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B418" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C418" t="s">
         <v>973</v>
@@ -24481,22 +24474,22 @@
         <v>1154</v>
       </c>
       <c r="G418" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="H418" t="s">
-        <v>1044</v>
+        <v>1160</v>
       </c>
       <c r="J418" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>8.25</v>
+        <v>15.9</v>
       </c>
       <c r="M418">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="P418" s="8">
         <v>46155</v>
@@ -24504,7 +24497,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B419" t="s">
         <v>56</v>
@@ -24519,13 +24512,16 @@
         <v>79</v>
       </c>
       <c r="F419" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="G419" t="s">
-        <v>1159</v>
+        <v>159</v>
       </c>
       <c r="H419" t="s">
-        <v>1160</v>
+        <v>1163</v>
+      </c>
+      <c r="I419" t="s">
+        <v>784</v>
       </c>
       <c r="J419" t="s">
         <v>82</v>
@@ -24534,10 +24530,7 @@
         <v>75</v>
       </c>
       <c r="L419">
-        <v>15.9</v>
-      </c>
-      <c r="M419">
-        <v>49</v>
+        <v>17.8</v>
       </c>
       <c r="P419" s="8">
         <v>46155</v>
@@ -24545,7 +24538,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B420" t="s">
         <v>56</v>
@@ -24560,25 +24553,25 @@
         <v>79</v>
       </c>
       <c r="F420" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="G420" t="s">
-        <v>159</v>
+        <v>1165</v>
       </c>
       <c r="H420" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I420" t="s">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="J420" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>17.8</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M420">
+        <v>53</v>
       </c>
       <c r="P420" s="8">
         <v>46155</v>
@@ -24586,7 +24579,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B421" t="s">
         <v>56</v>
@@ -24601,25 +24594,25 @@
         <v>79</v>
       </c>
       <c r="F421" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="G421" t="s">
-        <v>1165</v>
+        <v>159</v>
       </c>
       <c r="H421" t="s">
-        <v>1160</v>
+        <v>1168</v>
+      </c>
+      <c r="I421" t="s">
+        <v>784</v>
       </c>
       <c r="J421" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M421">
-        <v>53</v>
+        <v>22.3</v>
       </c>
       <c r="P421" s="8">
         <v>46155</v>
@@ -24627,7 +24620,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="B422" t="s">
         <v>56</v>
@@ -24642,25 +24635,28 @@
         <v>79</v>
       </c>
       <c r="F422" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="G422" t="s">
-        <v>159</v>
+        <v>1171</v>
       </c>
       <c r="H422" t="s">
-        <v>1168</v>
+        <v>1001</v>
       </c>
       <c r="I422" t="s">
-        <v>784</v>
+        <v>169</v>
       </c>
       <c r="J422" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>22.3</v>
+        <v>6.5</v>
+      </c>
+      <c r="M422">
+        <v>42</v>
       </c>
       <c r="P422" s="8">
         <v>46155</v>
@@ -24668,10 +24664,10 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B423" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C423" t="s">
         <v>973</v>
@@ -24686,13 +24682,10 @@
         <v>1170</v>
       </c>
       <c r="G423" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="H423" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I423" t="s">
-        <v>169</v>
+        <v>1174</v>
       </c>
       <c r="J423" t="s">
         <v>93</v>
@@ -24701,18 +24694,18 @@
         <v>75</v>
       </c>
       <c r="L423">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="M423">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="P423" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
-        <v>1172</v>
+      <c r="A424">
+        <v>16003124</v>
       </c>
       <c r="B424" t="s">
         <v>117</v>
@@ -24724,13 +24717,13 @@
         <v>974</v>
       </c>
       <c r="E424" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F424" t="s">
         <v>1170</v>
       </c>
       <c r="G424" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="H424" t="s">
         <v>1174</v>
@@ -24752,11 +24745,11 @@
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A425">
-        <v>16003124</v>
+      <c r="A425" t="s">
+        <v>1176</v>
       </c>
       <c r="B425" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C425" t="s">
         <v>973</v>
@@ -24765,28 +24758,31 @@
         <v>974</v>
       </c>
       <c r="E425" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F425" t="s">
         <v>1170</v>
       </c>
       <c r="G425" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="H425" t="s">
-        <v>1174</v>
+        <v>1001</v>
+      </c>
+      <c r="I425" t="s">
+        <v>169</v>
       </c>
       <c r="J425" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K425">
         <v>75</v>
       </c>
       <c r="L425">
-        <v>8.4</v>
+        <v>8.61</v>
       </c>
       <c r="M425">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P425" s="8">
         <v>46155</v>
@@ -24794,10 +24790,10 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B426" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C426" t="s">
         <v>973</v>
@@ -24812,13 +24808,13 @@
         <v>1170</v>
       </c>
       <c r="G426" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="H426" t="s">
-        <v>1001</v>
+        <v>1174</v>
       </c>
       <c r="I426" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J426" t="s">
         <v>63</v>
@@ -24827,10 +24823,10 @@
         <v>75</v>
       </c>
       <c r="L426">
-        <v>8.61</v>
+        <v>9.6</v>
       </c>
       <c r="M426">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P426" s="8">
         <v>46155</v>
@@ -24838,10 +24834,10 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B427" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C427" t="s">
         <v>973</v>
@@ -24856,13 +24852,13 @@
         <v>1170</v>
       </c>
       <c r="G427" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="H427" t="s">
-        <v>1174</v>
+        <v>1001</v>
       </c>
       <c r="I427" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="J427" t="s">
         <v>63</v>
@@ -24871,7 +24867,7 @@
         <v>75</v>
       </c>
       <c r="L427">
-        <v>9.6</v>
+        <v>13.82</v>
       </c>
       <c r="M427">
         <v>171</v>
@@ -24882,10 +24878,10 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B428" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C428" t="s">
         <v>973</v>
@@ -24900,25 +24896,19 @@
         <v>1170</v>
       </c>
       <c r="G428" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="H428" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I428" t="s">
-        <v>169</v>
+        <v>1184</v>
       </c>
       <c r="J428" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>13.82</v>
-      </c>
-      <c r="M428">
-        <v>171</v>
+        <v>18.3</v>
       </c>
       <c r="P428" s="8">
         <v>46155</v>
@@ -24926,10 +24916,10 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="B429" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C429" t="s">
         <v>973</v>
@@ -24941,22 +24931,28 @@
         <v>79</v>
       </c>
       <c r="F429" t="s">
-        <v>1170</v>
+        <v>59</v>
       </c>
       <c r="G429" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="H429" t="s">
-        <v>1184</v>
+        <v>1001</v>
+      </c>
+      <c r="I429" t="s">
+        <v>169</v>
       </c>
       <c r="J429" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>18.3</v>
+        <v>24.08</v>
+      </c>
+      <c r="M429">
+        <v>12</v>
       </c>
       <c r="P429" s="8">
         <v>46155</v>
@@ -24964,10 +24960,10 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B430" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C430" t="s">
         <v>973</v>
@@ -24979,28 +24975,19 @@
         <v>79</v>
       </c>
       <c r="F430" t="s">
-        <v>59</v>
-      </c>
-      <c r="G430" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="H430" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I430" t="s">
-        <v>169</v>
+        <v>1189</v>
       </c>
       <c r="J430" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="K430">
         <v>75</v>
       </c>
       <c r="L430">
-        <v>24.08</v>
-      </c>
-      <c r="M430">
-        <v>12</v>
+        <v>31.7</v>
       </c>
       <c r="P430" s="8">
         <v>46155</v>
@@ -25008,10 +24995,10 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="B431" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C431" t="s">
         <v>973</v>
@@ -25023,10 +25010,10 @@
         <v>79</v>
       </c>
       <c r="F431" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="H431" t="s">
-        <v>1189</v>
+        <v>977</v>
       </c>
       <c r="J431" t="s">
         <v>63</v>
@@ -25035,15 +25022,18 @@
         <v>75</v>
       </c>
       <c r="L431">
-        <v>31.7</v>
+        <v>7.05</v>
+      </c>
+      <c r="M431">
+        <v>30</v>
       </c>
       <c r="P431" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>1190</v>
+      <c r="A432">
+        <v>27100522</v>
       </c>
       <c r="B432" t="s">
         <v>56</v>
@@ -25058,33 +25048,36 @@
         <v>79</v>
       </c>
       <c r="F432" t="s">
-        <v>1191</v>
+        <v>1192</v>
+      </c>
+      <c r="G432" t="s">
+        <v>1193</v>
       </c>
       <c r="H432" t="s">
-        <v>977</v>
-      </c>
-      <c r="J432" t="s">
-        <v>63</v>
+        <v>1194</v>
+      </c>
+      <c r="I432" t="s">
+        <v>784</v>
+      </c>
+      <c r="J432">
+        <v>2022</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>7.05</v>
-      </c>
-      <c r="M432">
-        <v>30</v>
+        <v>17.8</v>
       </c>
       <c r="P432" s="8">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A433">
-        <v>27100522</v>
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="433" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>1195</v>
       </c>
       <c r="B433" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C433" t="s">
         <v>973</v>
@@ -25096,36 +25089,33 @@
         <v>79</v>
       </c>
       <c r="F433" t="s">
-        <v>1192</v>
+        <v>59</v>
       </c>
       <c r="G433" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="H433" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I433" t="s">
-        <v>784</v>
-      </c>
-      <c r="J433">
-        <v>2022</v>
+        <v>1197</v>
+      </c>
+      <c r="J433" t="s">
+        <v>1198</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>17.8</v>
+        <v>95</v>
       </c>
       <c r="P433" s="8">
-        <v>46178</v>
-      </c>
-    </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="434" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B434" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C434" t="s">
         <v>973</v>
@@ -25137,33 +25127,33 @@
         <v>79</v>
       </c>
       <c r="F434" t="s">
-        <v>59</v>
+        <v>1200</v>
       </c>
       <c r="G434" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="H434" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="J434" t="s">
-        <v>1198</v>
+        <v>93</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>95</v>
+        <v>7.35</v>
+      </c>
+      <c r="M434">
+        <v>2215</v>
       </c>
       <c r="P434" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>1199</v>
-      </c>
+    <row r="435" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B435" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C435" t="s">
         <v>973</v>
@@ -25178,19 +25168,19 @@
         <v>1200</v>
       </c>
       <c r="G435" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="H435" t="s">
         <v>1202</v>
       </c>
       <c r="J435" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K435">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L435">
-        <v>7.35</v>
+        <v>15.95</v>
       </c>
       <c r="M435">
         <v>2215</v>
@@ -25199,9 +25189,12 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>1204</v>
+      </c>
       <c r="B436" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C436" t="s">
         <v>973</v>
@@ -25216,30 +25209,30 @@
         <v>1200</v>
       </c>
       <c r="G436" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="H436" t="s">
         <v>1202</v>
       </c>
       <c r="J436" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K436">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L436">
-        <v>15.95</v>
+        <v>8.35</v>
       </c>
       <c r="M436">
-        <v>2215</v>
+        <v>279</v>
       </c>
       <c r="P436" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B437" t="s">
         <v>56</v>
@@ -25257,33 +25250,36 @@
         <v>1200</v>
       </c>
       <c r="G437" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="H437" t="s">
-        <v>1202</v>
+        <v>1208</v>
+      </c>
+      <c r="I437" t="s">
+        <v>1209</v>
       </c>
       <c r="J437" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>8.35</v>
+        <v>13.5</v>
       </c>
       <c r="M437">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="P437" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="B438" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C438" t="s">
         <v>973</v>
@@ -25298,33 +25294,27 @@
         <v>1200</v>
       </c>
       <c r="G438" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="H438" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I438" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="J438" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K438">
         <v>75</v>
       </c>
       <c r="L438">
-        <v>13.5</v>
-      </c>
-      <c r="M438">
-        <v>205</v>
+        <v>14.5</v>
       </c>
       <c r="P438" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B439" t="s">
         <v>117</v>
@@ -25342,10 +25332,10 @@
         <v>1200</v>
       </c>
       <c r="G439" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="H439" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="J439" t="s">
         <v>93</v>
@@ -25354,18 +25344,21 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>14.5</v>
+        <v>14.6</v>
+      </c>
+      <c r="M439">
+        <v>0</v>
       </c>
       <c r="P439" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="B440" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C440" t="s">
         <v>973</v>
@@ -25377,33 +25370,30 @@
         <v>79</v>
       </c>
       <c r="F440" t="s">
-        <v>1200</v>
+        <v>1024</v>
       </c>
       <c r="G440" t="s">
-        <v>1214</v>
+        <v>159</v>
       </c>
       <c r="H440" t="s">
-        <v>1215</v>
+        <v>1025</v>
       </c>
       <c r="J440" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>14.6</v>
-      </c>
-      <c r="M440">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P440" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -25415,33 +25405,36 @@
         <v>974</v>
       </c>
       <c r="E441" t="s">
-        <v>79</v>
+        <v>928</v>
       </c>
       <c r="F441" t="s">
-        <v>1024</v>
+        <v>975</v>
       </c>
       <c r="G441" t="s">
-        <v>159</v>
+        <v>976</v>
       </c>
       <c r="H441" t="s">
-        <v>1025</v>
+        <v>977</v>
       </c>
       <c r="J441" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>37</v>
+        <v>3.8</v>
+      </c>
+      <c r="M441">
+        <v>324</v>
       </c>
       <c r="P441" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B442" t="s">
         <v>56</v>
@@ -25459,10 +25452,10 @@
         <v>975</v>
       </c>
       <c r="G442" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="H442" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J442" t="s">
         <v>93</v>
@@ -25471,18 +25464,18 @@
         <v>75</v>
       </c>
       <c r="L442">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M442">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="P442" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B443" t="s">
         <v>56</v>
@@ -25500,10 +25493,10 @@
         <v>975</v>
       </c>
       <c r="G443" t="s">
-        <v>979</v>
+        <v>1220</v>
       </c>
       <c r="H443" t="s">
-        <v>980</v>
+        <v>285</v>
       </c>
       <c r="J443" t="s">
         <v>93</v>
@@ -25512,21 +25505,21 @@
         <v>75</v>
       </c>
       <c r="L443">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="M443">
-        <v>368</v>
+        <v>969</v>
       </c>
       <c r="P443" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B444" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C444" t="s">
         <v>973</v>
@@ -25541,33 +25534,33 @@
         <v>975</v>
       </c>
       <c r="G444" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="H444" t="s">
-        <v>285</v>
+        <v>1194</v>
       </c>
       <c r="J444" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>3.99</v>
+        <v>7.2</v>
       </c>
       <c r="M444">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="P444" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B445" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C445" t="s">
         <v>973</v>
@@ -25582,30 +25575,30 @@
         <v>975</v>
       </c>
       <c r="G445" t="s">
-        <v>1222</v>
+        <v>1087</v>
       </c>
       <c r="H445" t="s">
-        <v>1194</v>
+        <v>977</v>
       </c>
       <c r="J445" t="s">
-        <v>334</v>
+        <v>576</v>
       </c>
       <c r="K445">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="L445">
-        <v>7.2</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M445">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="P445" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B446" t="s">
         <v>56</v>
@@ -25623,71 +25616,71 @@
         <v>975</v>
       </c>
       <c r="G446" t="s">
-        <v>1087</v>
+        <v>1225</v>
       </c>
       <c r="H446" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="J446" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K446">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L446">
-        <v>16.399999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="M446">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="P446" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B447" t="s">
         <v>56</v>
       </c>
       <c r="C447" t="s">
-        <v>973</v>
+        <v>1227</v>
       </c>
       <c r="D447" t="s">
-        <v>974</v>
+        <v>1228</v>
       </c>
       <c r="E447" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F447" t="s">
-        <v>975</v>
+        <v>1229</v>
       </c>
       <c r="G447" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="H447" t="s">
-        <v>980</v>
+        <v>1231</v>
       </c>
       <c r="J447" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K447">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="L447">
-        <v>25.5</v>
+        <v>5</v>
       </c>
       <c r="M447">
-        <v>71</v>
+        <v>240</v>
       </c>
       <c r="P447" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="B448" t="s">
         <v>56</v>
@@ -25702,13 +25695,13 @@
         <v>58</v>
       </c>
       <c r="F448" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="G448" t="s">
-        <v>1230</v>
+        <v>108</v>
       </c>
       <c r="H448" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="J448" t="s">
         <v>334</v>
@@ -25717,18 +25710,21 @@
         <v>75</v>
       </c>
       <c r="L448">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="M448">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="P448" s="8">
         <v>46155</v>
       </c>
-    </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R448" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="B449" t="s">
         <v>56</v>
@@ -25740,39 +25736,36 @@
         <v>1228</v>
       </c>
       <c r="E449" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F449" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="G449" t="s">
-        <v>108</v>
+        <v>1236</v>
       </c>
       <c r="H449" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J449" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>9.1</v>
+        <v>5.55</v>
       </c>
       <c r="M449">
-        <v>66</v>
+        <v>549</v>
       </c>
       <c r="P449" s="8">
         <v>46155</v>
       </c>
-      <c r="R449" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B450" t="s">
         <v>56</v>
@@ -25784,36 +25777,36 @@
         <v>1228</v>
       </c>
       <c r="E450" t="s">
-        <v>928</v>
+        <v>79</v>
       </c>
       <c r="F450" t="s">
-        <v>1229</v>
+        <v>1238</v>
       </c>
       <c r="G450" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="H450" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="J450" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="M450">
-        <v>549</v>
+        <v>3</v>
       </c>
       <c r="P450" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="B451" t="s">
         <v>56</v>
@@ -25828,33 +25821,33 @@
         <v>79</v>
       </c>
       <c r="F451" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="G451" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="H451" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="J451" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="M451">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="P451" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B452" t="s">
         <v>56</v>
@@ -25869,33 +25862,33 @@
         <v>79</v>
       </c>
       <c r="F452" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
       <c r="G452" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="H452" t="s">
-        <v>1244</v>
+        <v>1231</v>
       </c>
       <c r="J452" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="M452">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="P452" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B453" t="s">
         <v>56</v>
@@ -25910,33 +25903,30 @@
         <v>79</v>
       </c>
       <c r="F453" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G453" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="H453" t="s">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="J453" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="M453">
-        <v>54</v>
+        <v>666</v>
       </c>
       <c r="P453" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B454" t="s">
         <v>56</v>
@@ -25951,30 +25941,36 @@
         <v>79</v>
       </c>
       <c r="F454" t="s">
-        <v>1248</v>
+        <v>1251</v>
+      </c>
+      <c r="G454" t="s">
+        <v>1252</v>
       </c>
       <c r="H454" t="s">
-        <v>1249</v>
+        <v>1253</v>
+      </c>
+      <c r="I454" t="s">
+        <v>62</v>
       </c>
       <c r="J454" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>6.85</v>
+        <v>8.25</v>
       </c>
       <c r="M454">
-        <v>666</v>
+        <v>318</v>
       </c>
       <c r="P454" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B455" t="s">
         <v>56</v>
@@ -25983,22 +25979,19 @@
         <v>1227</v>
       </c>
       <c r="D455" t="s">
-        <v>1228</v>
+        <v>1255</v>
       </c>
       <c r="E455" t="s">
         <v>79</v>
       </c>
       <c r="F455" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="G455" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="H455" t="s">
-        <v>1253</v>
-      </c>
-      <c r="I455" t="s">
-        <v>62</v>
+        <v>1258</v>
       </c>
       <c r="J455" t="s">
         <v>63</v>
@@ -26007,18 +26000,15 @@
         <v>75</v>
       </c>
       <c r="L455">
-        <v>8.25</v>
-      </c>
-      <c r="M455">
-        <v>318</v>
+        <v>4.95</v>
       </c>
       <c r="P455" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="456" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="B456" t="s">
         <v>56</v>
@@ -26036,30 +26026,33 @@
         <v>1256</v>
       </c>
       <c r="G456" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="H456" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="J456" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>4.95</v>
+        <v>6.1</v>
+      </c>
+      <c r="M456">
+        <v>133</v>
       </c>
       <c r="P456" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="457" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="B457" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C457" t="s">
         <v>1227</v>
@@ -26074,30 +26067,30 @@
         <v>1256</v>
       </c>
       <c r="G457" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="H457" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="J457" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>6.1</v>
+        <v>13.2</v>
       </c>
       <c r="M457">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="P457" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="458" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="B458" t="s">
         <v>117</v>
@@ -26115,19 +26108,19 @@
         <v>1256</v>
       </c>
       <c r="G458" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="H458" t="s">
         <v>1264</v>
       </c>
       <c r="J458" t="s">
-        <v>104</v>
+        <v>1198</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>13.2</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -26136,9 +26129,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="459" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B459" t="s">
         <v>117</v>
@@ -26153,22 +26146,22 @@
         <v>79</v>
       </c>
       <c r="F459" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="G459" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="H459" t="s">
         <v>1264</v>
       </c>
       <c r="J459" t="s">
-        <v>1198</v>
+        <v>63</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>16.350000000000001</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M459">
         <v>0</v>
@@ -26177,50 +26170,50 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="460" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="B460" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C460" t="s">
         <v>1227</v>
       </c>
       <c r="D460" t="s">
-        <v>1255</v>
+        <v>1271</v>
       </c>
       <c r="E460" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F460" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G460" t="s">
-        <v>1269</v>
+        <v>732</v>
       </c>
       <c r="H460" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="J460" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>5.0999999999999996</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M460">
-        <v>0</v>
+        <v>1327</v>
       </c>
       <c r="P460" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="461" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="B461" t="s">
         <v>56</v>
@@ -26229,39 +26222,39 @@
         <v>1227</v>
       </c>
       <c r="D461" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E461" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F461" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="G461" t="s">
-        <v>732</v>
+        <v>1276</v>
       </c>
       <c r="H461" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="J461" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K461">
         <v>75</v>
       </c>
       <c r="L461">
-        <v>4.6500000000000004</v>
+        <v>8.5</v>
       </c>
       <c r="M461">
-        <v>1327</v>
+        <v>6</v>
       </c>
       <c r="P461" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="462" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="B462" t="s">
         <v>56</v>
@@ -26279,7 +26272,7 @@
         <v>1275</v>
       </c>
       <c r="G462" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="H462" t="s">
         <v>1277</v>
@@ -26291,18 +26284,18 @@
         <v>75</v>
       </c>
       <c r="L462">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M462">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="P462" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="463" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B463" t="s">
         <v>56</v>
@@ -26320,7 +26313,7 @@
         <v>1275</v>
       </c>
       <c r="G463" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="H463" t="s">
         <v>1277</v>
@@ -26335,15 +26328,15 @@
         <v>8.6</v>
       </c>
       <c r="M463">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P463" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="464" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B464" t="s">
         <v>56</v>
@@ -26361,13 +26354,13 @@
         <v>1275</v>
       </c>
       <c r="G464" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="H464" t="s">
         <v>1277</v>
       </c>
       <c r="J464" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K464">
         <v>75</v>
@@ -26376,7 +26369,7 @@
         <v>8.6</v>
       </c>
       <c r="M464">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="P464" s="8">
         <v>46155</v>
@@ -26384,7 +26377,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B465" t="s">
         <v>56</v>
@@ -26402,7 +26395,7 @@
         <v>1275</v>
       </c>
       <c r="G465" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="H465" t="s">
         <v>1277</v>
@@ -26417,7 +26410,7 @@
         <v>8.6</v>
       </c>
       <c r="M465">
-        <v>18</v>
+        <v>662</v>
       </c>
       <c r="P465" s="8">
         <v>46155</v>
@@ -26425,7 +26418,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B466" t="s">
         <v>56</v>
@@ -26443,22 +26436,22 @@
         <v>1275</v>
       </c>
       <c r="G466" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="H466" t="s">
         <v>1277</v>
       </c>
       <c r="J466" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>8.6</v>
+        <v>12.05</v>
       </c>
       <c r="M466">
-        <v>662</v>
+        <v>64</v>
       </c>
       <c r="P466" s="8">
         <v>46155</v>
@@ -26466,7 +26459,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B467" t="s">
         <v>56</v>
@@ -26484,22 +26477,22 @@
         <v>1275</v>
       </c>
       <c r="G467" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="H467" t="s">
         <v>1277</v>
       </c>
       <c r="J467" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>12.05</v>
+        <v>13</v>
       </c>
       <c r="M467">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="P467" s="8">
         <v>46155</v>
@@ -26507,7 +26500,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B468" t="s">
         <v>56</v>
@@ -26525,7 +26518,7 @@
         <v>1275</v>
       </c>
       <c r="G468" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="H468" t="s">
         <v>1277</v>
@@ -26540,7 +26533,7 @@
         <v>13</v>
       </c>
       <c r="M468">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P468" s="8">
         <v>46155</v>
@@ -26548,7 +26541,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B469" t="s">
         <v>56</v>
@@ -26566,7 +26559,7 @@
         <v>1275</v>
       </c>
       <c r="G469" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="H469" t="s">
         <v>1277</v>
@@ -26578,7 +26571,7 @@
         <v>75</v>
       </c>
       <c r="L469">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M469">
         <v>36</v>
@@ -26589,7 +26582,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B470" t="s">
         <v>56</v>
@@ -26601,28 +26594,28 @@
         <v>1274</v>
       </c>
       <c r="E470" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F470" t="s">
         <v>1275</v>
       </c>
       <c r="G470" t="s">
-        <v>1292</v>
+        <v>1037</v>
       </c>
       <c r="H470" t="s">
         <v>1277</v>
       </c>
       <c r="J470" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>16</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M470">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="P470" s="8">
         <v>46155</v>
@@ -26630,40 +26623,40 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B471" t="s">
         <v>56</v>
       </c>
       <c r="C471" t="s">
-        <v>1227</v>
+        <v>1295</v>
       </c>
       <c r="D471" t="s">
-        <v>1274</v>
+        <v>1228</v>
       </c>
       <c r="E471" t="s">
-        <v>58</v>
+        <v>1295</v>
       </c>
       <c r="F471" t="s">
-        <v>1275</v>
+        <v>1296</v>
       </c>
       <c r="G471" t="s">
-        <v>1037</v>
+        <v>1297</v>
       </c>
       <c r="H471" t="s">
-        <v>1277</v>
+        <v>1231</v>
       </c>
       <c r="J471" t="s">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>8.0500000000000007</v>
+        <v>6.2</v>
       </c>
       <c r="M471">
-        <v>55</v>
+        <v>4411</v>
       </c>
       <c r="P471" s="8">
         <v>46155</v>
@@ -26671,7 +26664,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B472" t="s">
         <v>56</v>
@@ -26679,20 +26672,17 @@
       <c r="C472" t="s">
         <v>1295</v>
       </c>
-      <c r="D472" t="s">
-        <v>1228</v>
-      </c>
       <c r="E472" t="s">
         <v>1295</v>
       </c>
       <c r="F472" t="s">
-        <v>1296</v>
+        <v>59</v>
       </c>
       <c r="G472" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="H472" t="s">
-        <v>1231</v>
+        <v>996</v>
       </c>
       <c r="J472" t="s">
         <v>576</v>
@@ -26703,16 +26693,13 @@
       <c r="L472">
         <v>6.2</v>
       </c>
-      <c r="M472">
-        <v>4411</v>
-      </c>
       <c r="P472" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B473" t="s">
         <v>56</v>
@@ -26727,10 +26714,10 @@
         <v>59</v>
       </c>
       <c r="G473" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="H473" t="s">
-        <v>996</v>
+        <v>1302</v>
       </c>
       <c r="J473" t="s">
         <v>576</v>
@@ -26739,7 +26726,7 @@
         <v>75</v>
       </c>
       <c r="L473">
-        <v>6.2</v>
+        <v>8.99</v>
       </c>
       <c r="P473" s="8">
         <v>46155</v>
@@ -26747,7 +26734,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="B474" t="s">
         <v>56</v>
@@ -26759,22 +26746,25 @@
         <v>1295</v>
       </c>
       <c r="F474" t="s">
-        <v>59</v>
+        <v>1304</v>
       </c>
       <c r="G474" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="H474" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="J474" t="s">
         <v>576</v>
       </c>
       <c r="K474">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L474">
-        <v>8.99</v>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M474">
+        <v>5</v>
       </c>
       <c r="P474" s="8">
         <v>46155</v>
@@ -26782,7 +26772,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B475" t="s">
         <v>56</v>
@@ -26797,22 +26787,22 @@
         <v>1304</v>
       </c>
       <c r="G475" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="H475" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="J475" t="s">
         <v>576</v>
       </c>
       <c r="K475">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L475">
-        <v>16.899999999999999</v>
+        <v>16.45</v>
       </c>
       <c r="M475">
-        <v>5</v>
+        <v>6532</v>
       </c>
       <c r="P475" s="8">
         <v>46155</v>
@@ -26820,7 +26810,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B476" t="s">
         <v>56</v>
@@ -26835,10 +26825,10 @@
         <v>1304</v>
       </c>
       <c r="G476" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="H476" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="J476" t="s">
         <v>576</v>
@@ -26847,10 +26837,10 @@
         <v>75</v>
       </c>
       <c r="L476">
-        <v>16.45</v>
+        <v>23.5</v>
       </c>
       <c r="M476">
-        <v>6532</v>
+        <v>418</v>
       </c>
       <c r="P476" s="8">
         <v>46155</v>
@@ -26858,10 +26848,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B477" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C477" t="s">
         <v>1295</v>
@@ -26873,10 +26863,10 @@
         <v>1304</v>
       </c>
       <c r="G477" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="H477" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="J477" t="s">
         <v>576</v>
@@ -26885,10 +26875,7 @@
         <v>75</v>
       </c>
       <c r="L477">
-        <v>23.5</v>
-      </c>
-      <c r="M477">
-        <v>418</v>
+        <v>23.9</v>
       </c>
       <c r="P477" s="8">
         <v>46155</v>
@@ -26896,10 +26883,10 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B478" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C478" t="s">
         <v>1295</v>
@@ -26911,10 +26898,10 @@
         <v>1304</v>
       </c>
       <c r="G478" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="H478" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="J478" t="s">
         <v>576</v>
@@ -26923,7 +26910,10 @@
         <v>75</v>
       </c>
       <c r="L478">
-        <v>23.9</v>
+        <v>25.7</v>
+      </c>
+      <c r="M478">
+        <v>34</v>
       </c>
       <c r="P478" s="8">
         <v>46155</v>
@@ -26931,7 +26921,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="B479" t="s">
         <v>56</v>
@@ -26946,10 +26936,10 @@
         <v>1304</v>
       </c>
       <c r="G479" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="H479" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="J479" t="s">
         <v>576</v>
@@ -26958,10 +26948,10 @@
         <v>75</v>
       </c>
       <c r="L479">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="M479">
-        <v>34</v>
+        <v>995</v>
       </c>
       <c r="P479" s="8">
         <v>46155</v>
@@ -26969,7 +26959,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B480" t="s">
         <v>56</v>
@@ -26984,10 +26974,10 @@
         <v>1304</v>
       </c>
       <c r="G480" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="H480" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="J480" t="s">
         <v>576</v>
@@ -26996,10 +26986,10 @@
         <v>75</v>
       </c>
       <c r="L480">
-        <v>25.8</v>
+        <v>27.5</v>
       </c>
       <c r="M480">
-        <v>995</v>
+        <v>31</v>
       </c>
       <c r="P480" s="8">
         <v>46155</v>
@@ -27007,7 +26997,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B481" t="s">
         <v>56</v>
@@ -27022,10 +27012,10 @@
         <v>1304</v>
       </c>
       <c r="G481" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="H481" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="J481" t="s">
         <v>576</v>
@@ -27034,10 +27024,10 @@
         <v>75</v>
       </c>
       <c r="L481">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="M481">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P481" s="8">
         <v>46155</v>
@@ -27045,7 +27035,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="B482" t="s">
         <v>56</v>
@@ -27060,10 +27050,10 @@
         <v>1304</v>
       </c>
       <c r="G482" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="H482" t="s">
-        <v>1306</v>
+        <v>1321</v>
       </c>
       <c r="J482" t="s">
         <v>576</v>
@@ -27072,10 +27062,10 @@
         <v>75</v>
       </c>
       <c r="L482">
-        <v>29</v>
+        <v>29.35</v>
       </c>
       <c r="M482">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="P482" s="8">
         <v>46155</v>
@@ -27083,7 +27073,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="B483" t="s">
         <v>56</v>
@@ -27098,10 +27088,10 @@
         <v>1304</v>
       </c>
       <c r="G483" t="s">
-        <v>1328</v>
+        <v>923</v>
       </c>
       <c r="H483" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="J483" t="s">
         <v>576</v>
@@ -27110,10 +27100,10 @@
         <v>75</v>
       </c>
       <c r="L483">
-        <v>29.35</v>
+        <v>29.8</v>
       </c>
       <c r="M483">
-        <v>60</v>
+        <v>417</v>
       </c>
       <c r="P483" s="8">
         <v>46155</v>
@@ -27121,7 +27111,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B484" t="s">
         <v>56</v>
@@ -27136,10 +27126,10 @@
         <v>1304</v>
       </c>
       <c r="G484" t="s">
-        <v>923</v>
+        <v>1331</v>
       </c>
       <c r="H484" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="J484" t="s">
         <v>576</v>
@@ -27148,10 +27138,10 @@
         <v>75</v>
       </c>
       <c r="L484">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="M484">
-        <v>417</v>
+        <v>777</v>
       </c>
       <c r="P484" s="8">
         <v>46155</v>
@@ -27159,7 +27149,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="B485" t="s">
         <v>56</v>
@@ -27174,10 +27164,10 @@
         <v>1304</v>
       </c>
       <c r="G485" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="H485" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="J485" t="s">
         <v>576</v>
@@ -27186,10 +27176,10 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M485">
-        <v>777</v>
+        <v>428</v>
       </c>
       <c r="P485" s="8">
         <v>46155</v>
@@ -27197,7 +27187,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="B486" t="s">
         <v>56</v>
@@ -27212,10 +27202,10 @@
         <v>1304</v>
       </c>
       <c r="G486" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="H486" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="J486" t="s">
         <v>576</v>
@@ -27224,10 +27214,10 @@
         <v>75</v>
       </c>
       <c r="L486">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M486">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="P486" s="8">
         <v>46155</v>
@@ -27235,7 +27225,7 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B487" t="s">
         <v>56</v>
@@ -27250,10 +27240,10 @@
         <v>1304</v>
       </c>
       <c r="G487" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="H487" t="s">
-        <v>1338</v>
+        <v>1321</v>
       </c>
       <c r="J487" t="s">
         <v>576</v>
@@ -27262,10 +27252,10 @@
         <v>75</v>
       </c>
       <c r="L487">
-        <v>33</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M487">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P487" s="8">
         <v>46155</v>
@@ -27273,7 +27263,7 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="B488" t="s">
         <v>56</v>
@@ -27288,10 +27278,10 @@
         <v>1304</v>
       </c>
       <c r="G488" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="H488" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="J488" t="s">
         <v>576</v>
@@ -27300,10 +27290,10 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>34.200000000000003</v>
+        <v>39</v>
       </c>
       <c r="M488">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P488" s="8">
         <v>46155</v>
@@ -27311,10 +27301,10 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="B489" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C489" t="s">
         <v>1295</v>
@@ -27326,10 +27316,10 @@
         <v>1304</v>
       </c>
       <c r="G489" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="H489" t="s">
-        <v>1343</v>
+        <v>1306</v>
       </c>
       <c r="J489" t="s">
         <v>576</v>
@@ -27338,7 +27328,7 @@
         <v>75</v>
       </c>
       <c r="L489">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M489">
         <v>0</v>
@@ -27349,10 +27339,10 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B490" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C490" t="s">
         <v>1295</v>
@@ -27364,10 +27354,10 @@
         <v>1304</v>
       </c>
       <c r="G490" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="H490" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="J490" t="s">
         <v>576</v>
@@ -27376,10 +27366,10 @@
         <v>75</v>
       </c>
       <c r="L490">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M490">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P490" s="8">
         <v>46155</v>
@@ -27387,7 +27377,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B491" t="s">
         <v>56</v>
@@ -27402,7 +27392,7 @@
         <v>1304</v>
       </c>
       <c r="G491" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="H491" t="s">
         <v>1324</v>
@@ -27414,10 +27404,10 @@
         <v>75</v>
       </c>
       <c r="L491">
+        <v>47.3</v>
+      </c>
+      <c r="M491">
         <v>41</v>
-      </c>
-      <c r="M491">
-        <v>31</v>
       </c>
       <c r="P491" s="8">
         <v>46155</v>
@@ -27425,7 +27415,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B492" t="s">
         <v>56</v>
@@ -27440,10 +27430,10 @@
         <v>1304</v>
       </c>
       <c r="G492" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="H492" t="s">
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="J492" t="s">
         <v>576</v>
@@ -27452,10 +27442,10 @@
         <v>75</v>
       </c>
       <c r="L492">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M492">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P492" s="8">
         <v>46155</v>
@@ -27463,7 +27453,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B493" t="s">
         <v>56</v>
@@ -27478,10 +27468,10 @@
         <v>1304</v>
       </c>
       <c r="G493" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="H493" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="J493" t="s">
         <v>576</v>
@@ -27501,7 +27491,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B494" t="s">
         <v>56</v>
@@ -27516,22 +27506,22 @@
         <v>1304</v>
       </c>
       <c r="G494" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="H494" t="s">
-        <v>1355</v>
+        <v>1306</v>
       </c>
       <c r="J494" t="s">
-        <v>576</v>
+        <v>161</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="M494">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P494" s="8">
         <v>46155</v>
@@ -27539,7 +27529,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B495" t="s">
         <v>56</v>
@@ -27554,22 +27544,22 @@
         <v>1304</v>
       </c>
       <c r="G495" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="H495" t="s">
-        <v>1306</v>
-      </c>
-      <c r="J495" t="s">
-        <v>161</v>
+        <v>1338</v>
+      </c>
+      <c r="J495">
+        <v>2017</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="M495">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P495" s="8">
         <v>46155</v>
@@ -27577,7 +27567,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B496" t="s">
         <v>56</v>
@@ -27585,6 +27575,9 @@
       <c r="C496" t="s">
         <v>1295</v>
       </c>
+      <c r="D496" t="s">
+        <v>1003</v>
+      </c>
       <c r="E496" t="s">
         <v>1295</v>
       </c>
@@ -27592,22 +27585,22 @@
         <v>1304</v>
       </c>
       <c r="G496" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="H496" t="s">
-        <v>1338</v>
-      </c>
-      <c r="J496">
-        <v>2017</v>
+        <v>1324</v>
+      </c>
+      <c r="J496" t="s">
+        <v>576</v>
       </c>
       <c r="K496">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L496">
-        <v>199</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M496">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P496" s="8">
         <v>46155</v>
@@ -27615,7 +27608,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B497" t="s">
         <v>56</v>
@@ -27633,7 +27626,7 @@
         <v>1304</v>
       </c>
       <c r="G497" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="H497" t="s">
         <v>1324</v>
@@ -27645,10 +27638,10 @@
         <v>150</v>
       </c>
       <c r="L497">
-        <v>65.900000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="M497">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="P497" s="8">
         <v>46155</v>
@@ -27656,10 +27649,10 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B498" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C498" t="s">
         <v>1295</v>
@@ -27674,10 +27667,10 @@
         <v>1304</v>
       </c>
       <c r="G498" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="H498" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="J498" t="s">
         <v>576</v>
@@ -27686,10 +27679,10 @@
         <v>150</v>
       </c>
       <c r="L498">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="M498">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P498" s="8">
         <v>46155</v>
@@ -27697,7 +27690,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B499" t="s">
         <v>117</v>
@@ -27715,7 +27708,7 @@
         <v>1304</v>
       </c>
       <c r="G499" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="H499" t="s">
         <v>1306</v>
@@ -27724,10 +27717,10 @@
         <v>576</v>
       </c>
       <c r="K499">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L499">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M499">
         <v>5</v>
@@ -27738,7 +27731,7 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B500" t="s">
         <v>117</v>
@@ -27756,7 +27749,7 @@
         <v>1304</v>
       </c>
       <c r="G500" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="H500" t="s">
         <v>1306</v>
@@ -27765,10 +27758,10 @@
         <v>576</v>
       </c>
       <c r="K500">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L500">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="M500">
         <v>5</v>
@@ -27779,40 +27772,37 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B501" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C501" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D501" t="s">
-        <v>1003</v>
+        <v>1371</v>
       </c>
       <c r="E501" t="s">
-        <v>1295</v>
+        <v>1371</v>
       </c>
       <c r="F501" t="s">
-        <v>1304</v>
+        <v>1372</v>
       </c>
       <c r="G501" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="H501" t="s">
-        <v>1306</v>
+        <v>1374</v>
       </c>
       <c r="J501" t="s">
-        <v>576</v>
+        <v>1375</v>
       </c>
       <c r="K501">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="L501">
-        <v>359</v>
+        <v>13.8</v>
       </c>
       <c r="M501">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P501" s="8">
         <v>46155</v>
@@ -27820,7 +27810,7 @@
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="B502" t="s">
         <v>56</v>
@@ -27835,7 +27825,7 @@
         <v>1372</v>
       </c>
       <c r="G502" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="H502" t="s">
         <v>1374</v>
@@ -27847,7 +27837,7 @@
         <v>70</v>
       </c>
       <c r="L502">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M502">
         <v>6</v>
@@ -27858,7 +27848,7 @@
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B503" t="s">
         <v>56</v>
@@ -27873,22 +27863,19 @@
         <v>1372</v>
       </c>
       <c r="G503" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="H503" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="J503" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="K503">
         <v>70</v>
       </c>
       <c r="L503">
-        <v>14.3</v>
-      </c>
-      <c r="M503">
-        <v>6</v>
+        <v>14.85</v>
       </c>
       <c r="P503" s="8">
         <v>46155</v>
@@ -27896,7 +27883,7 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B504" t="s">
         <v>56</v>
@@ -27911,19 +27898,19 @@
         <v>1372</v>
       </c>
       <c r="G504" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="H504" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="J504" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="K504">
         <v>70</v>
       </c>
       <c r="L504">
-        <v>14.85</v>
+        <v>38.1</v>
       </c>
       <c r="P504" s="8">
         <v>46155</v>
@@ -27931,7 +27918,7 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="B505" t="s">
         <v>56</v>
@@ -27946,19 +27933,19 @@
         <v>1372</v>
       </c>
       <c r="G505" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="H505" t="s">
         <v>1384</v>
       </c>
       <c r="J505" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="K505">
         <v>70</v>
       </c>
       <c r="L505">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="P505" s="8">
         <v>46155</v>
@@ -27966,7 +27953,7 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="B506" t="s">
         <v>56</v>
@@ -27981,19 +27968,19 @@
         <v>1372</v>
       </c>
       <c r="G506" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="H506" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="J506" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="K506">
         <v>70</v>
       </c>
       <c r="L506">
-        <v>35.5</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P506" s="8">
         <v>46155</v>
@@ -28001,7 +27988,7 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="B507" t="s">
         <v>56</v>
@@ -28009,6 +27996,9 @@
       <c r="C507" t="s">
         <v>1371</v>
       </c>
+      <c r="D507" t="s">
+        <v>1003</v>
+      </c>
       <c r="E507" t="s">
         <v>1371</v>
       </c>
@@ -28016,19 +28006,19 @@
         <v>1372</v>
       </c>
       <c r="G507" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="H507" t="s">
         <v>1391</v>
       </c>
       <c r="J507" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="K507">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L507">
-        <v>16.149999999999999</v>
+        <v>112</v>
       </c>
       <c r="P507" s="8">
         <v>46155</v>
@@ -28036,7 +28026,7 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B508" t="s">
         <v>56</v>
@@ -28044,29 +28034,26 @@
       <c r="C508" t="s">
         <v>1371</v>
       </c>
-      <c r="D508" t="s">
-        <v>1003</v>
-      </c>
       <c r="E508" t="s">
         <v>1371</v>
       </c>
       <c r="F508" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G508" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="H508" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
       <c r="J508" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="K508">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L508">
-        <v>112</v>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M508">
+        <v>45</v>
       </c>
       <c r="P508" s="8">
         <v>46155</v>
@@ -28074,10 +28061,10 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="B509" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C509" t="s">
         <v>1371</v>
@@ -28088,17 +28075,17 @@
       <c r="F509" t="s">
         <v>1397</v>
       </c>
+      <c r="G509" t="s">
+        <v>1401</v>
+      </c>
       <c r="H509" t="s">
-        <v>1398</v>
-      </c>
-      <c r="J509" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="K509">
         <v>70</v>
       </c>
       <c r="L509">
-        <v>16.850000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M509">
         <v>45</v>
@@ -28109,10 +28096,10 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="B510" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C510" t="s">
         <v>1371</v>
@@ -28124,19 +28111,22 @@
         <v>1397</v>
       </c>
       <c r="G510" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="H510" t="s">
-        <v>1402</v>
+        <v>1001</v>
+      </c>
+      <c r="J510" t="s">
+        <v>1405</v>
       </c>
       <c r="K510">
         <v>70</v>
       </c>
       <c r="L510">
-        <v>17.95</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M510">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P510" s="8">
         <v>46155</v>
@@ -28144,7 +28134,7 @@
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="B511" t="s">
         <v>56</v>
@@ -28159,22 +28149,22 @@
         <v>1397</v>
       </c>
       <c r="G511" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="H511" t="s">
-        <v>1001</v>
+        <v>1408</v>
       </c>
       <c r="J511" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="K511">
         <v>70</v>
       </c>
       <c r="L511">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="M511">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="P511" s="8">
         <v>46155</v>
@@ -28182,7 +28172,7 @@
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="B512" t="s">
         <v>56</v>
@@ -28194,25 +28184,25 @@
         <v>1371</v>
       </c>
       <c r="F512" t="s">
-        <v>1397</v>
+        <v>1411</v>
       </c>
       <c r="G512" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="H512" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="J512" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="K512">
         <v>70</v>
       </c>
       <c r="L512">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="M512">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="P512" s="8">
         <v>46155</v>
@@ -28220,7 +28210,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="B513" t="s">
         <v>56</v>
@@ -28235,7 +28225,7 @@
         <v>1411</v>
       </c>
       <c r="G513" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="H513" t="s">
         <v>1413</v>
@@ -28247,55 +28237,17 @@
         <v>70</v>
       </c>
       <c r="L513">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="M513">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P513" s="8">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A514" t="s">
-        <v>1415</v>
-      </c>
-      <c r="B514" t="s">
-        <v>56</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E514" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F514" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G514" t="s">
-        <v>1416</v>
-      </c>
-      <c r="H514" t="s">
-        <v>1413</v>
-      </c>
-      <c r="J514" t="s">
-        <v>1414</v>
-      </c>
-      <c r="K514">
-        <v>70</v>
-      </c>
-      <c r="L514">
-        <v>40.5</v>
-      </c>
-      <c r="M514">
-        <v>5</v>
-      </c>
-      <c r="P514" s="8">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R514" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R513" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28626,361 +28578,351 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="22" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28993,6 +28935,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49806,6 +49758,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50086,29 +50060,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50126,30 +50104,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CAB2FD-EC72-9C48-8429-BD28D79CB2A4}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96FE0C6-5366-104F-AEBA-9418E82F2D59}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7151,10 +7151,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11520,7 +11520,7 @@
         <v>337</v>
       </c>
       <c r="J97" t="s">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="K97">
         <v>75</v>
@@ -28578,351 +28578,361 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28935,16 +28945,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49758,28 +49758,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50060,33 +50038,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50104,4 +50078,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C96FE0C6-5366-104F-AEBA-9418E82F2D59}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2448D5F-6265-3740-A83F-785F403FDB9B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10074" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10073" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -16584,8 +16584,8 @@
       <c r="H222" t="s">
         <v>562</v>
       </c>
-      <c r="J222" t="s">
-        <v>82</v>
+      <c r="J222">
+        <v>2024</v>
       </c>
       <c r="K222">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2448D5F-6265-3740-A83F-785F403FDB9B}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE419403-EEFB-1544-852E-F860EDC8DAA1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10073" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10072" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7151,10 +7151,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19072,8 +19072,8 @@
       <c r="H284" t="s">
         <v>769</v>
       </c>
-      <c r="J284" t="s">
-        <v>93</v>
+      <c r="J284">
+        <v>2025</v>
       </c>
       <c r="K284">
         <v>75</v>
@@ -28578,361 +28578,351 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="22" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28945,6 +28935,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49758,6 +49758,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50038,15 +50047,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -50061,6 +50061,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50080,28 +50088,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE419403-EEFB-1544-852E-F860EDC8DAA1}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15C14501-C30D-3843-8511-527452E06E3A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10072" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10071" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7151,10 +7151,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18552,8 +18552,8 @@
       <c r="I270" t="s">
         <v>784</v>
       </c>
-      <c r="J270" t="s">
-        <v>82</v>
+      <c r="J270">
+        <v>2023</v>
       </c>
       <c r="K270">
         <v>75</v>
@@ -28578,351 +28578,361 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28935,16 +28945,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49758,15 +49758,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50047,6 +50038,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -50061,14 +50061,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50088,20 +50080,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
     <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15C14501-C30D-3843-8511-527452E06E3A}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCF4022-9EC1-1F42-B167-40B550BDAF09}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10071" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="2282">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -18306,8 +18306,8 @@
       <c r="I264" t="s">
         <v>62</v>
       </c>
-      <c r="J264" t="s">
-        <v>82</v>
+      <c r="J264">
+        <v>2023</v>
       </c>
       <c r="K264">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCF4022-9EC1-1F42-B167-40B550BDAF09}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602474B9-4313-8145-B23C-FBB9C9EC206A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="2283">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6891,6 +6891,9 @@
   </si>
   <si>
     <t>8805</t>
+  </si>
+  <si>
+    <t>Domaine de la Perruche</t>
   </si>
 </sst>
 </file>
@@ -7151,10 +7154,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20085,7 +20088,7 @@
         <v>880</v>
       </c>
       <c r="H310" t="s">
-        <v>881</v>
+        <v>2282</v>
       </c>
       <c r="J310" t="s">
         <v>82</v>
@@ -28578,361 +28581,351 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="22" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28945,6 +28938,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -50039,15 +50042,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
@@ -50058,6 +50052,15 @@
     <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50081,27 +50084,27 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602474B9-4313-8145-B23C-FBB9C9EC206A}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E637EB-D434-6247-80A4-C0677860579B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10069" uniqueCount="2283">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7154,10 +7154,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20090,8 +20090,8 @@
       <c r="H310" t="s">
         <v>2282</v>
       </c>
-      <c r="J310" t="s">
-        <v>82</v>
+      <c r="J310">
+        <v>2023</v>
       </c>
       <c r="K310">
         <v>75</v>
@@ -28581,351 +28581,361 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28938,16 +28948,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49761,6 +49761,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50041,29 +50063,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50081,30 +50107,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0106AA1-F4BF-5A48-8D3A-4FAD2447DEC6}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B42D5233-3045-AD40-8671-85E52E9F44CE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10061" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10060" uniqueCount="2283">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -17835,8 +17835,8 @@
       <c r="H252" t="s">
         <v>633</v>
       </c>
-      <c r="J252" t="s">
-        <v>63</v>
+      <c r="J252">
+        <v>2024</v>
       </c>
       <c r="K252">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B42D5233-3045-AD40-8671-85E52E9F44CE}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3944630B-74D2-6F48-9BFE-A685858BDDEB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10060" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10058" uniqueCount="2283">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7154,10 +7154,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20704,8 +20704,8 @@
       <c r="H326" t="s">
         <v>919</v>
       </c>
-      <c r="J326" t="s">
-        <v>316</v>
+      <c r="J326">
+        <v>2024</v>
       </c>
       <c r="K326">
         <v>75</v>
@@ -20827,8 +20827,8 @@
       <c r="H329" t="s">
         <v>919</v>
       </c>
-      <c r="J329" t="s">
-        <v>926</v>
+      <c r="J329">
+        <v>2021</v>
       </c>
       <c r="K329">
         <v>75</v>
@@ -28546,351 +28546,361 @@
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1437</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1438</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1439</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1440</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1441</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1442</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1443</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1444</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1445</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1446</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1447</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1449</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1450</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1451</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1452</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1453</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1454</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -28903,16 +28913,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49726,6 +49726,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -50006,29 +50028,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50046,30 +50072,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3944630B-74D2-6F48-9BFE-A685858BDDEB}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CE42DD-CC4E-6647-A1C1-F9BDD35F65A5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$513</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10058" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10068" uniqueCount="2283">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7658,7 +7658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R512"/>
+  <dimension ref="A1:R513"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -20959,7 +20959,7 @@
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B333" t="s">
         <v>56</v>
@@ -20967,26 +20967,35 @@
       <c r="C333" t="s">
         <v>910</v>
       </c>
+      <c r="D333" t="s">
+        <v>911</v>
+      </c>
       <c r="E333" t="s">
         <v>928</v>
       </c>
       <c r="F333" t="s">
-        <v>934</v>
+        <v>912</v>
+      </c>
+      <c r="G333" t="s">
+        <v>913</v>
       </c>
       <c r="H333" t="s">
-        <v>935</v>
+        <v>914</v>
+      </c>
+      <c r="I333" t="s">
+        <v>915</v>
       </c>
       <c r="J333" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K333">
         <v>75</v>
       </c>
       <c r="L333">
-        <v>6.1</v>
+        <v>5.05</v>
       </c>
       <c r="M333">
-        <v>324</v>
+        <v>10955</v>
       </c>
       <c r="P333" s="8">
         <v>46155</v>
@@ -20994,7 +21003,7 @@
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B334" t="s">
         <v>56</v>
@@ -21006,13 +21015,10 @@
         <v>928</v>
       </c>
       <c r="F334" t="s">
-        <v>937</v>
-      </c>
-      <c r="G334" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="H334" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="J334" t="s">
         <v>93</v>
@@ -21021,10 +21027,10 @@
         <v>75</v>
       </c>
       <c r="L334">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="M334">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="P334" s="8">
         <v>46155</v>
@@ -21032,7 +21038,7 @@
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B335" t="s">
         <v>56</v>
@@ -21044,25 +21050,25 @@
         <v>928</v>
       </c>
       <c r="F335" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="G335" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="H335" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="J335" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K335">
         <v>75</v>
       </c>
       <c r="L335">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M335">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="P335" s="8">
         <v>46155</v>
@@ -21070,7 +21076,7 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B336" t="s">
         <v>56</v>
@@ -21078,35 +21084,29 @@
       <c r="C336" t="s">
         <v>910</v>
       </c>
-      <c r="D336" t="s">
-        <v>917</v>
-      </c>
       <c r="E336" t="s">
         <v>928</v>
       </c>
       <c r="F336" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="G336" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="H336" t="s">
-        <v>946</v>
-      </c>
-      <c r="I336" t="s">
-        <v>62</v>
+        <v>942</v>
       </c>
       <c r="J336" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K336">
         <v>75</v>
       </c>
       <c r="L336">
-        <v>6.45</v>
+        <v>6.6</v>
       </c>
       <c r="M336">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="P336" s="8">
         <v>46155</v>
@@ -21114,7 +21114,7 @@
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B337" t="s">
         <v>56</v>
@@ -21132,7 +21132,7 @@
         <v>944</v>
       </c>
       <c r="G337" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="H337" t="s">
         <v>946</v>
@@ -21147,10 +21147,10 @@
         <v>75</v>
       </c>
       <c r="L337">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M337">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P337" s="8">
         <v>46155</v>
@@ -21158,7 +21158,7 @@
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B338" t="s">
         <v>56</v>
@@ -21173,13 +21173,16 @@
         <v>928</v>
       </c>
       <c r="F338" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="G338" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="H338" t="s">
-        <v>285</v>
+        <v>946</v>
+      </c>
+      <c r="I338" t="s">
+        <v>62</v>
       </c>
       <c r="J338" t="s">
         <v>93</v>
@@ -21188,10 +21191,10 @@
         <v>75</v>
       </c>
       <c r="L338">
-        <v>5.65</v>
+        <v>6.55</v>
       </c>
       <c r="M338">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P338" s="8">
         <v>46155</v>
@@ -21199,7 +21202,7 @@
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B339" t="s">
         <v>56</v>
@@ -21216,11 +21219,11 @@
       <c r="F339" t="s">
         <v>950</v>
       </c>
+      <c r="G339" t="s">
+        <v>951</v>
+      </c>
       <c r="H339" t="s">
-        <v>953</v>
-      </c>
-      <c r="I339" t="s">
-        <v>62</v>
+        <v>285</v>
       </c>
       <c r="J339" t="s">
         <v>93</v>
@@ -21229,10 +21232,10 @@
         <v>75</v>
       </c>
       <c r="L339">
-        <v>6.6</v>
+        <v>5.65</v>
       </c>
       <c r="M339">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P339" s="8">
         <v>46155</v>
@@ -21240,10 +21243,10 @@
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B340" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C340" t="s">
         <v>910</v>
@@ -21257,26 +21260,23 @@
       <c r="F340" t="s">
         <v>950</v>
       </c>
-      <c r="G340" t="s">
-        <v>955</v>
-      </c>
       <c r="H340" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="I340" t="s">
         <v>62</v>
       </c>
       <c r="J340" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K340">
         <v>75</v>
       </c>
       <c r="L340">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M340">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P340" s="8">
         <v>46155</v>
@@ -21284,10 +21284,10 @@
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B341" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C341" t="s">
         <v>910</v>
@@ -21302,22 +21302,25 @@
         <v>950</v>
       </c>
       <c r="G341" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H341" t="s">
-        <v>924</v>
+        <v>956</v>
+      </c>
+      <c r="I341" t="s">
+        <v>62</v>
       </c>
       <c r="J341" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K341">
         <v>75</v>
       </c>
       <c r="L341">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M341">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P341" s="8">
         <v>46155</v>
@@ -21325,7 +21328,7 @@
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B342" t="s">
         <v>56</v>
@@ -21343,10 +21346,10 @@
         <v>950</v>
       </c>
       <c r="G342" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H342" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="J342" t="s">
         <v>93</v>
@@ -21358,7 +21361,7 @@
         <v>9.1</v>
       </c>
       <c r="M342">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P342" s="8">
         <v>46155</v>
@@ -21366,10 +21369,10 @@
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B343" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C343" t="s">
         <v>910</v>
@@ -21384,25 +21387,22 @@
         <v>950</v>
       </c>
       <c r="G343" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H343" t="s">
-        <v>956</v>
-      </c>
-      <c r="I343" t="s">
-        <v>62</v>
+        <v>939</v>
       </c>
       <c r="J343" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K343">
         <v>75</v>
       </c>
       <c r="L343">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M343">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P343" s="8">
         <v>46155</v>
@@ -21410,10 +21410,10 @@
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B344" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C344" t="s">
         <v>910</v>
@@ -21428,25 +21428,25 @@
         <v>950</v>
       </c>
       <c r="G344" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H344" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="I344" t="s">
         <v>62</v>
       </c>
       <c r="J344" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K344">
         <v>75</v>
       </c>
       <c r="L344">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M344">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P344" s="8">
         <v>46155</v>
@@ -21454,7 +21454,7 @@
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B345" t="s">
         <v>56</v>
@@ -21471,8 +21471,14 @@
       <c r="F345" t="s">
         <v>950</v>
       </c>
+      <c r="G345" t="s">
+        <v>964</v>
+      </c>
       <c r="H345" t="s">
-        <v>967</v>
+        <v>965</v>
+      </c>
+      <c r="I345" t="s">
+        <v>62</v>
       </c>
       <c r="J345" t="s">
         <v>93</v>
@@ -21484,7 +21490,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M345">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P345" s="8">
         <v>46155</v>
@@ -21492,7 +21498,7 @@
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B346" t="s">
         <v>56</v>
@@ -21507,25 +21513,22 @@
         <v>928</v>
       </c>
       <c r="F346" t="s">
-        <v>922</v>
-      </c>
-      <c r="G346" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="H346" t="s">
-        <v>924</v>
+        <v>967</v>
       </c>
       <c r="J346" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K346">
         <v>75</v>
       </c>
       <c r="L346">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M346">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P346" s="8">
         <v>46155</v>
@@ -21533,7 +21536,7 @@
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B347" t="s">
         <v>56</v>
@@ -21548,25 +21551,25 @@
         <v>928</v>
       </c>
       <c r="F347" t="s">
-        <v>950</v>
+        <v>922</v>
+      </c>
+      <c r="G347" t="s">
+        <v>923</v>
       </c>
       <c r="H347" t="s">
-        <v>965</v>
-      </c>
-      <c r="I347" t="s">
-        <v>62</v>
-      </c>
-      <c r="J347">
-        <v>2025</v>
+        <v>924</v>
+      </c>
+      <c r="J347" t="s">
+        <v>334</v>
       </c>
       <c r="K347">
         <v>75</v>
       </c>
       <c r="L347">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M347">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P347" s="8">
         <v>46155</v>
@@ -21574,40 +21577,40 @@
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B348" t="s">
         <v>56</v>
       </c>
       <c r="C348" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D348" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E348" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F348" t="s">
-        <v>975</v>
-      </c>
-      <c r="G348" t="s">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="H348" t="s">
-        <v>977</v>
-      </c>
-      <c r="J348" t="s">
-        <v>334</v>
+        <v>965</v>
+      </c>
+      <c r="I348" t="s">
+        <v>62</v>
+      </c>
+      <c r="J348">
+        <v>2025</v>
       </c>
       <c r="K348">
         <v>75</v>
       </c>
       <c r="L348">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M348">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P348" s="8">
         <v>46155</v>
@@ -21615,7 +21618,7 @@
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B349" t="s">
         <v>56</v>
@@ -21633,22 +21636,22 @@
         <v>975</v>
       </c>
       <c r="G349" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H349" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J349" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K349">
         <v>75</v>
       </c>
       <c r="L349">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M349">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P349" s="8">
         <v>46155</v>
@@ -21656,7 +21659,7 @@
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B350" t="s">
         <v>56</v>
@@ -21671,25 +21674,25 @@
         <v>58</v>
       </c>
       <c r="F350" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G350" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="H350" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J350" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K350">
         <v>75</v>
       </c>
       <c r="L350">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M350">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P350" s="8">
         <v>46155</v>
@@ -21697,7 +21700,7 @@
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B351" t="s">
         <v>56</v>
@@ -21712,25 +21715,25 @@
         <v>58</v>
       </c>
       <c r="F351" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G351" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="H351" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J351" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K351">
         <v>75</v>
       </c>
       <c r="L351">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M351">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P351" s="8">
         <v>46155</v>
@@ -21738,7 +21741,7 @@
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B352" t="s">
         <v>56</v>
@@ -21756,10 +21759,10 @@
         <v>975</v>
       </c>
       <c r="G352" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="H352" t="s">
-        <v>285</v>
+        <v>987</v>
       </c>
       <c r="J352" t="s">
         <v>93</v>
@@ -21768,10 +21771,10 @@
         <v>75</v>
       </c>
       <c r="L352">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M352">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P352" s="8">
         <v>46155</v>
@@ -21779,7 +21782,7 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B353" t="s">
         <v>56</v>
@@ -21797,7 +21800,7 @@
         <v>975</v>
       </c>
       <c r="G353" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H353" t="s">
         <v>285</v>
@@ -21809,10 +21812,10 @@
         <v>75</v>
       </c>
       <c r="L353">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M353">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P353" s="8">
         <v>46155</v>
@@ -21820,7 +21823,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B354" t="s">
         <v>56</v>
@@ -21838,22 +21841,22 @@
         <v>975</v>
       </c>
       <c r="G354" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H354" t="s">
-        <v>987</v>
+        <v>285</v>
       </c>
       <c r="J354" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K354">
         <v>75</v>
       </c>
       <c r="L354">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M354">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P354" s="8">
         <v>46155</v>
@@ -21861,7 +21864,7 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B355" t="s">
         <v>56</v>
@@ -21876,13 +21879,13 @@
         <v>58</v>
       </c>
       <c r="F355" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G355" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="H355" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="J355" t="s">
         <v>334</v>
@@ -21891,10 +21894,10 @@
         <v>75</v>
       </c>
       <c r="L355">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M355">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P355" s="8">
         <v>46155</v>
@@ -21902,7 +21905,7 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B356" t="s">
         <v>56</v>
@@ -21917,16 +21920,16 @@
         <v>58</v>
       </c>
       <c r="F356" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G356" t="s">
-        <v>108</v>
+        <v>995</v>
       </c>
       <c r="H356" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="J356" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K356">
         <v>75</v>
@@ -21935,18 +21938,15 @@
         <v>5.7</v>
       </c>
       <c r="M356">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P356" s="8">
         <v>46155</v>
-      </c>
-      <c r="R356" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B357" t="s">
         <v>56</v>
@@ -21964,39 +21964,42 @@
         <v>975</v>
       </c>
       <c r="G357" t="s">
-        <v>1000</v>
+        <v>108</v>
       </c>
       <c r="H357" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J357" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K357">
         <v>75</v>
       </c>
       <c r="L357">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M357">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P357" s="8">
         <v>46155</v>
+      </c>
+      <c r="R357" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B358" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C358" t="s">
         <v>973</v>
       </c>
       <c r="D358" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E358" t="s">
         <v>58</v>
@@ -22005,7 +22008,7 @@
         <v>975</v>
       </c>
       <c r="G358" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="H358" t="s">
         <v>1001</v>
@@ -22014,13 +22017,13 @@
         <v>334</v>
       </c>
       <c r="K358">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L358">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M358">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P358" s="8">
         <v>46155</v>
@@ -22028,16 +22031,16 @@
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B359" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C359" t="s">
         <v>973</v>
       </c>
       <c r="D359" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="E359" t="s">
         <v>58</v>
@@ -22046,25 +22049,22 @@
         <v>975</v>
       </c>
       <c r="G359" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H359" t="s">
-        <v>987</v>
-      </c>
-      <c r="I359" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="J359" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K359">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L359">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M359">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P359" s="8">
         <v>46155</v>
@@ -22072,7 +22072,7 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B360" t="s">
         <v>56</v>
@@ -22081,31 +22081,34 @@
         <v>973</v>
       </c>
       <c r="D360" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E360" t="s">
         <v>58</v>
       </c>
       <c r="F360" t="s">
-        <v>1010</v>
+        <v>975</v>
       </c>
       <c r="G360" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="H360" t="s">
-        <v>1012</v>
+        <v>987</v>
+      </c>
+      <c r="I360" t="s">
+        <v>1007</v>
       </c>
       <c r="J360" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K360">
         <v>75</v>
       </c>
       <c r="L360">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M360">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P360" s="8">
         <v>46155</v>
@@ -22113,7 +22116,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B361" t="s">
         <v>56</v>
@@ -22122,34 +22125,31 @@
         <v>973</v>
       </c>
       <c r="D361" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E361" t="s">
         <v>58</v>
       </c>
       <c r="F361" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G361" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="H361" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I361" t="s">
-        <v>784</v>
+        <v>1012</v>
       </c>
       <c r="J361" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K361">
         <v>75</v>
       </c>
       <c r="L361">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M361">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P361" s="8">
         <v>46155</v>
@@ -22157,7 +22157,7 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B362" t="s">
         <v>56</v>
@@ -22172,25 +22172,28 @@
         <v>58</v>
       </c>
       <c r="F362" t="s">
-        <v>975</v>
+        <v>1014</v>
       </c>
       <c r="G362" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H362" t="s">
-        <v>987</v>
+        <v>1016</v>
+      </c>
+      <c r="I362" t="s">
+        <v>784</v>
       </c>
       <c r="J362" t="s">
-        <v>334</v>
+        <v>63</v>
       </c>
       <c r="K362">
         <v>75</v>
       </c>
       <c r="L362">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M362">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P362" s="8">
         <v>46155</v>
@@ -22198,7 +22201,7 @@
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B363" t="s">
         <v>56</v>
@@ -22216,25 +22219,22 @@
         <v>975</v>
       </c>
       <c r="G363" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="H363" t="s">
         <v>987</v>
       </c>
-      <c r="I363" t="s">
-        <v>1007</v>
-      </c>
       <c r="J363" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K363">
         <v>75</v>
       </c>
       <c r="L363">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M363">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P363" s="8">
         <v>46155</v>
@@ -22242,7 +22242,7 @@
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B364" t="s">
         <v>56</v>
@@ -22260,22 +22260,25 @@
         <v>975</v>
       </c>
       <c r="G364" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="H364" t="s">
-        <v>605</v>
+        <v>987</v>
+      </c>
+      <c r="I364" t="s">
+        <v>1007</v>
       </c>
       <c r="J364" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K364">
         <v>75</v>
       </c>
       <c r="L364">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M364">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P364" s="8">
         <v>46155</v>
@@ -22283,7 +22286,7 @@
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B365" t="s">
         <v>56</v>
@@ -22298,22 +22301,25 @@
         <v>58</v>
       </c>
       <c r="F365" t="s">
-        <v>1024</v>
+        <v>975</v>
       </c>
       <c r="G365" t="s">
-        <v>159</v>
+        <v>1022</v>
       </c>
       <c r="H365" t="s">
-        <v>1025</v>
+        <v>605</v>
       </c>
       <c r="J365" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K365">
         <v>75</v>
       </c>
       <c r="L365">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M365">
+        <v>321</v>
       </c>
       <c r="P365" s="8">
         <v>46155</v>
@@ -22321,7 +22327,7 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B366" t="s">
         <v>56</v>
@@ -22336,13 +22342,13 @@
         <v>58</v>
       </c>
       <c r="F366" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="G366" t="s">
-        <v>1028</v>
+        <v>159</v>
       </c>
       <c r="H366" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="J366" t="s">
         <v>93</v>
@@ -22351,10 +22357,7 @@
         <v>75</v>
       </c>
       <c r="L366">
-        <v>3.95</v>
-      </c>
-      <c r="M366">
-        <v>351</v>
+        <v>37</v>
       </c>
       <c r="P366" s="8">
         <v>46155</v>
@@ -22362,7 +22365,7 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B367" t="s">
         <v>56</v>
@@ -22380,10 +22383,10 @@
         <v>1027</v>
       </c>
       <c r="G367" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="H367" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="J367" t="s">
         <v>93</v>
@@ -22392,10 +22395,10 @@
         <v>75</v>
       </c>
       <c r="L367">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M367">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P367" s="8">
         <v>46155</v>
@@ -22403,10 +22406,10 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B368" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C368" t="s">
         <v>973</v>
@@ -22418,33 +22421,33 @@
         <v>58</v>
       </c>
       <c r="F368" t="s">
-        <v>59</v>
+        <v>1027</v>
       </c>
       <c r="G368" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="H368" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="J368" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K368">
         <v>75</v>
       </c>
       <c r="L368">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M368">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P368" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A369">
-        <v>24003025</v>
+      <c r="A369" t="s">
+        <v>1033</v>
       </c>
       <c r="B369" t="s">
         <v>117</v>
@@ -22453,7 +22456,7 @@
         <v>973</v>
       </c>
       <c r="D369" t="s">
-        <v>1036</v>
+        <v>974</v>
       </c>
       <c r="E369" t="s">
         <v>58</v>
@@ -22462,16 +22465,13 @@
         <v>59</v>
       </c>
       <c r="G369" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="H369" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I369" t="s">
-        <v>62</v>
-      </c>
-      <c r="J369">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J369" t="s">
+        <v>334</v>
       </c>
       <c r="K369">
         <v>75</v>
@@ -22479,13 +22479,16 @@
       <c r="L369">
         <v>6.2</v>
       </c>
+      <c r="M369">
+        <v>0</v>
+      </c>
       <c r="P369" s="8">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A370" t="s">
-        <v>1039</v>
+      <c r="A370">
+        <v>24003025</v>
       </c>
       <c r="B370" t="s">
         <v>117</v>
@@ -22494,39 +22497,39 @@
         <v>973</v>
       </c>
       <c r="D370" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="E370" t="s">
         <v>58</v>
       </c>
       <c r="F370" t="s">
-        <v>1040</v>
+        <v>59</v>
       </c>
       <c r="G370" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="H370" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J370" t="s">
-        <v>82</v>
+        <v>1038</v>
+      </c>
+      <c r="I370" t="s">
+        <v>62</v>
+      </c>
+      <c r="J370">
+        <v>2025</v>
       </c>
       <c r="K370">
         <v>75</v>
       </c>
       <c r="L370">
-        <v>7.55</v>
-      </c>
-      <c r="M370">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P370" s="8">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B371" t="s">
         <v>117</v>
@@ -22535,28 +22538,28 @@
         <v>973</v>
       </c>
       <c r="D371" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E371" t="s">
         <v>58</v>
       </c>
       <c r="F371" t="s">
-        <v>59</v>
+        <v>1040</v>
       </c>
       <c r="G371" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H371" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="J371" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="K371">
         <v>75</v>
       </c>
       <c r="L371">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M371">
         <v>0</v>
@@ -22567,7 +22570,7 @@
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B372" t="s">
         <v>117</v>
@@ -22576,28 +22579,28 @@
         <v>973</v>
       </c>
       <c r="D372" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E372" t="s">
         <v>58</v>
       </c>
       <c r="F372" t="s">
-        <v>1046</v>
+        <v>59</v>
       </c>
       <c r="G372" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="H372" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="J372" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K372">
         <v>75</v>
       </c>
       <c r="L372">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M372">
         <v>0</v>
@@ -22608,7 +22611,7 @@
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B373" t="s">
         <v>117</v>
@@ -22617,34 +22620,31 @@
         <v>973</v>
       </c>
       <c r="D373" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E373" t="s">
         <v>58</v>
       </c>
       <c r="F373" t="s">
-        <v>59</v>
+        <v>1046</v>
       </c>
       <c r="G373" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H373" t="s">
-        <v>1050</v>
-      </c>
-      <c r="I373" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="J373" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K373">
         <v>75</v>
       </c>
       <c r="L373">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M373">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P373" s="8">
         <v>46155</v>
@@ -22652,7 +22652,7 @@
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="B374" t="s">
         <v>117</v>
@@ -22661,20 +22661,23 @@
         <v>973</v>
       </c>
       <c r="D374" t="s">
-        <v>1053</v>
+        <v>974</v>
       </c>
       <c r="E374" t="s">
         <v>58</v>
       </c>
       <c r="F374" t="s">
-        <v>1054</v>
+        <v>59</v>
       </c>
       <c r="G374" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="H374" t="s">
         <v>1050</v>
       </c>
+      <c r="I374" t="s">
+        <v>1051</v>
+      </c>
       <c r="J374" t="s">
         <v>93</v>
       </c>
@@ -22682,10 +22685,10 @@
         <v>75</v>
       </c>
       <c r="L374">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M374">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P374" s="8">
         <v>46155</v>
@@ -22693,7 +22696,7 @@
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B375" t="s">
         <v>117</v>
@@ -22702,28 +22705,28 @@
         <v>973</v>
       </c>
       <c r="D375" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E375" t="s">
         <v>58</v>
       </c>
       <c r="F375" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="G375" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H375" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="J375" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="K375">
         <v>75</v>
       </c>
       <c r="L375">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M375">
         <v>0</v>
@@ -22734,7 +22737,7 @@
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B376" t="s">
         <v>117</v>
@@ -22743,28 +22746,28 @@
         <v>973</v>
       </c>
       <c r="D376" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E376" t="s">
         <v>58</v>
       </c>
       <c r="F376" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="G376" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="H376" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="J376" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="K376">
         <v>75</v>
       </c>
       <c r="L376">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M376">
         <v>0</v>
@@ -22775,7 +22778,7 @@
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B377" t="s">
         <v>117</v>
@@ -22790,22 +22793,22 @@
         <v>58</v>
       </c>
       <c r="F377" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="G377" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="H377" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="J377" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="K377">
         <v>75</v>
       </c>
       <c r="L377">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M377">
         <v>0</v>
@@ -22816,7 +22819,7 @@
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B378" t="s">
         <v>117</v>
@@ -22834,10 +22837,10 @@
         <v>1062</v>
       </c>
       <c r="G378" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="H378" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="J378" t="s">
         <v>334</v>
@@ -22846,7 +22849,7 @@
         <v>75</v>
       </c>
       <c r="L378">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -22857,7 +22860,7 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B379" t="s">
         <v>117</v>
@@ -22875,19 +22878,19 @@
         <v>1062</v>
       </c>
       <c r="G379" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="H379" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="J379" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K379">
         <v>75</v>
       </c>
       <c r="L379">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="M379">
         <v>0</v>
@@ -22898,10 +22901,10 @@
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B380" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C380" t="s">
         <v>973</v>
@@ -22916,10 +22919,10 @@
         <v>1062</v>
       </c>
       <c r="G380" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H380" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="J380" t="s">
         <v>93</v>
@@ -22928,10 +22931,10 @@
         <v>75</v>
       </c>
       <c r="L380">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M380">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P380" s="8">
         <v>46155</v>
@@ -22939,7 +22942,7 @@
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B381" t="s">
         <v>56</v>
@@ -22948,19 +22951,19 @@
         <v>973</v>
       </c>
       <c r="D381" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E381" t="s">
         <v>58</v>
       </c>
       <c r="F381" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="G381" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="H381" t="s">
-        <v>1012</v>
+        <v>1072</v>
       </c>
       <c r="J381" t="s">
         <v>93</v>
@@ -22969,10 +22972,10 @@
         <v>75</v>
       </c>
       <c r="L381">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M381">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P381" s="8">
         <v>46155</v>
@@ -22980,7 +22983,7 @@
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B382" t="s">
         <v>56</v>
@@ -22998,10 +23001,10 @@
         <v>1027</v>
       </c>
       <c r="G382" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H382" t="s">
-        <v>1032</v>
+        <v>1012</v>
       </c>
       <c r="J382" t="s">
         <v>93</v>
@@ -23010,10 +23013,10 @@
         <v>75</v>
       </c>
       <c r="L382">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M382">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P382" s="8">
         <v>46155</v>
@@ -23021,7 +23024,7 @@
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B383" t="s">
         <v>56</v>
@@ -23036,13 +23039,13 @@
         <v>58</v>
       </c>
       <c r="F383" t="s">
-        <v>1078</v>
+        <v>1027</v>
       </c>
       <c r="G383" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H383" t="s">
-        <v>1080</v>
+        <v>1032</v>
       </c>
       <c r="J383" t="s">
         <v>93</v>
@@ -23051,7 +23054,10 @@
         <v>75</v>
       </c>
       <c r="L383">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M383">
+        <v>264</v>
       </c>
       <c r="P383" s="8">
         <v>46155</v>
@@ -23059,7 +23065,7 @@
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B384" t="s">
         <v>56</v>
@@ -23074,104 +23080,101 @@
         <v>58</v>
       </c>
       <c r="F384" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="G384" t="s">
         <v>1079</v>
       </c>
       <c r="H384" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="J384" t="s">
-        <v>521</v>
+        <v>93</v>
       </c>
       <c r="K384">
         <v>75</v>
       </c>
       <c r="L384">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P384" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A385">
-        <v>53800623</v>
+      <c r="A385" t="s">
+        <v>1081</v>
       </c>
       <c r="B385" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C385" t="s">
         <v>973</v>
       </c>
       <c r="D385" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E385" t="s">
         <v>58</v>
       </c>
       <c r="F385" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G385" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="H385" t="s">
-        <v>1060</v>
+        <v>1083</v>
       </c>
       <c r="J385" t="s">
-        <v>63</v>
+        <v>521</v>
       </c>
       <c r="K385">
         <v>75</v>
       </c>
       <c r="L385">
-        <v>11</v>
-      </c>
-      <c r="M385">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P385" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A386" t="s">
-        <v>1086</v>
+      <c r="A386">
+        <v>53800623</v>
       </c>
       <c r="B386" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C386" t="s">
         <v>973</v>
       </c>
       <c r="D386" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
       </c>
       <c r="F386" t="s">
-        <v>975</v>
+        <v>1084</v>
       </c>
       <c r="G386" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H386" t="s">
-        <v>977</v>
+        <v>1060</v>
       </c>
       <c r="J386" t="s">
-        <v>576</v>
+        <v>63</v>
       </c>
       <c r="K386">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L386">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M386">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P386" s="8">
         <v>46155</v>
@@ -23179,7 +23182,7 @@
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B387" t="s">
         <v>56</v>
@@ -23197,22 +23200,22 @@
         <v>975</v>
       </c>
       <c r="G387" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="H387" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J387" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K387">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L387">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M387">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P387" s="8">
         <v>46155</v>
@@ -23220,7 +23223,7 @@
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B388" t="s">
         <v>56</v>
@@ -23229,31 +23232,31 @@
         <v>973</v>
       </c>
       <c r="D388" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E388" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F388" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G388" t="s">
-        <v>983</v>
+        <v>1089</v>
       </c>
       <c r="H388" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J388" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K388">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L388">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M388">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P388" s="8">
         <v>46155</v>
@@ -23261,7 +23264,7 @@
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B389" t="s">
         <v>56</v>
@@ -23270,31 +23273,31 @@
         <v>973</v>
       </c>
       <c r="D389" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E389" t="s">
         <v>79</v>
       </c>
       <c r="F389" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G389" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="H389" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="J389" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K389">
         <v>75</v>
       </c>
       <c r="L389">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="M389">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P389" s="8">
         <v>46155</v>
@@ -23302,7 +23305,7 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B390" t="s">
         <v>56</v>
@@ -23320,22 +23323,22 @@
         <v>975</v>
       </c>
       <c r="G390" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H390" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J390" t="s">
-        <v>316</v>
+        <v>93</v>
       </c>
       <c r="K390">
         <v>75</v>
       </c>
       <c r="L390">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M390">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P390" s="8">
         <v>46155</v>
@@ -23343,7 +23346,7 @@
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B391" t="s">
         <v>56</v>
@@ -23361,22 +23364,22 @@
         <v>975</v>
       </c>
       <c r="G391" t="s">
-        <v>1094</v>
+        <v>979</v>
       </c>
       <c r="H391" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J391" t="s">
-        <v>93</v>
+        <v>316</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M391">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P391" s="8">
         <v>46155</v>
@@ -23384,7 +23387,7 @@
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
@@ -23402,10 +23405,10 @@
         <v>975</v>
       </c>
       <c r="G392" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="H392" t="s">
-        <v>980</v>
+        <v>285</v>
       </c>
       <c r="J392" t="s">
         <v>93</v>
@@ -23414,10 +23417,10 @@
         <v>75</v>
       </c>
       <c r="L392">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M392">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P392" s="8">
         <v>46155</v>
@@ -23425,7 +23428,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
@@ -23440,25 +23443,25 @@
         <v>79</v>
       </c>
       <c r="F393" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G393" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="H393" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="J393" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K393">
         <v>75</v>
       </c>
       <c r="L393">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M393">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P393" s="8">
         <v>46155</v>
@@ -23466,7 +23469,7 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
@@ -23481,25 +23484,25 @@
         <v>79</v>
       </c>
       <c r="F394" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G394" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="H394" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="J394" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M394">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P394" s="8">
         <v>46155</v>
@@ -23507,7 +23510,7 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
@@ -23525,22 +23528,22 @@
         <v>975</v>
       </c>
       <c r="G395" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="H395" t="s">
-        <v>1103</v>
+        <v>987</v>
       </c>
       <c r="J395" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M395">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P395" s="8">
         <v>46155</v>
@@ -23548,7 +23551,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
@@ -23566,25 +23569,22 @@
         <v>975</v>
       </c>
       <c r="G396" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="H396" t="s">
-        <v>977</v>
-      </c>
-      <c r="I396" t="s">
-        <v>289</v>
+        <v>1103</v>
       </c>
       <c r="J396" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M396">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P396" s="8">
         <v>46155</v>
@@ -23592,7 +23592,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
@@ -23610,13 +23610,13 @@
         <v>975</v>
       </c>
       <c r="G397" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H397" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="I397" t="s">
-        <v>1007</v>
+        <v>289</v>
       </c>
       <c r="J397" t="s">
         <v>63</v>
@@ -23625,10 +23625,10 @@
         <v>75</v>
       </c>
       <c r="L397">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M397">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P397" s="8">
         <v>46155</v>
@@ -23636,7 +23636,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
@@ -23651,13 +23651,16 @@
         <v>79</v>
       </c>
       <c r="F398" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G398" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H398" t="s">
-        <v>1012</v>
+        <v>987</v>
+      </c>
+      <c r="I398" t="s">
+        <v>1007</v>
       </c>
       <c r="J398" t="s">
         <v>63</v>
@@ -23666,10 +23669,10 @@
         <v>75</v>
       </c>
       <c r="L398">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M398">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P398" s="8">
         <v>46155</v>
@@ -23677,7 +23680,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
@@ -23686,19 +23689,19 @@
         <v>973</v>
       </c>
       <c r="D399" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E399" t="s">
         <v>79</v>
       </c>
       <c r="F399" t="s">
-        <v>1111</v>
+        <v>59</v>
       </c>
       <c r="G399" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="H399" t="s">
-        <v>1080</v>
+        <v>1012</v>
       </c>
       <c r="J399" t="s">
         <v>63</v>
@@ -23707,10 +23710,10 @@
         <v>75</v>
       </c>
       <c r="L399">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M399">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P399" s="8">
         <v>46155</v>
@@ -23718,7 +23721,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
@@ -23733,25 +23736,25 @@
         <v>79</v>
       </c>
       <c r="F400" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="G400" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="H400" t="s">
-        <v>1116</v>
+        <v>1080</v>
       </c>
       <c r="J400" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M400">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P400" s="8">
         <v>46155</v>
@@ -23759,7 +23762,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
@@ -23777,22 +23780,22 @@
         <v>1114</v>
       </c>
       <c r="G401" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="H401" t="s">
         <v>1116</v>
       </c>
       <c r="J401" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M401">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P401" s="8">
         <v>46155</v>
@@ -23800,37 +23803,40 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B402" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C402" t="s">
         <v>973</v>
       </c>
       <c r="D402" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E402" t="s">
         <v>79</v>
       </c>
       <c r="F402" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="G402" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="H402" t="s">
-        <v>1067</v>
+        <v>1116</v>
       </c>
       <c r="J402" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M402">
+        <v>36</v>
       </c>
       <c r="P402" s="8">
         <v>46155</v>
@@ -23838,7 +23844,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B403" t="s">
         <v>117</v>
@@ -23853,25 +23859,22 @@
         <v>79</v>
       </c>
       <c r="F403" t="s">
-        <v>1054</v>
+        <v>1120</v>
       </c>
       <c r="G403" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H403" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="J403" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>12.5</v>
-      </c>
-      <c r="M403">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P403" s="8">
         <v>46155</v>
@@ -23879,7 +23882,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B404" t="s">
         <v>117</v>
@@ -23894,22 +23897,22 @@
         <v>79</v>
       </c>
       <c r="F404" t="s">
-        <v>1125</v>
+        <v>1054</v>
       </c>
       <c r="G404" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="H404" t="s">
         <v>1060</v>
       </c>
       <c r="J404" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M404">
         <v>0</v>
@@ -23920,7 +23923,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B405" t="s">
         <v>117</v>
@@ -23938,19 +23941,19 @@
         <v>1125</v>
       </c>
       <c r="G405" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="H405" t="s">
-        <v>1129</v>
+        <v>1060</v>
       </c>
       <c r="J405" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M405">
         <v>0</v>
@@ -23961,10 +23964,10 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B406" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C406" t="s">
         <v>973</v>
@@ -23976,25 +23979,25 @@
         <v>79</v>
       </c>
       <c r="F406" t="s">
-        <v>1062</v>
+        <v>1125</v>
       </c>
       <c r="G406" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="H406" t="s">
-        <v>1072</v>
+        <v>1129</v>
       </c>
       <c r="J406" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M406">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P406" s="8">
         <v>46155</v>
@@ -24002,10 +24005,10 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B407" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C407" t="s">
         <v>973</v>
@@ -24020,13 +24023,10 @@
         <v>1062</v>
       </c>
       <c r="G407" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H407" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I407" t="s">
-        <v>62</v>
+        <v>1072</v>
       </c>
       <c r="J407" t="s">
         <v>63</v>
@@ -24035,10 +24035,10 @@
         <v>75</v>
       </c>
       <c r="L407">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M407">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P407" s="8">
         <v>46155</v>
@@ -24046,7 +24046,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B408" t="s">
         <v>117</v>
@@ -24064,10 +24064,13 @@
         <v>1062</v>
       </c>
       <c r="G408" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H408" t="s">
-        <v>1050</v>
+        <v>1060</v>
+      </c>
+      <c r="I408" t="s">
+        <v>62</v>
       </c>
       <c r="J408" t="s">
         <v>63</v>
@@ -24076,7 +24079,7 @@
         <v>75</v>
       </c>
       <c r="L408">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M408">
         <v>0</v>
@@ -24087,7 +24090,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B409" t="s">
         <v>117</v>
@@ -24105,22 +24108,19 @@
         <v>1062</v>
       </c>
       <c r="G409" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="H409" t="s">
         <v>1050</v>
       </c>
-      <c r="I409" t="s">
-        <v>1051</v>
-      </c>
       <c r="J409" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K409">
         <v>75</v>
       </c>
       <c r="L409">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24131,31 +24131,31 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B410" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C410" t="s">
         <v>973</v>
       </c>
       <c r="D410" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E410" t="s">
         <v>79</v>
       </c>
       <c r="F410" t="s">
-        <v>1139</v>
+        <v>1062</v>
       </c>
       <c r="G410" t="s">
-        <v>824</v>
+        <v>1137</v>
       </c>
       <c r="H410" t="s">
-        <v>1016</v>
+        <v>1050</v>
       </c>
       <c r="I410" t="s">
-        <v>784</v>
+        <v>1051</v>
       </c>
       <c r="J410" t="s">
         <v>93</v>
@@ -24164,10 +24164,10 @@
         <v>75</v>
       </c>
       <c r="L410">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M410">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P410" s="8">
         <v>46155</v>
@@ -24175,7 +24175,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B411" t="s">
         <v>56</v>
@@ -24190,28 +24190,28 @@
         <v>79</v>
       </c>
       <c r="F411" t="s">
-        <v>975</v>
+        <v>1139</v>
       </c>
       <c r="G411" t="s">
-        <v>1141</v>
+        <v>824</v>
       </c>
       <c r="H411" t="s">
-        <v>1142</v>
+        <v>1016</v>
       </c>
       <c r="I411" t="s">
-        <v>62</v>
+        <v>784</v>
       </c>
       <c r="J411" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K411">
         <v>75</v>
       </c>
       <c r="L411">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M411">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P411" s="8">
         <v>46155</v>
@@ -24219,10 +24219,10 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B412" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C412" t="s">
         <v>973</v>
@@ -24234,25 +24234,28 @@
         <v>79</v>
       </c>
       <c r="F412" t="s">
-        <v>1144</v>
+        <v>975</v>
       </c>
       <c r="G412" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="H412" t="s">
-        <v>1146</v>
+        <v>1142</v>
+      </c>
+      <c r="I412" t="s">
+        <v>62</v>
       </c>
       <c r="J412" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M412">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P412" s="8">
         <v>46155</v>
@@ -24260,7 +24263,7 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="B413" t="s">
         <v>117</v>
@@ -24278,19 +24281,22 @@
         <v>1144</v>
       </c>
       <c r="G413" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H413" t="s">
         <v>1146</v>
       </c>
       <c r="J413" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M413">
+        <v>0</v>
       </c>
       <c r="P413" s="8">
         <v>46155</v>
@@ -24298,10 +24304,10 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B414" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C414" t="s">
         <v>973</v>
@@ -24313,28 +24319,22 @@
         <v>79</v>
       </c>
       <c r="F414" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G414" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H414" t="s">
-        <v>1152</v>
-      </c>
-      <c r="I414" t="s">
-        <v>62</v>
+        <v>1146</v>
       </c>
       <c r="J414" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>7.6</v>
-      </c>
-      <c r="M414">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P414" s="8">
         <v>46155</v>
@@ -24342,10 +24342,10 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="B415" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C415" t="s">
         <v>973</v>
@@ -24357,25 +24357,28 @@
         <v>79</v>
       </c>
       <c r="F415" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="G415" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="H415" t="s">
-        <v>1044</v>
+        <v>1152</v>
+      </c>
+      <c r="I415" t="s">
+        <v>62</v>
       </c>
       <c r="J415" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M415">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P415" s="8">
         <v>46155</v>
@@ -24383,7 +24386,7 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B416" t="s">
         <v>117</v>
@@ -24401,22 +24404,22 @@
         <v>1154</v>
       </c>
       <c r="G416" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="H416" t="s">
         <v>1044</v>
       </c>
       <c r="J416" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M416">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P416" s="8">
         <v>46155</v>
@@ -24424,10 +24427,10 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B417" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C417" t="s">
         <v>973</v>
@@ -24442,22 +24445,22 @@
         <v>1154</v>
       </c>
       <c r="G417" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="H417" t="s">
-        <v>1160</v>
+        <v>1044</v>
       </c>
       <c r="J417" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>15.9</v>
+        <v>8.25</v>
       </c>
       <c r="M417">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="P417" s="8">
         <v>46155</v>
@@ -24465,7 +24468,7 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B418" t="s">
         <v>56</v>
@@ -24480,16 +24483,13 @@
         <v>79</v>
       </c>
       <c r="F418" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="G418" t="s">
-        <v>159</v>
+        <v>1159</v>
       </c>
       <c r="H418" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I418" t="s">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="J418" t="s">
         <v>82</v>
@@ -24498,7 +24498,10 @@
         <v>75</v>
       </c>
       <c r="L418">
-        <v>17.8</v>
+        <v>15.9</v>
+      </c>
+      <c r="M418">
+        <v>49</v>
       </c>
       <c r="P418" s="8">
         <v>46155</v>
@@ -24506,7 +24509,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="B419" t="s">
         <v>56</v>
@@ -24521,25 +24524,25 @@
         <v>79</v>
       </c>
       <c r="F419" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="G419" t="s">
-        <v>1165</v>
+        <v>159</v>
       </c>
       <c r="H419" t="s">
-        <v>1160</v>
+        <v>1163</v>
+      </c>
+      <c r="I419" t="s">
+        <v>784</v>
       </c>
       <c r="J419" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M419">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P419" s="8">
         <v>46155</v>
@@ -24547,7 +24550,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B420" t="s">
         <v>56</v>
@@ -24562,25 +24565,25 @@
         <v>79</v>
       </c>
       <c r="F420" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="G420" t="s">
-        <v>159</v>
+        <v>1165</v>
       </c>
       <c r="H420" t="s">
-        <v>1168</v>
-      </c>
-      <c r="I420" t="s">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="J420" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M420">
+        <v>53</v>
       </c>
       <c r="P420" s="8">
         <v>46155</v>
@@ -24588,7 +24591,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B421" t="s">
         <v>56</v>
@@ -24603,28 +24606,25 @@
         <v>79</v>
       </c>
       <c r="F421" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G421" t="s">
-        <v>1171</v>
+        <v>159</v>
       </c>
       <c r="H421" t="s">
-        <v>1001</v>
+        <v>1168</v>
       </c>
       <c r="I421" t="s">
-        <v>169</v>
+        <v>784</v>
       </c>
       <c r="J421" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>6.5</v>
-      </c>
-      <c r="M421">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P421" s="8">
         <v>46155</v>
@@ -24632,10 +24632,10 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B422" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C422" t="s">
         <v>973</v>
@@ -24650,10 +24650,13 @@
         <v>1170</v>
       </c>
       <c r="G422" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="H422" t="s">
-        <v>1174</v>
+        <v>1001</v>
+      </c>
+      <c r="I422" t="s">
+        <v>169</v>
       </c>
       <c r="J422" t="s">
         <v>93</v>
@@ -24662,18 +24665,18 @@
         <v>75</v>
       </c>
       <c r="L422">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M422">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P422" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A423">
-        <v>16003124</v>
+      <c r="A423" t="s">
+        <v>1172</v>
       </c>
       <c r="B423" t="s">
         <v>117</v>
@@ -24685,13 +24688,13 @@
         <v>974</v>
       </c>
       <c r="E423" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F423" t="s">
         <v>1170</v>
       </c>
       <c r="G423" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="H423" t="s">
         <v>1174</v>
@@ -24713,11 +24716,11 @@
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
-        <v>1176</v>
+      <c r="A424">
+        <v>16003124</v>
       </c>
       <c r="B424" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C424" t="s">
         <v>973</v>
@@ -24726,31 +24729,28 @@
         <v>974</v>
       </c>
       <c r="E424" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F424" t="s">
         <v>1170</v>
       </c>
       <c r="G424" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="H424" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I424" t="s">
-        <v>169</v>
+        <v>1174</v>
       </c>
       <c r="J424" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K424">
         <v>75</v>
       </c>
       <c r="L424">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M424">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P424" s="8">
         <v>46155</v>
@@ -24758,10 +24758,10 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B425" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C425" t="s">
         <v>973</v>
@@ -24776,13 +24776,13 @@
         <v>1170</v>
       </c>
       <c r="G425" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="H425" t="s">
-        <v>1174</v>
+        <v>1001</v>
       </c>
       <c r="I425" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="J425" t="s">
         <v>63</v>
@@ -24791,10 +24791,10 @@
         <v>75</v>
       </c>
       <c r="L425">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M425">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P425" s="8">
         <v>46155</v>
@@ -24802,10 +24802,10 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B426" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C426" t="s">
         <v>973</v>
@@ -24820,13 +24820,13 @@
         <v>1170</v>
       </c>
       <c r="G426" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="H426" t="s">
-        <v>1001</v>
+        <v>1174</v>
       </c>
       <c r="I426" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J426" t="s">
         <v>63</v>
@@ -24835,7 +24835,7 @@
         <v>75</v>
       </c>
       <c r="L426">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M426">
         <v>171</v>
@@ -24846,10 +24846,10 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B427" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C427" t="s">
         <v>973</v>
@@ -24864,19 +24864,25 @@
         <v>1170</v>
       </c>
       <c r="G427" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="H427" t="s">
-        <v>1184</v>
+        <v>1001</v>
+      </c>
+      <c r="I427" t="s">
+        <v>169</v>
       </c>
       <c r="J427" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K427">
         <v>75</v>
       </c>
       <c r="L427">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M427">
+        <v>171</v>
       </c>
       <c r="P427" s="8">
         <v>46155</v>
@@ -24884,10 +24890,10 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B428" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C428" t="s">
         <v>973</v>
@@ -24899,28 +24905,22 @@
         <v>79</v>
       </c>
       <c r="F428" t="s">
-        <v>59</v>
+        <v>1170</v>
       </c>
       <c r="G428" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="H428" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I428" t="s">
-        <v>169</v>
+        <v>1184</v>
       </c>
       <c r="J428" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>24.08</v>
-      </c>
-      <c r="M428">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P428" s="8">
         <v>46155</v>
@@ -24928,10 +24928,10 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B429" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C429" t="s">
         <v>973</v>
@@ -24943,19 +24943,28 @@
         <v>79</v>
       </c>
       <c r="F429" t="s">
-        <v>1188</v>
+        <v>59</v>
+      </c>
+      <c r="G429" t="s">
+        <v>1186</v>
       </c>
       <c r="H429" t="s">
-        <v>1189</v>
+        <v>1001</v>
+      </c>
+      <c r="I429" t="s">
+        <v>169</v>
       </c>
       <c r="J429" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M429">
+        <v>12</v>
       </c>
       <c r="P429" s="8">
         <v>46155</v>
@@ -24963,10 +24972,10 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="B430" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C430" t="s">
         <v>973</v>
@@ -24978,10 +24987,10 @@
         <v>79</v>
       </c>
       <c r="F430" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="H430" t="s">
-        <v>977</v>
+        <v>1189</v>
       </c>
       <c r="J430" t="s">
         <v>63</v>
@@ -24990,18 +24999,15 @@
         <v>75</v>
       </c>
       <c r="L430">
-        <v>7.05</v>
-      </c>
-      <c r="M430">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P430" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A431">
-        <v>27100522</v>
+      <c r="A431" t="s">
+        <v>1190</v>
       </c>
       <c r="B431" t="s">
         <v>56</v>
@@ -25016,36 +25022,33 @@
         <v>79</v>
       </c>
       <c r="F431" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G431" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="H431" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I431" t="s">
-        <v>784</v>
-      </c>
-      <c r="J431">
-        <v>2022</v>
+        <v>977</v>
+      </c>
+      <c r="J431" t="s">
+        <v>63</v>
       </c>
       <c r="K431">
         <v>75</v>
       </c>
       <c r="L431">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M431">
+        <v>30</v>
       </c>
       <c r="P431" s="8">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>1195</v>
+      <c r="A432">
+        <v>27100522</v>
       </c>
       <c r="B432" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C432" t="s">
         <v>973</v>
@@ -25057,33 +25060,36 @@
         <v>79</v>
       </c>
       <c r="F432" t="s">
-        <v>59</v>
+        <v>1192</v>
       </c>
       <c r="G432" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="H432" t="s">
-        <v>1197</v>
-      </c>
-      <c r="J432" t="s">
-        <v>1198</v>
+        <v>1194</v>
+      </c>
+      <c r="I432" t="s">
+        <v>784</v>
+      </c>
+      <c r="J432">
+        <v>2022</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P432" s="8">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="433" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="B433" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C433" t="s">
         <v>973</v>
@@ -25095,33 +25101,33 @@
         <v>79</v>
       </c>
       <c r="F433" t="s">
-        <v>1200</v>
+        <v>59</v>
       </c>
       <c r="G433" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="H433" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="J433" t="s">
-        <v>93</v>
+        <v>1198</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>7.35</v>
-      </c>
-      <c r="M433">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P433" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="434" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>1199</v>
+      </c>
       <c r="B434" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C434" t="s">
         <v>973</v>
@@ -25136,19 +25142,19 @@
         <v>1200</v>
       </c>
       <c r="G434" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H434" t="s">
         <v>1202</v>
       </c>
       <c r="J434" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K434">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L434">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M434">
         <v>2215</v>
@@ -25158,11 +25164,8 @@
       </c>
     </row>
     <row r="435" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>1204</v>
-      </c>
       <c r="B435" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C435" t="s">
         <v>973</v>
@@ -25177,22 +25180,22 @@
         <v>1200</v>
       </c>
       <c r="G435" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H435" t="s">
         <v>1202</v>
       </c>
       <c r="J435" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K435">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L435">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M435">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P435" s="8">
         <v>46155</v>
@@ -25200,7 +25203,7 @@
     </row>
     <row r="436" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B436" t="s">
         <v>56</v>
@@ -25218,25 +25221,22 @@
         <v>1200</v>
       </c>
       <c r="G436" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H436" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I436" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="J436" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K436">
         <v>75</v>
       </c>
       <c r="L436">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M436">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P436" s="8">
         <v>46155</v>
@@ -25244,10 +25244,10 @@
     </row>
     <row r="437" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B437" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C437" t="s">
         <v>973</v>
@@ -25262,19 +25262,25 @@
         <v>1200</v>
       </c>
       <c r="G437" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="H437" t="s">
-        <v>1212</v>
+        <v>1208</v>
+      </c>
+      <c r="I437" t="s">
+        <v>1209</v>
       </c>
       <c r="J437" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M437">
+        <v>205</v>
       </c>
       <c r="P437" s="8">
         <v>46155</v>
@@ -25282,7 +25288,7 @@
     </row>
     <row r="438" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B438" t="s">
         <v>117</v>
@@ -25300,10 +25306,10 @@
         <v>1200</v>
       </c>
       <c r="G438" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="H438" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="J438" t="s">
         <v>93</v>
@@ -25312,10 +25318,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>14.6</v>
-      </c>
-      <c r="M438">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P438" s="8">
         <v>46155</v>
@@ -25323,10 +25326,10 @@
     </row>
     <row r="439" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B439" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C439" t="s">
         <v>973</v>
@@ -25338,22 +25341,25 @@
         <v>79</v>
       </c>
       <c r="F439" t="s">
-        <v>1024</v>
+        <v>1200</v>
       </c>
       <c r="G439" t="s">
-        <v>159</v>
+        <v>1214</v>
       </c>
       <c r="H439" t="s">
-        <v>1025</v>
+        <v>1215</v>
       </c>
       <c r="J439" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K439">
         <v>75</v>
       </c>
       <c r="L439">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M439">
+        <v>0</v>
       </c>
       <c r="P439" s="8">
         <v>46155</v>
@@ -25361,7 +25367,7 @@
     </row>
     <row r="440" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B440" t="s">
         <v>56</v>
@@ -25373,28 +25379,25 @@
         <v>974</v>
       </c>
       <c r="E440" t="s">
-        <v>928</v>
+        <v>79</v>
       </c>
       <c r="F440" t="s">
-        <v>975</v>
+        <v>1024</v>
       </c>
       <c r="G440" t="s">
-        <v>976</v>
+        <v>159</v>
       </c>
       <c r="H440" t="s">
-        <v>977</v>
+        <v>1025</v>
       </c>
       <c r="J440" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>3.8</v>
-      </c>
-      <c r="M440">
-        <v>324</v>
+        <v>37</v>
       </c>
       <c r="P440" s="8">
         <v>46155</v>
@@ -25402,7 +25405,7 @@
     </row>
     <row r="441" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -25420,10 +25423,10 @@
         <v>975</v>
       </c>
       <c r="G441" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H441" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J441" t="s">
         <v>93</v>
@@ -25432,10 +25435,10 @@
         <v>75</v>
       </c>
       <c r="L441">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M441">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P441" s="8">
         <v>46155</v>
@@ -25443,7 +25446,7 @@
     </row>
     <row r="442" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B442" t="s">
         <v>56</v>
@@ -25461,10 +25464,10 @@
         <v>975</v>
       </c>
       <c r="G442" t="s">
-        <v>1220</v>
+        <v>979</v>
       </c>
       <c r="H442" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J442" t="s">
         <v>93</v>
@@ -25473,10 +25476,10 @@
         <v>75</v>
       </c>
       <c r="L442">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M442">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P442" s="8">
         <v>46155</v>
@@ -25484,10 +25487,10 @@
     </row>
     <row r="443" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B443" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C443" t="s">
         <v>973</v>
@@ -25502,22 +25505,22 @@
         <v>975</v>
       </c>
       <c r="G443" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="H443" t="s">
-        <v>1194</v>
+        <v>285</v>
       </c>
       <c r="J443" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M443">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P443" s="8">
         <v>46155</v>
@@ -25525,10 +25528,10 @@
     </row>
     <row r="444" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B444" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C444" t="s">
         <v>973</v>
@@ -25543,22 +25546,22 @@
         <v>975</v>
       </c>
       <c r="G444" t="s">
-        <v>1087</v>
+        <v>1222</v>
       </c>
       <c r="H444" t="s">
-        <v>977</v>
+        <v>1194</v>
       </c>
       <c r="J444" t="s">
-        <v>576</v>
+        <v>334</v>
       </c>
       <c r="K444">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L444">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M444">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P444" s="8">
         <v>46155</v>
@@ -25566,7 +25569,7 @@
     </row>
     <row r="445" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B445" t="s">
         <v>56</v>
@@ -25584,22 +25587,22 @@
         <v>975</v>
       </c>
       <c r="G445" t="s">
-        <v>1225</v>
+        <v>1087</v>
       </c>
       <c r="H445" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J445" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K445">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L445">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M445">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P445" s="8">
         <v>46155</v>
@@ -25607,40 +25610,40 @@
     </row>
     <row r="446" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B446" t="s">
         <v>56</v>
       </c>
       <c r="C446" t="s">
-        <v>1227</v>
+        <v>973</v>
       </c>
       <c r="D446" t="s">
-        <v>1228</v>
+        <v>974</v>
       </c>
       <c r="E446" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F446" t="s">
-        <v>1229</v>
+        <v>975</v>
       </c>
       <c r="G446" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="H446" t="s">
-        <v>1231</v>
+        <v>980</v>
       </c>
       <c r="J446" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K446">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L446">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M446">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P446" s="8">
         <v>46155</v>
@@ -25648,7 +25651,7 @@
     </row>
     <row r="447" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="B447" t="s">
         <v>56</v>
@@ -25663,13 +25666,13 @@
         <v>58</v>
       </c>
       <c r="F447" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="G447" t="s">
-        <v>108</v>
+        <v>1230</v>
       </c>
       <c r="H447" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J447" t="s">
         <v>334</v>
@@ -25678,21 +25681,18 @@
         <v>75</v>
       </c>
       <c r="L447">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M447">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P447" s="8">
         <v>46155</v>
-      </c>
-      <c r="R447" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="448" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B448" t="s">
         <v>56</v>
@@ -25704,36 +25704,39 @@
         <v>1228</v>
       </c>
       <c r="E448" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F448" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="G448" t="s">
-        <v>1236</v>
+        <v>108</v>
       </c>
       <c r="H448" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="J448" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M448">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P448" s="8">
         <v>46155</v>
+      </c>
+      <c r="R448" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B449" t="s">
         <v>56</v>
@@ -25745,28 +25748,28 @@
         <v>1228</v>
       </c>
       <c r="E449" t="s">
-        <v>79</v>
+        <v>928</v>
       </c>
       <c r="F449" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="G449" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="H449" t="s">
-        <v>1240</v>
+        <v>1231</v>
       </c>
       <c r="J449" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M449">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P449" s="8">
         <v>46155</v>
@@ -25774,7 +25777,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="B450" t="s">
         <v>56</v>
@@ -25789,25 +25792,25 @@
         <v>79</v>
       </c>
       <c r="F450" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="G450" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="H450" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="J450" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M450">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P450" s="8">
         <v>46155</v>
@@ -25815,7 +25818,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B451" t="s">
         <v>56</v>
@@ -25830,25 +25833,25 @@
         <v>79</v>
       </c>
       <c r="F451" t="s">
-        <v>1233</v>
+        <v>1242</v>
       </c>
       <c r="G451" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="H451" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="J451" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M451">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P451" s="8">
         <v>46155</v>
@@ -25856,7 +25859,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B452" t="s">
         <v>56</v>
@@ -25871,22 +25874,25 @@
         <v>79</v>
       </c>
       <c r="F452" t="s">
-        <v>1248</v>
+        <v>1233</v>
+      </c>
+      <c r="G452" t="s">
+        <v>1246</v>
       </c>
       <c r="H452" t="s">
-        <v>1249</v>
+        <v>1231</v>
       </c>
       <c r="J452" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M452">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P452" s="8">
         <v>46155</v>
@@ -25894,7 +25900,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B453" t="s">
         <v>56</v>
@@ -25909,28 +25915,22 @@
         <v>79</v>
       </c>
       <c r="F453" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G453" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H453" t="s">
-        <v>1253</v>
-      </c>
-      <c r="I453" t="s">
-        <v>62</v>
+        <v>1249</v>
       </c>
       <c r="J453" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M453">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P453" s="8">
         <v>46155</v>
@@ -25938,7 +25938,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="B454" t="s">
         <v>56</v>
@@ -25947,19 +25947,22 @@
         <v>1227</v>
       </c>
       <c r="D454" t="s">
-        <v>1255</v>
+        <v>1228</v>
       </c>
       <c r="E454" t="s">
         <v>79</v>
       </c>
       <c r="F454" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="G454" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="H454" t="s">
-        <v>1258</v>
+        <v>1253</v>
+      </c>
+      <c r="I454" t="s">
+        <v>62</v>
       </c>
       <c r="J454" t="s">
         <v>63</v>
@@ -25968,7 +25971,10 @@
         <v>75</v>
       </c>
       <c r="L454">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M454">
+        <v>318</v>
       </c>
       <c r="P454" s="8">
         <v>46155</v>
@@ -25976,7 +25982,7 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="B455" t="s">
         <v>56</v>
@@ -25994,22 +26000,19 @@
         <v>1256</v>
       </c>
       <c r="G455" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="H455" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="J455" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K455">
         <v>75</v>
       </c>
       <c r="L455">
-        <v>6.1</v>
-      </c>
-      <c r="M455">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P455" s="8">
         <v>46155</v>
@@ -26017,10 +26020,10 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B456" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C456" t="s">
         <v>1227</v>
@@ -26035,22 +26038,22 @@
         <v>1256</v>
       </c>
       <c r="G456" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="H456" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J456" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>13.2</v>
+        <v>6.1</v>
       </c>
       <c r="M456">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="P456" s="8">
         <v>46155</v>
@@ -26058,7 +26061,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B457" t="s">
         <v>117</v>
@@ -26076,19 +26079,19 @@
         <v>1256</v>
       </c>
       <c r="G457" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="H457" t="s">
         <v>1264</v>
       </c>
       <c r="J457" t="s">
-        <v>1198</v>
+        <v>104</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M457">
         <v>0</v>
@@ -26099,7 +26102,7 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B458" t="s">
         <v>117</v>
@@ -26114,22 +26117,22 @@
         <v>79</v>
       </c>
       <c r="F458" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="G458" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="H458" t="s">
         <v>1264</v>
       </c>
       <c r="J458" t="s">
-        <v>63</v>
+        <v>1198</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -26140,40 +26143,40 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B459" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C459" t="s">
         <v>1227</v>
       </c>
       <c r="D459" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="E459" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F459" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G459" t="s">
-        <v>732</v>
+        <v>1269</v>
       </c>
       <c r="H459" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="J459" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M459">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P459" s="8">
         <v>46155</v>
@@ -26181,7 +26184,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B460" t="s">
         <v>56</v>
@@ -26190,31 +26193,31 @@
         <v>1227</v>
       </c>
       <c r="D460" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="E460" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F460" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G460" t="s">
-        <v>1276</v>
+        <v>732</v>
       </c>
       <c r="H460" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="J460" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M460">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P460" s="8">
         <v>46155</v>
@@ -26222,7 +26225,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="B461" t="s">
         <v>56</v>
@@ -26240,7 +26243,7 @@
         <v>1275</v>
       </c>
       <c r="G461" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H461" t="s">
         <v>1277</v>
@@ -26252,10 +26255,10 @@
         <v>75</v>
       </c>
       <c r="L461">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M461">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P461" s="8">
         <v>46155</v>
@@ -26263,7 +26266,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B462" t="s">
         <v>56</v>
@@ -26281,7 +26284,7 @@
         <v>1275</v>
       </c>
       <c r="G462" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H462" t="s">
         <v>1277</v>
@@ -26296,7 +26299,7 @@
         <v>8.6</v>
       </c>
       <c r="M462">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P462" s="8">
         <v>46155</v>
@@ -26304,7 +26307,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B463" t="s">
         <v>56</v>
@@ -26322,13 +26325,13 @@
         <v>1275</v>
       </c>
       <c r="G463" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="H463" t="s">
         <v>1277</v>
       </c>
       <c r="J463" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="K463">
         <v>75</v>
@@ -26337,7 +26340,7 @@
         <v>8.6</v>
       </c>
       <c r="M463">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P463" s="8">
         <v>46155</v>
@@ -26345,7 +26348,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B464" t="s">
         <v>56</v>
@@ -26363,7 +26366,7 @@
         <v>1275</v>
       </c>
       <c r="G464" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="H464" t="s">
         <v>1277</v>
@@ -26378,7 +26381,7 @@
         <v>8.6</v>
       </c>
       <c r="M464">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P464" s="8">
         <v>46155</v>
@@ -26386,7 +26389,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B465" t="s">
         <v>56</v>
@@ -26404,22 +26407,22 @@
         <v>1275</v>
       </c>
       <c r="G465" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="H465" t="s">
         <v>1277</v>
       </c>
       <c r="J465" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K465">
         <v>75</v>
       </c>
       <c r="L465">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M465">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P465" s="8">
         <v>46155</v>
@@ -26427,7 +26430,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B466" t="s">
         <v>56</v>
@@ -26445,22 +26448,22 @@
         <v>1275</v>
       </c>
       <c r="G466" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="H466" t="s">
         <v>1277</v>
       </c>
       <c r="J466" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M466">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P466" s="8">
         <v>46155</v>
@@ -26468,7 +26471,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B467" t="s">
         <v>56</v>
@@ -26486,7 +26489,7 @@
         <v>1275</v>
       </c>
       <c r="G467" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="H467" t="s">
         <v>1277</v>
@@ -26501,7 +26504,7 @@
         <v>13</v>
       </c>
       <c r="M467">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P467" s="8">
         <v>46155</v>
@@ -26509,7 +26512,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B468" t="s">
         <v>56</v>
@@ -26527,7 +26530,7 @@
         <v>1275</v>
       </c>
       <c r="G468" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="H468" t="s">
         <v>1277</v>
@@ -26539,7 +26542,7 @@
         <v>75</v>
       </c>
       <c r="L468">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M468">
         <v>36</v>
@@ -26550,7 +26553,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B469" t="s">
         <v>56</v>
@@ -26562,28 +26565,28 @@
         <v>1274</v>
       </c>
       <c r="E469" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F469" t="s">
         <v>1275</v>
       </c>
       <c r="G469" t="s">
-        <v>1037</v>
+        <v>1292</v>
       </c>
       <c r="H469" t="s">
         <v>1277</v>
       </c>
       <c r="J469" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M469">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P469" s="8">
         <v>46155</v>
@@ -26591,40 +26594,40 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B470" t="s">
         <v>56</v>
       </c>
       <c r="C470" t="s">
-        <v>1295</v>
+        <v>1227</v>
       </c>
       <c r="D470" t="s">
-        <v>1228</v>
+        <v>1274</v>
       </c>
       <c r="E470" t="s">
-        <v>1295</v>
+        <v>58</v>
       </c>
       <c r="F470" t="s">
-        <v>1296</v>
+        <v>1275</v>
       </c>
       <c r="G470" t="s">
-        <v>1297</v>
+        <v>1037</v>
       </c>
       <c r="H470" t="s">
-        <v>1231</v>
+        <v>1277</v>
       </c>
       <c r="J470" t="s">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M470">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P470" s="8">
         <v>46155</v>
@@ -26632,7 +26635,7 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B471" t="s">
         <v>56</v>
@@ -26640,17 +26643,20 @@
       <c r="C471" t="s">
         <v>1295</v>
       </c>
+      <c r="D471" t="s">
+        <v>1228</v>
+      </c>
       <c r="E471" t="s">
         <v>1295</v>
       </c>
       <c r="F471" t="s">
-        <v>59</v>
+        <v>1296</v>
       </c>
       <c r="G471" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="H471" t="s">
-        <v>996</v>
+        <v>1231</v>
       </c>
       <c r="J471" t="s">
         <v>576</v>
@@ -26661,13 +26667,16 @@
       <c r="L471">
         <v>6.2</v>
       </c>
+      <c r="M471">
+        <v>4411</v>
+      </c>
       <c r="P471" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B472" t="s">
         <v>56</v>
@@ -26682,10 +26691,10 @@
         <v>59</v>
       </c>
       <c r="G472" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="H472" t="s">
-        <v>1302</v>
+        <v>996</v>
       </c>
       <c r="J472" t="s">
         <v>576</v>
@@ -26694,7 +26703,7 @@
         <v>75</v>
       </c>
       <c r="L472">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P472" s="8">
         <v>46155</v>
@@ -26702,7 +26711,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B473" t="s">
         <v>56</v>
@@ -26714,25 +26723,22 @@
         <v>1295</v>
       </c>
       <c r="F473" t="s">
-        <v>1304</v>
+        <v>59</v>
       </c>
       <c r="G473" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="H473" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="J473" t="s">
         <v>576</v>
       </c>
       <c r="K473">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L473">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M473">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P473" s="8">
         <v>46155</v>
@@ -26740,7 +26746,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="B474" t="s">
         <v>56</v>
@@ -26755,22 +26761,22 @@
         <v>1304</v>
       </c>
       <c r="G474" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="H474" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="J474" t="s">
         <v>576</v>
       </c>
       <c r="K474">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L474">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M474">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P474" s="8">
         <v>46155</v>
@@ -26778,7 +26784,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B475" t="s">
         <v>56</v>
@@ -26793,10 +26799,10 @@
         <v>1304</v>
       </c>
       <c r="G475" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="H475" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="J475" t="s">
         <v>576</v>
@@ -26805,10 +26811,10 @@
         <v>75</v>
       </c>
       <c r="L475">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M475">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P475" s="8">
         <v>46155</v>
@@ -26816,10 +26822,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B476" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C476" t="s">
         <v>1295</v>
@@ -26831,10 +26837,10 @@
         <v>1304</v>
       </c>
       <c r="G476" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="H476" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="J476" t="s">
         <v>576</v>
@@ -26843,7 +26849,10 @@
         <v>75</v>
       </c>
       <c r="L476">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M476">
+        <v>418</v>
       </c>
       <c r="P476" s="8">
         <v>46155</v>
@@ -26851,10 +26860,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B477" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C477" t="s">
         <v>1295</v>
@@ -26866,10 +26875,10 @@
         <v>1304</v>
       </c>
       <c r="G477" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="H477" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="J477" t="s">
         <v>576</v>
@@ -26878,10 +26887,7 @@
         <v>75</v>
       </c>
       <c r="L477">
-        <v>25.7</v>
-      </c>
-      <c r="M477">
-        <v>34</v>
+        <v>23.9</v>
       </c>
       <c r="P477" s="8">
         <v>46155</v>
@@ -26889,7 +26895,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B478" t="s">
         <v>56</v>
@@ -26904,10 +26910,10 @@
         <v>1304</v>
       </c>
       <c r="G478" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="H478" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="J478" t="s">
         <v>576</v>
@@ -26916,10 +26922,10 @@
         <v>75</v>
       </c>
       <c r="L478">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="M478">
-        <v>995</v>
+        <v>34</v>
       </c>
       <c r="P478" s="8">
         <v>46155</v>
@@ -26927,7 +26933,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B479" t="s">
         <v>56</v>
@@ -26942,10 +26948,10 @@
         <v>1304</v>
       </c>
       <c r="G479" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="H479" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J479" t="s">
         <v>576</v>
@@ -26954,10 +26960,10 @@
         <v>75</v>
       </c>
       <c r="L479">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M479">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P479" s="8">
         <v>46155</v>
@@ -26965,7 +26971,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B480" t="s">
         <v>56</v>
@@ -26980,10 +26986,10 @@
         <v>1304</v>
       </c>
       <c r="G480" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="H480" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="J480" t="s">
         <v>576</v>
@@ -26992,10 +26998,10 @@
         <v>75</v>
       </c>
       <c r="L480">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M480">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P480" s="8">
         <v>46155</v>
@@ -27003,7 +27009,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B481" t="s">
         <v>56</v>
@@ -27018,10 +27024,10 @@
         <v>1304</v>
       </c>
       <c r="G481" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H481" t="s">
-        <v>1321</v>
+        <v>1306</v>
       </c>
       <c r="J481" t="s">
         <v>576</v>
@@ -27030,10 +27036,10 @@
         <v>75</v>
       </c>
       <c r="L481">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M481">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P481" s="8">
         <v>46155</v>
@@ -27041,7 +27047,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B482" t="s">
         <v>56</v>
@@ -27056,10 +27062,10 @@
         <v>1304</v>
       </c>
       <c r="G482" t="s">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="H482" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J482" t="s">
         <v>576</v>
@@ -27068,10 +27074,10 @@
         <v>75</v>
       </c>
       <c r="L482">
-        <v>29.8</v>
+        <v>29.35</v>
       </c>
       <c r="M482">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P482" s="8">
         <v>46155</v>
@@ -27079,7 +27085,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B483" t="s">
         <v>56</v>
@@ -27094,10 +27100,10 @@
         <v>1304</v>
       </c>
       <c r="G483" t="s">
-        <v>1331</v>
+        <v>923</v>
       </c>
       <c r="H483" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="J483" t="s">
         <v>576</v>
@@ -27106,10 +27112,10 @@
         <v>75</v>
       </c>
       <c r="L483">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="M483">
-        <v>777</v>
+        <v>417</v>
       </c>
       <c r="P483" s="8">
         <v>46155</v>
@@ -27117,7 +27123,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B484" t="s">
         <v>56</v>
@@ -27132,10 +27138,10 @@
         <v>1304</v>
       </c>
       <c r="G484" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="H484" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="J484" t="s">
         <v>576</v>
@@ -27144,10 +27150,10 @@
         <v>75</v>
       </c>
       <c r="L484">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M484">
-        <v>428</v>
+        <v>777</v>
       </c>
       <c r="P484" s="8">
         <v>46155</v>
@@ -27155,7 +27161,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="B485" t="s">
         <v>56</v>
@@ -27170,10 +27176,10 @@
         <v>1304</v>
       </c>
       <c r="G485" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="H485" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="J485" t="s">
         <v>576</v>
@@ -27182,10 +27188,10 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M485">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P485" s="8">
         <v>46155</v>
@@ -27193,7 +27199,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B486" t="s">
         <v>56</v>
@@ -27208,10 +27214,10 @@
         <v>1304</v>
       </c>
       <c r="G486" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H486" t="s">
-        <v>1321</v>
+        <v>1338</v>
       </c>
       <c r="J486" t="s">
         <v>576</v>
@@ -27220,10 +27226,10 @@
         <v>75</v>
       </c>
       <c r="L486">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M486">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P486" s="8">
         <v>46155</v>
@@ -27231,7 +27237,7 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B487" t="s">
         <v>56</v>
@@ -27246,10 +27252,10 @@
         <v>1304</v>
       </c>
       <c r="G487" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="H487" t="s">
-        <v>1343</v>
+        <v>1321</v>
       </c>
       <c r="J487" t="s">
         <v>576</v>
@@ -27258,10 +27264,10 @@
         <v>75</v>
       </c>
       <c r="L487">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M487">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P487" s="8">
         <v>46155</v>
@@ -27269,10 +27275,10 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B488" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C488" t="s">
         <v>1295</v>
@@ -27284,10 +27290,10 @@
         <v>1304</v>
       </c>
       <c r="G488" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="H488" t="s">
-        <v>1306</v>
+        <v>1343</v>
       </c>
       <c r="J488" t="s">
         <v>576</v>
@@ -27296,7 +27302,7 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -27307,10 +27313,10 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B489" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C489" t="s">
         <v>1295</v>
@@ -27322,10 +27328,10 @@
         <v>1304</v>
       </c>
       <c r="G489" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="H489" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="J489" t="s">
         <v>576</v>
@@ -27334,10 +27340,10 @@
         <v>75</v>
       </c>
       <c r="L489">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M489">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P489" s="8">
         <v>46155</v>
@@ -27345,7 +27351,7 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B490" t="s">
         <v>56</v>
@@ -27360,7 +27366,7 @@
         <v>1304</v>
       </c>
       <c r="G490" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="H490" t="s">
         <v>1324</v>
@@ -27372,10 +27378,10 @@
         <v>75</v>
       </c>
       <c r="L490">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M490">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P490" s="8">
         <v>46155</v>
@@ -27383,7 +27389,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B491" t="s">
         <v>56</v>
@@ -27398,10 +27404,10 @@
         <v>1304</v>
       </c>
       <c r="G491" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="H491" t="s">
-        <v>1352</v>
+        <v>1324</v>
       </c>
       <c r="J491" t="s">
         <v>576</v>
@@ -27410,10 +27416,10 @@
         <v>75</v>
       </c>
       <c r="L491">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M491">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P491" s="8">
         <v>46155</v>
@@ -27421,7 +27427,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B492" t="s">
         <v>56</v>
@@ -27436,10 +27442,10 @@
         <v>1304</v>
       </c>
       <c r="G492" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H492" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="J492" t="s">
         <v>576</v>
@@ -27459,7 +27465,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B493" t="s">
         <v>56</v>
@@ -27474,22 +27480,22 @@
         <v>1304</v>
       </c>
       <c r="G493" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="H493" t="s">
-        <v>1306</v>
+        <v>1355</v>
       </c>
       <c r="J493" t="s">
-        <v>161</v>
+        <v>576</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M493">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P493" s="8">
         <v>46155</v>
@@ -27497,7 +27503,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B494" t="s">
         <v>56</v>
@@ -27512,22 +27518,22 @@
         <v>1304</v>
       </c>
       <c r="G494" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H494" t="s">
-        <v>1338</v>
-      </c>
-      <c r="J494">
-        <v>2017</v>
+        <v>1306</v>
+      </c>
+      <c r="J494" t="s">
+        <v>161</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M494">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P494" s="8">
         <v>46155</v>
@@ -27535,7 +27541,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B495" t="s">
         <v>56</v>
@@ -27543,9 +27549,6 @@
       <c r="C495" t="s">
         <v>1295</v>
       </c>
-      <c r="D495" t="s">
-        <v>1003</v>
-      </c>
       <c r="E495" t="s">
         <v>1295</v>
       </c>
@@ -27553,22 +27556,22 @@
         <v>1304</v>
       </c>
       <c r="G495" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="H495" t="s">
-        <v>1324</v>
-      </c>
-      <c r="J495" t="s">
-        <v>576</v>
+        <v>1338</v>
+      </c>
+      <c r="J495">
+        <v>2017</v>
       </c>
       <c r="K495">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L495">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M495">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P495" s="8">
         <v>46155</v>
@@ -27576,7 +27579,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B496" t="s">
         <v>56</v>
@@ -27594,7 +27597,7 @@
         <v>1304</v>
       </c>
       <c r="G496" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="H496" t="s">
         <v>1324</v>
@@ -27606,10 +27609,10 @@
         <v>150</v>
       </c>
       <c r="L496">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M496">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P496" s="8">
         <v>46155</v>
@@ -27617,10 +27620,10 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B497" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C497" t="s">
         <v>1295</v>
@@ -27635,10 +27638,10 @@
         <v>1304</v>
       </c>
       <c r="G497" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="H497" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="J497" t="s">
         <v>576</v>
@@ -27647,10 +27650,10 @@
         <v>150</v>
       </c>
       <c r="L497">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M497">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P497" s="8">
         <v>46155</v>
@@ -27658,7 +27661,7 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B498" t="s">
         <v>117</v>
@@ -27676,7 +27679,7 @@
         <v>1304</v>
       </c>
       <c r="G498" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H498" t="s">
         <v>1306</v>
@@ -27685,10 +27688,10 @@
         <v>576</v>
       </c>
       <c r="K498">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L498">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M498">
         <v>5</v>
@@ -27699,7 +27702,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B499" t="s">
         <v>117</v>
@@ -27717,7 +27720,7 @@
         <v>1304</v>
       </c>
       <c r="G499" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="H499" t="s">
         <v>1306</v>
@@ -27726,10 +27729,10 @@
         <v>576</v>
       </c>
       <c r="K499">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L499">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M499">
         <v>5</v>
@@ -27740,37 +27743,40 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B500" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C500" t="s">
-        <v>1371</v>
+        <v>1295</v>
+      </c>
+      <c r="D500" t="s">
+        <v>1003</v>
       </c>
       <c r="E500" t="s">
-        <v>1371</v>
+        <v>1295</v>
       </c>
       <c r="F500" t="s">
-        <v>1372</v>
+        <v>1304</v>
       </c>
       <c r="G500" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="H500" t="s">
-        <v>1374</v>
+        <v>1306</v>
       </c>
       <c r="J500" t="s">
-        <v>1375</v>
+        <v>576</v>
       </c>
       <c r="K500">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L500">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M500">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P500" s="8">
         <v>46155</v>
@@ -27778,7 +27784,7 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="B501" t="s">
         <v>56</v>
@@ -27793,7 +27799,7 @@
         <v>1372</v>
       </c>
       <c r="G501" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="H501" t="s">
         <v>1374</v>
@@ -27805,7 +27811,7 @@
         <v>70</v>
       </c>
       <c r="L501">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M501">
         <v>6</v>
@@ -27816,7 +27822,7 @@
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B502" t="s">
         <v>56</v>
@@ -27831,19 +27837,22 @@
         <v>1372</v>
       </c>
       <c r="G502" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="H502" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="J502" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="K502">
         <v>70</v>
       </c>
       <c r="L502">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M502">
+        <v>6</v>
       </c>
       <c r="P502" s="8">
         <v>46155</v>
@@ -27851,7 +27860,7 @@
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B503" t="s">
         <v>56</v>
@@ -27866,19 +27875,19 @@
         <v>1372</v>
       </c>
       <c r="G503" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="H503" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="J503" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="K503">
         <v>70</v>
       </c>
       <c r="L503">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P503" s="8">
         <v>46155</v>
@@ -27886,7 +27895,7 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B504" t="s">
         <v>56</v>
@@ -27901,19 +27910,19 @@
         <v>1372</v>
       </c>
       <c r="G504" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="H504" t="s">
         <v>1384</v>
       </c>
       <c r="J504" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="K504">
         <v>70</v>
       </c>
       <c r="L504">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P504" s="8">
         <v>46155</v>
@@ -27921,7 +27930,7 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B505" t="s">
         <v>56</v>
@@ -27936,19 +27945,19 @@
         <v>1372</v>
       </c>
       <c r="G505" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="H505" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="J505" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="K505">
         <v>70</v>
       </c>
       <c r="L505">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P505" s="8">
         <v>46155</v>
@@ -27956,7 +27965,7 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B506" t="s">
         <v>56</v>
@@ -27964,9 +27973,6 @@
       <c r="C506" t="s">
         <v>1371</v>
       </c>
-      <c r="D506" t="s">
-        <v>1003</v>
-      </c>
       <c r="E506" t="s">
         <v>1371</v>
       </c>
@@ -27974,19 +27980,19 @@
         <v>1372</v>
       </c>
       <c r="G506" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="H506" t="s">
         <v>1391</v>
       </c>
       <c r="J506" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="K506">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L506">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P506" s="8">
         <v>46155</v>
@@ -27994,7 +28000,7 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B507" t="s">
         <v>56</v>
@@ -28002,26 +28008,29 @@
       <c r="C507" t="s">
         <v>1371</v>
       </c>
+      <c r="D507" t="s">
+        <v>1003</v>
+      </c>
       <c r="E507" t="s">
         <v>1371</v>
       </c>
       <c r="F507" t="s">
-        <v>1397</v>
+        <v>1372</v>
+      </c>
+      <c r="G507" t="s">
+        <v>1394</v>
       </c>
       <c r="H507" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="J507" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="K507">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L507">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M507">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P507" s="8">
         <v>46155</v>
@@ -28029,10 +28038,10 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B508" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C508" t="s">
         <v>1371</v>
@@ -28043,17 +28052,17 @@
       <c r="F508" t="s">
         <v>1397</v>
       </c>
-      <c r="G508" t="s">
-        <v>1401</v>
-      </c>
       <c r="H508" t="s">
-        <v>1402</v>
+        <v>1398</v>
+      </c>
+      <c r="J508" t="s">
+        <v>1399</v>
       </c>
       <c r="K508">
         <v>70</v>
       </c>
       <c r="L508">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M508">
         <v>45</v>
@@ -28064,10 +28073,10 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B509" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C509" t="s">
         <v>1371</v>
@@ -28079,22 +28088,19 @@
         <v>1397</v>
       </c>
       <c r="G509" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="H509" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J509" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="K509">
         <v>70</v>
       </c>
       <c r="L509">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M509">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P509" s="8">
         <v>46155</v>
@@ -28102,7 +28108,7 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B510" t="s">
         <v>56</v>
@@ -28117,22 +28123,22 @@
         <v>1397</v>
       </c>
       <c r="G510" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="H510" t="s">
-        <v>1408</v>
+        <v>1001</v>
       </c>
       <c r="J510" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="K510">
         <v>70</v>
       </c>
       <c r="L510">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M510">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P510" s="8">
         <v>46155</v>
@@ -28140,7 +28146,7 @@
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B511" t="s">
         <v>56</v>
@@ -28152,25 +28158,25 @@
         <v>1371</v>
       </c>
       <c r="F511" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
       <c r="G511" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="H511" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="J511" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="K511">
         <v>70</v>
       </c>
       <c r="L511">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M511">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P511" s="8">
         <v>46155</v>
@@ -28178,7 +28184,7 @@
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="B512" t="s">
         <v>56</v>
@@ -28193,7 +28199,7 @@
         <v>1411</v>
       </c>
       <c r="G512" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="H512" t="s">
         <v>1413</v>
@@ -28205,17 +28211,55 @@
         <v>70</v>
       </c>
       <c r="L512">
+        <v>36.5</v>
+      </c>
+      <c r="M512">
+        <v>7</v>
+      </c>
+      <c r="P512" s="8">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="513" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A513" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B513" t="s">
+        <v>56</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E513" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F513" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G513" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H513" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J513" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K513">
+        <v>70</v>
+      </c>
+      <c r="L513">
         <v>40.5</v>
       </c>
-      <c r="M512">
+      <c r="M513">
         <v>5</v>
       </c>
-      <c r="P512" s="8">
+      <c r="P513" s="8">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R512" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R513" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CE42DD-CC4E-6647-A1C1-F9BDD35F65A5}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8260D4F5-4CF0-D949-85F6-A87FE5D785CD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$513</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$514</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10068" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10074" uniqueCount="2287">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6894,6 +6894,18 @@
   </si>
   <si>
     <t>Domaine de la Perruche</t>
+  </si>
+  <si>
+    <t>Calvi</t>
+  </si>
+  <si>
+    <t>Domaine Maestracci</t>
+  </si>
+  <si>
+    <t>Villa Maestracci</t>
+  </si>
+  <si>
+    <t>E Signurine</t>
   </si>
 </sst>
 </file>
@@ -7658,7 +7670,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R513"/>
+  <dimension ref="A1:R514"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -20958,11 +20970,11 @@
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A333" t="s">
-        <v>932</v>
+      <c r="A333">
+        <v>72400122</v>
       </c>
       <c r="B333" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C333" t="s">
         <v>910</v>
@@ -20971,66 +20983,75 @@
         <v>911</v>
       </c>
       <c r="E333" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F333" t="s">
-        <v>912</v>
+        <v>2283</v>
       </c>
       <c r="G333" t="s">
-        <v>913</v>
+        <v>2285</v>
       </c>
       <c r="H333" t="s">
-        <v>914</v>
+        <v>2284</v>
       </c>
       <c r="I333" t="s">
-        <v>915</v>
-      </c>
-      <c r="J333" t="s">
-        <v>576</v>
+        <v>762</v>
+      </c>
+      <c r="J333">
+        <v>2022</v>
       </c>
       <c r="K333">
         <v>75</v>
       </c>
       <c r="L333">
-        <v>5.05</v>
+        <v>19.8</v>
       </c>
       <c r="M333">
-        <v>10955</v>
+        <v>24</v>
       </c>
       <c r="P333" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A334" t="s">
-        <v>933</v>
+      <c r="A334">
+        <v>72400223</v>
       </c>
       <c r="B334" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C334" t="s">
         <v>910</v>
       </c>
+      <c r="D334" t="s">
+        <v>911</v>
+      </c>
       <c r="E334" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F334" t="s">
-        <v>934</v>
+        <v>2283</v>
+      </c>
+      <c r="G334" t="s">
+        <v>2286</v>
       </c>
       <c r="H334" t="s">
-        <v>935</v>
-      </c>
-      <c r="J334" t="s">
-        <v>93</v>
+        <v>2284</v>
+      </c>
+      <c r="I334" t="s">
+        <v>762</v>
+      </c>
+      <c r="J334">
+        <v>2022</v>
       </c>
       <c r="K334">
         <v>75</v>
       </c>
       <c r="L334">
-        <v>6.1</v>
+        <v>19.8</v>
       </c>
       <c r="M334">
-        <v>324</v>
+        <v>24</v>
       </c>
       <c r="P334" s="8">
         <v>46155</v>
@@ -21038,7 +21059,7 @@
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B335" t="s">
         <v>56</v>
@@ -21050,13 +21071,10 @@
         <v>928</v>
       </c>
       <c r="F335" t="s">
-        <v>937</v>
-      </c>
-      <c r="G335" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="H335" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="J335" t="s">
         <v>93</v>
@@ -21065,10 +21083,10 @@
         <v>75</v>
       </c>
       <c r="L335">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="M335">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="P335" s="8">
         <v>46155</v>
@@ -21076,7 +21094,7 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B336" t="s">
         <v>56</v>
@@ -21088,25 +21106,25 @@
         <v>928</v>
       </c>
       <c r="F336" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="G336" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="H336" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="J336" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K336">
         <v>75</v>
       </c>
       <c r="L336">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M336">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="P336" s="8">
         <v>46155</v>
@@ -21114,7 +21132,7 @@
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B337" t="s">
         <v>56</v>
@@ -21122,35 +21140,29 @@
       <c r="C337" t="s">
         <v>910</v>
       </c>
-      <c r="D337" t="s">
-        <v>917</v>
-      </c>
       <c r="E337" t="s">
         <v>928</v>
       </c>
       <c r="F337" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="G337" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="H337" t="s">
-        <v>946</v>
-      </c>
-      <c r="I337" t="s">
-        <v>62</v>
+        <v>942</v>
       </c>
       <c r="J337" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K337">
         <v>75</v>
       </c>
       <c r="L337">
-        <v>6.45</v>
+        <v>6.6</v>
       </c>
       <c r="M337">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="P337" s="8">
         <v>46155</v>
@@ -21158,7 +21170,7 @@
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B338" t="s">
         <v>56</v>
@@ -21176,7 +21188,7 @@
         <v>944</v>
       </c>
       <c r="G338" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="H338" t="s">
         <v>946</v>
@@ -21191,10 +21203,10 @@
         <v>75</v>
       </c>
       <c r="L338">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M338">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P338" s="8">
         <v>46155</v>
@@ -21202,7 +21214,7 @@
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B339" t="s">
         <v>56</v>
@@ -21217,13 +21229,16 @@
         <v>928</v>
       </c>
       <c r="F339" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="G339" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="H339" t="s">
-        <v>285</v>
+        <v>946</v>
+      </c>
+      <c r="I339" t="s">
+        <v>62</v>
       </c>
       <c r="J339" t="s">
         <v>93</v>
@@ -21232,10 +21247,10 @@
         <v>75</v>
       </c>
       <c r="L339">
-        <v>5.65</v>
+        <v>6.55</v>
       </c>
       <c r="M339">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P339" s="8">
         <v>46155</v>
@@ -21243,7 +21258,7 @@
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B340" t="s">
         <v>56</v>
@@ -21260,11 +21275,11 @@
       <c r="F340" t="s">
         <v>950</v>
       </c>
+      <c r="G340" t="s">
+        <v>951</v>
+      </c>
       <c r="H340" t="s">
-        <v>953</v>
-      </c>
-      <c r="I340" t="s">
-        <v>62</v>
+        <v>285</v>
       </c>
       <c r="J340" t="s">
         <v>93</v>
@@ -21273,10 +21288,10 @@
         <v>75</v>
       </c>
       <c r="L340">
-        <v>6.6</v>
+        <v>5.65</v>
       </c>
       <c r="M340">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P340" s="8">
         <v>46155</v>
@@ -21284,10 +21299,10 @@
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B341" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C341" t="s">
         <v>910</v>
@@ -21301,26 +21316,23 @@
       <c r="F341" t="s">
         <v>950</v>
       </c>
-      <c r="G341" t="s">
-        <v>955</v>
-      </c>
       <c r="H341" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="I341" t="s">
         <v>62</v>
       </c>
       <c r="J341" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K341">
         <v>75</v>
       </c>
       <c r="L341">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M341">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P341" s="8">
         <v>46155</v>
@@ -21328,10 +21340,10 @@
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B342" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C342" t="s">
         <v>910</v>
@@ -21346,22 +21358,25 @@
         <v>950</v>
       </c>
       <c r="G342" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H342" t="s">
-        <v>924</v>
+        <v>956</v>
+      </c>
+      <c r="I342" t="s">
+        <v>62</v>
       </c>
       <c r="J342" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K342">
         <v>75</v>
       </c>
       <c r="L342">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M342">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P342" s="8">
         <v>46155</v>
@@ -21369,7 +21384,7 @@
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B343" t="s">
         <v>56</v>
@@ -21387,10 +21402,10 @@
         <v>950</v>
       </c>
       <c r="G343" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="H343" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
       <c r="J343" t="s">
         <v>93</v>
@@ -21402,7 +21417,7 @@
         <v>9.1</v>
       </c>
       <c r="M343">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P343" s="8">
         <v>46155</v>
@@ -21410,10 +21425,10 @@
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B344" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C344" t="s">
         <v>910</v>
@@ -21428,25 +21443,22 @@
         <v>950</v>
       </c>
       <c r="G344" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H344" t="s">
-        <v>956</v>
-      </c>
-      <c r="I344" t="s">
-        <v>62</v>
+        <v>939</v>
       </c>
       <c r="J344" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K344">
         <v>75</v>
       </c>
       <c r="L344">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M344">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P344" s="8">
         <v>46155</v>
@@ -21454,10 +21466,10 @@
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B345" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C345" t="s">
         <v>910</v>
@@ -21472,25 +21484,25 @@
         <v>950</v>
       </c>
       <c r="G345" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H345" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="I345" t="s">
         <v>62</v>
       </c>
       <c r="J345" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K345">
         <v>75</v>
       </c>
       <c r="L345">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M345">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P345" s="8">
         <v>46155</v>
@@ -21498,7 +21510,7 @@
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B346" t="s">
         <v>56</v>
@@ -21515,8 +21527,14 @@
       <c r="F346" t="s">
         <v>950</v>
       </c>
+      <c r="G346" t="s">
+        <v>964</v>
+      </c>
       <c r="H346" t="s">
-        <v>967</v>
+        <v>965</v>
+      </c>
+      <c r="I346" t="s">
+        <v>62</v>
       </c>
       <c r="J346" t="s">
         <v>93</v>
@@ -21528,7 +21546,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M346">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P346" s="8">
         <v>46155</v>
@@ -21536,7 +21554,7 @@
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B347" t="s">
         <v>56</v>
@@ -21551,25 +21569,22 @@
         <v>928</v>
       </c>
       <c r="F347" t="s">
-        <v>922</v>
-      </c>
-      <c r="G347" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="H347" t="s">
-        <v>924</v>
+        <v>967</v>
       </c>
       <c r="J347" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K347">
         <v>75</v>
       </c>
       <c r="L347">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M347">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P347" s="8">
         <v>46155</v>
@@ -21577,7 +21592,7 @@
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B348" t="s">
         <v>56</v>
@@ -21592,25 +21607,25 @@
         <v>928</v>
       </c>
       <c r="F348" t="s">
-        <v>950</v>
+        <v>922</v>
+      </c>
+      <c r="G348" t="s">
+        <v>923</v>
       </c>
       <c r="H348" t="s">
-        <v>965</v>
-      </c>
-      <c r="I348" t="s">
-        <v>62</v>
-      </c>
-      <c r="J348">
-        <v>2025</v>
+        <v>924</v>
+      </c>
+      <c r="J348" t="s">
+        <v>334</v>
       </c>
       <c r="K348">
         <v>75</v>
       </c>
       <c r="L348">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M348">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P348" s="8">
         <v>46155</v>
@@ -21618,40 +21633,40 @@
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B349" t="s">
         <v>56</v>
       </c>
       <c r="C349" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D349" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E349" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F349" t="s">
-        <v>975</v>
-      </c>
-      <c r="G349" t="s">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="H349" t="s">
-        <v>977</v>
-      </c>
-      <c r="J349" t="s">
-        <v>334</v>
+        <v>965</v>
+      </c>
+      <c r="I349" t="s">
+        <v>62</v>
+      </c>
+      <c r="J349">
+        <v>2025</v>
       </c>
       <c r="K349">
         <v>75</v>
       </c>
       <c r="L349">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M349">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P349" s="8">
         <v>46155</v>
@@ -21659,7 +21674,7 @@
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B350" t="s">
         <v>56</v>
@@ -21677,22 +21692,22 @@
         <v>975</v>
       </c>
       <c r="G350" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H350" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J350" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K350">
         <v>75</v>
       </c>
       <c r="L350">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M350">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P350" s="8">
         <v>46155</v>
@@ -21700,7 +21715,7 @@
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B351" t="s">
         <v>56</v>
@@ -21715,25 +21730,25 @@
         <v>58</v>
       </c>
       <c r="F351" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G351" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="H351" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J351" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K351">
         <v>75</v>
       </c>
       <c r="L351">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M351">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P351" s="8">
         <v>46155</v>
@@ -21741,7 +21756,7 @@
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B352" t="s">
         <v>56</v>
@@ -21756,25 +21771,25 @@
         <v>58</v>
       </c>
       <c r="F352" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G352" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="H352" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J352" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K352">
         <v>75</v>
       </c>
       <c r="L352">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M352">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P352" s="8">
         <v>46155</v>
@@ -21782,7 +21797,7 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B353" t="s">
         <v>56</v>
@@ -21800,10 +21815,10 @@
         <v>975</v>
       </c>
       <c r="G353" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="H353" t="s">
-        <v>285</v>
+        <v>987</v>
       </c>
       <c r="J353" t="s">
         <v>93</v>
@@ -21812,10 +21827,10 @@
         <v>75</v>
       </c>
       <c r="L353">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M353">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P353" s="8">
         <v>46155</v>
@@ -21823,7 +21838,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B354" t="s">
         <v>56</v>
@@ -21841,7 +21856,7 @@
         <v>975</v>
       </c>
       <c r="G354" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="H354" t="s">
         <v>285</v>
@@ -21853,10 +21868,10 @@
         <v>75</v>
       </c>
       <c r="L354">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M354">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P354" s="8">
         <v>46155</v>
@@ -21864,7 +21879,7 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B355" t="s">
         <v>56</v>
@@ -21882,22 +21897,22 @@
         <v>975</v>
       </c>
       <c r="G355" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="H355" t="s">
-        <v>987</v>
+        <v>285</v>
       </c>
       <c r="J355" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K355">
         <v>75</v>
       </c>
       <c r="L355">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M355">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P355" s="8">
         <v>46155</v>
@@ -21905,7 +21920,7 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B356" t="s">
         <v>56</v>
@@ -21920,13 +21935,13 @@
         <v>58</v>
       </c>
       <c r="F356" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G356" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="H356" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="J356" t="s">
         <v>334</v>
@@ -21935,10 +21950,10 @@
         <v>75</v>
       </c>
       <c r="L356">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M356">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P356" s="8">
         <v>46155</v>
@@ -21946,7 +21961,7 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B357" t="s">
         <v>56</v>
@@ -21961,16 +21976,16 @@
         <v>58</v>
       </c>
       <c r="F357" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G357" t="s">
-        <v>108</v>
+        <v>995</v>
       </c>
       <c r="H357" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="J357" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K357">
         <v>75</v>
@@ -21979,18 +21994,15 @@
         <v>5.7</v>
       </c>
       <c r="M357">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P357" s="8">
         <v>46155</v>
-      </c>
-      <c r="R357" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B358" t="s">
         <v>56</v>
@@ -22008,39 +22020,42 @@
         <v>975</v>
       </c>
       <c r="G358" t="s">
-        <v>1000</v>
+        <v>108</v>
       </c>
       <c r="H358" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="J358" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K358">
         <v>75</v>
       </c>
       <c r="L358">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M358">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P358" s="8">
         <v>46155</v>
+      </c>
+      <c r="R358" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B359" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C359" t="s">
         <v>973</v>
       </c>
       <c r="D359" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E359" t="s">
         <v>58</v>
@@ -22049,7 +22064,7 @@
         <v>975</v>
       </c>
       <c r="G359" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="H359" t="s">
         <v>1001</v>
@@ -22058,13 +22073,13 @@
         <v>334</v>
       </c>
       <c r="K359">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L359">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M359">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P359" s="8">
         <v>46155</v>
@@ -22072,16 +22087,16 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B360" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C360" t="s">
         <v>973</v>
       </c>
       <c r="D360" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="E360" t="s">
         <v>58</v>
@@ -22090,25 +22105,22 @@
         <v>975</v>
       </c>
       <c r="G360" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H360" t="s">
-        <v>987</v>
-      </c>
-      <c r="I360" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="J360" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K360">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L360">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M360">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P360" s="8">
         <v>46155</v>
@@ -22116,7 +22128,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B361" t="s">
         <v>56</v>
@@ -22125,31 +22137,34 @@
         <v>973</v>
       </c>
       <c r="D361" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E361" t="s">
         <v>58</v>
       </c>
       <c r="F361" t="s">
-        <v>1010</v>
+        <v>975</v>
       </c>
       <c r="G361" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="H361" t="s">
-        <v>1012</v>
+        <v>987</v>
+      </c>
+      <c r="I361" t="s">
+        <v>1007</v>
       </c>
       <c r="J361" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K361">
         <v>75</v>
       </c>
       <c r="L361">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M361">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P361" s="8">
         <v>46155</v>
@@ -22157,7 +22172,7 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B362" t="s">
         <v>56</v>
@@ -22166,34 +22181,31 @@
         <v>973</v>
       </c>
       <c r="D362" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E362" t="s">
         <v>58</v>
       </c>
       <c r="F362" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="G362" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="H362" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I362" t="s">
-        <v>784</v>
+        <v>1012</v>
       </c>
       <c r="J362" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K362">
         <v>75</v>
       </c>
       <c r="L362">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M362">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P362" s="8">
         <v>46155</v>
@@ -22201,7 +22213,7 @@
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B363" t="s">
         <v>56</v>
@@ -22216,25 +22228,28 @@
         <v>58</v>
       </c>
       <c r="F363" t="s">
-        <v>975</v>
+        <v>1014</v>
       </c>
       <c r="G363" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="H363" t="s">
-        <v>987</v>
+        <v>1016</v>
+      </c>
+      <c r="I363" t="s">
+        <v>784</v>
       </c>
       <c r="J363" t="s">
-        <v>334</v>
+        <v>63</v>
       </c>
       <c r="K363">
         <v>75</v>
       </c>
       <c r="L363">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M363">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P363" s="8">
         <v>46155</v>
@@ -22242,7 +22257,7 @@
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B364" t="s">
         <v>56</v>
@@ -22260,25 +22275,22 @@
         <v>975</v>
       </c>
       <c r="G364" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="H364" t="s">
         <v>987</v>
       </c>
-      <c r="I364" t="s">
-        <v>1007</v>
-      </c>
       <c r="J364" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K364">
         <v>75</v>
       </c>
       <c r="L364">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M364">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P364" s="8">
         <v>46155</v>
@@ -22286,7 +22298,7 @@
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B365" t="s">
         <v>56</v>
@@ -22304,22 +22316,25 @@
         <v>975</v>
       </c>
       <c r="G365" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="H365" t="s">
-        <v>605</v>
+        <v>987</v>
+      </c>
+      <c r="I365" t="s">
+        <v>1007</v>
       </c>
       <c r="J365" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K365">
         <v>75</v>
       </c>
       <c r="L365">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M365">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P365" s="8">
         <v>46155</v>
@@ -22327,7 +22342,7 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B366" t="s">
         <v>56</v>
@@ -22342,22 +22357,25 @@
         <v>58</v>
       </c>
       <c r="F366" t="s">
-        <v>1024</v>
+        <v>975</v>
       </c>
       <c r="G366" t="s">
-        <v>159</v>
+        <v>1022</v>
       </c>
       <c r="H366" t="s">
-        <v>1025</v>
+        <v>605</v>
       </c>
       <c r="J366" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K366">
         <v>75</v>
       </c>
       <c r="L366">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M366">
+        <v>321</v>
       </c>
       <c r="P366" s="8">
         <v>46155</v>
@@ -22365,7 +22383,7 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B367" t="s">
         <v>56</v>
@@ -22380,13 +22398,13 @@
         <v>58</v>
       </c>
       <c r="F367" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="G367" t="s">
-        <v>1028</v>
+        <v>159</v>
       </c>
       <c r="H367" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="J367" t="s">
         <v>93</v>
@@ -22395,10 +22413,7 @@
         <v>75</v>
       </c>
       <c r="L367">
-        <v>3.95</v>
-      </c>
-      <c r="M367">
-        <v>351</v>
+        <v>37</v>
       </c>
       <c r="P367" s="8">
         <v>46155</v>
@@ -22406,7 +22421,7 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B368" t="s">
         <v>56</v>
@@ -22424,10 +22439,10 @@
         <v>1027</v>
       </c>
       <c r="G368" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="H368" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="J368" t="s">
         <v>93</v>
@@ -22436,10 +22451,10 @@
         <v>75</v>
       </c>
       <c r="L368">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M368">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P368" s="8">
         <v>46155</v>
@@ -22447,10 +22462,10 @@
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B369" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C369" t="s">
         <v>973</v>
@@ -22462,33 +22477,33 @@
         <v>58</v>
       </c>
       <c r="F369" t="s">
-        <v>59</v>
+        <v>1027</v>
       </c>
       <c r="G369" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="H369" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="J369" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K369">
         <v>75</v>
       </c>
       <c r="L369">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M369">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P369" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A370">
-        <v>24003025</v>
+      <c r="A370" t="s">
+        <v>1033</v>
       </c>
       <c r="B370" t="s">
         <v>117</v>
@@ -22497,7 +22512,7 @@
         <v>973</v>
       </c>
       <c r="D370" t="s">
-        <v>1036</v>
+        <v>974</v>
       </c>
       <c r="E370" t="s">
         <v>58</v>
@@ -22506,16 +22521,13 @@
         <v>59</v>
       </c>
       <c r="G370" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="H370" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I370" t="s">
-        <v>62</v>
-      </c>
-      <c r="J370">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J370" t="s">
+        <v>334</v>
       </c>
       <c r="K370">
         <v>75</v>
@@ -22523,13 +22535,16 @@
       <c r="L370">
         <v>6.2</v>
       </c>
+      <c r="M370">
+        <v>0</v>
+      </c>
       <c r="P370" s="8">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A371" t="s">
-        <v>1039</v>
+      <c r="A371">
+        <v>24003025</v>
       </c>
       <c r="B371" t="s">
         <v>117</v>
@@ -22538,39 +22553,39 @@
         <v>973</v>
       </c>
       <c r="D371" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="E371" t="s">
         <v>58</v>
       </c>
       <c r="F371" t="s">
-        <v>1040</v>
+        <v>59</v>
       </c>
       <c r="G371" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="H371" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J371" t="s">
-        <v>82</v>
+        <v>1038</v>
+      </c>
+      <c r="I371" t="s">
+        <v>62</v>
+      </c>
+      <c r="J371">
+        <v>2025</v>
       </c>
       <c r="K371">
         <v>75</v>
       </c>
       <c r="L371">
-        <v>7.55</v>
-      </c>
-      <c r="M371">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P371" s="8">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B372" t="s">
         <v>117</v>
@@ -22579,28 +22594,28 @@
         <v>973</v>
       </c>
       <c r="D372" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E372" t="s">
         <v>58</v>
       </c>
       <c r="F372" t="s">
-        <v>59</v>
+        <v>1040</v>
       </c>
       <c r="G372" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="H372" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="J372" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="K372">
         <v>75</v>
       </c>
       <c r="L372">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M372">
         <v>0</v>
@@ -22611,7 +22626,7 @@
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B373" t="s">
         <v>117</v>
@@ -22620,28 +22635,28 @@
         <v>973</v>
       </c>
       <c r="D373" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E373" t="s">
         <v>58</v>
       </c>
       <c r="F373" t="s">
-        <v>1046</v>
+        <v>59</v>
       </c>
       <c r="G373" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="H373" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="J373" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K373">
         <v>75</v>
       </c>
       <c r="L373">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M373">
         <v>0</v>
@@ -22652,7 +22667,7 @@
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B374" t="s">
         <v>117</v>
@@ -22661,34 +22676,31 @@
         <v>973</v>
       </c>
       <c r="D374" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E374" t="s">
         <v>58</v>
       </c>
       <c r="F374" t="s">
-        <v>59</v>
+        <v>1046</v>
       </c>
       <c r="G374" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H374" t="s">
-        <v>1050</v>
-      </c>
-      <c r="I374" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="J374" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K374">
         <v>75</v>
       </c>
       <c r="L374">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M374">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P374" s="8">
         <v>46155</v>
@@ -22696,7 +22708,7 @@
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="B375" t="s">
         <v>117</v>
@@ -22705,20 +22717,23 @@
         <v>973</v>
       </c>
       <c r="D375" t="s">
-        <v>1053</v>
+        <v>974</v>
       </c>
       <c r="E375" t="s">
         <v>58</v>
       </c>
       <c r="F375" t="s">
-        <v>1054</v>
+        <v>59</v>
       </c>
       <c r="G375" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="H375" t="s">
         <v>1050</v>
       </c>
+      <c r="I375" t="s">
+        <v>1051</v>
+      </c>
       <c r="J375" t="s">
         <v>93</v>
       </c>
@@ -22726,10 +22741,10 @@
         <v>75</v>
       </c>
       <c r="L375">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M375">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P375" s="8">
         <v>46155</v>
@@ -22737,7 +22752,7 @@
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B376" t="s">
         <v>117</v>
@@ -22746,28 +22761,28 @@
         <v>973</v>
       </c>
       <c r="D376" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E376" t="s">
         <v>58</v>
       </c>
       <c r="F376" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="G376" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H376" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="J376" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="K376">
         <v>75</v>
       </c>
       <c r="L376">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M376">
         <v>0</v>
@@ -22778,7 +22793,7 @@
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B377" t="s">
         <v>117</v>
@@ -22787,28 +22802,28 @@
         <v>973</v>
       </c>
       <c r="D377" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E377" t="s">
         <v>58</v>
       </c>
       <c r="F377" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="G377" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="H377" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="J377" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="K377">
         <v>75</v>
       </c>
       <c r="L377">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M377">
         <v>0</v>
@@ -22819,7 +22834,7 @@
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B378" t="s">
         <v>117</v>
@@ -22834,22 +22849,22 @@
         <v>58</v>
       </c>
       <c r="F378" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="G378" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="H378" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="J378" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="K378">
         <v>75</v>
       </c>
       <c r="L378">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -22860,7 +22875,7 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B379" t="s">
         <v>117</v>
@@ -22878,10 +22893,10 @@
         <v>1062</v>
       </c>
       <c r="G379" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="H379" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="J379" t="s">
         <v>334</v>
@@ -22890,7 +22905,7 @@
         <v>75</v>
       </c>
       <c r="L379">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="M379">
         <v>0</v>
@@ -22901,7 +22916,7 @@
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B380" t="s">
         <v>117</v>
@@ -22919,19 +22934,19 @@
         <v>1062</v>
       </c>
       <c r="G380" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="H380" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="J380" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K380">
         <v>75</v>
       </c>
       <c r="L380">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="M380">
         <v>0</v>
@@ -22942,10 +22957,10 @@
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B381" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C381" t="s">
         <v>973</v>
@@ -22960,10 +22975,10 @@
         <v>1062</v>
       </c>
       <c r="G381" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H381" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="J381" t="s">
         <v>93</v>
@@ -22972,10 +22987,10 @@
         <v>75</v>
       </c>
       <c r="L381">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M381">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P381" s="8">
         <v>46155</v>
@@ -22983,7 +22998,7 @@
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B382" t="s">
         <v>56</v>
@@ -22992,19 +23007,19 @@
         <v>973</v>
       </c>
       <c r="D382" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E382" t="s">
         <v>58</v>
       </c>
       <c r="F382" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="G382" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="H382" t="s">
-        <v>1012</v>
+        <v>1072</v>
       </c>
       <c r="J382" t="s">
         <v>93</v>
@@ -23013,10 +23028,10 @@
         <v>75</v>
       </c>
       <c r="L382">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M382">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P382" s="8">
         <v>46155</v>
@@ -23024,7 +23039,7 @@
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B383" t="s">
         <v>56</v>
@@ -23042,10 +23057,10 @@
         <v>1027</v>
       </c>
       <c r="G383" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H383" t="s">
-        <v>1032</v>
+        <v>1012</v>
       </c>
       <c r="J383" t="s">
         <v>93</v>
@@ -23054,10 +23069,10 @@
         <v>75</v>
       </c>
       <c r="L383">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M383">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P383" s="8">
         <v>46155</v>
@@ -23065,7 +23080,7 @@
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B384" t="s">
         <v>56</v>
@@ -23080,13 +23095,13 @@
         <v>58</v>
       </c>
       <c r="F384" t="s">
-        <v>1078</v>
+        <v>1027</v>
       </c>
       <c r="G384" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H384" t="s">
-        <v>1080</v>
+        <v>1032</v>
       </c>
       <c r="J384" t="s">
         <v>93</v>
@@ -23095,7 +23110,10 @@
         <v>75</v>
       </c>
       <c r="L384">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M384">
+        <v>264</v>
       </c>
       <c r="P384" s="8">
         <v>46155</v>
@@ -23103,7 +23121,7 @@
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B385" t="s">
         <v>56</v>
@@ -23118,104 +23136,101 @@
         <v>58</v>
       </c>
       <c r="F385" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="G385" t="s">
         <v>1079</v>
       </c>
       <c r="H385" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="J385" t="s">
-        <v>521</v>
+        <v>93</v>
       </c>
       <c r="K385">
         <v>75</v>
       </c>
       <c r="L385">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P385" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A386">
-        <v>53800623</v>
+      <c r="A386" t="s">
+        <v>1081</v>
       </c>
       <c r="B386" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C386" t="s">
         <v>973</v>
       </c>
       <c r="D386" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
       </c>
       <c r="F386" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G386" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="H386" t="s">
-        <v>1060</v>
+        <v>1083</v>
       </c>
       <c r="J386" t="s">
-        <v>63</v>
+        <v>521</v>
       </c>
       <c r="K386">
         <v>75</v>
       </c>
       <c r="L386">
-        <v>11</v>
-      </c>
-      <c r="M386">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P386" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A387" t="s">
-        <v>1086</v>
+      <c r="A387">
+        <v>53800623</v>
       </c>
       <c r="B387" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C387" t="s">
         <v>973</v>
       </c>
       <c r="D387" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E387" t="s">
         <v>58</v>
       </c>
       <c r="F387" t="s">
-        <v>975</v>
+        <v>1084</v>
       </c>
       <c r="G387" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="H387" t="s">
-        <v>977</v>
+        <v>1060</v>
       </c>
       <c r="J387" t="s">
-        <v>576</v>
+        <v>63</v>
       </c>
       <c r="K387">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L387">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M387">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P387" s="8">
         <v>46155</v>
@@ -23223,7 +23238,7 @@
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B388" t="s">
         <v>56</v>
@@ -23241,22 +23256,22 @@
         <v>975</v>
       </c>
       <c r="G388" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="H388" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J388" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K388">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L388">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M388">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P388" s="8">
         <v>46155</v>
@@ -23264,7 +23279,7 @@
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B389" t="s">
         <v>56</v>
@@ -23273,31 +23288,31 @@
         <v>973</v>
       </c>
       <c r="D389" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E389" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F389" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G389" t="s">
-        <v>983</v>
+        <v>1089</v>
       </c>
       <c r="H389" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J389" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K389">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L389">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M389">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P389" s="8">
         <v>46155</v>
@@ -23305,7 +23320,7 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B390" t="s">
         <v>56</v>
@@ -23314,31 +23329,31 @@
         <v>973</v>
       </c>
       <c r="D390" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E390" t="s">
         <v>79</v>
       </c>
       <c r="F390" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G390" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="H390" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="J390" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K390">
         <v>75</v>
       </c>
       <c r="L390">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="M390">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P390" s="8">
         <v>46155</v>
@@ -23346,7 +23361,7 @@
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B391" t="s">
         <v>56</v>
@@ -23364,22 +23379,22 @@
         <v>975</v>
       </c>
       <c r="G391" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H391" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J391" t="s">
-        <v>316</v>
+        <v>93</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M391">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P391" s="8">
         <v>46155</v>
@@ -23387,7 +23402,7 @@
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
@@ -23405,22 +23420,22 @@
         <v>975</v>
       </c>
       <c r="G392" t="s">
-        <v>1094</v>
+        <v>979</v>
       </c>
       <c r="H392" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J392" t="s">
-        <v>93</v>
+        <v>316</v>
       </c>
       <c r="K392">
         <v>75</v>
       </c>
       <c r="L392">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M392">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P392" s="8">
         <v>46155</v>
@@ -23428,7 +23443,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
@@ -23446,10 +23461,10 @@
         <v>975</v>
       </c>
       <c r="G393" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="H393" t="s">
-        <v>980</v>
+        <v>285</v>
       </c>
       <c r="J393" t="s">
         <v>93</v>
@@ -23458,10 +23473,10 @@
         <v>75</v>
       </c>
       <c r="L393">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M393">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P393" s="8">
         <v>46155</v>
@@ -23469,7 +23484,7 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
@@ -23484,25 +23499,25 @@
         <v>79</v>
       </c>
       <c r="F394" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G394" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="H394" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="J394" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M394">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P394" s="8">
         <v>46155</v>
@@ -23510,7 +23525,7 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
@@ -23525,25 +23540,25 @@
         <v>79</v>
       </c>
       <c r="F395" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G395" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="H395" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="J395" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M395">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P395" s="8">
         <v>46155</v>
@@ -23551,7 +23566,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
@@ -23569,22 +23584,22 @@
         <v>975</v>
       </c>
       <c r="G396" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="H396" t="s">
-        <v>1103</v>
+        <v>987</v>
       </c>
       <c r="J396" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M396">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P396" s="8">
         <v>46155</v>
@@ -23592,7 +23607,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
@@ -23610,25 +23625,22 @@
         <v>975</v>
       </c>
       <c r="G397" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="H397" t="s">
-        <v>977</v>
-      </c>
-      <c r="I397" t="s">
-        <v>289</v>
+        <v>1103</v>
       </c>
       <c r="J397" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M397">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P397" s="8">
         <v>46155</v>
@@ -23636,7 +23648,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
@@ -23654,13 +23666,13 @@
         <v>975</v>
       </c>
       <c r="G398" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H398" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="I398" t="s">
-        <v>1007</v>
+        <v>289</v>
       </c>
       <c r="J398" t="s">
         <v>63</v>
@@ -23669,10 +23681,10 @@
         <v>75</v>
       </c>
       <c r="L398">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M398">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P398" s="8">
         <v>46155</v>
@@ -23680,7 +23692,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
@@ -23695,13 +23707,16 @@
         <v>79</v>
       </c>
       <c r="F399" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G399" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H399" t="s">
-        <v>1012</v>
+        <v>987</v>
+      </c>
+      <c r="I399" t="s">
+        <v>1007</v>
       </c>
       <c r="J399" t="s">
         <v>63</v>
@@ -23710,10 +23725,10 @@
         <v>75</v>
       </c>
       <c r="L399">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M399">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P399" s="8">
         <v>46155</v>
@@ -23721,7 +23736,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
@@ -23730,19 +23745,19 @@
         <v>973</v>
       </c>
       <c r="D400" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E400" t="s">
         <v>79</v>
       </c>
       <c r="F400" t="s">
-        <v>1111</v>
+        <v>59</v>
       </c>
       <c r="G400" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="H400" t="s">
-        <v>1080</v>
+        <v>1012</v>
       </c>
       <c r="J400" t="s">
         <v>63</v>
@@ -23751,10 +23766,10 @@
         <v>75</v>
       </c>
       <c r="L400">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M400">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P400" s="8">
         <v>46155</v>
@@ -23762,7 +23777,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
@@ -23777,25 +23792,25 @@
         <v>79</v>
       </c>
       <c r="F401" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="G401" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="H401" t="s">
-        <v>1116</v>
+        <v>1080</v>
       </c>
       <c r="J401" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M401">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P401" s="8">
         <v>46155</v>
@@ -23803,7 +23818,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B402" t="s">
         <v>56</v>
@@ -23821,22 +23836,22 @@
         <v>1114</v>
       </c>
       <c r="G402" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="H402" t="s">
         <v>1116</v>
       </c>
       <c r="J402" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M402">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P402" s="8">
         <v>46155</v>
@@ -23844,37 +23859,40 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B403" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C403" t="s">
         <v>973</v>
       </c>
       <c r="D403" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E403" t="s">
         <v>79</v>
       </c>
       <c r="F403" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="G403" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="H403" t="s">
-        <v>1067</v>
+        <v>1116</v>
       </c>
       <c r="J403" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M403">
+        <v>36</v>
       </c>
       <c r="P403" s="8">
         <v>46155</v>
@@ -23882,7 +23900,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B404" t="s">
         <v>117</v>
@@ -23897,25 +23915,22 @@
         <v>79</v>
       </c>
       <c r="F404" t="s">
-        <v>1054</v>
+        <v>1120</v>
       </c>
       <c r="G404" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H404" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="J404" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>12.5</v>
-      </c>
-      <c r="M404">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P404" s="8">
         <v>46155</v>
@@ -23923,7 +23938,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B405" t="s">
         <v>117</v>
@@ -23938,22 +23953,22 @@
         <v>79</v>
       </c>
       <c r="F405" t="s">
-        <v>1125</v>
+        <v>1054</v>
       </c>
       <c r="G405" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="H405" t="s">
         <v>1060</v>
       </c>
       <c r="J405" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M405">
         <v>0</v>
@@ -23964,7 +23979,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B406" t="s">
         <v>117</v>
@@ -23982,19 +23997,19 @@
         <v>1125</v>
       </c>
       <c r="G406" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="H406" t="s">
-        <v>1129</v>
+        <v>1060</v>
       </c>
       <c r="J406" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M406">
         <v>0</v>
@@ -24005,10 +24020,10 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B407" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C407" t="s">
         <v>973</v>
@@ -24020,25 +24035,25 @@
         <v>79</v>
       </c>
       <c r="F407" t="s">
-        <v>1062</v>
+        <v>1125</v>
       </c>
       <c r="G407" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="H407" t="s">
-        <v>1072</v>
+        <v>1129</v>
       </c>
       <c r="J407" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M407">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P407" s="8">
         <v>46155</v>
@@ -24046,10 +24061,10 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B408" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C408" t="s">
         <v>973</v>
@@ -24064,13 +24079,10 @@
         <v>1062</v>
       </c>
       <c r="G408" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H408" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I408" t="s">
-        <v>62</v>
+        <v>1072</v>
       </c>
       <c r="J408" t="s">
         <v>63</v>
@@ -24079,10 +24091,10 @@
         <v>75</v>
       </c>
       <c r="L408">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M408">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P408" s="8">
         <v>46155</v>
@@ -24090,7 +24102,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B409" t="s">
         <v>117</v>
@@ -24108,10 +24120,13 @@
         <v>1062</v>
       </c>
       <c r="G409" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H409" t="s">
-        <v>1050</v>
+        <v>1060</v>
+      </c>
+      <c r="I409" t="s">
+        <v>62</v>
       </c>
       <c r="J409" t="s">
         <v>63</v>
@@ -24120,7 +24135,7 @@
         <v>75</v>
       </c>
       <c r="L409">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24131,7 +24146,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B410" t="s">
         <v>117</v>
@@ -24149,22 +24164,19 @@
         <v>1062</v>
       </c>
       <c r="G410" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="H410" t="s">
         <v>1050</v>
       </c>
-      <c r="I410" t="s">
-        <v>1051</v>
-      </c>
       <c r="J410" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K410">
         <v>75</v>
       </c>
       <c r="L410">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M410">
         <v>0</v>
@@ -24175,31 +24187,31 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B411" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C411" t="s">
         <v>973</v>
       </c>
       <c r="D411" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E411" t="s">
         <v>79</v>
       </c>
       <c r="F411" t="s">
-        <v>1139</v>
+        <v>1062</v>
       </c>
       <c r="G411" t="s">
-        <v>824</v>
+        <v>1137</v>
       </c>
       <c r="H411" t="s">
-        <v>1016</v>
+        <v>1050</v>
       </c>
       <c r="I411" t="s">
-        <v>784</v>
+        <v>1051</v>
       </c>
       <c r="J411" t="s">
         <v>93</v>
@@ -24208,10 +24220,10 @@
         <v>75</v>
       </c>
       <c r="L411">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M411">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P411" s="8">
         <v>46155</v>
@@ -24219,7 +24231,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B412" t="s">
         <v>56</v>
@@ -24234,28 +24246,28 @@
         <v>79</v>
       </c>
       <c r="F412" t="s">
-        <v>975</v>
+        <v>1139</v>
       </c>
       <c r="G412" t="s">
-        <v>1141</v>
+        <v>824</v>
       </c>
       <c r="H412" t="s">
-        <v>1142</v>
+        <v>1016</v>
       </c>
       <c r="I412" t="s">
-        <v>62</v>
+        <v>784</v>
       </c>
       <c r="J412" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M412">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P412" s="8">
         <v>46155</v>
@@ -24263,10 +24275,10 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B413" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C413" t="s">
         <v>973</v>
@@ -24278,25 +24290,28 @@
         <v>79</v>
       </c>
       <c r="F413" t="s">
-        <v>1144</v>
+        <v>975</v>
       </c>
       <c r="G413" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="H413" t="s">
-        <v>1146</v>
+        <v>1142</v>
+      </c>
+      <c r="I413" t="s">
+        <v>62</v>
       </c>
       <c r="J413" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M413">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P413" s="8">
         <v>46155</v>
@@ -24304,7 +24319,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="B414" t="s">
         <v>117</v>
@@ -24322,19 +24337,22 @@
         <v>1144</v>
       </c>
       <c r="G414" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H414" t="s">
         <v>1146</v>
       </c>
       <c r="J414" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M414">
+        <v>0</v>
       </c>
       <c r="P414" s="8">
         <v>46155</v>
@@ -24342,10 +24360,10 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B415" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C415" t="s">
         <v>973</v>
@@ -24357,28 +24375,22 @@
         <v>79</v>
       </c>
       <c r="F415" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G415" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H415" t="s">
-        <v>1152</v>
-      </c>
-      <c r="I415" t="s">
-        <v>62</v>
+        <v>1146</v>
       </c>
       <c r="J415" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>7.6</v>
-      </c>
-      <c r="M415">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P415" s="8">
         <v>46155</v>
@@ -24386,10 +24398,10 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="B416" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C416" t="s">
         <v>973</v>
@@ -24401,25 +24413,28 @@
         <v>79</v>
       </c>
       <c r="F416" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="G416" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="H416" t="s">
-        <v>1044</v>
+        <v>1152</v>
+      </c>
+      <c r="I416" t="s">
+        <v>62</v>
       </c>
       <c r="J416" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M416">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P416" s="8">
         <v>46155</v>
@@ -24427,7 +24442,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B417" t="s">
         <v>117</v>
@@ -24445,22 +24460,22 @@
         <v>1154</v>
       </c>
       <c r="G417" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="H417" t="s">
         <v>1044</v>
       </c>
       <c r="J417" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M417">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P417" s="8">
         <v>46155</v>
@@ -24468,10 +24483,10 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B418" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C418" t="s">
         <v>973</v>
@@ -24486,22 +24501,22 @@
         <v>1154</v>
       </c>
       <c r="G418" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="H418" t="s">
-        <v>1160</v>
+        <v>1044</v>
       </c>
       <c r="J418" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>15.9</v>
+        <v>8.25</v>
       </c>
       <c r="M418">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="P418" s="8">
         <v>46155</v>
@@ -24509,7 +24524,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B419" t="s">
         <v>56</v>
@@ -24524,16 +24539,13 @@
         <v>79</v>
       </c>
       <c r="F419" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="G419" t="s">
-        <v>159</v>
+        <v>1159</v>
       </c>
       <c r="H419" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I419" t="s">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="J419" t="s">
         <v>82</v>
@@ -24542,7 +24554,10 @@
         <v>75</v>
       </c>
       <c r="L419">
-        <v>17.8</v>
+        <v>15.9</v>
+      </c>
+      <c r="M419">
+        <v>49</v>
       </c>
       <c r="P419" s="8">
         <v>46155</v>
@@ -24550,7 +24565,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="B420" t="s">
         <v>56</v>
@@ -24565,25 +24580,25 @@
         <v>79</v>
       </c>
       <c r="F420" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="G420" t="s">
-        <v>1165</v>
+        <v>159</v>
       </c>
       <c r="H420" t="s">
-        <v>1160</v>
+        <v>1163</v>
+      </c>
+      <c r="I420" t="s">
+        <v>784</v>
       </c>
       <c r="J420" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M420">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P420" s="8">
         <v>46155</v>
@@ -24591,7 +24606,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B421" t="s">
         <v>56</v>
@@ -24606,25 +24621,25 @@
         <v>79</v>
       </c>
       <c r="F421" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="G421" t="s">
-        <v>159</v>
+        <v>1165</v>
       </c>
       <c r="H421" t="s">
-        <v>1168</v>
-      </c>
-      <c r="I421" t="s">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="J421" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M421">
+        <v>53</v>
       </c>
       <c r="P421" s="8">
         <v>46155</v>
@@ -24632,7 +24647,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B422" t="s">
         <v>56</v>
@@ -24647,28 +24662,25 @@
         <v>79</v>
       </c>
       <c r="F422" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G422" t="s">
-        <v>1171</v>
+        <v>159</v>
       </c>
       <c r="H422" t="s">
-        <v>1001</v>
+        <v>1168</v>
       </c>
       <c r="I422" t="s">
-        <v>169</v>
+        <v>784</v>
       </c>
       <c r="J422" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>6.5</v>
-      </c>
-      <c r="M422">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P422" s="8">
         <v>46155</v>
@@ -24676,10 +24688,10 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B423" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C423" t="s">
         <v>973</v>
@@ -24694,10 +24706,13 @@
         <v>1170</v>
       </c>
       <c r="G423" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="H423" t="s">
-        <v>1174</v>
+        <v>1001</v>
+      </c>
+      <c r="I423" t="s">
+        <v>169</v>
       </c>
       <c r="J423" t="s">
         <v>93</v>
@@ -24706,18 +24721,18 @@
         <v>75</v>
       </c>
       <c r="L423">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M423">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P423" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A424">
-        <v>16003124</v>
+      <c r="A424" t="s">
+        <v>1172</v>
       </c>
       <c r="B424" t="s">
         <v>117</v>
@@ -24729,13 +24744,13 @@
         <v>974</v>
       </c>
       <c r="E424" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F424" t="s">
         <v>1170</v>
       </c>
       <c r="G424" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="H424" t="s">
         <v>1174</v>
@@ -24757,11 +24772,11 @@
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
-        <v>1176</v>
+      <c r="A425">
+        <v>16003124</v>
       </c>
       <c r="B425" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C425" t="s">
         <v>973</v>
@@ -24770,31 +24785,28 @@
         <v>974</v>
       </c>
       <c r="E425" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F425" t="s">
         <v>1170</v>
       </c>
       <c r="G425" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="H425" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I425" t="s">
-        <v>169</v>
+        <v>1174</v>
       </c>
       <c r="J425" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K425">
         <v>75</v>
       </c>
       <c r="L425">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M425">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P425" s="8">
         <v>46155</v>
@@ -24802,10 +24814,10 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B426" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C426" t="s">
         <v>973</v>
@@ -24820,13 +24832,13 @@
         <v>1170</v>
       </c>
       <c r="G426" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="H426" t="s">
-        <v>1174</v>
+        <v>1001</v>
       </c>
       <c r="I426" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="J426" t="s">
         <v>63</v>
@@ -24835,10 +24847,10 @@
         <v>75</v>
       </c>
       <c r="L426">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M426">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P426" s="8">
         <v>46155</v>
@@ -24846,10 +24858,10 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B427" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C427" t="s">
         <v>973</v>
@@ -24864,13 +24876,13 @@
         <v>1170</v>
       </c>
       <c r="G427" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="H427" t="s">
-        <v>1001</v>
+        <v>1174</v>
       </c>
       <c r="I427" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J427" t="s">
         <v>63</v>
@@ -24879,7 +24891,7 @@
         <v>75</v>
       </c>
       <c r="L427">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M427">
         <v>171</v>
@@ -24890,10 +24902,10 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B428" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C428" t="s">
         <v>973</v>
@@ -24908,19 +24920,25 @@
         <v>1170</v>
       </c>
       <c r="G428" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="H428" t="s">
-        <v>1184</v>
+        <v>1001</v>
+      </c>
+      <c r="I428" t="s">
+        <v>169</v>
       </c>
       <c r="J428" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M428">
+        <v>171</v>
       </c>
       <c r="P428" s="8">
         <v>46155</v>
@@ -24928,10 +24946,10 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B429" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C429" t="s">
         <v>973</v>
@@ -24943,28 +24961,22 @@
         <v>79</v>
       </c>
       <c r="F429" t="s">
-        <v>59</v>
+        <v>1170</v>
       </c>
       <c r="G429" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="H429" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I429" t="s">
-        <v>169</v>
+        <v>1184</v>
       </c>
       <c r="J429" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>24.08</v>
-      </c>
-      <c r="M429">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P429" s="8">
         <v>46155</v>
@@ -24972,10 +24984,10 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B430" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C430" t="s">
         <v>973</v>
@@ -24987,19 +24999,28 @@
         <v>79</v>
       </c>
       <c r="F430" t="s">
-        <v>1188</v>
+        <v>59</v>
+      </c>
+      <c r="G430" t="s">
+        <v>1186</v>
       </c>
       <c r="H430" t="s">
-        <v>1189</v>
+        <v>1001</v>
+      </c>
+      <c r="I430" t="s">
+        <v>169</v>
       </c>
       <c r="J430" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="K430">
         <v>75</v>
       </c>
       <c r="L430">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M430">
+        <v>12</v>
       </c>
       <c r="P430" s="8">
         <v>46155</v>
@@ -25007,10 +25028,10 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="B431" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C431" t="s">
         <v>973</v>
@@ -25022,10 +25043,10 @@
         <v>79</v>
       </c>
       <c r="F431" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="H431" t="s">
-        <v>977</v>
+        <v>1189</v>
       </c>
       <c r="J431" t="s">
         <v>63</v>
@@ -25034,18 +25055,15 @@
         <v>75</v>
       </c>
       <c r="L431">
-        <v>7.05</v>
-      </c>
-      <c r="M431">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P431" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A432">
-        <v>27100522</v>
+      <c r="A432" t="s">
+        <v>1190</v>
       </c>
       <c r="B432" t="s">
         <v>56</v>
@@ -25060,36 +25078,33 @@
         <v>79</v>
       </c>
       <c r="F432" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G432" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="H432" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I432" t="s">
-        <v>784</v>
-      </c>
-      <c r="J432">
-        <v>2022</v>
+        <v>977</v>
+      </c>
+      <c r="J432" t="s">
+        <v>63</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M432">
+        <v>30</v>
       </c>
       <c r="P432" s="8">
-        <v>46178</v>
-      </c>
-    </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>1195</v>
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A433">
+        <v>27100522</v>
       </c>
       <c r="B433" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C433" t="s">
         <v>973</v>
@@ -25101,33 +25116,36 @@
         <v>79</v>
       </c>
       <c r="F433" t="s">
-        <v>59</v>
+        <v>1192</v>
       </c>
       <c r="G433" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="H433" t="s">
-        <v>1197</v>
-      </c>
-      <c r="J433" t="s">
-        <v>1198</v>
+        <v>1194</v>
+      </c>
+      <c r="I433" t="s">
+        <v>784</v>
+      </c>
+      <c r="J433">
+        <v>2022</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P433" s="8">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="B434" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C434" t="s">
         <v>973</v>
@@ -25139,33 +25157,33 @@
         <v>79</v>
       </c>
       <c r="F434" t="s">
-        <v>1200</v>
+        <v>59</v>
       </c>
       <c r="G434" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="H434" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="J434" t="s">
-        <v>93</v>
+        <v>1198</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>7.35</v>
-      </c>
-      <c r="M434">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P434" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>1199</v>
+      </c>
       <c r="B435" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C435" t="s">
         <v>973</v>
@@ -25180,19 +25198,19 @@
         <v>1200</v>
       </c>
       <c r="G435" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H435" t="s">
         <v>1202</v>
       </c>
       <c r="J435" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K435">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L435">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M435">
         <v>2215</v>
@@ -25201,12 +25219,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>1204</v>
-      </c>
+    <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B436" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C436" t="s">
         <v>973</v>
@@ -25221,30 +25236,30 @@
         <v>1200</v>
       </c>
       <c r="G436" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H436" t="s">
         <v>1202</v>
       </c>
       <c r="J436" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K436">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L436">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M436">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P436" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B437" t="s">
         <v>56</v>
@@ -25262,36 +25277,33 @@
         <v>1200</v>
       </c>
       <c r="G437" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H437" t="s">
-        <v>1208</v>
-      </c>
-      <c r="I437" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="J437" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M437">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P437" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B438" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C438" t="s">
         <v>973</v>
@@ -25306,27 +25318,33 @@
         <v>1200</v>
       </c>
       <c r="G438" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="H438" t="s">
-        <v>1212</v>
+        <v>1208</v>
+      </c>
+      <c r="I438" t="s">
+        <v>1209</v>
       </c>
       <c r="J438" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K438">
         <v>75</v>
       </c>
       <c r="L438">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M438">
+        <v>205</v>
       </c>
       <c r="P438" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B439" t="s">
         <v>117</v>
@@ -25344,10 +25362,10 @@
         <v>1200</v>
       </c>
       <c r="G439" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="H439" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="J439" t="s">
         <v>93</v>
@@ -25356,21 +25374,18 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>14.6</v>
-      </c>
-      <c r="M439">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P439" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B440" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C440" t="s">
         <v>973</v>
@@ -25382,30 +25397,33 @@
         <v>79</v>
       </c>
       <c r="F440" t="s">
-        <v>1024</v>
+        <v>1200</v>
       </c>
       <c r="G440" t="s">
-        <v>159</v>
+        <v>1214</v>
       </c>
       <c r="H440" t="s">
-        <v>1025</v>
+        <v>1215</v>
       </c>
       <c r="J440" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M440">
+        <v>0</v>
       </c>
       <c r="P440" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B441" t="s">
         <v>56</v>
@@ -25417,36 +25435,33 @@
         <v>974</v>
       </c>
       <c r="E441" t="s">
-        <v>928</v>
+        <v>79</v>
       </c>
       <c r="F441" t="s">
-        <v>975</v>
+        <v>1024</v>
       </c>
       <c r="G441" t="s">
-        <v>976</v>
+        <v>159</v>
       </c>
       <c r="H441" t="s">
-        <v>977</v>
+        <v>1025</v>
       </c>
       <c r="J441" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>3.8</v>
-      </c>
-      <c r="M441">
-        <v>324</v>
+        <v>37</v>
       </c>
       <c r="P441" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B442" t="s">
         <v>56</v>
@@ -25464,10 +25479,10 @@
         <v>975</v>
       </c>
       <c r="G442" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="H442" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J442" t="s">
         <v>93</v>
@@ -25476,18 +25491,18 @@
         <v>75</v>
       </c>
       <c r="L442">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M442">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P442" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B443" t="s">
         <v>56</v>
@@ -25505,10 +25520,10 @@
         <v>975</v>
       </c>
       <c r="G443" t="s">
-        <v>1220</v>
+        <v>979</v>
       </c>
       <c r="H443" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J443" t="s">
         <v>93</v>
@@ -25517,21 +25532,21 @@
         <v>75</v>
       </c>
       <c r="L443">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M443">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P443" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B444" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C444" t="s">
         <v>973</v>
@@ -25546,33 +25561,33 @@
         <v>975</v>
       </c>
       <c r="G444" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="H444" t="s">
-        <v>1194</v>
+        <v>285</v>
       </c>
       <c r="J444" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M444">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P444" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B445" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C445" t="s">
         <v>973</v>
@@ -25587,30 +25602,30 @@
         <v>975</v>
       </c>
       <c r="G445" t="s">
-        <v>1087</v>
+        <v>1222</v>
       </c>
       <c r="H445" t="s">
-        <v>977</v>
+        <v>1194</v>
       </c>
       <c r="J445" t="s">
-        <v>576</v>
+        <v>334</v>
       </c>
       <c r="K445">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L445">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M445">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P445" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B446" t="s">
         <v>56</v>
@@ -25628,71 +25643,71 @@
         <v>975</v>
       </c>
       <c r="G446" t="s">
-        <v>1225</v>
+        <v>1087</v>
       </c>
       <c r="H446" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J446" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K446">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L446">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M446">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P446" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B447" t="s">
         <v>56</v>
       </c>
       <c r="C447" t="s">
-        <v>1227</v>
+        <v>973</v>
       </c>
       <c r="D447" t="s">
-        <v>1228</v>
+        <v>974</v>
       </c>
       <c r="E447" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F447" t="s">
-        <v>1229</v>
+        <v>975</v>
       </c>
       <c r="G447" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="H447" t="s">
-        <v>1231</v>
+        <v>980</v>
       </c>
       <c r="J447" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K447">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L447">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M447">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P447" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="B448" t="s">
         <v>56</v>
@@ -25707,13 +25722,13 @@
         <v>58</v>
       </c>
       <c r="F448" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="G448" t="s">
-        <v>108</v>
+        <v>1230</v>
       </c>
       <c r="H448" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J448" t="s">
         <v>334</v>
@@ -25722,21 +25737,18 @@
         <v>75</v>
       </c>
       <c r="L448">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M448">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P448" s="8">
         <v>46155</v>
       </c>
-      <c r="R448" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="449" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B449" t="s">
         <v>56</v>
@@ -25748,36 +25760,39 @@
         <v>1228</v>
       </c>
       <c r="E449" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F449" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="G449" t="s">
-        <v>1236</v>
+        <v>108</v>
       </c>
       <c r="H449" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="J449" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M449">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P449" s="8">
         <v>46155</v>
       </c>
-    </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R449" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="450" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B450" t="s">
         <v>56</v>
@@ -25789,36 +25804,36 @@
         <v>1228</v>
       </c>
       <c r="E450" t="s">
-        <v>79</v>
+        <v>928</v>
       </c>
       <c r="F450" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="G450" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="H450" t="s">
-        <v>1240</v>
+        <v>1231</v>
       </c>
       <c r="J450" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M450">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P450" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="B451" t="s">
         <v>56</v>
@@ -25833,33 +25848,33 @@
         <v>79</v>
       </c>
       <c r="F451" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="G451" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="H451" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="J451" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M451">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P451" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B452" t="s">
         <v>56</v>
@@ -25874,33 +25889,33 @@
         <v>79</v>
       </c>
       <c r="F452" t="s">
-        <v>1233</v>
+        <v>1242</v>
       </c>
       <c r="G452" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="H452" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="J452" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M452">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P452" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B453" t="s">
         <v>56</v>
@@ -25915,30 +25930,33 @@
         <v>79</v>
       </c>
       <c r="F453" t="s">
-        <v>1248</v>
+        <v>1233</v>
+      </c>
+      <c r="G453" t="s">
+        <v>1246</v>
       </c>
       <c r="H453" t="s">
-        <v>1249</v>
+        <v>1231</v>
       </c>
       <c r="J453" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M453">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P453" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B454" t="s">
         <v>56</v>
@@ -25953,36 +25971,30 @@
         <v>79</v>
       </c>
       <c r="F454" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G454" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H454" t="s">
-        <v>1253</v>
-      </c>
-      <c r="I454" t="s">
-        <v>62</v>
+        <v>1249</v>
       </c>
       <c r="J454" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M454">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P454" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="B455" t="s">
         <v>56</v>
@@ -25991,19 +26003,22 @@
         <v>1227</v>
       </c>
       <c r="D455" t="s">
-        <v>1255</v>
+        <v>1228</v>
       </c>
       <c r="E455" t="s">
         <v>79</v>
       </c>
       <c r="F455" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="G455" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="H455" t="s">
-        <v>1258</v>
+        <v>1253</v>
+      </c>
+      <c r="I455" t="s">
+        <v>62</v>
       </c>
       <c r="J455" t="s">
         <v>63</v>
@@ -26012,15 +26027,18 @@
         <v>75</v>
       </c>
       <c r="L455">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M455">
+        <v>318</v>
       </c>
       <c r="P455" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="B456" t="s">
         <v>56</v>
@@ -26038,33 +26056,30 @@
         <v>1256</v>
       </c>
       <c r="G456" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="H456" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="J456" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>6.1</v>
-      </c>
-      <c r="M456">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P456" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="B457" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C457" t="s">
         <v>1227</v>
@@ -26079,30 +26094,30 @@
         <v>1256</v>
       </c>
       <c r="G457" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="H457" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J457" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>13.2</v>
+        <v>6.1</v>
       </c>
       <c r="M457">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="P457" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B458" t="s">
         <v>117</v>
@@ -26120,19 +26135,19 @@
         <v>1256</v>
       </c>
       <c r="G458" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="H458" t="s">
         <v>1264</v>
       </c>
       <c r="J458" t="s">
-        <v>1198</v>
+        <v>104</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -26141,9 +26156,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B459" t="s">
         <v>117</v>
@@ -26158,22 +26173,22 @@
         <v>79</v>
       </c>
       <c r="F459" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="G459" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="H459" t="s">
         <v>1264</v>
       </c>
       <c r="J459" t="s">
-        <v>63</v>
+        <v>1198</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M459">
         <v>0</v>
@@ -26182,50 +26197,50 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B460" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C460" t="s">
         <v>1227</v>
       </c>
       <c r="D460" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="E460" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F460" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G460" t="s">
-        <v>732</v>
+        <v>1269</v>
       </c>
       <c r="H460" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="J460" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M460">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P460" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B461" t="s">
         <v>56</v>
@@ -26234,39 +26249,39 @@
         <v>1227</v>
       </c>
       <c r="D461" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="E461" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F461" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G461" t="s">
-        <v>1276</v>
+        <v>732</v>
       </c>
       <c r="H461" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="J461" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K461">
         <v>75</v>
       </c>
       <c r="L461">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M461">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P461" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="B462" t="s">
         <v>56</v>
@@ -26284,7 +26299,7 @@
         <v>1275</v>
       </c>
       <c r="G462" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H462" t="s">
         <v>1277</v>
@@ -26296,18 +26311,18 @@
         <v>75</v>
       </c>
       <c r="L462">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M462">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P462" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B463" t="s">
         <v>56</v>
@@ -26325,7 +26340,7 @@
         <v>1275</v>
       </c>
       <c r="G463" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="H463" t="s">
         <v>1277</v>
@@ -26340,15 +26355,15 @@
         <v>8.6</v>
       </c>
       <c r="M463">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P463" s="8">
         <v>46155</v>
       </c>
     </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B464" t="s">
         <v>56</v>
@@ -26366,13 +26381,13 @@
         <v>1275</v>
       </c>
       <c r="G464" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="H464" t="s">
         <v>1277</v>
       </c>
       <c r="J464" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="K464">
         <v>75</v>
@@ -26381,7 +26396,7 @@
         <v>8.6</v>
       </c>
       <c r="M464">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P464" s="8">
         <v>46155</v>
@@ -26389,7 +26404,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B465" t="s">
         <v>56</v>
@@ -26407,7 +26422,7 @@
         <v>1275</v>
       </c>
       <c r="G465" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="H465" t="s">
         <v>1277</v>
@@ -26422,7 +26437,7 @@
         <v>8.6</v>
       </c>
       <c r="M465">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P465" s="8">
         <v>46155</v>
@@ -26430,7 +26445,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B466" t="s">
         <v>56</v>
@@ -26448,22 +26463,22 @@
         <v>1275</v>
       </c>
       <c r="G466" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="H466" t="s">
         <v>1277</v>
       </c>
       <c r="J466" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M466">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P466" s="8">
         <v>46155</v>
@@ -26471,7 +26486,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B467" t="s">
         <v>56</v>
@@ -26489,22 +26504,22 @@
         <v>1275</v>
       </c>
       <c r="G467" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="H467" t="s">
         <v>1277</v>
       </c>
       <c r="J467" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M467">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P467" s="8">
         <v>46155</v>
@@ -26512,7 +26527,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B468" t="s">
         <v>56</v>
@@ -26530,7 +26545,7 @@
         <v>1275</v>
       </c>
       <c r="G468" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="H468" t="s">
         <v>1277</v>
@@ -26545,7 +26560,7 @@
         <v>13</v>
       </c>
       <c r="M468">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P468" s="8">
         <v>46155</v>
@@ -26553,7 +26568,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B469" t="s">
         <v>56</v>
@@ -26571,7 +26586,7 @@
         <v>1275</v>
       </c>
       <c r="G469" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="H469" t="s">
         <v>1277</v>
@@ -26583,7 +26598,7 @@
         <v>75</v>
       </c>
       <c r="L469">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M469">
         <v>36</v>
@@ -26594,7 +26609,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B470" t="s">
         <v>56</v>
@@ -26606,28 +26621,28 @@
         <v>1274</v>
       </c>
       <c r="E470" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F470" t="s">
         <v>1275</v>
       </c>
       <c r="G470" t="s">
-        <v>1037</v>
+        <v>1292</v>
       </c>
       <c r="H470" t="s">
         <v>1277</v>
       </c>
       <c r="J470" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M470">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P470" s="8">
         <v>46155</v>
@@ -26635,40 +26650,40 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B471" t="s">
         <v>56</v>
       </c>
       <c r="C471" t="s">
-        <v>1295</v>
+        <v>1227</v>
       </c>
       <c r="D471" t="s">
-        <v>1228</v>
+        <v>1274</v>
       </c>
       <c r="E471" t="s">
-        <v>1295</v>
+        <v>58</v>
       </c>
       <c r="F471" t="s">
-        <v>1296</v>
+        <v>1275</v>
       </c>
       <c r="G471" t="s">
-        <v>1297</v>
+        <v>1037</v>
       </c>
       <c r="H471" t="s">
-        <v>1231</v>
+        <v>1277</v>
       </c>
       <c r="J471" t="s">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M471">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P471" s="8">
         <v>46155</v>
@@ -26676,7 +26691,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B472" t="s">
         <v>56</v>
@@ -26684,17 +26699,20 @@
       <c r="C472" t="s">
         <v>1295</v>
       </c>
+      <c r="D472" t="s">
+        <v>1228</v>
+      </c>
       <c r="E472" t="s">
         <v>1295</v>
       </c>
       <c r="F472" t="s">
-        <v>59</v>
+        <v>1296</v>
       </c>
       <c r="G472" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="H472" t="s">
-        <v>996</v>
+        <v>1231</v>
       </c>
       <c r="J472" t="s">
         <v>576</v>
@@ -26705,13 +26723,16 @@
       <c r="L472">
         <v>6.2</v>
       </c>
+      <c r="M472">
+        <v>4411</v>
+      </c>
       <c r="P472" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B473" t="s">
         <v>56</v>
@@ -26726,10 +26747,10 @@
         <v>59</v>
       </c>
       <c r="G473" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="H473" t="s">
-        <v>1302</v>
+        <v>996</v>
       </c>
       <c r="J473" t="s">
         <v>576</v>
@@ -26738,7 +26759,7 @@
         <v>75</v>
       </c>
       <c r="L473">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P473" s="8">
         <v>46155</v>
@@ -26746,7 +26767,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B474" t="s">
         <v>56</v>
@@ -26758,25 +26779,22 @@
         <v>1295</v>
       </c>
       <c r="F474" t="s">
-        <v>1304</v>
+        <v>59</v>
       </c>
       <c r="G474" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="H474" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="J474" t="s">
         <v>576</v>
       </c>
       <c r="K474">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L474">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M474">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P474" s="8">
         <v>46155</v>
@@ -26784,7 +26802,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="B475" t="s">
         <v>56</v>
@@ -26799,22 +26817,22 @@
         <v>1304</v>
       </c>
       <c r="G475" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="H475" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="J475" t="s">
         <v>576</v>
       </c>
       <c r="K475">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L475">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M475">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P475" s="8">
         <v>46155</v>
@@ -26822,7 +26840,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B476" t="s">
         <v>56</v>
@@ -26837,10 +26855,10 @@
         <v>1304</v>
       </c>
       <c r="G476" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="H476" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="J476" t="s">
         <v>576</v>
@@ -26849,10 +26867,10 @@
         <v>75</v>
       </c>
       <c r="L476">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M476">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P476" s="8">
         <v>46155</v>
@@ -26860,10 +26878,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B477" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C477" t="s">
         <v>1295</v>
@@ -26875,10 +26893,10 @@
         <v>1304</v>
       </c>
       <c r="G477" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="H477" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="J477" t="s">
         <v>576</v>
@@ -26887,7 +26905,10 @@
         <v>75</v>
       </c>
       <c r="L477">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M477">
+        <v>418</v>
       </c>
       <c r="P477" s="8">
         <v>46155</v>
@@ -26895,10 +26916,10 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B478" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C478" t="s">
         <v>1295</v>
@@ -26910,10 +26931,10 @@
         <v>1304</v>
       </c>
       <c r="G478" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="H478" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="J478" t="s">
         <v>576</v>
@@ -26922,10 +26943,7 @@
         <v>75</v>
       </c>
       <c r="L478">
-        <v>25.7</v>
-      </c>
-      <c r="M478">
-        <v>34</v>
+        <v>23.9</v>
       </c>
       <c r="P478" s="8">
         <v>46155</v>
@@ -26933,7 +26951,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B479" t="s">
         <v>56</v>
@@ -26948,10 +26966,10 @@
         <v>1304</v>
       </c>
       <c r="G479" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="H479" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="J479" t="s">
         <v>576</v>
@@ -26960,10 +26978,10 @@
         <v>75</v>
       </c>
       <c r="L479">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="M479">
-        <v>995</v>
+        <v>34</v>
       </c>
       <c r="P479" s="8">
         <v>46155</v>
@@ -26971,7 +26989,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B480" t="s">
         <v>56</v>
@@ -26986,10 +27004,10 @@
         <v>1304</v>
       </c>
       <c r="G480" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="H480" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J480" t="s">
         <v>576</v>
@@ -26998,10 +27016,10 @@
         <v>75</v>
       </c>
       <c r="L480">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M480">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P480" s="8">
         <v>46155</v>
@@ -27009,7 +27027,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B481" t="s">
         <v>56</v>
@@ -27024,10 +27042,10 @@
         <v>1304</v>
       </c>
       <c r="G481" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="H481" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="J481" t="s">
         <v>576</v>
@@ -27036,10 +27054,10 @@
         <v>75</v>
       </c>
       <c r="L481">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M481">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P481" s="8">
         <v>46155</v>
@@ -27047,7 +27065,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B482" t="s">
         <v>56</v>
@@ -27062,10 +27080,10 @@
         <v>1304</v>
       </c>
       <c r="G482" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="H482" t="s">
-        <v>1321</v>
+        <v>1306</v>
       </c>
       <c r="J482" t="s">
         <v>576</v>
@@ -27074,10 +27092,10 @@
         <v>75</v>
       </c>
       <c r="L482">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M482">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P482" s="8">
         <v>46155</v>
@@ -27085,7 +27103,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B483" t="s">
         <v>56</v>
@@ -27100,10 +27118,10 @@
         <v>1304</v>
       </c>
       <c r="G483" t="s">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="H483" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J483" t="s">
         <v>576</v>
@@ -27112,10 +27130,10 @@
         <v>75</v>
       </c>
       <c r="L483">
-        <v>29.8</v>
+        <v>29.35</v>
       </c>
       <c r="M483">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P483" s="8">
         <v>46155</v>
@@ -27123,7 +27141,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B484" t="s">
         <v>56</v>
@@ -27138,10 +27156,10 @@
         <v>1304</v>
       </c>
       <c r="G484" t="s">
-        <v>1331</v>
+        <v>923</v>
       </c>
       <c r="H484" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="J484" t="s">
         <v>576</v>
@@ -27150,10 +27168,10 @@
         <v>75</v>
       </c>
       <c r="L484">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="M484">
-        <v>777</v>
+        <v>417</v>
       </c>
       <c r="P484" s="8">
         <v>46155</v>
@@ -27161,7 +27179,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B485" t="s">
         <v>56</v>
@@ -27176,10 +27194,10 @@
         <v>1304</v>
       </c>
       <c r="G485" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="H485" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="J485" t="s">
         <v>576</v>
@@ -27188,10 +27206,10 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M485">
-        <v>428</v>
+        <v>777</v>
       </c>
       <c r="P485" s="8">
         <v>46155</v>
@@ -27199,7 +27217,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="B486" t="s">
         <v>56</v>
@@ -27214,10 +27232,10 @@
         <v>1304</v>
       </c>
       <c r="G486" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="H486" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="J486" t="s">
         <v>576</v>
@@ -27226,10 +27244,10 @@
         <v>75</v>
       </c>
       <c r="L486">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M486">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P486" s="8">
         <v>46155</v>
@@ -27237,7 +27255,7 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B487" t="s">
         <v>56</v>
@@ -27252,10 +27270,10 @@
         <v>1304</v>
       </c>
       <c r="G487" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H487" t="s">
-        <v>1321</v>
+        <v>1338</v>
       </c>
       <c r="J487" t="s">
         <v>576</v>
@@ -27264,10 +27282,10 @@
         <v>75</v>
       </c>
       <c r="L487">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M487">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P487" s="8">
         <v>46155</v>
@@ -27275,7 +27293,7 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B488" t="s">
         <v>56</v>
@@ -27290,10 +27308,10 @@
         <v>1304</v>
       </c>
       <c r="G488" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="H488" t="s">
-        <v>1343</v>
+        <v>1321</v>
       </c>
       <c r="J488" t="s">
         <v>576</v>
@@ -27302,10 +27320,10 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M488">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P488" s="8">
         <v>46155</v>
@@ -27313,10 +27331,10 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B489" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C489" t="s">
         <v>1295</v>
@@ -27328,10 +27346,10 @@
         <v>1304</v>
       </c>
       <c r="G489" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="H489" t="s">
-        <v>1306</v>
+        <v>1343</v>
       </c>
       <c r="J489" t="s">
         <v>576</v>
@@ -27340,7 +27358,7 @@
         <v>75</v>
       </c>
       <c r="L489">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M489">
         <v>0</v>
@@ -27351,10 +27369,10 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B490" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C490" t="s">
         <v>1295</v>
@@ -27366,10 +27384,10 @@
         <v>1304</v>
       </c>
       <c r="G490" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="H490" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="J490" t="s">
         <v>576</v>
@@ -27378,10 +27396,10 @@
         <v>75</v>
       </c>
       <c r="L490">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M490">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P490" s="8">
         <v>46155</v>
@@ -27389,7 +27407,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B491" t="s">
         <v>56</v>
@@ -27404,7 +27422,7 @@
         <v>1304</v>
       </c>
       <c r="G491" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="H491" t="s">
         <v>1324</v>
@@ -27416,10 +27434,10 @@
         <v>75</v>
       </c>
       <c r="L491">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M491">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P491" s="8">
         <v>46155</v>
@@ -27427,7 +27445,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B492" t="s">
         <v>56</v>
@@ -27442,10 +27460,10 @@
         <v>1304</v>
       </c>
       <c r="G492" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="H492" t="s">
-        <v>1352</v>
+        <v>1324</v>
       </c>
       <c r="J492" t="s">
         <v>576</v>
@@ -27454,10 +27472,10 @@
         <v>75</v>
       </c>
       <c r="L492">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M492">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P492" s="8">
         <v>46155</v>
@@ -27465,7 +27483,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B493" t="s">
         <v>56</v>
@@ -27480,10 +27498,10 @@
         <v>1304</v>
       </c>
       <c r="G493" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H493" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="J493" t="s">
         <v>576</v>
@@ -27503,7 +27521,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B494" t="s">
         <v>56</v>
@@ -27518,22 +27536,22 @@
         <v>1304</v>
       </c>
       <c r="G494" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="H494" t="s">
-        <v>1306</v>
+        <v>1355</v>
       </c>
       <c r="J494" t="s">
-        <v>161</v>
+        <v>576</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M494">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P494" s="8">
         <v>46155</v>
@@ -27541,7 +27559,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B495" t="s">
         <v>56</v>
@@ -27556,22 +27574,22 @@
         <v>1304</v>
       </c>
       <c r="G495" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="H495" t="s">
-        <v>1338</v>
-      </c>
-      <c r="J495">
-        <v>2017</v>
+        <v>1306</v>
+      </c>
+      <c r="J495" t="s">
+        <v>161</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M495">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P495" s="8">
         <v>46155</v>
@@ -27579,7 +27597,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B496" t="s">
         <v>56</v>
@@ -27587,9 +27605,6 @@
       <c r="C496" t="s">
         <v>1295</v>
       </c>
-      <c r="D496" t="s">
-        <v>1003</v>
-      </c>
       <c r="E496" t="s">
         <v>1295</v>
       </c>
@@ -27597,22 +27612,22 @@
         <v>1304</v>
       </c>
       <c r="G496" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="H496" t="s">
-        <v>1324</v>
-      </c>
-      <c r="J496" t="s">
-        <v>576</v>
+        <v>1338</v>
+      </c>
+      <c r="J496">
+        <v>2017</v>
       </c>
       <c r="K496">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L496">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M496">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P496" s="8">
         <v>46155</v>
@@ -27620,7 +27635,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B497" t="s">
         <v>56</v>
@@ -27638,7 +27653,7 @@
         <v>1304</v>
       </c>
       <c r="G497" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="H497" t="s">
         <v>1324</v>
@@ -27650,10 +27665,10 @@
         <v>150</v>
       </c>
       <c r="L497">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M497">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P497" s="8">
         <v>46155</v>
@@ -27661,10 +27676,10 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B498" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C498" t="s">
         <v>1295</v>
@@ -27679,10 +27694,10 @@
         <v>1304</v>
       </c>
       <c r="G498" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="H498" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="J498" t="s">
         <v>576</v>
@@ -27691,10 +27706,10 @@
         <v>150</v>
       </c>
       <c r="L498">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M498">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P498" s="8">
         <v>46155</v>
@@ -27702,7 +27717,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B499" t="s">
         <v>117</v>
@@ -27720,7 +27735,7 @@
         <v>1304</v>
       </c>
       <c r="G499" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H499" t="s">
         <v>1306</v>
@@ -27729,10 +27744,10 @@
         <v>576</v>
       </c>
       <c r="K499">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L499">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M499">
         <v>5</v>
@@ -27743,7 +27758,7 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B500" t="s">
         <v>117</v>
@@ -27761,7 +27776,7 @@
         <v>1304</v>
       </c>
       <c r="G500" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="H500" t="s">
         <v>1306</v>
@@ -27770,10 +27785,10 @@
         <v>576</v>
       </c>
       <c r="K500">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L500">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M500">
         <v>5</v>
@@ -27784,37 +27799,40 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B501" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C501" t="s">
-        <v>1371</v>
+        <v>1295</v>
+      </c>
+      <c r="D501" t="s">
+        <v>1003</v>
       </c>
       <c r="E501" t="s">
-        <v>1371</v>
+        <v>1295</v>
       </c>
       <c r="F501" t="s">
-        <v>1372</v>
+        <v>1304</v>
       </c>
       <c r="G501" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="H501" t="s">
-        <v>1374</v>
+        <v>1306</v>
       </c>
       <c r="J501" t="s">
-        <v>1375</v>
+        <v>576</v>
       </c>
       <c r="K501">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L501">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M501">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P501" s="8">
         <v>46155</v>
@@ -27822,7 +27840,7 @@
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="B502" t="s">
         <v>56</v>
@@ -27837,7 +27855,7 @@
         <v>1372</v>
       </c>
       <c r="G502" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="H502" t="s">
         <v>1374</v>
@@ -27849,7 +27867,7 @@
         <v>70</v>
       </c>
       <c r="L502">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M502">
         <v>6</v>
@@ -27860,7 +27878,7 @@
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B503" t="s">
         <v>56</v>
@@ -27875,19 +27893,22 @@
         <v>1372</v>
       </c>
       <c r="G503" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="H503" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="J503" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="K503">
         <v>70</v>
       </c>
       <c r="L503">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M503">
+        <v>6</v>
       </c>
       <c r="P503" s="8">
         <v>46155</v>
@@ -27895,7 +27916,7 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B504" t="s">
         <v>56</v>
@@ -27910,19 +27931,19 @@
         <v>1372</v>
       </c>
       <c r="G504" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="H504" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="J504" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="K504">
         <v>70</v>
       </c>
       <c r="L504">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P504" s="8">
         <v>46155</v>
@@ -27930,7 +27951,7 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B505" t="s">
         <v>56</v>
@@ -27945,19 +27966,19 @@
         <v>1372</v>
       </c>
       <c r="G505" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="H505" t="s">
         <v>1384</v>
       </c>
       <c r="J505" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="K505">
         <v>70</v>
       </c>
       <c r="L505">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P505" s="8">
         <v>46155</v>
@@ -27965,7 +27986,7 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B506" t="s">
         <v>56</v>
@@ -27980,19 +28001,19 @@
         <v>1372</v>
       </c>
       <c r="G506" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="H506" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="J506" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="K506">
         <v>70</v>
       </c>
       <c r="L506">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P506" s="8">
         <v>46155</v>
@@ -28000,7 +28021,7 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B507" t="s">
         <v>56</v>
@@ -28008,9 +28029,6 @@
       <c r="C507" t="s">
         <v>1371</v>
       </c>
-      <c r="D507" t="s">
-        <v>1003</v>
-      </c>
       <c r="E507" t="s">
         <v>1371</v>
       </c>
@@ -28018,19 +28036,19 @@
         <v>1372</v>
       </c>
       <c r="G507" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="H507" t="s">
         <v>1391</v>
       </c>
       <c r="J507" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="K507">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L507">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P507" s="8">
         <v>46155</v>
@@ -28038,7 +28056,7 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B508" t="s">
         <v>56</v>
@@ -28046,26 +28064,29 @@
       <c r="C508" t="s">
         <v>1371</v>
       </c>
+      <c r="D508" t="s">
+        <v>1003</v>
+      </c>
       <c r="E508" t="s">
         <v>1371</v>
       </c>
       <c r="F508" t="s">
-        <v>1397</v>
+        <v>1372</v>
+      </c>
+      <c r="G508" t="s">
+        <v>1394</v>
       </c>
       <c r="H508" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="J508" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="K508">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L508">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M508">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P508" s="8">
         <v>46155</v>
@@ -28073,10 +28094,10 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B509" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C509" t="s">
         <v>1371</v>
@@ -28087,17 +28108,17 @@
       <c r="F509" t="s">
         <v>1397</v>
       </c>
-      <c r="G509" t="s">
-        <v>1401</v>
-      </c>
       <c r="H509" t="s">
-        <v>1402</v>
+        <v>1398</v>
+      </c>
+      <c r="J509" t="s">
+        <v>1399</v>
       </c>
       <c r="K509">
         <v>70</v>
       </c>
       <c r="L509">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M509">
         <v>45</v>
@@ -28108,10 +28129,10 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B510" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C510" t="s">
         <v>1371</v>
@@ -28123,22 +28144,19 @@
         <v>1397</v>
       </c>
       <c r="G510" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="H510" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J510" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="K510">
         <v>70</v>
       </c>
       <c r="L510">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M510">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P510" s="8">
         <v>46155</v>
@@ -28146,7 +28164,7 @@
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B511" t="s">
         <v>56</v>
@@ -28161,22 +28179,22 @@
         <v>1397</v>
       </c>
       <c r="G511" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="H511" t="s">
-        <v>1408</v>
+        <v>1001</v>
       </c>
       <c r="J511" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="K511">
         <v>70</v>
       </c>
       <c r="L511">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M511">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P511" s="8">
         <v>46155</v>
@@ -28184,7 +28202,7 @@
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B512" t="s">
         <v>56</v>
@@ -28196,25 +28214,25 @@
         <v>1371</v>
       </c>
       <c r="F512" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
       <c r="G512" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="H512" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="J512" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="K512">
         <v>70</v>
       </c>
       <c r="L512">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M512">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P512" s="8">
         <v>46155</v>
@@ -28222,7 +28240,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="B513" t="s">
         <v>56</v>
@@ -28237,7 +28255,7 @@
         <v>1411</v>
       </c>
       <c r="G513" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="H513" t="s">
         <v>1413</v>
@@ -28249,17 +28267,55 @@
         <v>70</v>
       </c>
       <c r="L513">
+        <v>36.5</v>
+      </c>
+      <c r="M513">
+        <v>7</v>
+      </c>
+      <c r="P513" s="8">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="514" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A514" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B514" t="s">
+        <v>56</v>
+      </c>
+      <c r="C514" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E514" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F514" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G514" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H514" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J514" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K514">
+        <v>70</v>
+      </c>
+      <c r="L514">
         <v>40.5</v>
       </c>
-      <c r="M513">
+      <c r="M514">
         <v>5</v>
       </c>
-      <c r="P513" s="8">
+      <c r="P514" s="8">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R513" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R514" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8260D4F5-4CF0-D949-85F6-A87FE5D785CD}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="13_ncr:1_{641ED796-E10E-4877-96BF-4A71D8601ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3610101B-DF5C-5F4B-A7A2-FD8E5ED1980A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$518</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10074" uniqueCount="2287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10106" uniqueCount="2291">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -6906,6 +6906,18 @@
   </si>
   <si>
     <t>E Signurine</t>
+  </si>
+  <si>
+    <t>Les Marottes d'Anaïs</t>
+  </si>
+  <si>
+    <t>E Prove rouge</t>
+  </si>
+  <si>
+    <t>E Prove blanc</t>
+  </si>
+  <si>
+    <t>E Prove rosé</t>
   </si>
 </sst>
 </file>
@@ -7670,7 +7682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R514"/>
+  <dimension ref="A1:R518"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -21042,13 +21054,13 @@
         <v>762</v>
       </c>
       <c r="J334">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K334">
         <v>75</v>
       </c>
       <c r="L334">
-        <v>19.8</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="M334">
         <v>24</v>
@@ -21058,155 +21070,176 @@
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A335" t="s">
-        <v>933</v>
+      <c r="A335">
+        <v>72400324</v>
       </c>
       <c r="B335" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C335" t="s">
         <v>910</v>
       </c>
+      <c r="D335" t="s">
+        <v>911</v>
+      </c>
       <c r="E335" t="s">
-        <v>928</v>
+        <v>79</v>
       </c>
       <c r="F335" t="s">
-        <v>934</v>
+        <v>2283</v>
+      </c>
+      <c r="G335" t="s">
+        <v>2287</v>
       </c>
       <c r="H335" t="s">
-        <v>935</v>
-      </c>
-      <c r="J335" t="s">
-        <v>93</v>
+        <v>2284</v>
+      </c>
+      <c r="I335" t="s">
+        <v>762</v>
+      </c>
+      <c r="J335">
+        <v>2024</v>
       </c>
       <c r="K335">
         <v>75</v>
       </c>
       <c r="L335">
-        <v>6.1</v>
+        <v>14.9</v>
       </c>
       <c r="M335">
-        <v>324</v>
+        <v>24</v>
       </c>
       <c r="P335" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A336" t="s">
-        <v>936</v>
+      <c r="A336">
+        <v>72400424</v>
       </c>
       <c r="B336" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C336" t="s">
         <v>910</v>
       </c>
+      <c r="D336" t="s">
+        <v>911</v>
+      </c>
       <c r="E336" t="s">
-        <v>928</v>
+        <v>79</v>
       </c>
       <c r="F336" t="s">
-        <v>937</v>
+        <v>2283</v>
       </c>
       <c r="G336" t="s">
-        <v>938</v>
+        <v>2288</v>
       </c>
       <c r="H336" t="s">
-        <v>939</v>
-      </c>
-      <c r="J336" t="s">
-        <v>93</v>
+        <v>2284</v>
+      </c>
+      <c r="I336" t="s">
+        <v>762</v>
+      </c>
+      <c r="J336">
+        <v>2024</v>
       </c>
       <c r="K336">
         <v>75</v>
       </c>
       <c r="L336">
-        <v>6.4</v>
+        <v>13.9</v>
       </c>
       <c r="M336">
-        <v>483</v>
+        <v>24</v>
       </c>
       <c r="P336" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="337" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A337" t="s">
-        <v>940</v>
+      <c r="A337">
+        <v>72400524</v>
       </c>
       <c r="B337" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C337" t="s">
         <v>910</v>
       </c>
+      <c r="D337" t="s">
+        <v>911</v>
+      </c>
       <c r="E337" t="s">
-        <v>928</v>
+        <v>58</v>
       </c>
       <c r="F337" t="s">
-        <v>934</v>
+        <v>2283</v>
       </c>
       <c r="G337" t="s">
-        <v>941</v>
+        <v>2289</v>
       </c>
       <c r="H337" t="s">
-        <v>942</v>
-      </c>
-      <c r="J337" t="s">
-        <v>334</v>
+        <v>2284</v>
+      </c>
+      <c r="I337" t="s">
+        <v>762</v>
+      </c>
+      <c r="J337">
+        <v>2024</v>
       </c>
       <c r="K337">
         <v>75</v>
       </c>
       <c r="L337">
-        <v>6.6</v>
+        <v>13.9</v>
       </c>
       <c r="M337">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P337" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="338" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A338" t="s">
-        <v>943</v>
+      <c r="A338">
+        <v>72400625</v>
       </c>
       <c r="B338" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C338" t="s">
         <v>910</v>
       </c>
       <c r="D338" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="E338" t="s">
         <v>928</v>
       </c>
       <c r="F338" t="s">
-        <v>944</v>
+        <v>2283</v>
       </c>
       <c r="G338" t="s">
-        <v>945</v>
+        <v>2290</v>
       </c>
       <c r="H338" t="s">
-        <v>946</v>
+        <v>2284</v>
       </c>
       <c r="I338" t="s">
-        <v>62</v>
-      </c>
-      <c r="J338" t="s">
-        <v>93</v>
+        <v>762</v>
+      </c>
+      <c r="J338">
+        <v>2025</v>
       </c>
       <c r="K338">
         <v>75</v>
       </c>
       <c r="L338">
-        <v>6.45</v>
+        <v>13.9</v>
       </c>
       <c r="M338">
-        <v>501</v>
+        <v>24</v>
       </c>
       <c r="P338" s="8">
         <v>46155</v>
@@ -21214,7 +21247,7 @@
     </row>
     <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="B339" t="s">
         <v>56</v>
@@ -21222,23 +21255,14 @@
       <c r="C339" t="s">
         <v>910</v>
       </c>
-      <c r="D339" t="s">
-        <v>917</v>
-      </c>
       <c r="E339" t="s">
         <v>928</v>
       </c>
       <c r="F339" t="s">
-        <v>944</v>
-      </c>
-      <c r="G339" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="H339" t="s">
-        <v>946</v>
-      </c>
-      <c r="I339" t="s">
-        <v>62</v>
+        <v>935</v>
       </c>
       <c r="J339" t="s">
         <v>93</v>
@@ -21247,10 +21271,10 @@
         <v>75</v>
       </c>
       <c r="L339">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="M339">
-        <v>741</v>
+        <v>324</v>
       </c>
       <c r="P339" s="8">
         <v>46155</v>
@@ -21258,7 +21282,7 @@
     </row>
     <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="B340" t="s">
         <v>56</v>
@@ -21266,20 +21290,17 @@
       <c r="C340" t="s">
         <v>910</v>
       </c>
-      <c r="D340" t="s">
-        <v>917</v>
-      </c>
       <c r="E340" t="s">
         <v>928</v>
       </c>
       <c r="F340" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="G340" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="H340" t="s">
-        <v>285</v>
+        <v>939</v>
       </c>
       <c r="J340" t="s">
         <v>93</v>
@@ -21288,10 +21309,10 @@
         <v>75</v>
       </c>
       <c r="L340">
-        <v>5.65</v>
+        <v>6.4</v>
       </c>
       <c r="M340">
-        <v>648</v>
+        <v>483</v>
       </c>
       <c r="P340" s="8">
         <v>46155</v>
@@ -21299,7 +21320,7 @@
     </row>
     <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="B341" t="s">
         <v>56</v>
@@ -21307,23 +21328,20 @@
       <c r="C341" t="s">
         <v>910</v>
       </c>
-      <c r="D341" t="s">
-        <v>917</v>
-      </c>
       <c r="E341" t="s">
         <v>928</v>
       </c>
       <c r="F341" t="s">
-        <v>950</v>
+        <v>934</v>
+      </c>
+      <c r="G341" t="s">
+        <v>941</v>
       </c>
       <c r="H341" t="s">
-        <v>953</v>
-      </c>
-      <c r="I341" t="s">
-        <v>62</v>
+        <v>942</v>
       </c>
       <c r="J341" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K341">
         <v>75</v>
@@ -21332,7 +21350,7 @@
         <v>6.6</v>
       </c>
       <c r="M341">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="P341" s="8">
         <v>46155</v>
@@ -21340,10 +21358,10 @@
     </row>
     <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="B342" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C342" t="s">
         <v>910</v>
@@ -21355,28 +21373,28 @@
         <v>928</v>
       </c>
       <c r="F342" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="G342" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="H342" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="I342" t="s">
         <v>62</v>
       </c>
       <c r="J342" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K342">
         <v>75</v>
       </c>
       <c r="L342">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="M342">
-        <v>66</v>
+        <v>501</v>
       </c>
       <c r="P342" s="8">
         <v>46155</v>
@@ -21384,7 +21402,7 @@
     </row>
     <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="B343" t="s">
         <v>56</v>
@@ -21399,13 +21417,16 @@
         <v>928</v>
       </c>
       <c r="F343" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="G343" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="H343" t="s">
-        <v>924</v>
+        <v>946</v>
+      </c>
+      <c r="I343" t="s">
+        <v>62</v>
       </c>
       <c r="J343" t="s">
         <v>93</v>
@@ -21414,10 +21435,10 @@
         <v>75</v>
       </c>
       <c r="L343">
-        <v>9.1</v>
+        <v>6.55</v>
       </c>
       <c r="M343">
-        <v>253</v>
+        <v>741</v>
       </c>
       <c r="P343" s="8">
         <v>46155</v>
@@ -21425,7 +21446,7 @@
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="B344" t="s">
         <v>56</v>
@@ -21443,10 +21464,10 @@
         <v>950</v>
       </c>
       <c r="G344" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="H344" t="s">
-        <v>939</v>
+        <v>285</v>
       </c>
       <c r="J344" t="s">
         <v>93</v>
@@ -21455,10 +21476,10 @@
         <v>75</v>
       </c>
       <c r="L344">
-        <v>9.1</v>
+        <v>5.65</v>
       </c>
       <c r="M344">
-        <v>575</v>
+        <v>648</v>
       </c>
       <c r="P344" s="8">
         <v>46155</v>
@@ -21466,10 +21487,10 @@
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="B345" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C345" t="s">
         <v>910</v>
@@ -21483,26 +21504,23 @@
       <c r="F345" t="s">
         <v>950</v>
       </c>
-      <c r="G345" t="s">
-        <v>962</v>
-      </c>
       <c r="H345" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="I345" t="s">
         <v>62</v>
       </c>
       <c r="J345" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K345">
         <v>75</v>
       </c>
       <c r="L345">
-        <v>9.3000000000000007</v>
+        <v>6.6</v>
       </c>
       <c r="M345">
-        <v>12</v>
+        <v>574</v>
       </c>
       <c r="P345" s="8">
         <v>46155</v>
@@ -21510,10 +21528,10 @@
     </row>
     <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B346" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C346" t="s">
         <v>910</v>
@@ -21528,25 +21546,25 @@
         <v>950</v>
       </c>
       <c r="G346" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="H346" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="I346" t="s">
         <v>62</v>
       </c>
       <c r="J346" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K346">
         <v>75</v>
       </c>
       <c r="L346">
-        <v>9.9499999999999993</v>
+        <v>7.5</v>
       </c>
       <c r="M346">
-        <v>341</v>
+        <v>66</v>
       </c>
       <c r="P346" s="8">
         <v>46155</v>
@@ -21554,7 +21572,7 @@
     </row>
     <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B347" t="s">
         <v>56</v>
@@ -21571,8 +21589,11 @@
       <c r="F347" t="s">
         <v>950</v>
       </c>
+      <c r="G347" t="s">
+        <v>958</v>
+      </c>
       <c r="H347" t="s">
-        <v>967</v>
+        <v>924</v>
       </c>
       <c r="J347" t="s">
         <v>93</v>
@@ -21581,10 +21602,10 @@
         <v>75</v>
       </c>
       <c r="L347">
-        <v>9.9499999999999993</v>
+        <v>9.1</v>
       </c>
       <c r="M347">
-        <v>394</v>
+        <v>253</v>
       </c>
       <c r="P347" s="8">
         <v>46155</v>
@@ -21592,7 +21613,7 @@
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B348" t="s">
         <v>56</v>
@@ -21607,25 +21628,25 @@
         <v>928</v>
       </c>
       <c r="F348" t="s">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="G348" t="s">
-        <v>923</v>
+        <v>960</v>
       </c>
       <c r="H348" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="J348" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K348">
         <v>75</v>
       </c>
       <c r="L348">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="M348">
-        <v>281</v>
+        <v>575</v>
       </c>
       <c r="P348" s="8">
         <v>46155</v>
@@ -21633,10 +21654,10 @@
     </row>
     <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="B349" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C349" t="s">
         <v>910</v>
@@ -21650,23 +21671,26 @@
       <c r="F349" t="s">
         <v>950</v>
       </c>
+      <c r="G349" t="s">
+        <v>962</v>
+      </c>
       <c r="H349" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="I349" t="s">
         <v>62</v>
       </c>
-      <c r="J349">
-        <v>2025</v>
+      <c r="J349" t="s">
+        <v>334</v>
       </c>
       <c r="K349">
         <v>75</v>
       </c>
       <c r="L349">
-        <v>12.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M349">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="P349" s="8">
         <v>46155</v>
@@ -21674,40 +21698,43 @@
     </row>
     <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B350" t="s">
         <v>56</v>
       </c>
       <c r="C350" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D350" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E350" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F350" t="s">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G350" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="H350" t="s">
-        <v>977</v>
+        <v>965</v>
+      </c>
+      <c r="I350" t="s">
+        <v>62</v>
       </c>
       <c r="J350" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K350">
         <v>75</v>
       </c>
       <c r="L350">
-        <v>3.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M350">
-        <v>60</v>
+        <v>341</v>
       </c>
       <c r="P350" s="8">
         <v>46155</v>
@@ -21715,28 +21742,25 @@
     </row>
     <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="B351" t="s">
         <v>56</v>
       </c>
       <c r="C351" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D351" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E351" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F351" t="s">
-        <v>975</v>
-      </c>
-      <c r="G351" t="s">
-        <v>979</v>
+        <v>950</v>
       </c>
       <c r="H351" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="J351" t="s">
         <v>93</v>
@@ -21745,10 +21769,10 @@
         <v>75</v>
       </c>
       <c r="L351">
-        <v>4</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M351">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="P351" s="8">
         <v>46155</v>
@@ -21756,40 +21780,40 @@
     </row>
     <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="B352" t="s">
         <v>56</v>
       </c>
       <c r="C352" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D352" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E352" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F352" t="s">
-        <v>982</v>
+        <v>922</v>
       </c>
       <c r="G352" t="s">
-        <v>983</v>
+        <v>923</v>
       </c>
       <c r="H352" t="s">
-        <v>984</v>
+        <v>924</v>
       </c>
       <c r="J352" t="s">
-        <v>576</v>
+        <v>334</v>
       </c>
       <c r="K352">
         <v>75</v>
       </c>
       <c r="L352">
-        <v>4.8</v>
+        <v>11.8</v>
       </c>
       <c r="M352">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="P352" s="8">
         <v>46155</v>
@@ -21797,40 +21821,40 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="B353" t="s">
         <v>56</v>
       </c>
       <c r="C353" t="s">
-        <v>973</v>
+        <v>910</v>
       </c>
       <c r="D353" t="s">
-        <v>974</v>
+        <v>917</v>
       </c>
       <c r="E353" t="s">
-        <v>58</v>
+        <v>928</v>
       </c>
       <c r="F353" t="s">
-        <v>975</v>
-      </c>
-      <c r="G353" t="s">
-        <v>986</v>
+        <v>950</v>
       </c>
       <c r="H353" t="s">
-        <v>987</v>
-      </c>
-      <c r="J353" t="s">
-        <v>93</v>
+        <v>965</v>
+      </c>
+      <c r="I353" t="s">
+        <v>62</v>
+      </c>
+      <c r="J353">
+        <v>2025</v>
       </c>
       <c r="K353">
         <v>75</v>
       </c>
       <c r="L353">
-        <v>5.0999999999999996</v>
+        <v>12.3</v>
       </c>
       <c r="M353">
-        <v>693</v>
+        <v>27</v>
       </c>
       <c r="P353" s="8">
         <v>46155</v>
@@ -21838,7 +21862,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="B354" t="s">
         <v>56</v>
@@ -21856,22 +21880,22 @@
         <v>975</v>
       </c>
       <c r="G354" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="H354" t="s">
-        <v>285</v>
+        <v>977</v>
       </c>
       <c r="J354" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K354">
         <v>75</v>
       </c>
       <c r="L354">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="M354">
-        <v>363</v>
+        <v>60</v>
       </c>
       <c r="P354" s="8">
         <v>46155</v>
@@ -21879,7 +21903,7 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="B355" t="s">
         <v>56</v>
@@ -21897,10 +21921,10 @@
         <v>975</v>
       </c>
       <c r="G355" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="H355" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J355" t="s">
         <v>93</v>
@@ -21909,10 +21933,10 @@
         <v>75</v>
       </c>
       <c r="L355">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="M355">
-        <v>1425</v>
+        <v>368</v>
       </c>
       <c r="P355" s="8">
         <v>46155</v>
@@ -21920,7 +21944,7 @@
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="B356" t="s">
         <v>56</v>
@@ -21935,25 +21959,25 @@
         <v>58</v>
       </c>
       <c r="F356" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G356" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
       <c r="H356" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J356" t="s">
-        <v>334</v>
+        <v>576</v>
       </c>
       <c r="K356">
         <v>75</v>
       </c>
       <c r="L356">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="M356">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="P356" s="8">
         <v>46155</v>
@@ -21961,7 +21985,7 @@
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="B357" t="s">
         <v>56</v>
@@ -21976,25 +22000,25 @@
         <v>58</v>
       </c>
       <c r="F357" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G357" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="H357" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="J357" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K357">
         <v>75</v>
       </c>
       <c r="L357">
-        <v>5.7</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M357">
-        <v>42</v>
+        <v>693</v>
       </c>
       <c r="P357" s="8">
         <v>46155</v>
@@ -22002,7 +22026,7 @@
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="B358" t="s">
         <v>56</v>
@@ -22020,10 +22044,10 @@
         <v>975</v>
       </c>
       <c r="G358" t="s">
-        <v>108</v>
+        <v>989</v>
       </c>
       <c r="H358" t="s">
-        <v>998</v>
+        <v>285</v>
       </c>
       <c r="J358" t="s">
         <v>93</v>
@@ -22032,21 +22056,18 @@
         <v>75</v>
       </c>
       <c r="L358">
-        <v>5.7</v>
+        <v>4.25</v>
       </c>
       <c r="M358">
-        <v>165</v>
+        <v>363</v>
       </c>
       <c r="P358" s="8">
         <v>46155</v>
-      </c>
-      <c r="R358" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="B359" t="s">
         <v>56</v>
@@ -22064,22 +22085,22 @@
         <v>975</v>
       </c>
       <c r="G359" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="H359" t="s">
-        <v>1001</v>
+        <v>285</v>
       </c>
       <c r="J359" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K359">
         <v>75</v>
       </c>
       <c r="L359">
-        <v>5.85</v>
+        <v>4.05</v>
       </c>
       <c r="M359">
-        <v>3214</v>
+        <v>1425</v>
       </c>
       <c r="P359" s="8">
         <v>46155</v>
@@ -22087,16 +22108,16 @@
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="B360" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C360" t="s">
         <v>973</v>
       </c>
       <c r="D360" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E360" t="s">
         <v>58</v>
@@ -22105,22 +22126,22 @@
         <v>975</v>
       </c>
       <c r="G360" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="H360" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="J360" t="s">
         <v>334</v>
       </c>
       <c r="K360">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L360">
-        <v>12.9</v>
+        <v>5.25</v>
       </c>
       <c r="M360">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P360" s="8">
         <v>46155</v>
@@ -22128,7 +22149,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="B361" t="s">
         <v>56</v>
@@ -22143,28 +22164,25 @@
         <v>58</v>
       </c>
       <c r="F361" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G361" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="H361" t="s">
-        <v>987</v>
-      </c>
-      <c r="I361" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="J361" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K361">
         <v>75</v>
       </c>
       <c r="L361">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="M361">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P361" s="8">
         <v>46155</v>
@@ -22172,7 +22190,7 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="B362" t="s">
         <v>56</v>
@@ -22181,39 +22199,42 @@
         <v>973</v>
       </c>
       <c r="D362" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E362" t="s">
         <v>58</v>
       </c>
       <c r="F362" t="s">
-        <v>1010</v>
+        <v>975</v>
       </c>
       <c r="G362" t="s">
-        <v>1011</v>
+        <v>108</v>
       </c>
       <c r="H362" t="s">
-        <v>1012</v>
+        <v>998</v>
       </c>
       <c r="J362" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K362">
         <v>75</v>
       </c>
       <c r="L362">
-        <v>14.5</v>
+        <v>5.7</v>
       </c>
       <c r="M362">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P362" s="8">
         <v>46155</v>
+      </c>
+      <c r="R362" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
       <c r="B363" t="s">
         <v>56</v>
@@ -22228,28 +22249,25 @@
         <v>58</v>
       </c>
       <c r="F363" t="s">
-        <v>1014</v>
+        <v>975</v>
       </c>
       <c r="G363" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="H363" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I363" t="s">
-        <v>784</v>
+        <v>1001</v>
       </c>
       <c r="J363" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K363">
         <v>75</v>
       </c>
       <c r="L363">
-        <v>13.5</v>
+        <v>5.85</v>
       </c>
       <c r="M363">
-        <v>182</v>
+        <v>3214</v>
       </c>
       <c r="P363" s="8">
         <v>46155</v>
@@ -22257,16 +22275,16 @@
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="B364" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C364" t="s">
         <v>973</v>
       </c>
       <c r="D364" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="E364" t="s">
         <v>58</v>
@@ -22275,22 +22293,22 @@
         <v>975</v>
       </c>
       <c r="G364" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="H364" t="s">
-        <v>987</v>
+        <v>1001</v>
       </c>
       <c r="J364" t="s">
         <v>334</v>
       </c>
       <c r="K364">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L364">
-        <v>5.4</v>
+        <v>12.9</v>
       </c>
       <c r="M364">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="P364" s="8">
         <v>46155</v>
@@ -22298,7 +22316,7 @@
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="B365" t="s">
         <v>56</v>
@@ -22316,7 +22334,7 @@
         <v>975</v>
       </c>
       <c r="G365" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="H365" t="s">
         <v>987</v>
@@ -22334,7 +22352,7 @@
         <v>6.05</v>
       </c>
       <c r="M365">
-        <v>474</v>
+        <v>165</v>
       </c>
       <c r="P365" s="8">
         <v>46155</v>
@@ -22342,7 +22360,7 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="B366" t="s">
         <v>56</v>
@@ -22351,31 +22369,31 @@
         <v>973</v>
       </c>
       <c r="D366" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E366" t="s">
         <v>58</v>
       </c>
       <c r="F366" t="s">
-        <v>975</v>
+        <v>1010</v>
       </c>
       <c r="G366" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="H366" t="s">
-        <v>605</v>
+        <v>1012</v>
       </c>
       <c r="J366" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="K366">
         <v>75</v>
       </c>
       <c r="L366">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="M366">
-        <v>321</v>
+        <v>24</v>
       </c>
       <c r="P366" s="8">
         <v>46155</v>
@@ -22383,7 +22401,7 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="B367" t="s">
         <v>56</v>
@@ -22398,22 +22416,28 @@
         <v>58</v>
       </c>
       <c r="F367" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="G367" t="s">
-        <v>159</v>
+        <v>1015</v>
       </c>
       <c r="H367" t="s">
-        <v>1025</v>
+        <v>1016</v>
+      </c>
+      <c r="I367" t="s">
+        <v>784</v>
       </c>
       <c r="J367" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K367">
         <v>75</v>
       </c>
       <c r="L367">
-        <v>37</v>
+        <v>13.5</v>
+      </c>
+      <c r="M367">
+        <v>182</v>
       </c>
       <c r="P367" s="8">
         <v>46155</v>
@@ -22421,7 +22445,7 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="B368" t="s">
         <v>56</v>
@@ -22436,25 +22460,25 @@
         <v>58</v>
       </c>
       <c r="F368" t="s">
-        <v>1027</v>
+        <v>975</v>
       </c>
       <c r="G368" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="H368" t="s">
-        <v>1029</v>
+        <v>987</v>
       </c>
       <c r="J368" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K368">
         <v>75</v>
       </c>
       <c r="L368">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="M368">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P368" s="8">
         <v>46155</v>
@@ -22462,7 +22486,7 @@
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="B369" t="s">
         <v>56</v>
@@ -22477,13 +22501,16 @@
         <v>58</v>
       </c>
       <c r="F369" t="s">
-        <v>1027</v>
+        <v>975</v>
       </c>
       <c r="G369" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="H369" t="s">
-        <v>1032</v>
+        <v>987</v>
+      </c>
+      <c r="I369" t="s">
+        <v>1007</v>
       </c>
       <c r="J369" t="s">
         <v>93</v>
@@ -22492,10 +22519,10 @@
         <v>75</v>
       </c>
       <c r="L369">
-        <v>4.75</v>
+        <v>6.05</v>
       </c>
       <c r="M369">
-        <v>14790</v>
+        <v>474</v>
       </c>
       <c r="P369" s="8">
         <v>46155</v>
@@ -22503,10 +22530,10 @@
     </row>
     <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="B370" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C370" t="s">
         <v>973</v>
@@ -22518,13 +22545,13 @@
         <v>58</v>
       </c>
       <c r="F370" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G370" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="H370" t="s">
-        <v>1035</v>
+        <v>605</v>
       </c>
       <c r="J370" t="s">
         <v>334</v>
@@ -22533,92 +22560,89 @@
         <v>75</v>
       </c>
       <c r="L370">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="M370">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="P370" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A371">
-        <v>24003025</v>
+      <c r="A371" t="s">
+        <v>1023</v>
       </c>
       <c r="B371" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C371" t="s">
         <v>973</v>
       </c>
       <c r="D371" t="s">
-        <v>1036</v>
+        <v>974</v>
       </c>
       <c r="E371" t="s">
         <v>58</v>
       </c>
       <c r="F371" t="s">
-        <v>59</v>
+        <v>1024</v>
       </c>
       <c r="G371" t="s">
-        <v>1037</v>
+        <v>159</v>
       </c>
       <c r="H371" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I371" t="s">
-        <v>62</v>
-      </c>
-      <c r="J371">
-        <v>2025</v>
+        <v>1025</v>
+      </c>
+      <c r="J371" t="s">
+        <v>93</v>
       </c>
       <c r="K371">
         <v>75</v>
       </c>
       <c r="L371">
-        <v>6.2</v>
+        <v>37</v>
       </c>
       <c r="P371" s="8">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="B372" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C372" t="s">
         <v>973</v>
       </c>
       <c r="D372" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E372" t="s">
         <v>58</v>
       </c>
       <c r="F372" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
       <c r="G372" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="H372" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="J372" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K372">
         <v>75</v>
       </c>
       <c r="L372">
-        <v>7.55</v>
+        <v>3.95</v>
       </c>
       <c r="M372">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="P372" s="8">
         <v>46155</v>
@@ -22626,10 +22650,10 @@
     </row>
     <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B373" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C373" t="s">
         <v>973</v>
@@ -22641,25 +22665,25 @@
         <v>58</v>
       </c>
       <c r="F373" t="s">
-        <v>59</v>
+        <v>1027</v>
       </c>
       <c r="G373" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="H373" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="J373" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K373">
         <v>75</v>
       </c>
       <c r="L373">
-        <v>10.5</v>
+        <v>4.75</v>
       </c>
       <c r="M373">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P373" s="8">
         <v>46155</v>
@@ -22667,7 +22691,7 @@
     </row>
     <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="B374" t="s">
         <v>117</v>
@@ -22676,28 +22700,28 @@
         <v>973</v>
       </c>
       <c r="D374" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E374" t="s">
         <v>58</v>
       </c>
       <c r="F374" t="s">
-        <v>1046</v>
+        <v>59</v>
       </c>
       <c r="G374" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="H374" t="s">
         <v>1035</v>
       </c>
       <c r="J374" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K374">
         <v>75</v>
       </c>
       <c r="L374">
-        <v>10.65</v>
+        <v>6.2</v>
       </c>
       <c r="M374">
         <v>0</v>
@@ -22707,8 +22731,8 @@
       </c>
     </row>
     <row r="375" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A375" t="s">
-        <v>1048</v>
+      <c r="A375">
+        <v>24003025</v>
       </c>
       <c r="B375" t="s">
         <v>117</v>
@@ -22717,7 +22741,7 @@
         <v>973</v>
       </c>
       <c r="D375" t="s">
-        <v>974</v>
+        <v>1036</v>
       </c>
       <c r="E375" t="s">
         <v>58</v>
@@ -22726,33 +22750,30 @@
         <v>59</v>
       </c>
       <c r="G375" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="H375" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="I375" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J375" t="s">
-        <v>93</v>
+        <v>62</v>
+      </c>
+      <c r="J375">
+        <v>2025</v>
       </c>
       <c r="K375">
         <v>75</v>
       </c>
       <c r="L375">
-        <v>11.5</v>
-      </c>
-      <c r="M375">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P375" s="8">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
       <c r="B376" t="s">
         <v>117</v>
@@ -22761,28 +22782,28 @@
         <v>973</v>
       </c>
       <c r="D376" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E376" t="s">
         <v>58</v>
       </c>
       <c r="F376" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="G376" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
       <c r="H376" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="J376" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K376">
         <v>75</v>
       </c>
       <c r="L376">
-        <v>12.2</v>
+        <v>7.55</v>
       </c>
       <c r="M376">
         <v>0</v>
@@ -22793,7 +22814,7 @@
     </row>
     <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
       <c r="B377" t="s">
         <v>117</v>
@@ -22802,28 +22823,28 @@
         <v>973</v>
       </c>
       <c r="D377" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E377" t="s">
         <v>58</v>
       </c>
       <c r="F377" t="s">
-        <v>1040</v>
+        <v>59</v>
       </c>
       <c r="G377" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
       <c r="H377" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="J377" t="s">
-        <v>128</v>
+        <v>334</v>
       </c>
       <c r="K377">
         <v>75</v>
       </c>
       <c r="L377">
-        <v>13.95</v>
+        <v>10.5</v>
       </c>
       <c r="M377">
         <v>0</v>
@@ -22834,7 +22855,7 @@
     </row>
     <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="B378" t="s">
         <v>117</v>
@@ -22843,28 +22864,28 @@
         <v>973</v>
       </c>
       <c r="D378" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E378" t="s">
         <v>58</v>
       </c>
       <c r="F378" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="G378" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="H378" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="J378" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="K378">
         <v>75</v>
       </c>
       <c r="L378">
-        <v>14.8</v>
+        <v>10.65</v>
       </c>
       <c r="M378">
         <v>0</v>
@@ -22875,7 +22896,7 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="B379" t="s">
         <v>117</v>
@@ -22884,31 +22905,34 @@
         <v>973</v>
       </c>
       <c r="D379" t="s">
-        <v>1053</v>
+        <v>974</v>
       </c>
       <c r="E379" t="s">
         <v>58</v>
       </c>
       <c r="F379" t="s">
-        <v>1062</v>
+        <v>59</v>
       </c>
       <c r="G379" t="s">
-        <v>1063</v>
+        <v>1049</v>
       </c>
       <c r="H379" t="s">
-        <v>1064</v>
+        <v>1050</v>
+      </c>
+      <c r="I379" t="s">
+        <v>1051</v>
       </c>
       <c r="J379" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K379">
         <v>75</v>
       </c>
       <c r="L379">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="M379">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P379" s="8">
         <v>46155</v>
@@ -22916,7 +22940,7 @@
     </row>
     <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
       <c r="B380" t="s">
         <v>117</v>
@@ -22931,22 +22955,22 @@
         <v>58</v>
       </c>
       <c r="F380" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="G380" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="H380" t="s">
-        <v>1067</v>
+        <v>1050</v>
       </c>
       <c r="J380" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K380">
         <v>75</v>
       </c>
       <c r="L380">
-        <v>7.6</v>
+        <v>12.2</v>
       </c>
       <c r="M380">
         <v>0</v>
@@ -22957,7 +22981,7 @@
     </row>
     <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="B381" t="s">
         <v>117</v>
@@ -22966,28 +22990,28 @@
         <v>973</v>
       </c>
       <c r="D381" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E381" t="s">
         <v>58</v>
       </c>
       <c r="F381" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="G381" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="H381" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="J381" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="K381">
         <v>75</v>
       </c>
       <c r="L381">
-        <v>16.5</v>
+        <v>13.95</v>
       </c>
       <c r="M381">
         <v>0</v>
@@ -22998,10 +23022,10 @@
     </row>
     <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="B382" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C382" t="s">
         <v>973</v>
@@ -23013,25 +23037,25 @@
         <v>58</v>
       </c>
       <c r="F382" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="G382" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="H382" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="J382" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K382">
         <v>75</v>
       </c>
       <c r="L382">
-        <v>5.2</v>
+        <v>14.8</v>
       </c>
       <c r="M382">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P382" s="8">
         <v>46155</v>
@@ -23039,40 +23063,40 @@
     </row>
     <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="B383" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C383" t="s">
         <v>973</v>
       </c>
       <c r="D383" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E383" t="s">
         <v>58</v>
       </c>
       <c r="F383" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="G383" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="H383" t="s">
-        <v>1012</v>
+        <v>1064</v>
       </c>
       <c r="J383" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K383">
         <v>75</v>
       </c>
       <c r="L383">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M383">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="P383" s="8">
         <v>46155</v>
@@ -23080,40 +23104,40 @@
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="B384" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C384" t="s">
         <v>973</v>
       </c>
       <c r="D384" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E384" t="s">
         <v>58</v>
       </c>
       <c r="F384" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="G384" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="H384" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="J384" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="K384">
         <v>75</v>
       </c>
       <c r="L384">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="M384">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="P384" s="8">
         <v>46155</v>
@@ -23121,28 +23145,28 @@
     </row>
     <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="B385" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C385" t="s">
         <v>973</v>
       </c>
       <c r="D385" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E385" t="s">
         <v>58</v>
       </c>
       <c r="F385" t="s">
-        <v>1078</v>
+        <v>1062</v>
       </c>
       <c r="G385" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="H385" t="s">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="J385" t="s">
         <v>93</v>
@@ -23151,7 +23175,10 @@
         <v>75</v>
       </c>
       <c r="L385">
-        <v>7.1</v>
+        <v>16.5</v>
+      </c>
+      <c r="M385">
+        <v>0</v>
       </c>
       <c r="P385" s="8">
         <v>46155</v>
@@ -23159,7 +23186,7 @@
     </row>
     <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="B386" t="s">
         <v>56</v>
@@ -23168,69 +23195,72 @@
         <v>973</v>
       </c>
       <c r="D386" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="E386" t="s">
         <v>58</v>
       </c>
       <c r="F386" t="s">
-        <v>1082</v>
+        <v>1062</v>
       </c>
       <c r="G386" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="H386" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="J386" t="s">
-        <v>521</v>
+        <v>93</v>
       </c>
       <c r="K386">
         <v>75</v>
       </c>
       <c r="L386">
-        <v>8.1999999999999993</v>
+        <v>5.2</v>
+      </c>
+      <c r="M386">
+        <v>37</v>
       </c>
       <c r="P386" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="387" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A387">
-        <v>53800623</v>
+      <c r="A387" t="s">
+        <v>1073</v>
       </c>
       <c r="B387" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C387" t="s">
         <v>973</v>
       </c>
       <c r="D387" t="s">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="E387" t="s">
         <v>58</v>
       </c>
       <c r="F387" t="s">
-        <v>1084</v>
+        <v>1027</v>
       </c>
       <c r="G387" t="s">
-        <v>1085</v>
+        <v>1074</v>
       </c>
       <c r="H387" t="s">
-        <v>1060</v>
+        <v>1012</v>
       </c>
       <c r="J387" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K387">
         <v>75</v>
       </c>
       <c r="L387">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="M387">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="P387" s="8">
         <v>46155</v>
@@ -23238,7 +23268,7 @@
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
       <c r="B388" t="s">
         <v>56</v>
@@ -23247,31 +23277,31 @@
         <v>973</v>
       </c>
       <c r="D388" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E388" t="s">
         <v>58</v>
       </c>
       <c r="F388" t="s">
-        <v>975</v>
+        <v>1027</v>
       </c>
       <c r="G388" t="s">
-        <v>1087</v>
+        <v>1076</v>
       </c>
       <c r="H388" t="s">
-        <v>977</v>
+        <v>1032</v>
       </c>
       <c r="J388" t="s">
-        <v>576</v>
+        <v>93</v>
       </c>
       <c r="K388">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L388">
-        <v>16.399999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="M388">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="P388" s="8">
         <v>46155</v>
@@ -23279,7 +23309,7 @@
     </row>
     <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>1088</v>
+        <v>1077</v>
       </c>
       <c r="B389" t="s">
         <v>56</v>
@@ -23288,31 +23318,28 @@
         <v>973</v>
       </c>
       <c r="D389" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E389" t="s">
         <v>58</v>
       </c>
       <c r="F389" t="s">
-        <v>975</v>
+        <v>1078</v>
       </c>
       <c r="G389" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="H389" t="s">
-        <v>980</v>
+        <v>1080</v>
       </c>
       <c r="J389" t="s">
         <v>93</v>
       </c>
       <c r="K389">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="L389">
-        <v>25.5</v>
-      </c>
-      <c r="M389">
-        <v>71</v>
+        <v>7.1</v>
       </c>
       <c r="P389" s="8">
         <v>46155</v>
@@ -23320,7 +23347,7 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="B390" t="s">
         <v>56</v>
@@ -23332,69 +23359,66 @@
         <v>1009</v>
       </c>
       <c r="E390" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F390" t="s">
-        <v>982</v>
+        <v>1082</v>
       </c>
       <c r="G390" t="s">
-        <v>983</v>
+        <v>1079</v>
       </c>
       <c r="H390" t="s">
-        <v>984</v>
+        <v>1083</v>
       </c>
       <c r="J390" t="s">
-        <v>576</v>
+        <v>521</v>
       </c>
       <c r="K390">
         <v>75</v>
       </c>
       <c r="L390">
-        <v>4.8</v>
-      </c>
-      <c r="M390">
-        <v>152</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P390" s="8">
         <v>46155</v>
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
-        <v>1091</v>
+      <c r="A391">
+        <v>53800623</v>
       </c>
       <c r="B391" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="C391" t="s">
         <v>973</v>
       </c>
       <c r="D391" t="s">
-        <v>974</v>
+        <v>1053</v>
       </c>
       <c r="E391" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F391" t="s">
-        <v>975</v>
+        <v>1084</v>
       </c>
       <c r="G391" t="s">
-        <v>976</v>
+        <v>1085</v>
       </c>
       <c r="H391" t="s">
-        <v>977</v>
+        <v>1060</v>
       </c>
       <c r="J391" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="M391">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="P391" s="8">
         <v>46155</v>
@@ -23402,7 +23426,7 @@
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
@@ -23414,28 +23438,28 @@
         <v>974</v>
       </c>
       <c r="E392" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F392" t="s">
         <v>975</v>
       </c>
       <c r="G392" t="s">
-        <v>979</v>
+        <v>1087</v>
       </c>
       <c r="H392" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J392" t="s">
-        <v>316</v>
+        <v>576</v>
       </c>
       <c r="K392">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="L392">
-        <v>4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M392">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="P392" s="8">
         <v>46155</v>
@@ -23443,7 +23467,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
@@ -23455,28 +23479,28 @@
         <v>974</v>
       </c>
       <c r="E393" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F393" t="s">
         <v>975</v>
       </c>
       <c r="G393" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="H393" t="s">
-        <v>285</v>
+        <v>980</v>
       </c>
       <c r="J393" t="s">
         <v>93</v>
       </c>
       <c r="K393">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L393">
-        <v>4.0999999999999996</v>
+        <v>25.5</v>
       </c>
       <c r="M393">
-        <v>915</v>
+        <v>71</v>
       </c>
       <c r="P393" s="8">
         <v>46155</v>
@@ -23484,7 +23508,7 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
@@ -23493,31 +23517,31 @@
         <v>973</v>
       </c>
       <c r="D394" t="s">
-        <v>974</v>
+        <v>1009</v>
       </c>
       <c r="E394" t="s">
         <v>79</v>
       </c>
       <c r="F394" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="G394" t="s">
-        <v>1096</v>
+        <v>983</v>
       </c>
       <c r="H394" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="J394" t="s">
-        <v>93</v>
+        <v>576</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>4.8499999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M394">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="P394" s="8">
         <v>46155</v>
@@ -23525,7 +23549,7 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
@@ -23540,25 +23564,25 @@
         <v>79</v>
       </c>
       <c r="F395" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G395" t="s">
-        <v>1098</v>
+        <v>976</v>
       </c>
       <c r="H395" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
       <c r="J395" t="s">
-        <v>334</v>
+        <v>93</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="M395">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="P395" s="8">
         <v>46155</v>
@@ -23566,7 +23590,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
@@ -23584,22 +23608,22 @@
         <v>975</v>
       </c>
       <c r="G396" t="s">
-        <v>1100</v>
+        <v>979</v>
       </c>
       <c r="H396" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="J396" t="s">
-        <v>93</v>
+        <v>316</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M396">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="P396" s="8">
         <v>46155</v>
@@ -23607,7 +23631,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
@@ -23625,22 +23649,22 @@
         <v>975</v>
       </c>
       <c r="G397" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="H397" t="s">
-        <v>1103</v>
+        <v>285</v>
       </c>
       <c r="J397" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>5.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M397">
-        <v>27</v>
+        <v>915</v>
       </c>
       <c r="P397" s="8">
         <v>46155</v>
@@ -23648,7 +23672,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
@@ -23666,25 +23690,22 @@
         <v>975</v>
       </c>
       <c r="G398" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="H398" t="s">
-        <v>977</v>
-      </c>
-      <c r="I398" t="s">
-        <v>289</v>
+        <v>980</v>
       </c>
       <c r="J398" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>5.4</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M398">
-        <v>303</v>
+        <v>219</v>
       </c>
       <c r="P398" s="8">
         <v>46155</v>
@@ -23692,7 +23713,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
@@ -23707,28 +23728,25 @@
         <v>79</v>
       </c>
       <c r="F399" t="s">
-        <v>975</v>
+        <v>59</v>
       </c>
       <c r="G399" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="H399" t="s">
-        <v>987</v>
-      </c>
-      <c r="I399" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="J399" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="M399">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="P399" s="8">
         <v>46155</v>
@@ -23736,7 +23754,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
@@ -23751,25 +23769,25 @@
         <v>79</v>
       </c>
       <c r="F400" t="s">
-        <v>59</v>
+        <v>975</v>
       </c>
       <c r="G400" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="H400" t="s">
-        <v>1012</v>
+        <v>987</v>
       </c>
       <c r="J400" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="M400">
-        <v>340</v>
+        <v>219</v>
       </c>
       <c r="P400" s="8">
         <v>46155</v>
@@ -23777,7 +23795,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
@@ -23786,31 +23804,31 @@
         <v>973</v>
       </c>
       <c r="D401" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
       <c r="E401" t="s">
         <v>79</v>
       </c>
       <c r="F401" t="s">
-        <v>1111</v>
+        <v>975</v>
       </c>
       <c r="G401" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
       <c r="H401" t="s">
-        <v>1080</v>
+        <v>1103</v>
       </c>
       <c r="J401" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>6.15</v>
+        <v>5.3</v>
       </c>
       <c r="M401">
-        <v>46</v>
+       